--- a/Results/Phase 2/Ammonia/ammonia water use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia water use results.xlsx
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.398762762559155</v>
+        <v>2.398762762559154</v>
       </c>
       <c r="C2" t="n">
-        <v>2.448247051777015</v>
+        <v>2.448247051777014</v>
       </c>
       <c r="D2" t="n">
-        <v>2.443667367988473</v>
+        <v>2.443667367988472</v>
       </c>
       <c r="E2" t="n">
         <v>2.439411279524754</v>
       </c>
       <c r="F2" t="n">
-        <v>2.44013206173294</v>
+        <v>2.440132061732939</v>
       </c>
       <c r="G2" t="n">
         <v>2.402474827229611</v>
       </c>
       <c r="H2" t="n">
-        <v>2.402550824764572</v>
+        <v>2.402550824764571</v>
       </c>
       <c r="I2" t="n">
         <v>2.418093629817522</v>
@@ -613,34 +613,34 @@
         <v>2.406098952689786</v>
       </c>
       <c r="K2" t="n">
-        <v>2.407434198040656</v>
+        <v>2.407434198040655</v>
       </c>
       <c r="L2" t="n">
-        <v>2.405319443734014</v>
+        <v>2.405319443734015</v>
       </c>
       <c r="M2" t="n">
-        <v>2.405534098306804</v>
+        <v>2.405534098306803</v>
       </c>
       <c r="N2" t="n">
-        <v>2.399534619686748</v>
+        <v>2.399534619686747</v>
       </c>
       <c r="O2" t="n">
-        <v>2.432791516808025</v>
+        <v>2.432791516808024</v>
       </c>
       <c r="P2" t="n">
         <v>2.404423063666184</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.399113142914568</v>
+        <v>2.399113142914567</v>
       </c>
       <c r="R2" t="n">
-        <v>2.415776032675754</v>
+        <v>2.415776032675753</v>
       </c>
       <c r="S2" t="n">
-        <v>2.408621220781621</v>
+        <v>2.40862122078162</v>
       </c>
       <c r="T2" t="n">
-        <v>2.400228899264485</v>
+        <v>2.400228899264484</v>
       </c>
       <c r="U2" t="n">
         <v>2.440914429850308</v>
@@ -655,13 +655,13 @@
         <v>2.407353944709033</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.402019164311198</v>
+        <v>2.402019164311196</v>
       </c>
       <c r="Z2" t="n">
         <v>2.419967251171326</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.416940555471566</v>
+        <v>2.416940555471567</v>
       </c>
       <c r="AB2" t="n">
         <v>2.39934693942697</v>
@@ -680,28 +680,28 @@
         <v>2.723202633962577</v>
       </c>
       <c r="D3" t="n">
-        <v>2.721974310753084</v>
+        <v>2.721974310753083</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6905382905955</v>
+        <v>2.690538290595501</v>
       </c>
       <c r="F3" t="n">
-        <v>2.697085717015384</v>
+        <v>2.697085717015383</v>
       </c>
       <c r="G3" t="n">
-        <v>2.426886279116288</v>
+        <v>2.426886279116287</v>
       </c>
       <c r="H3" t="n">
-        <v>2.427732218904314</v>
+        <v>2.427732218904315</v>
       </c>
       <c r="I3" t="n">
-        <v>2.539002782982619</v>
+        <v>2.539002782982618</v>
       </c>
       <c r="J3" t="n">
         <v>2.452841880778343</v>
       </c>
       <c r="K3" t="n">
-        <v>2.462557676805836</v>
+        <v>2.462557676805835</v>
       </c>
       <c r="L3" t="n">
         <v>2.447266857528136</v>
@@ -710,7 +710,7 @@
         <v>2.449871077376991</v>
       </c>
       <c r="N3" t="n">
-        <v>2.406014994164036</v>
+        <v>2.406014994164035</v>
       </c>
       <c r="O3" t="n">
         <v>2.468205838293971</v>
@@ -719,7 +719,7 @@
         <v>2.440723612187166</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.403010096487617</v>
+        <v>2.403010096487618</v>
       </c>
       <c r="R3" t="n">
         <v>2.52250438027234</v>
@@ -731,22 +731,22 @@
         <v>2.411017467613465</v>
       </c>
       <c r="U3" t="n">
-        <v>2.526637669026702</v>
+        <v>2.526637669026701</v>
       </c>
       <c r="V3" t="n">
-        <v>2.455278568937039</v>
+        <v>2.45527856893704</v>
       </c>
       <c r="W3" t="n">
         <v>2.502153930273403</v>
       </c>
       <c r="X3" t="n">
-        <v>2.461963229353471</v>
+        <v>2.46196322935347</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.423739733399768</v>
+        <v>2.423739733399767</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.448402230569883</v>
+        <v>2.448402230569882</v>
       </c>
       <c r="AA3" t="n">
         <v>2.530310365418609</v>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.118489376979915</v>
+        <v>2.118489376979914</v>
       </c>
       <c r="C4" t="n">
         <v>2.613898021319005</v>
@@ -771,13 +771,13 @@
         <v>2.625707552443139</v>
       </c>
       <c r="E4" t="n">
-        <v>2.577633075348013</v>
+        <v>2.577633075348012</v>
       </c>
       <c r="F4" t="n">
         <v>2.585774641965674</v>
       </c>
       <c r="G4" t="n">
-        <v>2.160418855066832</v>
+        <v>2.160418855066833</v>
       </c>
       <c r="H4" t="n">
         <v>2.161277282184813</v>
@@ -789,19 +789,19 @@
         <v>2.201375412264218</v>
       </c>
       <c r="K4" t="n">
-        <v>2.216437229800873</v>
+        <v>2.216437229800872</v>
       </c>
       <c r="L4" t="n">
-        <v>2.192550107072325</v>
+        <v>2.192550107072324</v>
       </c>
       <c r="M4" t="n">
-        <v>2.196499846324495</v>
+        <v>2.196499846324494</v>
       </c>
       <c r="N4" t="n">
-        <v>2.127207858307912</v>
+        <v>2.127207858307911</v>
       </c>
       <c r="O4" t="n">
-        <v>2.142504886512029</v>
+        <v>2.142504886512028</v>
       </c>
       <c r="P4" t="n">
         <v>2.182425081850977</v>
@@ -819,7 +819,7 @@
         <v>2.135050065522829</v>
       </c>
       <c r="U4" t="n">
-        <v>2.235289456228168</v>
+        <v>2.235289456228167</v>
       </c>
       <c r="V4" t="n">
         <v>2.205607843703008</v>
@@ -828,7 +828,7 @@
         <v>2.185127753928624</v>
       </c>
       <c r="X4" t="n">
-        <v>2.215530731501842</v>
+        <v>2.215530731501841</v>
       </c>
       <c r="Y4" t="n">
         <v>2.155380535763236</v>
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.439803203323068</v>
+        <v>2.439803203323066</v>
       </c>
       <c r="C5" t="n">
-        <v>12.84851129548314</v>
+        <v>12.84851129548315</v>
       </c>
       <c r="D5" t="n">
-        <v>13.26905319403545</v>
+        <v>13.26905319403547</v>
       </c>
       <c r="E5" t="n">
-        <v>11.67086375936638</v>
+        <v>11.67086375936637</v>
       </c>
       <c r="F5" t="n">
-        <v>12.66878981369111</v>
+        <v>12.66878981369109</v>
       </c>
       <c r="G5" t="n">
-        <v>3.24843683495848</v>
+        <v>3.248436834958488</v>
       </c>
       <c r="H5" t="n">
         <v>3.446133567982946</v>
       </c>
       <c r="I5" t="n">
-        <v>7.184145627228224</v>
+        <v>7.184145627228222</v>
       </c>
       <c r="J5" t="n">
-        <v>4.126337335681397</v>
+        <v>4.126337335681396</v>
       </c>
       <c r="K5" t="n">
-        <v>4.540638831809183</v>
+        <v>4.540638831809181</v>
       </c>
       <c r="L5" t="n">
         <v>3.942093272376534</v>
@@ -886,49 +886,49 @@
         <v>4.166411815211916</v>
       </c>
       <c r="N5" t="n">
-        <v>4.639130811425075</v>
+        <v>4.639130811425069</v>
       </c>
       <c r="O5" t="n">
         <v>2.874246323719088</v>
       </c>
       <c r="P5" t="n">
-        <v>3.651578827831763</v>
+        <v>3.651578827831759</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.552905320011271</v>
+        <v>2.552905320011268</v>
       </c>
       <c r="R5" t="n">
-        <v>6.682173036139444</v>
+        <v>6.682173036139442</v>
       </c>
       <c r="S5" t="n">
-        <v>4.590377829949597</v>
+        <v>4.590377829949591</v>
       </c>
       <c r="T5" t="n">
-        <v>2.832950183663249</v>
+        <v>2.832950183663244</v>
       </c>
       <c r="U5" t="n">
-        <v>4.74710380637015</v>
+        <v>4.747103806370143</v>
       </c>
       <c r="V5" t="n">
         <v>4.082561220276288</v>
       </c>
       <c r="W5" t="n">
-        <v>3.80825770819464</v>
+        <v>3.808257708194636</v>
       </c>
       <c r="X5" t="n">
-        <v>4.509501124061797</v>
+        <v>4.509501124061793</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.207518489766648</v>
+        <v>3.20751848976664</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.956646264027966</v>
+        <v>2.956646264027963</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.646754364909609</v>
+        <v>6.64675436490961</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.696019428279666</v>
+        <v>2.696019428279663</v>
       </c>
     </row>
     <row r="6">
@@ -938,40 +938,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.375793685240402</v>
+        <v>17.58561142182269</v>
       </c>
       <c r="C6" t="n">
-        <v>18.08102006616179</v>
+        <v>18.08102006616178</v>
       </c>
       <c r="D6" t="n">
-        <v>3.883011860703628</v>
+        <v>3.883011860703629</v>
       </c>
       <c r="E6" t="n">
-        <v>18.04475512019082</v>
+        <v>3.834937383608501</v>
       </c>
       <c r="F6" t="n">
-        <v>3.843078950226162</v>
+        <v>18.05289668680844</v>
       </c>
       <c r="G6" t="n">
-        <v>3.417723163327326</v>
+        <v>17.62754089990963</v>
       </c>
       <c r="H6" t="n">
-        <v>17.62839932702761</v>
+        <v>17.6283993270276</v>
       </c>
       <c r="I6" t="n">
-        <v>17.80396246014423</v>
+        <v>3.594144723561956</v>
       </c>
       <c r="J6" t="n">
-        <v>3.458679720524709</v>
+        <v>17.66849745710701</v>
       </c>
       <c r="K6" t="n">
-        <v>3.473741538061364</v>
+        <v>3.473741538061365</v>
       </c>
       <c r="L6" t="n">
-        <v>17.65967215191512</v>
+        <v>3.449854415332819</v>
       </c>
       <c r="M6" t="n">
-        <v>3.453804154584979</v>
+        <v>3.45380415458498</v>
       </c>
       <c r="N6" t="n">
         <v>3.382200296829949</v>
@@ -980,40 +980,40 @@
         <v>17.60875234395061</v>
       </c>
       <c r="P6" t="n">
-        <v>17.64867256943309</v>
+        <v>17.64867256943308</v>
       </c>
       <c r="Q6" t="n">
         <v>3.379751392537729</v>
       </c>
       <c r="R6" t="n">
-        <v>17.77778413428062</v>
+        <v>3.567966397698323</v>
       </c>
       <c r="S6" t="n">
-        <v>17.6969672425603</v>
+        <v>17.69696724256031</v>
       </c>
       <c r="T6" t="n">
         <v>3.392354373783323</v>
       </c>
       <c r="U6" t="n">
-        <v>3.492485161513471</v>
+        <v>3.492485161513472</v>
       </c>
       <c r="V6" t="n">
-        <v>17.6727298885458</v>
+        <v>17.67272988854579</v>
       </c>
       <c r="W6" t="n">
-        <v>3.443026756878039</v>
+        <v>17.65137523522131</v>
       </c>
       <c r="X6" t="n">
-        <v>17.68265277634462</v>
+        <v>17.68265277634463</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.431336521533247</v>
+        <v>3.431336521533246</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.402523812506752</v>
+        <v>3.402523812506751</v>
       </c>
       <c r="AA6" t="n">
-        <v>17.79093795496629</v>
+        <v>3.581120218383981</v>
       </c>
       <c r="AB6" t="n">
         <v>3.381841639762779</v>
@@ -1029,82 +1029,82 @@
         <v>2.190412316825233</v>
       </c>
       <c r="C7" t="n">
-        <v>2.685820961164323</v>
+        <v>2.685820961164322</v>
       </c>
       <c r="D7" t="n">
-        <v>2.697630492288458</v>
+        <v>2.697630492288456</v>
       </c>
       <c r="E7" t="n">
-        <v>2.649556015193332</v>
+        <v>2.649556015193331</v>
       </c>
       <c r="F7" t="n">
-        <v>2.657697581810993</v>
+        <v>2.657697581810991</v>
       </c>
       <c r="G7" t="n">
-        <v>2.232341794912151</v>
+        <v>2.23234179491215</v>
       </c>
       <c r="H7" t="n">
-        <v>2.233200222030131</v>
+        <v>2.23320022203013</v>
       </c>
       <c r="I7" t="n">
         <v>2.408763355146784</v>
       </c>
       <c r="J7" t="n">
-        <v>2.273298352109537</v>
+        <v>2.273298352109536</v>
       </c>
       <c r="K7" t="n">
-        <v>2.288360169646192</v>
+        <v>2.288360169646191</v>
       </c>
       <c r="L7" t="n">
-        <v>2.264473046917643</v>
+        <v>2.264473046917642</v>
       </c>
       <c r="M7" t="n">
-        <v>2.268422786169814</v>
+        <v>2.268422786169813</v>
       </c>
       <c r="N7" t="n">
-        <v>2.19913079815323</v>
+        <v>2.199130798153229</v>
       </c>
       <c r="O7" t="n">
-        <v>2.214422764048463</v>
+        <v>2.214422764048461</v>
       </c>
       <c r="P7" t="n">
-        <v>2.254342959387411</v>
+        <v>2.25434295938741</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.194370024122553</v>
+        <v>2.194370024122552</v>
       </c>
       <c r="R7" t="n">
-        <v>2.382585029283151</v>
+        <v>2.38258502928315</v>
       </c>
       <c r="S7" t="n">
-        <v>2.301768137562834</v>
+        <v>2.301768137562833</v>
       </c>
       <c r="T7" t="n">
-        <v>2.206973005368148</v>
+        <v>2.206973005368147</v>
       </c>
       <c r="U7" t="n">
-        <v>2.307099289389491</v>
+        <v>2.30709928938949</v>
       </c>
       <c r="V7" t="n">
-        <v>2.277530783548327</v>
+        <v>2.277530783548326</v>
       </c>
       <c r="W7" t="n">
-        <v>2.257050693773942</v>
+        <v>2.257050693773941</v>
       </c>
       <c r="X7" t="n">
-        <v>2.287453671347161</v>
+        <v>2.28745367134716</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.227194872633377</v>
+        <v>2.227194872633376</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.217142444091579</v>
+        <v>2.217142444091578</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.395738849968814</v>
+        <v>2.395738849968813</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.199282561070827</v>
+        <v>2.199282561070825</v>
       </c>
     </row>
     <row r="8">
@@ -1114,22 +1114,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.201351692158542</v>
+        <v>2.201351692158541</v>
       </c>
       <c r="C8" t="n">
-        <v>2.755421613224014</v>
+        <v>2.755421613224013</v>
       </c>
       <c r="D8" t="n">
-        <v>2.767231144348145</v>
+        <v>2.767231144348144</v>
       </c>
       <c r="E8" t="n">
-        <v>2.719156667253021</v>
+        <v>2.687921267796962</v>
       </c>
       <c r="F8" t="n">
-        <v>2.677775698468858</v>
+        <v>2.677775698468857</v>
       </c>
       <c r="G8" t="n">
-        <v>2.301942446971842</v>
+        <v>2.314106244843261</v>
       </c>
       <c r="H8" t="n">
         <v>2.302800874089821</v>
@@ -1138,25 +1138,25 @@
         <v>2.478364007206473</v>
       </c>
       <c r="J8" t="n">
-        <v>2.342899004169228</v>
+        <v>2.342899004169226</v>
       </c>
       <c r="K8" t="n">
         <v>2.357960821705881</v>
       </c>
       <c r="L8" t="n">
-        <v>2.334073698977334</v>
+        <v>2.334073698977333</v>
       </c>
       <c r="M8" t="n">
-        <v>2.338023438229504</v>
+        <v>2.338023438229501</v>
       </c>
       <c r="N8" t="n">
-        <v>2.223259146930716</v>
+        <v>2.223259146930715</v>
       </c>
       <c r="O8" t="n">
-        <v>2.251052358903073</v>
+        <v>2.251052358903072</v>
       </c>
       <c r="P8" t="n">
-        <v>2.287909437650617</v>
+        <v>2.287909437650616</v>
       </c>
       <c r="Q8" t="n">
         <v>2.19378111970267</v>
@@ -1165,34 +1165,34 @@
         <v>2.452185681342842</v>
       </c>
       <c r="S8" t="n">
-        <v>2.371368789622524</v>
+        <v>2.371368789622523</v>
       </c>
       <c r="T8" t="n">
         <v>2.276573657427839</v>
       </c>
       <c r="U8" t="n">
-        <v>2.340607756321778</v>
+        <v>2.348073091828905</v>
       </c>
       <c r="V8" t="n">
-        <v>2.347131435608016</v>
+        <v>2.331098901647664</v>
       </c>
       <c r="W8" t="n">
         <v>2.326662874449335</v>
       </c>
       <c r="X8" t="n">
-        <v>2.292241189497215</v>
+        <v>2.292241189497214</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.355121837491489</v>
+        <v>2.355121837491488</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.286743096151269</v>
+        <v>2.226992156093626</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.465339502028504</v>
+        <v>2.465339502028503</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.330159821841513</v>
+        <v>2.330159821841512</v>
       </c>
     </row>
     <row r="9">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.733058946855225</v>
+        <v>2.733058946855224</v>
       </c>
       <c r="C9" t="n">
-        <v>3.401046449731302</v>
+        <v>3.4010464497313</v>
       </c>
       <c r="D9" t="n">
         <v>3.412855980855432</v>
       </c>
       <c r="E9" t="n">
-        <v>3.364781503760305</v>
+        <v>3.324951015951839</v>
       </c>
       <c r="F9" t="n">
-        <v>3.372923070377968</v>
+        <v>2.975081685268604</v>
       </c>
       <c r="G9" t="n">
-        <v>2.947567283479126</v>
+        <v>2.947567294926722</v>
       </c>
       <c r="H9" t="n">
-        <v>2.948425710597107</v>
+        <v>2.948425710597105</v>
       </c>
       <c r="I9" t="n">
         <v>3.123988843713758</v>
@@ -1232,55 +1232,55 @@
         <v>3.003585658213165</v>
       </c>
       <c r="L9" t="n">
-        <v>2.979698535484621</v>
+        <v>2.97969853548462</v>
       </c>
       <c r="M9" t="n">
-        <v>2.983648274736789</v>
+        <v>2.983648274736788</v>
       </c>
       <c r="N9" t="n">
         <v>2.914356286720204</v>
       </c>
       <c r="O9" t="n">
-        <v>2.986845737912236</v>
+        <v>2.986845737912234</v>
       </c>
       <c r="P9" t="n">
-        <v>3.039204301504391</v>
+        <v>3.03920430150439</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.909595524137125</v>
+        <v>2.909595524137124</v>
       </c>
       <c r="R9" t="n">
         <v>3.097810517850125</v>
       </c>
       <c r="S9" t="n">
-        <v>3.016993626129807</v>
+        <v>3.016993626129806</v>
       </c>
       <c r="T9" t="n">
-        <v>2.922198493935123</v>
+        <v>2.922198493935122</v>
       </c>
       <c r="U9" t="n">
-        <v>3.022329281665282</v>
+        <v>3.022329281665281</v>
       </c>
       <c r="V9" t="n">
-        <v>2.992756272115302</v>
+        <v>3.191908501350334</v>
       </c>
       <c r="W9" t="n">
         <v>2.972276182340917</v>
       </c>
       <c r="X9" t="n">
-        <v>3.002679159914134</v>
+        <v>3.002679159914133</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.942420361200354</v>
+        <v>2.942420361200353</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.932367932658555</v>
+        <v>2.82831823181738</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.110964338535786</v>
+        <v>3.110964338535785</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.914508049637804</v>
+        <v>2.914508049637803</v>
       </c>
     </row>
   </sheetData>
@@ -1449,22 +1449,22 @@
         <v>2.391280928544738</v>
       </c>
       <c r="C2" t="n">
-        <v>2.433071272595622</v>
+        <v>2.433071272595621</v>
       </c>
       <c r="D2" t="n">
         <v>2.399182350803846</v>
       </c>
       <c r="E2" t="n">
-        <v>2.417759209882346</v>
+        <v>2.417759209882345</v>
       </c>
       <c r="F2" t="n">
-        <v>2.436171733987307</v>
+        <v>2.436171733987306</v>
       </c>
       <c r="G2" t="n">
-        <v>2.393525434624903</v>
+        <v>2.393525434624902</v>
       </c>
       <c r="H2" t="n">
-        <v>2.397229327828335</v>
+        <v>2.397229327828334</v>
       </c>
       <c r="I2" t="n">
         <v>2.398452535241633</v>
@@ -1473,13 +1473,13 @@
         <v>2.398611500928109</v>
       </c>
       <c r="K2" t="n">
-        <v>2.400460609202908</v>
+        <v>2.400460609202907</v>
       </c>
       <c r="L2" t="n">
-        <v>2.40442834455124</v>
+        <v>2.404428344551239</v>
       </c>
       <c r="M2" t="n">
-        <v>2.402450456201668</v>
+        <v>2.402450456201667</v>
       </c>
       <c r="N2" t="n">
         <v>2.392530005152984</v>
@@ -1494,7 +1494,7 @@
         <v>2.391685848318817</v>
       </c>
       <c r="R2" t="n">
-        <v>2.399522495210289</v>
+        <v>2.399522495210288</v>
       </c>
       <c r="S2" t="n">
         <v>2.403540885314018</v>
@@ -1506,22 +1506,22 @@
         <v>2.428340086474766</v>
       </c>
       <c r="V2" t="n">
-        <v>2.397528546789444</v>
+        <v>2.397528546789443</v>
       </c>
       <c r="W2" t="n">
-        <v>2.430085084197406</v>
+        <v>2.430085084197405</v>
       </c>
       <c r="X2" t="n">
         <v>2.402856833618326</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.393064339602458</v>
+        <v>2.393064339602457</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.409597747827682</v>
+        <v>2.409597747827681</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.397125652097348</v>
+        <v>2.397125652097347</v>
       </c>
       <c r="AB2" t="n">
         <v>2.394942429295534</v>
@@ -1540,25 +1540,25 @@
         <v>2.658954072250728</v>
       </c>
       <c r="D3" t="n">
-        <v>2.444984272932359</v>
+        <v>2.444984272932358</v>
       </c>
       <c r="E3" t="n">
         <v>2.576752273022413</v>
       </c>
       <c r="F3" t="n">
-        <v>2.709344705562102</v>
+        <v>2.709344705562101</v>
       </c>
       <c r="G3" t="n">
         <v>2.404526382693799</v>
       </c>
       <c r="H3" t="n">
-        <v>2.431257373712198</v>
+        <v>2.431257373712197</v>
       </c>
       <c r="I3" t="n">
-        <v>2.439897750266268</v>
+        <v>2.439897750266267</v>
       </c>
       <c r="J3" t="n">
-        <v>2.440826447043818</v>
+        <v>2.440826447043817</v>
       </c>
       <c r="K3" t="n">
         <v>2.453832009426869</v>
@@ -1573,13 +1573,13 @@
         <v>2.397536219217789</v>
       </c>
       <c r="O3" t="n">
-        <v>2.47650462316903</v>
+        <v>2.476504623169029</v>
       </c>
       <c r="P3" t="n">
-        <v>2.444295794473844</v>
+        <v>2.444295794473843</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.391496855255021</v>
+        <v>2.391496855255022</v>
       </c>
       <c r="R3" t="n">
         <v>2.447654368541342</v>
@@ -1597,13 +1597,13 @@
         <v>2.432934349427993</v>
       </c>
       <c r="W3" t="n">
-        <v>2.475336776976369</v>
+        <v>2.475336776976368</v>
       </c>
       <c r="X3" t="n">
-        <v>2.471120823841588</v>
+        <v>2.471120823841586</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.401345349780475</v>
+        <v>2.401345349780474</v>
       </c>
       <c r="Z3" t="n">
         <v>2.425337264607395</v>
@@ -1646,19 +1646,19 @@
         <v>2.177842374795395</v>
       </c>
       <c r="J4" t="n">
-        <v>2.17966618957939</v>
+        <v>2.179666189579389</v>
       </c>
       <c r="K4" t="n">
         <v>2.200524493947655</v>
       </c>
       <c r="L4" t="n">
-        <v>2.245341889955499</v>
+        <v>2.2453418899555</v>
       </c>
       <c r="M4" t="n">
         <v>2.223278724601687</v>
       </c>
       <c r="N4" t="n">
-        <v>2.461655237951348</v>
+        <v>2.461655237951347</v>
       </c>
       <c r="O4" t="n">
         <v>2.152195927784768</v>
@@ -1688,7 +1688,7 @@
         <v>2.143535549266991</v>
       </c>
       <c r="X4" t="n">
-        <v>2.227590951037497</v>
+        <v>2.227590951037498</v>
       </c>
       <c r="Y4" t="n">
         <v>2.117259224417912</v>
@@ -1697,7 +1697,7 @@
         <v>2.110349984428961</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.162854619284286</v>
+        <v>2.162854619284287</v>
       </c>
       <c r="AB4" t="n">
         <v>2.139282924855844</v>
@@ -1713,82 +1713,82 @@
         <v>2.200509437172228</v>
       </c>
       <c r="C5" t="n">
-        <v>9.354019532855375</v>
+        <v>9.354019532855384</v>
       </c>
       <c r="D5" t="n">
-        <v>3.775070789718171</v>
+        <v>3.775070789718172</v>
       </c>
       <c r="E5" t="n">
-        <v>7.063478923807866</v>
+        <v>7.063478923807874</v>
       </c>
       <c r="F5" t="n">
-        <v>11.35410621736747</v>
+        <v>11.35410621736746</v>
       </c>
       <c r="G5" t="n">
-        <v>2.601305381689862</v>
+        <v>2.601305381689869</v>
       </c>
       <c r="H5" t="n">
-        <v>3.494721896259026</v>
+        <v>3.494721896259027</v>
       </c>
       <c r="I5" t="n">
-        <v>3.692599958653718</v>
+        <v>3.692599958653714</v>
       </c>
       <c r="J5" t="n">
-        <v>3.617710002734403</v>
+        <v>3.617710002734397</v>
       </c>
       <c r="K5" t="n">
-        <v>3.887794592508186</v>
+        <v>3.887794592508185</v>
       </c>
       <c r="L5" t="n">
-        <v>4.583257366252183</v>
+        <v>4.58325736625218</v>
       </c>
       <c r="M5" t="n">
-        <v>4.464792989827332</v>
+        <v>4.46479298982733</v>
       </c>
       <c r="N5" t="n">
-        <v>2.461655237951348</v>
+        <v>2.461655237951347</v>
       </c>
       <c r="O5" t="n">
         <v>3.064549852192891</v>
       </c>
       <c r="P5" t="n">
-        <v>3.5969898487514</v>
+        <v>3.596989848751395</v>
       </c>
       <c r="Q5" t="n">
         <v>2.285457663050181</v>
       </c>
       <c r="R5" t="n">
-        <v>3.968677361192238</v>
+        <v>3.968677361192239</v>
       </c>
       <c r="S5" t="n">
-        <v>4.392625016039462</v>
+        <v>4.392625016039456</v>
       </c>
       <c r="T5" t="n">
-        <v>2.92611196241177</v>
+        <v>2.926111962411771</v>
       </c>
       <c r="U5" t="n">
-        <v>3.357134736777419</v>
+        <v>3.357134736777416</v>
       </c>
       <c r="V5" t="n">
-        <v>3.316966582800005</v>
+        <v>3.316966582800007</v>
       </c>
       <c r="W5" t="n">
-        <v>3.027283513137325</v>
+        <v>3.027283513137324</v>
       </c>
       <c r="X5" t="n">
-        <v>4.463335324642951</v>
+        <v>4.463335324642946</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.566102502558524</v>
+        <v>2.566102502558523</v>
       </c>
       <c r="Z5" t="n">
         <v>2.407844828562325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.384913813205772</v>
+        <v>3.384913813205773</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.023699941506059</v>
+        <v>3.023699941506062</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.57726259969096</v>
+        <v>3.189399630609591</v>
       </c>
       <c r="C6" t="n">
-        <v>15.99323740168362</v>
+        <v>3.605374432602262</v>
       </c>
       <c r="D6" t="n">
         <v>15.66651279894139</v>
       </c>
       <c r="E6" t="n">
-        <v>15.87634696801045</v>
+        <v>3.488483998929081</v>
       </c>
       <c r="F6" t="n">
-        <v>16.08432489795553</v>
+        <v>3.696461928874174</v>
       </c>
       <c r="G6" t="n">
-        <v>3.214752359308854</v>
+        <v>15.6026153283902</v>
       </c>
       <c r="H6" t="n">
-        <v>3.256589536916687</v>
+        <v>15.64445250599805</v>
       </c>
       <c r="I6" t="n">
-        <v>3.270406227353096</v>
+        <v>15.65826919643444</v>
       </c>
       <c r="J6" t="n">
-        <v>3.272230042137092</v>
+        <v>15.66009301121846</v>
       </c>
       <c r="K6" t="n">
-        <v>15.68095131558673</v>
+        <v>3.293088346505364</v>
       </c>
       <c r="L6" t="n">
-        <v>3.337905742513204</v>
+        <v>15.72576871159455</v>
       </c>
       <c r="M6" t="n">
-        <v>3.315842577159391</v>
+        <v>15.70370554624076</v>
       </c>
       <c r="N6" t="n">
-        <v>2.461655237951348</v>
+        <v>2.461655237951347</v>
       </c>
       <c r="O6" t="n">
         <v>15.63150574089236</v>
       </c>
       <c r="P6" t="n">
-        <v>3.273956298757529</v>
+        <v>15.66482164193153</v>
       </c>
       <c r="Q6" t="n">
         <v>15.58183635481148</v>
       </c>
       <c r="R6" t="n">
-        <v>3.282491917404969</v>
+        <v>15.67035488648634</v>
       </c>
       <c r="S6" t="n">
-        <v>3.327881482177362</v>
+        <v>15.71574445125873</v>
       </c>
       <c r="T6" t="n">
-        <v>15.61600833355051</v>
+        <v>3.22814536446915</v>
       </c>
       <c r="U6" t="n">
-        <v>3.262611217845885</v>
+        <v>15.65047418692726</v>
       </c>
       <c r="V6" t="n">
-        <v>3.260076080689489</v>
+        <v>15.64793904977086</v>
       </c>
       <c r="W6" t="n">
-        <v>3.237200971185965</v>
+        <v>3.237200971185964</v>
       </c>
       <c r="X6" t="n">
-        <v>3.320154803595198</v>
+        <v>3.320154803595199</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.226494648132479</v>
+        <v>3.226494648132481</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.59077680606803</v>
+        <v>3.202913836986667</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.255418471841992</v>
+        <v>3.255418471841994</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.230444668954726</v>
+        <v>3.230444668954727</v>
       </c>
     </row>
     <row r="7">
@@ -1907,10 +1907,10 @@
         <v>2.224142189869161</v>
       </c>
       <c r="I7" t="n">
-        <v>2.23795888030558</v>
+        <v>2.237958880305579</v>
       </c>
       <c r="J7" t="n">
-        <v>2.239782695089574</v>
+        <v>2.239782695089573</v>
       </c>
       <c r="K7" t="n">
         <v>2.26064099945784</v>
@@ -1919,10 +1919,10 @@
         <v>2.305458395465683</v>
       </c>
       <c r="M7" t="n">
-        <v>2.283395230111872</v>
+        <v>2.283395230111871</v>
       </c>
       <c r="N7" t="n">
-        <v>2.461655237951348</v>
+        <v>2.461655237951347</v>
       </c>
       <c r="O7" t="n">
         <v>2.212308020281305</v>
@@ -1977,22 +1977,22 @@
         <v>2.165664103836845</v>
       </c>
       <c r="C8" t="n">
-        <v>2.630100112176043</v>
+        <v>2.630100112176044</v>
       </c>
       <c r="D8" t="n">
-        <v>2.303375509433819</v>
+        <v>2.30337550943382</v>
       </c>
       <c r="E8" t="n">
-        <v>2.513209678502863</v>
+        <v>2.487405515640562</v>
       </c>
       <c r="F8" t="n">
         <v>2.680276091671722</v>
       </c>
       <c r="G8" t="n">
-        <v>2.239478038882642</v>
+        <v>2.249526785713652</v>
       </c>
       <c r="H8" t="n">
-        <v>2.281315216490462</v>
+        <v>2.281315216490463</v>
       </c>
       <c r="I8" t="n">
         <v>2.295131906926881</v>
@@ -2007,16 +2007,16 @@
         <v>2.362631422086986</v>
       </c>
       <c r="M8" t="n">
-        <v>2.340568256733173</v>
+        <v>2.340568256733186</v>
       </c>
       <c r="N8" t="n">
-        <v>2.461655237951348</v>
+        <v>2.461655237951347</v>
       </c>
       <c r="O8" t="n">
         <v>2.242243254812063</v>
       </c>
       <c r="P8" t="n">
-        <v>2.273025877908791</v>
+        <v>2.273025877908792</v>
       </c>
       <c r="Q8" t="n">
         <v>2.160714125838591</v>
@@ -2031,10 +2031,10 @@
         <v>2.252871044042929</v>
       </c>
       <c r="U8" t="n">
-        <v>2.257543860534811</v>
+        <v>2.263712880360678</v>
       </c>
       <c r="V8" t="n">
-        <v>2.284801760263269</v>
+        <v>2.271588844809025</v>
       </c>
       <c r="W8" t="n">
         <v>2.260834605409608</v>
@@ -2046,7 +2046,7 @@
         <v>2.282503672787383</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.227639516560447</v>
+        <v>2.178278118426508</v>
       </c>
       <c r="AA8" t="n">
         <v>2.280144151415772</v>
@@ -2071,34 +2071,34 @@
         <v>2.658923757593452</v>
       </c>
       <c r="E9" t="n">
-        <v>2.868757926662493</v>
+        <v>2.844743913502074</v>
       </c>
       <c r="F9" t="n">
-        <v>3.076735856607586</v>
+        <v>2.836875408757331</v>
       </c>
       <c r="G9" t="n">
-        <v>2.595026287042274</v>
+        <v>2.595026267090311</v>
       </c>
       <c r="H9" t="n">
-        <v>2.636863464650094</v>
+        <v>2.636863464650095</v>
       </c>
       <c r="I9" t="n">
         <v>2.650680155086513</v>
       </c>
       <c r="J9" t="n">
-        <v>2.65250396987051</v>
+        <v>2.652503969870509</v>
       </c>
       <c r="K9" t="n">
         <v>2.673362274238773</v>
       </c>
       <c r="L9" t="n">
-        <v>2.718179670246613</v>
+        <v>2.718179670246614</v>
       </c>
       <c r="M9" t="n">
         <v>2.6961165048928</v>
       </c>
       <c r="N9" t="n">
-        <v>2.461655237951348</v>
+        <v>2.461655237951347</v>
       </c>
       <c r="O9" t="n">
         <v>2.659515258979388</v>
@@ -2113,7 +2113,7 @@
         <v>2.662765845138383</v>
       </c>
       <c r="S9" t="n">
-        <v>2.708155409910777</v>
+        <v>2.708155409910776</v>
       </c>
       <c r="T9" t="n">
         <v>2.608419292202561</v>
@@ -2122,7 +2122,7 @@
         <v>2.642885145579302</v>
       </c>
       <c r="V9" t="n">
-        <v>2.6403500084229</v>
+        <v>2.76041977407089</v>
       </c>
       <c r="W9" t="n">
         <v>2.616373329558109</v>
@@ -2134,7 +2134,7 @@
         <v>2.589818006649561</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.583187764720077</v>
+        <v>2.520455689410739</v>
       </c>
       <c r="AA9" t="n">
         <v>2.635692399575404</v>
@@ -2312,7 +2312,7 @@
         <v>2.44713505950887</v>
       </c>
       <c r="D2" t="n">
-        <v>2.426132106396518</v>
+        <v>2.426132106396519</v>
       </c>
       <c r="E2" t="n">
         <v>2.43818358583104</v>
@@ -2327,7 +2327,7 @@
         <v>2.404839269708559</v>
       </c>
       <c r="I2" t="n">
-        <v>2.422065674666781</v>
+        <v>2.422065674666782</v>
       </c>
       <c r="J2" t="n">
         <v>2.406633707000734</v>
@@ -2351,19 +2351,19 @@
         <v>2.404556244199608</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.399504598522659</v>
+        <v>2.39950459852266</v>
       </c>
       <c r="R2" t="n">
         <v>2.415380073938699</v>
       </c>
       <c r="S2" t="n">
-        <v>2.411833435561665</v>
+        <v>2.411833435561666</v>
       </c>
       <c r="T2" t="n">
         <v>2.400372807290191</v>
       </c>
       <c r="U2" t="n">
-        <v>2.440614239225635</v>
+        <v>2.440614239225634</v>
       </c>
       <c r="V2" t="n">
         <v>2.407791482191274</v>
@@ -2384,7 +2384,7 @@
         <v>2.413479116794893</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.399683627378592</v>
+        <v>2.399683627378591</v>
       </c>
     </row>
     <row r="3">
@@ -2409,7 +2409,7 @@
         <v>2.722243705587065</v>
       </c>
       <c r="G3" t="n">
-        <v>2.425814507068224</v>
+        <v>2.425814507068225</v>
       </c>
       <c r="H3" t="n">
         <v>2.442110958723986</v>
@@ -2421,7 +2421,7 @@
         <v>2.454614099127701</v>
       </c>
       <c r="K3" t="n">
-        <v>2.475083757987525</v>
+        <v>2.475083757987526</v>
       </c>
       <c r="L3" t="n">
         <v>2.46555399613972</v>
@@ -2430,13 +2430,13 @@
         <v>2.451210826923119</v>
       </c>
       <c r="N3" t="n">
-        <v>2.405245969296817</v>
+        <v>2.405245969296818</v>
       </c>
       <c r="O3" t="n">
         <v>2.478241928980586</v>
       </c>
       <c r="P3" t="n">
-        <v>2.439655164017572</v>
+        <v>2.439655164017573</v>
       </c>
       <c r="Q3" t="n">
         <v>2.403783696990968</v>
@@ -2460,10 +2460,10 @@
         <v>2.496004282029384</v>
       </c>
       <c r="X3" t="n">
-        <v>2.465100053346036</v>
+        <v>2.465100053346037</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.42424168798322</v>
+        <v>2.424241687983221</v>
       </c>
       <c r="Z3" t="n">
         <v>2.449159504094738</v>
@@ -2485,16 +2485,16 @@
         <v>2.11595887212932</v>
       </c>
       <c r="C4" t="n">
-        <v>2.599642321686719</v>
+        <v>2.59964232168672</v>
       </c>
       <c r="D4" t="n">
-        <v>2.423904096970122</v>
+        <v>2.423904096970123</v>
       </c>
       <c r="E4" t="n">
         <v>2.560031101137481</v>
       </c>
       <c r="F4" t="n">
-        <v>2.625558320699132</v>
+        <v>2.625558320699131</v>
       </c>
       <c r="G4" t="n">
         <v>2.158196360491135</v>
@@ -2503,13 +2503,13 @@
         <v>2.183391711390805</v>
       </c>
       <c r="I4" t="n">
-        <v>2.377971879931734</v>
+        <v>2.377971879931735</v>
       </c>
       <c r="J4" t="n">
-        <v>2.203690853853927</v>
+        <v>2.203690853853928</v>
       </c>
       <c r="K4" t="n">
-        <v>2.236142312832488</v>
+        <v>2.236142312832489</v>
       </c>
       <c r="L4" t="n">
         <v>2.22095687535607</v>
@@ -2533,7 +2533,7 @@
         <v>2.302454944179753</v>
       </c>
       <c r="S4" t="n">
-        <v>2.262394032176899</v>
+        <v>2.2623940321769</v>
       </c>
       <c r="T4" t="n">
         <v>2.132940963701119</v>
@@ -2548,7 +2548,7 @@
         <v>2.173144160560683</v>
       </c>
       <c r="X4" t="n">
-        <v>2.219976737803773</v>
+        <v>2.219976737803774</v>
       </c>
       <c r="Y4" t="n">
         <v>2.155876362679044</v>
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.368959748903622</v>
+        <v>2.368959748903621</v>
       </c>
       <c r="C5" t="n">
-        <v>11.64691047607936</v>
+        <v>11.64691047607934</v>
       </c>
       <c r="D5" t="n">
-        <v>8.548639997264109</v>
+        <v>8.548639997264093</v>
       </c>
       <c r="E5" t="n">
         <v>10.71925731150388</v>
@@ -2585,70 +2585,70 @@
         <v>12.58891767169357</v>
       </c>
       <c r="G5" t="n">
-        <v>3.125861592047941</v>
+        <v>3.125861592047955</v>
       </c>
       <c r="H5" t="n">
-        <v>3.811777245578802</v>
+        <v>3.811777245578803</v>
       </c>
       <c r="I5" t="n">
-        <v>7.698159731700861</v>
+        <v>7.698159731700859</v>
       </c>
       <c r="J5" t="n">
-        <v>4.026065856365774</v>
+        <v>4.026065856365781</v>
       </c>
       <c r="K5" t="n">
         <v>4.610227675095381</v>
       </c>
       <c r="L5" t="n">
-        <v>4.359350032793902</v>
+        <v>4.359350032793905</v>
       </c>
       <c r="M5" t="n">
-        <v>4.056436681620543</v>
+        <v>4.056436681620546</v>
       </c>
       <c r="N5" t="n">
-        <v>4.228537814053322</v>
+        <v>4.228537814053319</v>
       </c>
       <c r="O5" t="n">
-        <v>3.017550176114052</v>
+        <v>3.017550176114054</v>
       </c>
       <c r="P5" t="n">
-        <v>3.50894403527938</v>
+        <v>3.508944035279381</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.531477541018646</v>
+        <v>2.531477541018647</v>
       </c>
       <c r="R5" t="n">
-        <v>6.227080853587302</v>
+        <v>6.227080853587307</v>
       </c>
       <c r="S5" t="n">
-        <v>4.994438540020085</v>
+        <v>4.994438540020091</v>
       </c>
       <c r="T5" t="n">
-        <v>2.737991103906234</v>
+        <v>2.737991103906233</v>
       </c>
       <c r="U5" t="n">
-        <v>4.324681480833068</v>
+        <v>4.324681480833065</v>
       </c>
       <c r="V5" t="n">
-        <v>4.085408201531063</v>
+        <v>4.085408201531059</v>
       </c>
       <c r="W5" t="n">
         <v>3.47076883039917</v>
       </c>
       <c r="X5" t="n">
-        <v>4.432782067920492</v>
+        <v>4.432782067920497</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.130952129778042</v>
+        <v>3.130952129778045</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.89287824015035</v>
+        <v>2.892878240150349</v>
       </c>
       <c r="AA5" t="n">
         <v>5.51581803351219</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.651879847365035</v>
+        <v>2.651879847365034</v>
       </c>
     </row>
     <row r="6">
@@ -2658,43 +2658,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.58892447748065</v>
+        <v>3.292054924412529</v>
       </c>
       <c r="C6" t="n">
         <v>17.07260792703803</v>
       </c>
       <c r="D6" t="n">
-        <v>3.600000149253337</v>
+        <v>16.89686970232144</v>
       </c>
       <c r="E6" t="n">
-        <v>3.736127153420688</v>
+        <v>3.736127153420687</v>
       </c>
       <c r="F6" t="n">
-        <v>17.09852392605045</v>
+        <v>3.801654372982334</v>
       </c>
       <c r="G6" t="n">
-        <v>16.63116196584244</v>
+        <v>3.334292412774348</v>
       </c>
       <c r="H6" t="n">
-        <v>3.359487763674015</v>
+        <v>16.65635731674212</v>
       </c>
       <c r="I6" t="n">
-        <v>3.554067932214942</v>
+        <v>3.554067932214943</v>
       </c>
       <c r="J6" t="n">
         <v>16.67665645920524</v>
       </c>
       <c r="K6" t="n">
-        <v>3.412238365115689</v>
+        <v>16.70910791818381</v>
       </c>
       <c r="L6" t="n">
         <v>3.397052927639286</v>
       </c>
       <c r="M6" t="n">
-        <v>3.374176675247581</v>
+        <v>3.37417667524758</v>
       </c>
       <c r="N6" t="n">
-        <v>3.299487353152403</v>
+        <v>3.299487353152404</v>
       </c>
       <c r="O6" t="n">
         <v>16.62647643186902</v>
@@ -2703,19 +2703,19 @@
         <v>16.65228493839375</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.299230198559297</v>
+        <v>16.59609975162741</v>
       </c>
       <c r="R6" t="n">
-        <v>3.478550996462961</v>
+        <v>16.77542054953106</v>
       </c>
       <c r="S6" t="n">
-        <v>3.438490084460112</v>
+        <v>16.73535963752823</v>
       </c>
       <c r="T6" t="n">
-        <v>16.60590656905243</v>
+        <v>3.309037015984329</v>
       </c>
       <c r="U6" t="n">
-        <v>16.69456229771067</v>
+        <v>3.39769274464257</v>
       </c>
       <c r="V6" t="n">
         <v>16.68982470842395</v>
@@ -2724,16 +2724,16 @@
         <v>16.64523120920316</v>
       </c>
       <c r="X6" t="n">
-        <v>3.39607279008698</v>
+        <v>16.69294234315509</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.349346321250125</v>
+        <v>3.349346321250126</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.321225596216394</v>
+        <v>16.61809514928452</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.75394836410829</v>
+        <v>3.45707881104019</v>
       </c>
       <c r="AB6" t="n">
         <v>3.300844094155423</v>
@@ -2755,19 +2755,19 @@
         <v>2.491883407347502</v>
       </c>
       <c r="E7" t="n">
-        <v>2.62801041151486</v>
+        <v>2.628010411514861</v>
       </c>
       <c r="F7" t="n">
-        <v>2.693537631076511</v>
+        <v>2.693537631076512</v>
       </c>
       <c r="G7" t="n">
-        <v>2.226175670868515</v>
+        <v>2.226175670868514</v>
       </c>
       <c r="H7" t="n">
-        <v>2.251371021768184</v>
+        <v>2.251371021768185</v>
       </c>
       <c r="I7" t="n">
-        <v>2.445951190309114</v>
+        <v>2.445951190309115</v>
       </c>
       <c r="J7" t="n">
         <v>2.271670164231307</v>
@@ -2843,13 +2843,13 @@
         <v>2.558460255033309</v>
       </c>
       <c r="E8" t="n">
-        <v>2.694587259200667</v>
+        <v>2.664885198421373</v>
       </c>
       <c r="F8" t="n">
         <v>2.713022993394445</v>
       </c>
       <c r="G8" t="n">
-        <v>2.292752518554322</v>
+        <v>2.304319198346396</v>
       </c>
       <c r="H8" t="n">
         <v>2.317947869453991</v>
@@ -2867,19 +2867,19 @@
         <v>2.355513033419257</v>
       </c>
       <c r="M8" t="n">
-        <v>2.332636781027555</v>
+        <v>2.332636781027547</v>
       </c>
       <c r="N8" t="n">
         <v>2.216769105418243</v>
       </c>
       <c r="O8" t="n">
-        <v>2.257586399268193</v>
+        <v>2.257586399268194</v>
       </c>
       <c r="P8" t="n">
         <v>2.280480887955826</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.190946337272062</v>
+        <v>2.190946337272063</v>
       </c>
       <c r="R8" t="n">
         <v>2.437011102242938</v>
@@ -2891,10 +2891,10 @@
         <v>2.267497121764305</v>
       </c>
       <c r="U8" t="n">
-        <v>2.321835612768115</v>
+        <v>2.328934962231667</v>
       </c>
       <c r="V8" t="n">
-        <v>2.351415261135819</v>
+        <v>2.336178538619646</v>
       </c>
       <c r="W8" t="n">
         <v>2.30771128130286</v>
@@ -2906,7 +2906,7 @@
         <v>2.345583133704299</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.279685701996371</v>
+        <v>2.222867922037912</v>
       </c>
       <c r="AA8" t="n">
         <v>2.415538916820168</v>
@@ -2925,19 +2925,19 @@
         <v>2.622304608230426</v>
       </c>
       <c r="C9" t="n">
-        <v>3.248514178566552</v>
+        <v>3.248514178566553</v>
       </c>
       <c r="D9" t="n">
-        <v>3.072775953849953</v>
+        <v>3.072775953849955</v>
       </c>
       <c r="E9" t="n">
-        <v>3.208902958017312</v>
+        <v>3.176008514278129</v>
       </c>
       <c r="F9" t="n">
-        <v>3.274430177578963</v>
+        <v>2.945868564034739</v>
       </c>
       <c r="G9" t="n">
-        <v>2.807068217370964</v>
+        <v>2.807068222029157</v>
       </c>
       <c r="H9" t="n">
         <v>2.832263568270639</v>
@@ -2952,7 +2952,7 @@
         <v>2.885014169712321</v>
       </c>
       <c r="L9" t="n">
-        <v>2.869828732235902</v>
+        <v>2.869828732235903</v>
       </c>
       <c r="M9" t="n">
         <v>2.846952479844201</v>
@@ -2961,10 +2961,10 @@
         <v>2.77432488245945</v>
       </c>
       <c r="O9" t="n">
-        <v>2.850492403374815</v>
+        <v>2.850492403374817</v>
       </c>
       <c r="P9" t="n">
-        <v>2.886572001841577</v>
+        <v>2.886572001841578</v>
       </c>
       <c r="Q9" t="n">
         <v>2.772006007814113</v>
@@ -2979,28 +2979,28 @@
         <v>2.781812820580948</v>
       </c>
       <c r="U9" t="n">
-        <v>2.870468549239192</v>
+        <v>2.870468549239193</v>
       </c>
       <c r="V9" t="n">
-        <v>2.865730959952465</v>
+        <v>3.030202969594644</v>
       </c>
       <c r="W9" t="n">
-        <v>2.822016017440513</v>
+        <v>2.822016017440514</v>
       </c>
       <c r="X9" t="n">
-        <v>2.868848594683604</v>
+        <v>2.868848594683605</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.804422130523008</v>
+        <v>2.804422130523009</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.794001400813013</v>
+        <v>2.708070825750363</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.929854615636813</v>
+        <v>2.929854615636814</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.776158249961721</v>
+        <v>2.776158249961722</v>
       </c>
     </row>
   </sheetData>
@@ -3184,7 +3184,7 @@
         <v>2.399868376831045</v>
       </c>
       <c r="H2" t="n">
-        <v>2.401763841166304</v>
+        <v>2.401763841166303</v>
       </c>
       <c r="I2" t="n">
         <v>2.407181714659363</v>
@@ -3193,7 +3193,7 @@
         <v>2.403007547495728</v>
       </c>
       <c r="K2" t="n">
-        <v>2.404597643892148</v>
+        <v>2.404597643892147</v>
       </c>
       <c r="L2" t="n">
         <v>2.405370401487377</v>
@@ -3202,10 +3202,10 @@
         <v>2.401623401824076</v>
       </c>
       <c r="N2" t="n">
-        <v>2.396992422906926</v>
+        <v>2.396992422906925</v>
       </c>
       <c r="O2" t="n">
-        <v>2.434095913918475</v>
+        <v>2.434095913918474</v>
       </c>
       <c r="P2" t="n">
         <v>2.401686455280143</v>
@@ -3220,7 +3220,7 @@
         <v>2.406084036410856</v>
       </c>
       <c r="T2" t="n">
-        <v>2.398754399662095</v>
+        <v>2.398754399662094</v>
       </c>
       <c r="U2" t="n">
         <v>2.434085168554694</v>
@@ -3238,10 +3238,10 @@
         <v>2.399312603977031</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.417772554614866</v>
+        <v>2.417772554614865</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.406005390129371</v>
+        <v>2.40600539012937</v>
       </c>
       <c r="AB2" t="n">
         <v>2.39807934524726</v>
@@ -3272,7 +3272,7 @@
         <v>2.421731303774957</v>
       </c>
       <c r="H3" t="n">
-        <v>2.435643289352185</v>
+        <v>2.435643289352186</v>
       </c>
       <c r="I3" t="n">
         <v>2.474341891344105</v>
@@ -3284,13 +3284,13 @@
         <v>2.455391312427664</v>
       </c>
       <c r="L3" t="n">
-        <v>2.461081237999128</v>
+        <v>2.461081237999127</v>
       </c>
       <c r="M3" t="n">
         <v>2.435235731887647</v>
       </c>
       <c r="N3" t="n">
-        <v>2.401339289643507</v>
+        <v>2.401339289643508</v>
       </c>
       <c r="O3" t="n">
         <v>2.481823578762151</v>
@@ -3311,16 +3311,16 @@
         <v>2.413976402959335</v>
       </c>
       <c r="U3" t="n">
-        <v>2.487172127256853</v>
+        <v>2.487172127256854</v>
       </c>
       <c r="V3" t="n">
-        <v>2.454289980545445</v>
+        <v>2.454289980545444</v>
       </c>
       <c r="W3" t="n">
         <v>2.490290004851808</v>
       </c>
       <c r="X3" t="n">
-        <v>2.46536099186417</v>
+        <v>2.465360991864171</v>
       </c>
       <c r="Y3" t="n">
         <v>2.417882747745082</v>
@@ -3348,13 +3348,13 @@
         <v>2.500483439900913</v>
       </c>
       <c r="D4" t="n">
-        <v>2.29732773856568</v>
+        <v>2.297327738565679</v>
       </c>
       <c r="E4" t="n">
         <v>2.432013352966645</v>
       </c>
       <c r="F4" t="n">
-        <v>2.585589425317979</v>
+        <v>2.58558942531798</v>
       </c>
       <c r="G4" t="n">
         <v>2.150773404910559</v>
@@ -3381,7 +3381,7 @@
         <v>2.118288182333465</v>
       </c>
       <c r="O4" t="n">
-        <v>2.158371669923438</v>
+        <v>2.158371669923439</v>
       </c>
       <c r="P4" t="n">
         <v>2.17130943735053</v>
@@ -3399,7 +3399,7 @@
         <v>2.138190520332451</v>
       </c>
       <c r="U4" t="n">
-        <v>2.169505972080807</v>
+        <v>2.169505972080808</v>
       </c>
       <c r="V4" t="n">
         <v>2.202846522114238</v>
@@ -3433,79 +3433,79 @@
         <v>2.335404985892862</v>
       </c>
       <c r="C5" t="n">
-        <v>9.095151522829912</v>
+        <v>9.095151522829909</v>
       </c>
       <c r="D5" t="n">
         <v>5.801061239321728</v>
       </c>
       <c r="E5" t="n">
-        <v>7.997740794802313</v>
+        <v>7.997740794802306</v>
       </c>
       <c r="F5" t="n">
-        <v>11.09480617309459</v>
+        <v>11.09480617309458</v>
       </c>
       <c r="G5" t="n">
-        <v>2.986257798924971</v>
+        <v>2.986257798924969</v>
       </c>
       <c r="H5" t="n">
-        <v>3.563910131044291</v>
+        <v>3.56391013104429</v>
       </c>
       <c r="I5" t="n">
-        <v>4.662335450376658</v>
+        <v>4.662335450376659</v>
       </c>
       <c r="J5" t="n">
-        <v>3.650196281925236</v>
+        <v>3.650196281925235</v>
       </c>
       <c r="K5" t="n">
         <v>3.882867261821818</v>
       </c>
       <c r="L5" t="n">
-        <v>4.127790075026627</v>
+        <v>4.127790075026628</v>
       </c>
       <c r="M5" t="n">
-        <v>3.508432543098823</v>
+        <v>3.508432543098824</v>
       </c>
       <c r="N5" t="n">
-        <v>3.277881117971707</v>
+        <v>3.277881117971717</v>
       </c>
       <c r="O5" t="n">
-        <v>3.07031194140529</v>
+        <v>3.070311941405291</v>
       </c>
       <c r="P5" t="n">
-        <v>3.318942220800467</v>
+        <v>3.318942220800471</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.523060893197421</v>
+        <v>2.523060893197423</v>
       </c>
       <c r="R5" t="n">
         <v>5.862276747940213</v>
       </c>
       <c r="S5" t="n">
-        <v>4.158758441564092</v>
+        <v>4.158758441564095</v>
       </c>
       <c r="T5" t="n">
-        <v>2.865078533427642</v>
+        <v>2.865078533427645</v>
       </c>
       <c r="U5" t="n">
-        <v>3.328747149466561</v>
+        <v>3.328747149466573</v>
       </c>
       <c r="V5" t="n">
-        <v>3.770619776218929</v>
+        <v>3.770619776218922</v>
       </c>
       <c r="W5" t="n">
-        <v>3.254872465380092</v>
+        <v>3.254872465380091</v>
       </c>
       <c r="X5" t="n">
-        <v>4.329449011387239</v>
+        <v>4.329449011387246</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.936388328064769</v>
+        <v>2.936388328064778</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.714877305096774</v>
+        <v>2.714877305096775</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.286104634747329</v>
+        <v>4.286104634747328</v>
       </c>
       <c r="AB5" t="n">
         <v>2.786293151101757</v>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.59455579530637</v>
+        <v>3.205123562599156</v>
       </c>
       <c r="C6" t="n">
         <v>3.594321892336104</v>
@@ -3530,25 +3530,25 @@
         <v>3.525851805401837</v>
       </c>
       <c r="F6" t="n">
-        <v>3.679427877753168</v>
+        <v>16.06886011046039</v>
       </c>
       <c r="G6" t="n">
-        <v>15.63404409005297</v>
+        <v>3.244611857345745</v>
       </c>
       <c r="H6" t="n">
         <v>3.266021998969165</v>
       </c>
       <c r="I6" t="n">
-        <v>15.71665160512545</v>
+        <v>3.327219372418213</v>
       </c>
       <c r="J6" t="n">
-        <v>15.6695346321332</v>
+        <v>15.66953463213319</v>
       </c>
       <c r="K6" t="n">
-        <v>3.29803110437124</v>
+        <v>15.68746333707845</v>
       </c>
       <c r="L6" t="n">
-        <v>15.69619198960264</v>
+        <v>3.306759756895406</v>
       </c>
       <c r="M6" t="n">
         <v>15.65513987999323</v>
@@ -3557,7 +3557,7 @@
         <v>3.210769053414966</v>
       </c>
       <c r="O6" t="n">
-        <v>15.64093289562581</v>
+        <v>3.250852541004938</v>
       </c>
       <c r="P6" t="n">
         <v>15.65387214022694</v>
@@ -3566,34 +3566,34 @@
         <v>15.60410395764295</v>
       </c>
       <c r="R6" t="n">
-        <v>15.77692640112146</v>
+        <v>15.77692640112145</v>
       </c>
       <c r="S6" t="n">
-        <v>3.314820591644388</v>
+        <v>3.314820591644389</v>
       </c>
       <c r="T6" t="n">
         <v>3.232028972767642</v>
       </c>
       <c r="U6" t="n">
-        <v>15.65242489897074</v>
+        <v>3.262992666263511</v>
       </c>
       <c r="V6" t="n">
         <v>15.68611720725664</v>
       </c>
       <c r="W6" t="n">
-        <v>15.64480797537584</v>
+        <v>3.257195685271112</v>
       </c>
       <c r="X6" t="n">
-        <v>3.313268837136132</v>
+        <v>3.313268837136133</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.255339689216645</v>
+        <v>3.255339689216644</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.61887865285937</v>
+        <v>3.229446420152145</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.313932245715935</v>
+        <v>15.70336447842316</v>
       </c>
       <c r="AB6" t="n">
         <v>3.224389390493549</v>
@@ -3639,7 +3639,7 @@
         <v>2.275724122662026</v>
       </c>
       <c r="M7" t="n">
-        <v>2.234672013052628</v>
+        <v>2.234672013052629</v>
       </c>
       <c r="N7" t="n">
         <v>2.181091000535271</v>
@@ -3648,10 +3648,10 @@
         <v>2.221170002126745</v>
       </c>
       <c r="P7" t="n">
-        <v>2.234107769553835</v>
+        <v>2.234107769553836</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.183636090702359</v>
+        <v>2.18363609070236</v>
       </c>
       <c r="R7" t="n">
         <v>2.356458534180838</v>
@@ -3681,7 +3681,7 @@
         <v>2.198410785918762</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.282896611482548</v>
+        <v>2.282896611482547</v>
       </c>
       <c r="AB7" t="n">
         <v>2.19499186196468</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.183581757670392</v>
+        <v>2.183581757670391</v>
       </c>
       <c r="C8" t="n">
         <v>2.624011306029988</v>
@@ -3703,13 +3703,13 @@
         <v>2.420855604694753</v>
       </c>
       <c r="E8" t="n">
-        <v>2.555541219095719</v>
+        <v>2.528262106406588</v>
       </c>
       <c r="F8" t="n">
         <v>2.66586729793342</v>
       </c>
       <c r="G8" t="n">
-        <v>2.274301271039632</v>
+        <v>2.284924397961084</v>
       </c>
       <c r="H8" t="n">
         <v>2.295711412663047</v>
@@ -3727,16 +3727,16 @@
         <v>2.336449170589293</v>
       </c>
       <c r="M8" t="n">
-        <v>2.295397060979895</v>
+        <v>2.295397060979889</v>
       </c>
       <c r="N8" t="n">
         <v>2.202103283232673</v>
       </c>
       <c r="O8" t="n">
-        <v>2.253100183525605</v>
+        <v>2.253100183525606</v>
       </c>
       <c r="P8" t="n">
-        <v>2.263362809794444</v>
+        <v>2.263362809794445</v>
       </c>
       <c r="Q8" t="n">
         <v>2.183061816253506</v>
@@ -3745,31 +3745,31 @@
         <v>2.417183582108106</v>
       </c>
       <c r="S8" t="n">
-        <v>2.344510005338272</v>
+        <v>2.344510005338273</v>
       </c>
       <c r="T8" t="n">
-        <v>2.261718386461524</v>
+        <v>2.261718386461525</v>
       </c>
       <c r="U8" t="n">
-        <v>2.261180022139807</v>
+        <v>2.26770126488963</v>
       </c>
       <c r="V8" t="n">
-        <v>2.32637438824331</v>
+        <v>2.312399101245055</v>
       </c>
       <c r="W8" t="n">
-        <v>2.285785888096735</v>
+        <v>2.285785888096736</v>
       </c>
       <c r="X8" t="n">
         <v>2.28635437143575</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.319003437742806</v>
+        <v>2.319003437742807</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.259135833846031</v>
+        <v>2.206952969035794</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.343621659409815</v>
+        <v>2.343621659409814</v>
       </c>
       <c r="AB8" t="n">
         <v>2.309232201623662</v>
@@ -3785,31 +3785,31 @@
         <v>2.529654914256165</v>
       </c>
       <c r="C9" t="n">
-        <v>3.036860098819964</v>
+        <v>3.036860098819963</v>
       </c>
       <c r="D9" t="n">
         <v>2.833704397484729</v>
       </c>
       <c r="E9" t="n">
-        <v>2.968390011885695</v>
+        <v>2.941154513973026</v>
       </c>
       <c r="F9" t="n">
-        <v>3.12196608423703</v>
+        <v>2.849928071915104</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68715006382961</v>
+        <v>2.68715006752198</v>
       </c>
       <c r="H9" t="n">
-        <v>2.708560205453026</v>
+        <v>2.708560205453025</v>
       </c>
       <c r="I9" t="n">
-        <v>2.769757578902071</v>
+        <v>2.769757578902072</v>
       </c>
       <c r="J9" t="n">
-        <v>2.722640605909835</v>
+        <v>2.722640605909834</v>
       </c>
       <c r="K9" t="n">
-        <v>2.740569310855099</v>
+        <v>2.740569310855098</v>
       </c>
       <c r="L9" t="n">
         <v>2.749297963379269</v>
@@ -3830,34 +3830,34 @@
         <v>2.657209935111977</v>
       </c>
       <c r="R9" t="n">
-        <v>2.830032374898085</v>
+        <v>2.830032374898084</v>
       </c>
       <c r="S9" t="n">
-        <v>2.757358798128249</v>
+        <v>2.757358798128248</v>
       </c>
       <c r="T9" t="n">
         <v>2.6745671792515</v>
       </c>
       <c r="U9" t="n">
-        <v>2.70553087274737</v>
+        <v>2.705530872747371</v>
       </c>
       <c r="V9" t="n">
-        <v>2.739223181033287</v>
+        <v>2.875400494777086</v>
       </c>
       <c r="W9" t="n">
         <v>2.698624612488947</v>
       </c>
       <c r="X9" t="n">
-        <v>2.755807043619988</v>
+        <v>2.755807043619989</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.68087235377538</v>
+        <v>2.680872353775379</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.671984626636008</v>
+        <v>2.600836988220614</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.756470452199789</v>
+        <v>2.756470452199788</v>
       </c>
       <c r="AB9" t="n">
         <v>2.668565702681921</v>
@@ -4032,25 +4032,25 @@
         <v>2.434390983828913</v>
       </c>
       <c r="D2" t="n">
-        <v>2.406835265592564</v>
+        <v>2.406835265592563</v>
       </c>
       <c r="E2" t="n">
-        <v>2.419721496553546</v>
+        <v>2.419721496553547</v>
       </c>
       <c r="F2" t="n">
-        <v>2.430871095140023</v>
+        <v>2.430871095140024</v>
       </c>
       <c r="G2" t="n">
         <v>2.397037890930552</v>
       </c>
       <c r="H2" t="n">
-        <v>2.398355543094871</v>
+        <v>2.39835554309487</v>
       </c>
       <c r="I2" t="n">
         <v>2.400663529732786</v>
       </c>
       <c r="J2" t="n">
-        <v>2.400184989038868</v>
+        <v>2.400184989038867</v>
       </c>
       <c r="K2" t="n">
         <v>2.400202534624392</v>
@@ -4065,7 +4065,7 @@
         <v>2.39439370930593</v>
       </c>
       <c r="O2" t="n">
-        <v>2.430559650566174</v>
+        <v>2.430559650566173</v>
       </c>
       <c r="P2" t="n">
         <v>2.39807740271504</v>
@@ -4098,7 +4098,7 @@
         <v>2.395670094149189</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.414171076772125</v>
+        <v>2.414171076772126</v>
       </c>
       <c r="AA2" t="n">
         <v>2.401285782095883</v>
@@ -4114,19 +4114,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.395214292179796</v>
+        <v>2.395214292179797</v>
       </c>
       <c r="C3" t="n">
         <v>2.655201024871143</v>
       </c>
       <c r="D3" t="n">
-        <v>2.486782369281611</v>
+        <v>2.486782369281612</v>
       </c>
       <c r="E3" t="n">
         <v>2.578059449866423</v>
       </c>
       <c r="F3" t="n">
-        <v>2.658781588938878</v>
+        <v>2.658781588938879</v>
       </c>
       <c r="G3" t="n">
         <v>2.416688201062831</v>
@@ -4147,7 +4147,7 @@
         <v>2.461093373459369</v>
       </c>
       <c r="M3" t="n">
-        <v>2.445241492609474</v>
+        <v>2.445241492609473</v>
       </c>
       <c r="N3" t="n">
         <v>2.397977320113392</v>
@@ -4156,7 +4156,7 @@
         <v>2.47522367768725</v>
       </c>
       <c r="P3" t="n">
-        <v>2.424055219813028</v>
+        <v>2.424055219813029</v>
       </c>
       <c r="Q3" t="n">
         <v>2.402215325206414</v>
@@ -4186,7 +4186,7 @@
         <v>2.407087625247443</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.435333200533972</v>
+        <v>2.435333200533971</v>
       </c>
       <c r="AA3" t="n">
         <v>2.447187518712332</v>
@@ -4247,13 +4247,13 @@
         <v>2.155100303753059</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.120232446562387</v>
+        <v>2.120232446562386</v>
       </c>
       <c r="R4" t="n">
         <v>2.247393317369518</v>
       </c>
       <c r="S4" t="n">
-        <v>2.20523319995516</v>
+        <v>2.205233199955159</v>
       </c>
       <c r="T4" t="n">
         <v>2.139942413200975</v>
@@ -4293,16 +4293,16 @@
         <v>2.334989303752998</v>
       </c>
       <c r="C5" t="n">
-        <v>9.218087797069037</v>
+        <v>9.218087797069041</v>
       </c>
       <c r="D5" t="n">
-        <v>4.925593472815542</v>
+        <v>4.925593472815544</v>
       </c>
       <c r="E5" t="n">
-        <v>7.141071505097024</v>
+        <v>7.141071505097034</v>
       </c>
       <c r="F5" t="n">
-        <v>9.962876397709804</v>
+        <v>9.96287639770981</v>
       </c>
       <c r="G5" t="n">
         <v>2.88028195882886</v>
@@ -4311,37 +4311,37 @@
         <v>3.339032664166067</v>
       </c>
       <c r="I5" t="n">
-        <v>3.753552341789849</v>
+        <v>3.75355234178985</v>
       </c>
       <c r="J5" t="n">
-        <v>3.544860373122417</v>
+        <v>3.544860373122416</v>
       </c>
       <c r="K5" t="n">
-        <v>3.506920366964067</v>
+        <v>3.50692036696407</v>
       </c>
       <c r="L5" t="n">
-        <v>4.105859232670295</v>
+        <v>4.105859232670298</v>
       </c>
       <c r="M5" t="n">
         <v>3.793840100760383</v>
       </c>
       <c r="N5" t="n">
-        <v>2.806535578604485</v>
+        <v>2.806535578604489</v>
       </c>
       <c r="O5" t="n">
-        <v>2.974858691283791</v>
+        <v>2.97485869128379</v>
       </c>
       <c r="P5" t="n">
-        <v>3.060991882579808</v>
+        <v>3.060991882579812</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.543485757714991</v>
+        <v>2.543485757714992</v>
       </c>
       <c r="R5" t="n">
-        <v>5.019028638716704</v>
+        <v>5.019028638716709</v>
       </c>
       <c r="S5" t="n">
-        <v>3.910443749621918</v>
+        <v>3.910443749621916</v>
       </c>
       <c r="T5" t="n">
         <v>2.940594100464804</v>
@@ -4353,19 +4353,19 @@
         <v>3.469076258805698</v>
       </c>
       <c r="W5" t="n">
-        <v>3.046183043758905</v>
+        <v>3.046183043758903</v>
       </c>
       <c r="X5" t="n">
-        <v>4.325582773425109</v>
+        <v>4.325582773425107</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.690696611844578</v>
+        <v>2.690696611844587</v>
       </c>
       <c r="Z5" t="n">
         <v>2.541164405987972</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.823189276872242</v>
+        <v>3.823189276872244</v>
       </c>
       <c r="AB5" t="n">
         <v>2.788844201870317</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.201322947946993</v>
+        <v>15.59026396630406</v>
       </c>
       <c r="C6" t="n">
         <v>3.600640426421414</v>
@@ -4387,58 +4387,58 @@
         <v>3.346154652841924</v>
       </c>
       <c r="E6" t="n">
-        <v>3.491710559505344</v>
+        <v>15.88065157786243</v>
       </c>
       <c r="F6" t="n">
         <v>3.61765040460835</v>
       </c>
       <c r="G6" t="n">
-        <v>3.235488799019489</v>
+        <v>15.62442981737656</v>
       </c>
       <c r="H6" t="n">
-        <v>15.63931330472249</v>
+        <v>3.250372286365413</v>
       </c>
       <c r="I6" t="n">
-        <v>3.276442057166972</v>
+        <v>3.276442057166971</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2710660287279</v>
+        <v>15.66000704708498</v>
       </c>
       <c r="K6" t="n">
-        <v>15.66017592370652</v>
+        <v>15.66017592370651</v>
       </c>
       <c r="L6" t="n">
-        <v>3.305822879540916</v>
+        <v>15.694763897898</v>
       </c>
       <c r="M6" t="n">
         <v>3.280427630391647</v>
       </c>
       <c r="N6" t="n">
-        <v>3.20432549234806</v>
+        <v>3.204325492348059</v>
       </c>
       <c r="O6" t="n">
-        <v>3.240878467074543</v>
+        <v>15.63036068059225</v>
       </c>
       <c r="P6" t="n">
-        <v>15.63541801037832</v>
+        <v>3.24309179183546</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.60130372399074</v>
+        <v>15.60130372399073</v>
       </c>
       <c r="R6" t="n">
-        <v>15.72846459479786</v>
+        <v>15.72846459479785</v>
       </c>
       <c r="S6" t="n">
-        <v>15.68630447738349</v>
+        <v>15.6863044773835</v>
       </c>
       <c r="T6" t="n">
-        <v>3.232072672272242</v>
+        <v>15.62101369062931</v>
       </c>
       <c r="U6" t="n">
-        <v>15.61998884233672</v>
+        <v>3.231047823979658</v>
       </c>
       <c r="V6" t="n">
-        <v>15.6632557694846</v>
+        <v>3.274314751127525</v>
       </c>
       <c r="W6" t="n">
         <v>15.62851372963509</v>
@@ -4456,7 +4456,7 @@
         <v>15.67241170221545</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.221150574456777</v>
+        <v>3.221150574456776</v>
       </c>
     </row>
     <row r="7">
@@ -4496,7 +4496,7 @@
         <v>2.241498729530313</v>
       </c>
       <c r="L7" t="n">
-        <v>2.276086703721788</v>
+        <v>2.276086703721789</v>
       </c>
       <c r="M7" t="n">
         <v>2.250691454572519</v>
@@ -4505,13 +4505,13 @@
         <v>2.175885375366608</v>
       </c>
       <c r="O7" t="n">
-        <v>2.212433883708909</v>
+        <v>2.212433883708908</v>
       </c>
       <c r="P7" t="n">
         <v>2.217489920621015</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.182626529814526</v>
+        <v>2.182626529814525</v>
       </c>
       <c r="R7" t="n">
         <v>2.309787400621656</v>
@@ -4520,7 +4520,7 @@
         <v>2.267627283207299</v>
       </c>
       <c r="T7" t="n">
-        <v>2.202336496453114</v>
+        <v>2.202336496453113</v>
       </c>
       <c r="U7" t="n">
         <v>2.201363744366061</v>
@@ -4532,13 +4532,13 @@
         <v>2.210591982684133</v>
       </c>
       <c r="X7" t="n">
-        <v>2.283055466505752</v>
+        <v>2.283055466505751</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.190302729337264</v>
+        <v>2.190302729337265</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.185862510192018</v>
+        <v>2.185862510192017</v>
       </c>
       <c r="AA7" t="n">
         <v>2.253734508039252</v>
@@ -4557,19 +4557,19 @@
         <v>2.18068889303772</v>
       </c>
       <c r="C8" t="n">
-        <v>2.630684875622959</v>
+        <v>2.630684875622958</v>
       </c>
       <c r="D8" t="n">
         <v>2.376199102043469</v>
       </c>
       <c r="E8" t="n">
-        <v>2.521755008706887</v>
+        <v>2.494770200191172</v>
       </c>
       <c r="F8" t="n">
         <v>2.604911468346912</v>
       </c>
       <c r="G8" t="n">
-        <v>2.265533248221034</v>
+        <v>2.276041766187878</v>
       </c>
       <c r="H8" t="n">
         <v>2.280416735566956</v>
@@ -4593,7 +4593,7 @@
         <v>2.196381681371303</v>
       </c>
       <c r="O8" t="n">
-        <v>2.243730328061227</v>
+        <v>2.243730328061226</v>
       </c>
       <c r="P8" t="n">
         <v>2.24614008491533</v>
@@ -4608,25 +4608,25 @@
         <v>2.327407908227971</v>
       </c>
       <c r="T8" t="n">
-        <v>2.262117121473786</v>
+        <v>2.262117121473785</v>
       </c>
       <c r="U8" t="n">
-        <v>2.229948520549239</v>
+        <v>2.236400606339106</v>
       </c>
       <c r="V8" t="n">
-        <v>2.304359200329072</v>
+        <v>2.290556349315086</v>
       </c>
       <c r="W8" t="n">
         <v>2.270382567478706</v>
       </c>
       <c r="X8" t="n">
-        <v>2.286842890277521</v>
+        <v>2.28684289027752</v>
       </c>
       <c r="Y8" t="n">
         <v>2.300546825755481</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.245643135212691</v>
+        <v>2.194023251870082</v>
       </c>
       <c r="AA8" t="n">
         <v>2.313515133059924</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.484450818421984</v>
+        <v>2.484450818421983</v>
       </c>
       <c r="C9" t="n">
         <v>2.989833205647962</v>
@@ -4651,43 +4651,43 @@
         <v>2.735347432068472</v>
       </c>
       <c r="E9" t="n">
-        <v>2.880903338731891</v>
+        <v>2.856423985053226</v>
       </c>
       <c r="F9" t="n">
-        <v>3.006843183834899</v>
+        <v>2.762334630414284</v>
       </c>
       <c r="G9" t="n">
-        <v>2.624681578246037</v>
+        <v>2.624681571265214</v>
       </c>
       <c r="H9" t="n">
-        <v>2.63956506559196</v>
+        <v>2.639565065591959</v>
       </c>
       <c r="I9" t="n">
-        <v>2.665634836393517</v>
+        <v>2.665634836393516</v>
       </c>
       <c r="J9" t="n">
-        <v>2.660258807954449</v>
+        <v>2.660258807954448</v>
       </c>
       <c r="K9" t="n">
-        <v>2.66042768457599</v>
+        <v>2.660427684575989</v>
       </c>
       <c r="L9" t="n">
-        <v>2.695015658767465</v>
+        <v>2.695015658767464</v>
       </c>
       <c r="M9" t="n">
-        <v>2.669620409618195</v>
+        <v>2.669620409618194</v>
       </c>
       <c r="N9" t="n">
-        <v>2.594814330412285</v>
+        <v>2.594814330412284</v>
       </c>
       <c r="O9" t="n">
         <v>2.666517067724786</v>
       </c>
       <c r="P9" t="n">
-        <v>2.679217576448948</v>
+        <v>2.679217576448947</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.601555477879379</v>
+        <v>2.601555477879378</v>
       </c>
       <c r="R9" t="n">
         <v>2.728716355667332</v>
@@ -4702,19 +4702,19 @@
         <v>2.620240603206207</v>
       </c>
       <c r="V9" t="n">
-        <v>2.663507530354077</v>
+        <v>2.785904073843589</v>
       </c>
       <c r="W9" t="n">
-        <v>2.629520937729811</v>
+        <v>2.62952093772981</v>
       </c>
       <c r="X9" t="n">
-        <v>2.701984421551428</v>
+        <v>2.701984421551427</v>
       </c>
       <c r="Y9" t="n">
         <v>2.60923168438294</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.604791465237694</v>
+        <v>2.540843754148223</v>
       </c>
       <c r="AA9" t="n">
         <v>2.672663463084928</v>
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.399249649647782</v>
+        <v>2.399249649647783</v>
       </c>
       <c r="C2" t="n">
         <v>2.453103058309987</v>
       </c>
       <c r="D2" t="n">
-        <v>2.415907271477019</v>
+        <v>2.41590727147702</v>
       </c>
       <c r="E2" t="n">
         <v>2.442901932875979</v>
@@ -4907,7 +4907,7 @@
         <v>2.407583540121621</v>
       </c>
       <c r="I2" t="n">
-        <v>2.424884121909319</v>
+        <v>2.42488412190932</v>
       </c>
       <c r="J2" t="n">
         <v>2.409515988771772</v>
@@ -4949,10 +4949,10 @@
         <v>2.409376202552697</v>
       </c>
       <c r="W2" t="n">
-        <v>2.443858473437396</v>
+        <v>2.443858473437397</v>
       </c>
       <c r="X2" t="n">
-        <v>2.411079256386696</v>
+        <v>2.411079256386697</v>
       </c>
       <c r="Y2" t="n">
         <v>2.403703448149393</v>
@@ -4980,16 +4980,16 @@
         <v>2.749021266309682</v>
       </c>
       <c r="D3" t="n">
-        <v>2.514847682211702</v>
+        <v>2.514847682211703</v>
       </c>
       <c r="E3" t="n">
-        <v>2.707119426380298</v>
+        <v>2.707119426380299</v>
       </c>
       <c r="F3" t="n">
-        <v>2.788309960756173</v>
+        <v>2.788309960756174</v>
       </c>
       <c r="G3" t="n">
-        <v>2.413745250256627</v>
+        <v>2.413745250256628</v>
       </c>
       <c r="H3" t="n">
         <v>2.455501803832772</v>
@@ -4998,10 +4998,10 @@
         <v>2.579211648072867</v>
       </c>
       <c r="J3" t="n">
-        <v>2.468807936186606</v>
+        <v>2.468807936186607</v>
       </c>
       <c r="K3" t="n">
-        <v>2.497595628549563</v>
+        <v>2.497595628549564</v>
       </c>
       <c r="L3" t="n">
         <v>2.516286868133541</v>
@@ -5013,10 +5013,10 @@
         <v>2.409314868557934</v>
       </c>
       <c r="O3" t="n">
-        <v>2.491673790344924</v>
+        <v>2.491673790344925</v>
       </c>
       <c r="P3" t="n">
-        <v>2.467519702278371</v>
+        <v>2.467519702278372</v>
       </c>
       <c r="Q3" t="n">
         <v>2.403769216730124</v>
@@ -5025,31 +5025,31 @@
         <v>2.515997932811822</v>
       </c>
       <c r="S3" t="n">
-        <v>2.557499631173187</v>
+        <v>2.557499631173188</v>
       </c>
       <c r="T3" t="n">
-        <v>2.423178023788533</v>
+        <v>2.423178023788534</v>
       </c>
       <c r="U3" t="n">
-        <v>2.505700824217119</v>
+        <v>2.50570082421712</v>
       </c>
       <c r="V3" t="n">
-        <v>2.467566721249348</v>
+        <v>2.467566721249349</v>
       </c>
       <c r="W3" t="n">
-        <v>2.513982521173942</v>
+        <v>2.513982521173943</v>
       </c>
       <c r="X3" t="n">
         <v>2.480250793613695</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.427477830330387</v>
+        <v>2.427477830330388</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.451275916641918</v>
+        <v>2.451275916641919</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.523891709580379</v>
+        <v>2.52389170958038</v>
       </c>
       <c r="AB3" t="n">
         <v>2.482735615459239</v>
@@ -5092,7 +5092,7 @@
         <v>2.273297054244047</v>
       </c>
       <c r="L4" t="n">
-        <v>2.303657715287356</v>
+        <v>2.303657715287357</v>
       </c>
       <c r="M4" t="n">
         <v>2.337686509939046</v>
@@ -5104,7 +5104,7 @@
         <v>2.173378627224226</v>
       </c>
       <c r="P4" t="n">
-        <v>2.225688294544199</v>
+        <v>2.2256882945442</v>
       </c>
       <c r="Q4" t="n">
         <v>2.124341319936036</v>
@@ -5119,7 +5119,7 @@
         <v>2.155022131159968</v>
       </c>
       <c r="U4" t="n">
-        <v>2.202889876357306</v>
+        <v>2.202889876357307</v>
       </c>
       <c r="V4" t="n">
         <v>2.226127263121045</v>
@@ -5150,70 +5150,70 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.240524336508798</v>
+        <v>2.240524336508799</v>
       </c>
       <c r="C5" t="n">
         <v>12.60761199754195</v>
       </c>
       <c r="D5" t="n">
-        <v>5.946634962247174</v>
+        <v>5.946634962247173</v>
       </c>
       <c r="E5" t="n">
-        <v>11.49480128532113</v>
+        <v>11.49480128532114</v>
       </c>
       <c r="F5" t="n">
-        <v>14.37449912816198</v>
+        <v>14.37449912816199</v>
       </c>
       <c r="G5" t="n">
-        <v>2.719545451885993</v>
+        <v>2.719545451885995</v>
       </c>
       <c r="H5" t="n">
         <v>4.202836018887528</v>
       </c>
       <c r="I5" t="n">
-        <v>8.028326837843963</v>
+        <v>8.028326837843967</v>
       </c>
       <c r="J5" t="n">
-        <v>4.34538698853062</v>
+        <v>4.345386988530619</v>
       </c>
       <c r="K5" t="n">
-        <v>5.139294054870833</v>
+        <v>5.139294054870828</v>
       </c>
       <c r="L5" t="n">
-        <v>5.439623401457951</v>
+        <v>5.439623401457952</v>
       </c>
       <c r="M5" t="n">
-        <v>6.354323565231368</v>
+        <v>6.354323565231363</v>
       </c>
       <c r="N5" t="n">
-        <v>3.802732113697945</v>
+        <v>3.802732113697948</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2703505582015</v>
+        <v>3.270350558201499</v>
       </c>
       <c r="P5" t="n">
-        <v>4.242296243695074</v>
+        <v>4.242296243695077</v>
       </c>
       <c r="Q5" t="n">
         <v>2.484941656542493</v>
       </c>
       <c r="R5" t="n">
-        <v>6.135358370309617</v>
+        <v>6.13535837030962</v>
       </c>
       <c r="S5" t="n">
-        <v>6.262242254328267</v>
+        <v>6.262242254328265</v>
       </c>
       <c r="T5" t="n">
         <v>3.077898616803052</v>
       </c>
       <c r="U5" t="n">
-        <v>3.872067969323046</v>
+        <v>3.872067969323045</v>
       </c>
       <c r="V5" t="n">
-        <v>4.180214738487905</v>
+        <v>4.1802147384879</v>
       </c>
       <c r="W5" t="n">
-        <v>3.987478755453575</v>
+        <v>3.987478755453574</v>
       </c>
       <c r="X5" t="n">
         <v>4.838135859529175</v>
@@ -5225,10 +5225,10 @@
         <v>2.892257090502551</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.086699106980213</v>
+        <v>6.086699106980214</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.011806814489114</v>
+        <v>5.011806814489113</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.288797081224148</v>
+        <v>3.288797081224149</v>
       </c>
       <c r="C6" t="n">
-        <v>17.13077971157248</v>
+        <v>17.13077971157247</v>
       </c>
       <c r="D6" t="n">
-        <v>16.77411188576229</v>
+        <v>3.476952582670011</v>
       </c>
       <c r="E6" t="n">
-        <v>17.07902900442129</v>
+        <v>3.78186970132902</v>
       </c>
       <c r="F6" t="n">
-        <v>17.20617159460989</v>
+        <v>17.20617159460988</v>
       </c>
       <c r="G6" t="n">
-        <v>3.317549138917039</v>
+        <v>16.61470844200931</v>
       </c>
       <c r="H6" t="n">
-        <v>3.382932207905172</v>
+        <v>3.382932207905171</v>
       </c>
       <c r="I6" t="n">
-        <v>16.87550954095033</v>
+        <v>3.578350237858061</v>
       </c>
       <c r="J6" t="n">
-        <v>3.404797862693292</v>
+        <v>3.404797862693291</v>
       </c>
       <c r="K6" t="n">
-        <v>16.74768333797217</v>
+        <v>3.450524034879906</v>
       </c>
       <c r="L6" t="n">
-        <v>16.7780439990155</v>
+        <v>3.480884695923209</v>
       </c>
       <c r="M6" t="n">
-        <v>3.514913490574898</v>
+        <v>16.81207279366718</v>
       </c>
       <c r="N6" t="n">
         <v>3.308024091480914</v>
       </c>
       <c r="O6" t="n">
-        <v>16.64671124461568</v>
+        <v>16.64671124461569</v>
       </c>
       <c r="P6" t="n">
-        <v>16.69902209384733</v>
+        <v>3.397300227885636</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.59872760366416</v>
+        <v>16.59872760366415</v>
       </c>
       <c r="R6" t="n">
-        <v>16.7754682597967</v>
+        <v>3.478308956704447</v>
       </c>
       <c r="S6" t="n">
-        <v>16.84450449361119</v>
+        <v>3.547345190518891</v>
       </c>
       <c r="T6" t="n">
-        <v>3.332249111795825</v>
+        <v>16.62940841488808</v>
       </c>
       <c r="U6" t="n">
-        <v>16.6768428639324</v>
+        <v>3.379683560840121</v>
       </c>
       <c r="V6" t="n">
-        <v>3.403354243756898</v>
+        <v>16.70051354684916</v>
       </c>
       <c r="W6" t="n">
         <v>3.381238575609607</v>
       </c>
       <c r="X6" t="n">
-        <v>3.42241793122814</v>
+        <v>3.422417931228139</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.356620231981224</v>
+        <v>3.356620231981223</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.327593942569341</v>
+        <v>16.62475324566159</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.491658832184762</v>
+        <v>16.78881813527703</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.424043899934437</v>
+        <v>3.424043899934438</v>
       </c>
     </row>
     <row r="7">
@@ -5329,16 +5329,16 @@
         <v>2.180240081690417</v>
       </c>
       <c r="C7" t="n">
-        <v>2.725063408946473</v>
+        <v>2.725063408946472</v>
       </c>
       <c r="D7" t="n">
-        <v>2.36839558313628</v>
+        <v>2.368395583136281</v>
       </c>
       <c r="E7" t="n">
         <v>2.673312701795294</v>
       </c>
       <c r="F7" t="n">
-        <v>2.800455291983879</v>
+        <v>2.800455291983878</v>
       </c>
       <c r="G7" t="n">
         <v>2.208992139383309</v>
@@ -5356,7 +5356,7 @@
         <v>2.34196703534617</v>
       </c>
       <c r="L7" t="n">
-        <v>2.372327696389479</v>
+        <v>2.37232769638948</v>
       </c>
       <c r="M7" t="n">
         <v>2.40635649104117</v>
@@ -5368,7 +5368,7 @@
         <v>2.242043805871095</v>
       </c>
       <c r="P7" t="n">
-        <v>2.294353473191068</v>
+        <v>2.294353473191069</v>
       </c>
       <c r="Q7" t="n">
         <v>2.19301130103816</v>
@@ -5380,13 +5380,13 @@
         <v>2.438788190985159</v>
       </c>
       <c r="T7" t="n">
-        <v>2.223692112262091</v>
+        <v>2.223692112262092</v>
       </c>
       <c r="U7" t="n">
         <v>2.271162786600727</v>
       </c>
       <c r="V7" t="n">
-        <v>2.29479724422317</v>
+        <v>2.294797244223169</v>
       </c>
       <c r="W7" t="n">
         <v>2.272138244439411</v>
@@ -5417,25 +5417,25 @@
         <v>2.192109092566989</v>
       </c>
       <c r="C8" t="n">
-        <v>2.793837664507976</v>
+        <v>2.793837664507977</v>
       </c>
       <c r="D8" t="n">
         <v>2.437169838697786</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7420869573568</v>
+        <v>2.711786593162925</v>
       </c>
       <c r="F8" t="n">
         <v>2.821189474916212</v>
       </c>
       <c r="G8" t="n">
-        <v>2.277766394944814</v>
+        <v>2.289566068133097</v>
       </c>
       <c r="H8" t="n">
         <v>2.343149463932946</v>
       </c>
       <c r="I8" t="n">
-        <v>2.538567493885832</v>
+        <v>2.538567493885833</v>
       </c>
       <c r="J8" t="n">
         <v>2.365015118721063</v>
@@ -5447,10 +5447,10 @@
         <v>2.441101951950986</v>
       </c>
       <c r="M8" t="n">
-        <v>2.475130746602678</v>
+        <v>2.475130746602673</v>
       </c>
       <c r="N8" t="n">
-        <v>2.226453876570698</v>
+        <v>2.226453876570699</v>
       </c>
       <c r="O8" t="n">
         <v>2.278833888291182</v>
@@ -5471,10 +5471,10 @@
         <v>2.292466367823599</v>
       </c>
       <c r="U8" t="n">
-        <v>2.304914147741407</v>
+        <v>2.312157921938736</v>
       </c>
       <c r="V8" t="n">
-        <v>2.363571499784676</v>
+        <v>2.348053507886693</v>
       </c>
       <c r="W8" t="n">
         <v>2.340923683506941</v>
@@ -5486,7 +5486,7 @@
         <v>2.355956022565331</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.287811198597117</v>
+        <v>2.229848909777524</v>
       </c>
       <c r="AA8" t="n">
         <v>2.451876088212536</v>
@@ -5502,28 +5502,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.616127213739272</v>
+        <v>2.616127213739273</v>
       </c>
       <c r="C9" t="n">
-        <v>3.302983151523255</v>
+        <v>3.302983151523256</v>
       </c>
       <c r="D9" t="n">
-        <v>2.946315325713065</v>
+        <v>2.946315325713066</v>
       </c>
       <c r="E9" t="n">
-        <v>3.251232444372076</v>
+        <v>3.218451869265313</v>
       </c>
       <c r="F9" t="n">
-        <v>3.378375034560666</v>
+        <v>3.050951150323763</v>
       </c>
       <c r="G9" t="n">
-        <v>2.786911881960088</v>
+        <v>2.786911845640255</v>
       </c>
       <c r="H9" t="n">
-        <v>2.852294950948225</v>
+        <v>2.852294950948226</v>
       </c>
       <c r="I9" t="n">
-        <v>3.047712980901109</v>
+        <v>3.04771298090111</v>
       </c>
       <c r="J9" t="n">
         <v>2.87416060573634</v>
@@ -5532,55 +5532,55 @@
         <v>2.919886777922955</v>
       </c>
       <c r="L9" t="n">
-        <v>2.950247438966261</v>
+        <v>2.950247438966262</v>
       </c>
       <c r="M9" t="n">
-        <v>2.984276233617952</v>
+        <v>2.984276233617954</v>
       </c>
       <c r="N9" t="n">
-        <v>2.779710448258069</v>
+        <v>2.77971044825807</v>
       </c>
       <c r="O9" t="n">
-        <v>2.867037723700234</v>
+        <v>2.867037723700237</v>
       </c>
       <c r="P9" t="n">
-        <v>2.929584179927819</v>
+        <v>2.92958417992782</v>
       </c>
       <c r="Q9" t="n">
         <v>2.770931007295103</v>
       </c>
       <c r="R9" t="n">
-        <v>2.947671699747499</v>
+        <v>2.9476716997475</v>
       </c>
       <c r="S9" t="n">
         <v>3.016707933561944</v>
       </c>
       <c r="T9" t="n">
-        <v>2.801611854838876</v>
+        <v>2.801611854838877</v>
       </c>
       <c r="U9" t="n">
-        <v>2.84904630388317</v>
+        <v>2.849046303883171</v>
       </c>
       <c r="V9" t="n">
-        <v>2.872716986799951</v>
+        <v>3.036619407257195</v>
       </c>
       <c r="W9" t="n">
         <v>2.850057987016196</v>
       </c>
       <c r="X9" t="n">
-        <v>2.891780674271191</v>
+        <v>2.891780674271192</v>
       </c>
       <c r="Y9" t="n">
         <v>2.808467527191423</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.796956685612394</v>
+        <v>2.711323637074408</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.961021575227813</v>
+        <v>2.961021575227814</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.895486169504857</v>
+        <v>2.895486169504858</v>
       </c>
     </row>
   </sheetData>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.393946904007542</v>
+        <v>2.393946904007541</v>
       </c>
       <c r="C2" t="n">
         <v>2.437024840396869</v>
@@ -5755,10 +5755,10 @@
         <v>2.402833122741637</v>
       </c>
       <c r="E2" t="n">
-        <v>2.419920467322824</v>
+        <v>2.419920467322823</v>
       </c>
       <c r="F2" t="n">
-        <v>2.437009485476386</v>
+        <v>2.437009485476385</v>
       </c>
       <c r="G2" t="n">
         <v>2.395647294897497</v>
@@ -5776,7 +5776,7 @@
         <v>2.401471149942931</v>
       </c>
       <c r="L2" t="n">
-        <v>2.402682812610895</v>
+        <v>2.402682812610894</v>
       </c>
       <c r="M2" t="n">
         <v>2.406165827872074</v>
@@ -5785,22 +5785,22 @@
         <v>2.395631636600878</v>
       </c>
       <c r="O2" t="n">
-        <v>2.433442489966771</v>
+        <v>2.43344248996677</v>
       </c>
       <c r="P2" t="n">
-        <v>2.40332057255938</v>
+        <v>2.403320572559379</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.39433950075818</v>
+        <v>2.394339500758179</v>
       </c>
       <c r="R2" t="n">
         <v>2.404298425676036</v>
       </c>
       <c r="S2" t="n">
-        <v>2.408789180754696</v>
+        <v>2.408789180754695</v>
       </c>
       <c r="T2" t="n">
-        <v>2.396689940289665</v>
+        <v>2.396689940289664</v>
       </c>
       <c r="U2" t="n">
         <v>2.433372593247965</v>
@@ -5809,19 +5809,19 @@
         <v>2.402086726144977</v>
       </c>
       <c r="W2" t="n">
-        <v>2.435790549339985</v>
+        <v>2.435790549339984</v>
       </c>
       <c r="X2" t="n">
-        <v>2.404098570796535</v>
+        <v>2.404098570796534</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.397068509691872</v>
+        <v>2.397068509691871</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.414026497208086</v>
+        <v>2.414026497208085</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.40096590350427</v>
+        <v>2.400965903504269</v>
       </c>
       <c r="AB2" t="n">
         <v>2.402043260253626</v>
@@ -5834,28 +5834,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.392472665946071</v>
+        <v>2.39247266594607</v>
       </c>
       <c r="C3" t="n">
         <v>2.671801234697973</v>
       </c>
       <c r="D3" t="n">
-        <v>2.455836793116689</v>
+        <v>2.455836793116688</v>
       </c>
       <c r="E3" t="n">
-        <v>2.577717960747927</v>
+        <v>2.577717960747926</v>
       </c>
       <c r="F3" t="n">
         <v>2.699938981668902</v>
       </c>
       <c r="G3" t="n">
-        <v>2.404520671217627</v>
+        <v>2.404520671217626</v>
       </c>
       <c r="H3" t="n">
         <v>2.436078091034101</v>
       </c>
       <c r="I3" t="n">
-        <v>2.470870983001038</v>
+        <v>2.470870983001037</v>
       </c>
       <c r="J3" t="n">
         <v>2.446033839238289</v>
@@ -5864,7 +5864,7 @@
         <v>2.445970501859845</v>
       </c>
       <c r="L3" t="n">
-        <v>2.454151526008679</v>
+        <v>2.454151526008678</v>
       </c>
       <c r="M3" t="n">
         <v>2.479314026342677</v>
@@ -5879,25 +5879,25 @@
         <v>2.459059888866415</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.395277857230512</v>
+        <v>2.395277857230511</v>
       </c>
       <c r="R3" t="n">
-        <v>2.466583061303306</v>
+        <v>2.466583061303305</v>
       </c>
       <c r="S3" t="n">
         <v>2.497450143169754</v>
       </c>
       <c r="T3" t="n">
-        <v>2.412059753969881</v>
+        <v>2.41205975396988</v>
       </c>
       <c r="U3" t="n">
-        <v>2.497255232913288</v>
+        <v>2.497255232913287</v>
       </c>
       <c r="V3" t="n">
-        <v>2.45017501898908</v>
+        <v>2.450175018989079</v>
       </c>
       <c r="W3" t="n">
-        <v>2.490879703789659</v>
+        <v>2.490879703789658</v>
       </c>
       <c r="X3" t="n">
         <v>2.464811842073144</v>
@@ -5909,7 +5909,7 @@
         <v>2.43420572990988</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.442586123696639</v>
+        <v>2.442586123696638</v>
       </c>
       <c r="AB3" t="n">
         <v>2.450549868816112</v>
@@ -5925,25 +5925,25 @@
         <v>2.104912158210644</v>
       </c>
       <c r="C4" t="n">
-        <v>2.534989713846243</v>
+        <v>2.534989713846242</v>
       </c>
       <c r="D4" t="n">
-        <v>2.205286086674832</v>
+        <v>2.205286086674831</v>
       </c>
       <c r="E4" t="n">
         <v>2.398295504286203</v>
       </c>
       <c r="F4" t="n">
-        <v>2.59132382566742</v>
+        <v>2.591323825667421</v>
       </c>
       <c r="G4" t="n">
-        <v>2.124118855531142</v>
+        <v>2.124118855531141</v>
       </c>
       <c r="H4" t="n">
-        <v>2.173566137320226</v>
+        <v>2.173566137320225</v>
       </c>
       <c r="I4" t="n">
-        <v>2.228779793653508</v>
+        <v>2.228779793653507</v>
       </c>
       <c r="J4" t="n">
         <v>2.190018865391091</v>
@@ -5955,13 +5955,13 @@
         <v>2.203588264602022</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2431062746499</v>
+        <v>2.243106274649899</v>
       </c>
       <c r="N4" t="n">
         <v>2.123941987867656</v>
       </c>
       <c r="O4" t="n">
-        <v>2.168319266999167</v>
+        <v>2.168319266999168</v>
       </c>
       <c r="P4" t="n">
         <v>2.210792056604227</v>
@@ -5973,7 +5973,7 @@
         <v>2.221837357391519</v>
       </c>
       <c r="S4" t="n">
-        <v>2.272562501854388</v>
+        <v>2.272562501854387</v>
       </c>
       <c r="T4" t="n">
         <v>2.135896014876252</v>
@@ -5988,16 +5988,16 @@
         <v>2.165509273866759</v>
       </c>
       <c r="X4" t="n">
-        <v>2.219579904589763</v>
+        <v>2.219579904589764</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.14063416767819</v>
+        <v>2.140634167678189</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.122743457309741</v>
+        <v>2.12274345730974</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.184194986425482</v>
+        <v>2.184194986425481</v>
       </c>
       <c r="AB4" t="n">
         <v>2.19674694094144</v>
@@ -6016,67 +6016,67 @@
         <v>9.65388740915518</v>
       </c>
       <c r="D5" t="n">
-        <v>3.99354730079498</v>
+        <v>3.993547300794976</v>
       </c>
       <c r="E5" t="n">
-        <v>7.369892785341377</v>
+        <v>7.369892785341383</v>
       </c>
       <c r="F5" t="n">
-        <v>10.91650310884393</v>
+        <v>10.91650310884392</v>
       </c>
       <c r="G5" t="n">
-        <v>2.542159666297154</v>
+        <v>2.542159666297153</v>
       </c>
       <c r="H5" t="n">
-        <v>3.579488736435259</v>
+        <v>3.579488736435257</v>
       </c>
       <c r="I5" t="n">
         <v>4.507360418196137</v>
       </c>
       <c r="J5" t="n">
-        <v>3.655534863004859</v>
+        <v>3.655534863004857</v>
       </c>
       <c r="K5" t="n">
-        <v>3.645884608066345</v>
+        <v>3.645884608066343</v>
       </c>
       <c r="L5" t="n">
-        <v>3.646107863807101</v>
+        <v>3.6461078638071</v>
       </c>
       <c r="M5" t="n">
-        <v>4.453129015320439</v>
+        <v>4.453129015320437</v>
       </c>
       <c r="N5" t="n">
-        <v>3.421665269874387</v>
+        <v>3.421665269874386</v>
       </c>
       <c r="O5" t="n">
-        <v>3.231404164794386</v>
+        <v>3.231404164794385</v>
       </c>
       <c r="P5" t="n">
         <v>3.958337586836553</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.328037092827725</v>
+        <v>2.328037092827724</v>
       </c>
       <c r="R5" t="n">
-        <v>4.435702569649266</v>
+        <v>4.43570256964927</v>
       </c>
       <c r="S5" t="n">
         <v>4.719458110618162</v>
       </c>
       <c r="T5" t="n">
-        <v>2.801073483803517</v>
+        <v>2.801073483803516</v>
       </c>
       <c r="U5" t="n">
         <v>3.485271562185585</v>
       </c>
       <c r="V5" t="n">
-        <v>3.671180905098001</v>
+        <v>3.671180905098007</v>
       </c>
       <c r="W5" t="n">
-        <v>3.269720792370945</v>
+        <v>3.269720792370946</v>
       </c>
       <c r="X5" t="n">
-        <v>4.217068606849207</v>
+        <v>4.217068606849211</v>
       </c>
       <c r="Y5" t="n">
         <v>2.882659863269563</v>
@@ -6085,10 +6085,10 @@
         <v>2.525540113221016</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.659780906362351</v>
+        <v>3.659780906362348</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.916327725607713</v>
+        <v>3.91632772560771</v>
       </c>
     </row>
     <row r="6">
@@ -6101,28 +6101,28 @@
         <v>3.19821147700188</v>
       </c>
       <c r="C6" t="n">
-        <v>16.01670347222133</v>
+        <v>3.628289032637476</v>
       </c>
       <c r="D6" t="n">
-        <v>3.298585405466067</v>
+        <v>3.298585405466066</v>
       </c>
       <c r="E6" t="n">
-        <v>15.88000926266127</v>
+        <v>15.88000926266128</v>
       </c>
       <c r="F6" t="n">
-        <v>16.0730375840425</v>
+        <v>16.07303758404252</v>
       </c>
       <c r="G6" t="n">
-        <v>15.60583261390622</v>
+        <v>3.217418174322374</v>
       </c>
       <c r="H6" t="n">
-        <v>15.65527989569531</v>
+        <v>3.266865456111455</v>
       </c>
       <c r="I6" t="n">
-        <v>3.322079112444736</v>
+        <v>3.322079112444737</v>
       </c>
       <c r="J6" t="n">
-        <v>15.67173262376619</v>
+        <v>3.28331818418232</v>
       </c>
       <c r="K6" t="n">
         <v>3.28320129616624</v>
@@ -6131,52 +6131,52 @@
         <v>15.68530202297712</v>
       </c>
       <c r="M6" t="n">
-        <v>3.336405593441129</v>
+        <v>15.72482003302498</v>
       </c>
       <c r="N6" t="n">
-        <v>3.216045163513273</v>
+        <v>3.216045163513274</v>
       </c>
       <c r="O6" t="n">
         <v>3.260422442644785</v>
       </c>
       <c r="P6" t="n">
-        <v>15.69171917145566</v>
+        <v>3.29999464721414</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.59106047748763</v>
+        <v>3.202646037903766</v>
       </c>
       <c r="R6" t="n">
-        <v>15.7035511157666</v>
+        <v>15.70355111576661</v>
       </c>
       <c r="S6" t="n">
-        <v>15.75427626022949</v>
+        <v>3.365861820645624</v>
       </c>
       <c r="T6" t="n">
         <v>15.61760977325133</v>
       </c>
       <c r="U6" t="n">
-        <v>3.280847598970089</v>
+        <v>3.28084759897009</v>
       </c>
       <c r="V6" t="n">
-        <v>3.290354454225609</v>
+        <v>15.67876889380947</v>
       </c>
       <c r="W6" t="n">
-        <v>3.260088974569236</v>
+        <v>3.260088974569234</v>
       </c>
       <c r="X6" t="n">
         <v>3.312879223381</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.250656349822596</v>
+        <v>3.250656349822597</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.60445721568482</v>
+        <v>15.60445721568483</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.277494305216711</v>
+        <v>15.66590874480056</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.288949240237655</v>
+        <v>3.288949240237654</v>
       </c>
     </row>
     <row r="7">
@@ -6201,7 +6201,7 @@
         <v>2.653633014816345</v>
       </c>
       <c r="G7" t="n">
-        <v>2.186428044680064</v>
+        <v>2.186428044680063</v>
       </c>
       <c r="H7" t="n">
         <v>2.235875326469147</v>
@@ -6225,10 +6225,10 @@
         <v>2.186251177016579</v>
       </c>
       <c r="O7" t="n">
-        <v>2.230623997272951</v>
+        <v>2.23062399727295</v>
       </c>
       <c r="P7" t="n">
-        <v>2.27309678687801</v>
+        <v>2.273096786878009</v>
       </c>
       <c r="Q7" t="n">
         <v>2.171655908261456</v>
@@ -6249,10 +6249,10 @@
         <v>2.259364324583296</v>
       </c>
       <c r="W7" t="n">
-        <v>2.227818463015681</v>
+        <v>2.22781846301568</v>
       </c>
       <c r="X7" t="n">
-        <v>2.281889093738684</v>
+        <v>2.281889093738685</v>
       </c>
       <c r="Y7" t="n">
         <v>2.202481319573641</v>
@@ -6261,7 +6261,7 @@
         <v>2.185052646458662</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.246504175574403</v>
+        <v>2.246504175574404</v>
       </c>
       <c r="AB7" t="n">
         <v>2.259056130090362</v>
@@ -6274,22 +6274,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.176620982121343</v>
+        <v>2.176620982121344</v>
       </c>
       <c r="C8" t="n">
         <v>2.657397126279549</v>
       </c>
       <c r="D8" t="n">
-        <v>2.327693499108137</v>
+        <v>2.327693499108136</v>
       </c>
       <c r="E8" t="n">
-        <v>2.520702916719507</v>
+        <v>2.493707413847042</v>
       </c>
       <c r="F8" t="n">
-        <v>2.670930897142544</v>
+        <v>2.670930897142545</v>
       </c>
       <c r="G8" t="n">
-        <v>2.246526267964445</v>
+        <v>2.257038950564884</v>
       </c>
       <c r="H8" t="n">
         <v>2.295973549753528</v>
@@ -6307,7 +6307,7 @@
         <v>2.325995677035323</v>
       </c>
       <c r="M8" t="n">
-        <v>2.365513687083202</v>
+        <v>2.365513687083203</v>
       </c>
       <c r="N8" t="n">
         <v>2.207049512505724</v>
@@ -6328,31 +6328,31 @@
         <v>2.394969914287691</v>
       </c>
       <c r="T8" t="n">
-        <v>2.258303427309555</v>
+        <v>2.258303427309556</v>
       </c>
       <c r="U8" t="n">
-        <v>2.278791013491909</v>
+        <v>2.285245098534895</v>
       </c>
       <c r="V8" t="n">
-        <v>2.319462547867677</v>
+        <v>2.305644143643244</v>
       </c>
       <c r="W8" t="n">
-        <v>2.287926650020804</v>
+        <v>2.287926650020803</v>
       </c>
       <c r="X8" t="n">
-        <v>2.285971925093201</v>
+        <v>2.285971925093202</v>
       </c>
       <c r="Y8" t="n">
         <v>2.31304737470351</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.245150869743043</v>
+        <v>2.193510528910424</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.306602398858784</v>
+        <v>2.306602398858785</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.372113268429191</v>
+        <v>2.37211326842919</v>
       </c>
     </row>
     <row r="9">
@@ -6362,25 +6362,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.516261016951802</v>
+        <v>2.516261016951801</v>
       </c>
       <c r="C9" t="n">
-        <v>3.062334514839457</v>
+        <v>3.062334514839456</v>
       </c>
       <c r="D9" t="n">
         <v>2.732630887668042</v>
       </c>
       <c r="E9" t="n">
-        <v>2.925640305279416</v>
+        <v>2.898868895440077</v>
       </c>
       <c r="F9" t="n">
-        <v>3.11866862666063</v>
+        <v>2.851266354573941</v>
       </c>
       <c r="G9" t="n">
-        <v>2.651463656524351</v>
+        <v>2.651463631165174</v>
       </c>
       <c r="H9" t="n">
-        <v>2.700910938313434</v>
+        <v>2.700910938313433</v>
       </c>
       <c r="I9" t="n">
         <v>2.756124594646717</v>
@@ -6389,16 +6389,16 @@
         <v>2.7173636663843</v>
       </c>
       <c r="K9" t="n">
-        <v>2.717246778368216</v>
+        <v>2.717246778368215</v>
       </c>
       <c r="L9" t="n">
         <v>2.730933065595231</v>
       </c>
       <c r="M9" t="n">
-        <v>2.770451075643107</v>
+        <v>2.770451075643106</v>
       </c>
       <c r="N9" t="n">
-        <v>2.651286788860866</v>
+        <v>2.651286788860865</v>
       </c>
       <c r="O9" t="n">
         <v>2.734104937607966</v>
@@ -6413,16 +6413,16 @@
         <v>2.749182158384731</v>
       </c>
       <c r="S9" t="n">
-        <v>2.799907302847598</v>
+        <v>2.799907302847597</v>
       </c>
       <c r="T9" t="n">
         <v>2.663240815869462</v>
       </c>
       <c r="U9" t="n">
-        <v>2.714893081172066</v>
+        <v>2.714893081172065</v>
       </c>
       <c r="V9" t="n">
-        <v>2.724399936427583</v>
+        <v>2.858256646666222</v>
       </c>
       <c r="W9" t="n">
         <v>2.692854074859969</v>
@@ -6431,16 +6431,16 @@
         <v>2.746924705582969</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.667516931417929</v>
+        <v>2.667516931417928</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.650088258302951</v>
+        <v>2.580153009816793</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.711539787418692</v>
+        <v>2.711539787418693</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.724091741934652</v>
+        <v>2.72409174193465</v>
       </c>
     </row>
   </sheetData>
@@ -6615,7 +6615,7 @@
         <v>2.396651209166582</v>
       </c>
       <c r="E2" t="n">
-        <v>2.400639535542122</v>
+        <v>2.400639535542123</v>
       </c>
       <c r="F2" t="n">
         <v>2.425941249772477</v>
@@ -6627,7 +6627,7 @@
         <v>2.394227884962982</v>
       </c>
       <c r="I2" t="n">
-        <v>2.394516045220628</v>
+        <v>2.394516045220629</v>
       </c>
       <c r="J2" t="n">
         <v>2.395116119213768</v>
@@ -6669,7 +6669,7 @@
         <v>2.395155130558781</v>
       </c>
       <c r="W2" t="n">
-        <v>2.428511479847757</v>
+        <v>2.428511479847756</v>
       </c>
       <c r="X2" t="n">
         <v>2.397587577339094</v>
@@ -6700,7 +6700,7 @@
         <v>2.638137123063468</v>
       </c>
       <c r="D3" t="n">
-        <v>2.439660748545027</v>
+        <v>2.439660748545026</v>
       </c>
       <c r="E3" t="n">
         <v>2.467793110752786</v>
@@ -6709,7 +6709,7 @@
         <v>2.649184329543241</v>
       </c>
       <c r="G3" t="n">
-        <v>2.394347761048432</v>
+        <v>2.394347761048433</v>
       </c>
       <c r="H3" t="n">
         <v>2.422512700771601</v>
@@ -6730,7 +6730,7 @@
         <v>2.450822533729553</v>
       </c>
       <c r="N3" t="n">
-        <v>2.395210056247219</v>
+        <v>2.395210056247218</v>
       </c>
       <c r="O3" t="n">
         <v>2.475666734324332</v>
@@ -6751,7 +6751,7 @@
         <v>2.404951979557563</v>
       </c>
       <c r="U3" t="n">
-        <v>2.482308699286246</v>
+        <v>2.482308699286245</v>
       </c>
       <c r="V3" t="n">
         <v>2.428743527023522</v>
@@ -6797,7 +6797,7 @@
         <v>2.510459895118666</v>
       </c>
       <c r="G4" t="n">
-        <v>2.10797210012063</v>
+        <v>2.107972100120631</v>
       </c>
       <c r="H4" t="n">
         <v>2.152242850726841</v>
@@ -6806,7 +6806,7 @@
         <v>2.155497753397225</v>
       </c>
       <c r="J4" t="n">
-        <v>2.162312629720688</v>
+        <v>2.162312629720689</v>
       </c>
       <c r="K4" t="n">
         <v>2.151359543101481</v>
@@ -6873,82 +6873,82 @@
         <v>2.268960927685448</v>
       </c>
       <c r="C5" t="n">
-        <v>8.91257858969243</v>
+        <v>8.912578589692437</v>
       </c>
       <c r="D5" t="n">
-        <v>3.673857469839389</v>
+        <v>3.673857469839385</v>
       </c>
       <c r="E5" t="n">
-        <v>4.298319638719936</v>
+        <v>4.298319638719938</v>
       </c>
       <c r="F5" t="n">
         <v>9.773670059464797</v>
       </c>
       <c r="G5" t="n">
-        <v>2.383368079140308</v>
+        <v>2.383368079140309</v>
       </c>
       <c r="H5" t="n">
         <v>3.266082671389222</v>
       </c>
       <c r="I5" t="n">
-        <v>3.291158880320141</v>
+        <v>3.291158880320139</v>
       </c>
       <c r="J5" t="n">
-        <v>3.328071545779326</v>
+        <v>3.328071545779328</v>
       </c>
       <c r="K5" t="n">
         <v>3.142377782395708</v>
       </c>
       <c r="L5" t="n">
-        <v>3.569346950758147</v>
+        <v>3.569346950758144</v>
       </c>
       <c r="M5" t="n">
-        <v>3.965069729150112</v>
+        <v>3.965069729150113</v>
       </c>
       <c r="N5" t="n">
-        <v>3.197810315372181</v>
+        <v>3.19781031537218</v>
       </c>
       <c r="O5" t="n">
         <v>3.070241100834594</v>
       </c>
       <c r="P5" t="n">
-        <v>3.755107286642194</v>
+        <v>3.755107286642191</v>
       </c>
       <c r="Q5" t="n">
         <v>2.263003182526381</v>
       </c>
       <c r="R5" t="n">
-        <v>3.680353947702265</v>
+        <v>3.680353947702267</v>
       </c>
       <c r="S5" t="n">
-        <v>4.229212527818209</v>
+        <v>4.229212527818206</v>
       </c>
       <c r="T5" t="n">
-        <v>2.713958450904938</v>
+        <v>2.713958450904939</v>
       </c>
       <c r="U5" t="n">
-        <v>3.252630877723056</v>
+        <v>3.252630877723059</v>
       </c>
       <c r="V5" t="n">
-        <v>3.250952093228306</v>
+        <v>3.250952093228308</v>
       </c>
       <c r="W5" t="n">
-        <v>2.78702779117352</v>
+        <v>2.787027791173518</v>
       </c>
       <c r="X5" t="n">
-        <v>3.782316232388841</v>
+        <v>3.78231623238884</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.689642499756871</v>
+        <v>2.689642499756872</v>
       </c>
       <c r="Z5" t="n">
         <v>2.321478135387426</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.785011435323649</v>
+        <v>2.785011435323648</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.194633839511683</v>
+        <v>3.194633839511685</v>
       </c>
     </row>
     <row r="6">
@@ -6958,34 +6958,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.57796465394289</v>
+        <v>15.5779646539429</v>
       </c>
       <c r="C6" t="n">
-        <v>15.95875736245146</v>
+        <v>15.95875736245147</v>
       </c>
       <c r="D6" t="n">
-        <v>15.65668372454306</v>
+        <v>15.65668372454305</v>
       </c>
       <c r="E6" t="n">
         <v>15.70173370567557</v>
       </c>
       <c r="F6" t="n">
-        <v>3.600717020429501</v>
+        <v>15.98752820727101</v>
       </c>
       <c r="G6" t="n">
-        <v>3.198229225431467</v>
+        <v>15.585040412273</v>
       </c>
       <c r="H6" t="n">
-        <v>3.24249997603768</v>
+        <v>3.242499976037679</v>
       </c>
       <c r="I6" t="n">
-        <v>15.63256606554958</v>
+        <v>3.24575487870806</v>
       </c>
       <c r="J6" t="n">
-        <v>15.63938094187303</v>
+        <v>3.25256975503153</v>
       </c>
       <c r="K6" t="n">
-        <v>3.24161666841232</v>
+        <v>15.62842785525383</v>
       </c>
       <c r="L6" t="n">
         <v>15.66378530177853</v>
@@ -6997,16 +6997,16 @@
         <v>3.199135545364193</v>
       </c>
       <c r="O6" t="n">
-        <v>3.242221404014269</v>
+        <v>15.6286253356743</v>
       </c>
       <c r="P6" t="n">
-        <v>15.67181382122085</v>
+        <v>15.67181382122084</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.5769719547483</v>
+        <v>15.57697195474829</v>
       </c>
       <c r="R6" t="n">
-        <v>15.65186278493399</v>
+        <v>3.265051598092469</v>
       </c>
       <c r="S6" t="n">
         <v>3.315833454321672</v>
@@ -7015,28 +7015,28 @@
         <v>15.60171420350809</v>
       </c>
       <c r="U6" t="n">
-        <v>15.64116033223456</v>
+        <v>15.64116033223455</v>
       </c>
       <c r="V6" t="n">
-        <v>3.253137336534612</v>
+        <v>3.253137336534613</v>
       </c>
       <c r="W6" t="n">
-        <v>15.60698930046569</v>
+        <v>15.60698930046567</v>
       </c>
       <c r="X6" t="n">
-        <v>15.66726043380221</v>
+        <v>3.280449246960701</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.231757487136261</v>
+        <v>3.23175748713626</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.58150103810356</v>
+        <v>3.194689851262066</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.60638261011058</v>
+        <v>3.219571423269074</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.238737309079042</v>
+        <v>3.238737309079043</v>
       </c>
     </row>
     <row r="7">
@@ -7061,7 +7061,7 @@
         <v>2.571418025803088</v>
       </c>
       <c r="G7" t="n">
-        <v>2.168930230805054</v>
+        <v>2.168930230805055</v>
       </c>
       <c r="H7" t="n">
         <v>2.213200981411264</v>
@@ -7143,13 +7143,13 @@
         <v>2.297399861651262</v>
       </c>
       <c r="E8" t="n">
-        <v>2.342449842783775</v>
+        <v>2.31647025919852</v>
       </c>
       <c r="F8" t="n">
-        <v>2.587054704732402</v>
+        <v>2.587054704732403</v>
       </c>
       <c r="G8" t="n">
-        <v>2.225756549381183</v>
+        <v>2.235873609160108</v>
       </c>
       <c r="H8" t="n">
         <v>2.270027299987395</v>
@@ -7167,7 +7167,7 @@
         <v>2.304501438886744</v>
       </c>
       <c r="M8" t="n">
-        <v>2.315162954986787</v>
+        <v>2.315162954986793</v>
       </c>
       <c r="N8" t="n">
         <v>2.189234988274684</v>
@@ -7191,22 +7191,22 @@
         <v>2.242430340616287</v>
       </c>
       <c r="U8" t="n">
-        <v>2.251876154704533</v>
+        <v>2.258086804485079</v>
       </c>
       <c r="V8" t="n">
-        <v>2.280664660484323</v>
+        <v>2.267356353722464</v>
       </c>
       <c r="W8" t="n">
-        <v>2.248516007061841</v>
+        <v>2.24851600706184</v>
       </c>
       <c r="X8" t="n">
-        <v>2.25406920109479</v>
+        <v>2.254069201094789</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.289976278348413</v>
+        <v>2.289976278348412</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.222217175211777</v>
+        <v>2.1725202105962</v>
       </c>
       <c r="AA8" t="n">
         <v>2.24709874721879</v>
@@ -7225,19 +7225,19 @@
         <v>2.466966389457021</v>
       </c>
       <c r="C9" t="n">
-        <v>2.951153371868823</v>
+        <v>2.951153371868824</v>
       </c>
       <c r="D9" t="n">
         <v>2.649079733960428</v>
       </c>
       <c r="E9" t="n">
-        <v>2.694129715092941</v>
+        <v>2.670266720727196</v>
       </c>
       <c r="F9" t="n">
-        <v>2.979924216688382</v>
+        <v>2.741572226379013</v>
       </c>
       <c r="G9" t="n">
-        <v>2.577436421690348</v>
+        <v>2.577436398697198</v>
       </c>
       <c r="H9" t="n">
         <v>2.621707172296557</v>
@@ -7252,7 +7252,7 @@
         <v>2.620823864671199</v>
       </c>
       <c r="L9" t="n">
-        <v>2.656181311195907</v>
+        <v>2.656181311195908</v>
       </c>
       <c r="M9" t="n">
         <v>2.666842827295951</v>
@@ -7276,13 +7276,13 @@
         <v>2.695040650580554</v>
       </c>
       <c r="T9" t="n">
-        <v>2.594110212925452</v>
+        <v>2.594110212925451</v>
       </c>
       <c r="U9" t="n">
-        <v>2.633556341651909</v>
+        <v>2.633556341651908</v>
       </c>
       <c r="V9" t="n">
-        <v>2.632344532793487</v>
+        <v>2.751659199456386</v>
       </c>
       <c r="W9" t="n">
         <v>2.600186290614174</v>
@@ -7291,16 +7291,16 @@
         <v>2.659656443219582</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.593102970428955</v>
+        <v>2.593102970428956</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.57389704752094</v>
+        <v>2.511559485404576</v>
       </c>
       <c r="AA9" t="n">
         <v>2.598778619527954</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.618356467796529</v>
+        <v>2.61835646779653</v>
       </c>
     </row>
   </sheetData>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.399860144523657</v>
+        <v>2.399860144523656</v>
       </c>
       <c r="C2" t="n">
         <v>2.451667880151802</v>
@@ -7475,28 +7475,28 @@
         <v>2.42990608014566</v>
       </c>
       <c r="E2" t="n">
-        <v>2.44087967784792</v>
+        <v>2.440879677847919</v>
       </c>
       <c r="F2" t="n">
         <v>2.450170427623138</v>
       </c>
       <c r="G2" t="n">
-        <v>2.403740927222539</v>
+        <v>2.403740927222538</v>
       </c>
       <c r="H2" t="n">
         <v>2.406790498056912</v>
       </c>
       <c r="I2" t="n">
-        <v>2.421419885929956</v>
+        <v>2.421419885929955</v>
       </c>
       <c r="J2" t="n">
-        <v>2.408439838142776</v>
+        <v>2.408439838142775</v>
       </c>
       <c r="K2" t="n">
         <v>2.41243667811995</v>
       </c>
       <c r="L2" t="n">
-        <v>2.411658555752755</v>
+        <v>2.411658555752754</v>
       </c>
       <c r="M2" t="n">
         <v>2.407513492804671</v>
@@ -7508,19 +7508,19 @@
         <v>2.437425139740939</v>
       </c>
       <c r="P2" t="n">
-        <v>2.406295051983703</v>
+        <v>2.406295051983702</v>
       </c>
       <c r="Q2" t="n">
         <v>2.400429142449243</v>
       </c>
       <c r="R2" t="n">
-        <v>2.414660157665164</v>
+        <v>2.414660157665163</v>
       </c>
       <c r="S2" t="n">
-        <v>2.415311789268616</v>
+        <v>2.415311789268615</v>
       </c>
       <c r="T2" t="n">
-        <v>2.401695899268884</v>
+        <v>2.401695899268883</v>
       </c>
       <c r="U2" t="n">
         <v>2.440454579154299</v>
@@ -7532,13 +7532,13 @@
         <v>2.443574316731982</v>
       </c>
       <c r="X2" t="n">
-        <v>2.410227226700653</v>
+        <v>2.410227226700652</v>
       </c>
       <c r="Y2" t="n">
         <v>2.403670505529415</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.421776829109975</v>
+        <v>2.421776829109974</v>
       </c>
       <c r="AA2" t="n">
         <v>2.416813600839796</v>
@@ -7554,19 +7554,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.398756639740655</v>
+        <v>2.398756639740654</v>
       </c>
       <c r="C3" t="n">
         <v>2.737308371297231</v>
       </c>
       <c r="D3" t="n">
-        <v>2.613886917266251</v>
+        <v>2.61388691726625</v>
       </c>
       <c r="E3" t="n">
         <v>2.691417473823047</v>
       </c>
       <c r="F3" t="n">
-        <v>2.758707348857718</v>
+        <v>2.758707348857717</v>
       </c>
       <c r="G3" t="n">
         <v>2.42631665707256</v>
@@ -7593,7 +7593,7 @@
         <v>2.406026618166018</v>
       </c>
       <c r="O3" t="n">
-        <v>2.482063314998019</v>
+        <v>2.482063314998018</v>
       </c>
       <c r="P3" t="n">
         <v>2.44452689604841</v>
@@ -7602,7 +7602,7 @@
         <v>2.402848045152385</v>
       </c>
       <c r="R3" t="n">
-        <v>2.504913334112053</v>
+        <v>2.504913334112052</v>
       </c>
       <c r="S3" t="n">
         <v>2.508353240549448</v>
@@ -7611,22 +7611,22 @@
         <v>2.411939788971156</v>
       </c>
       <c r="U3" t="n">
-        <v>2.51181804128454</v>
+        <v>2.511818041284539</v>
       </c>
       <c r="V3" t="n">
         <v>2.466599303285227</v>
       </c>
       <c r="W3" t="n">
-        <v>2.509702789742062</v>
+        <v>2.509702789742063</v>
       </c>
       <c r="X3" t="n">
-        <v>2.472923808572096</v>
+        <v>2.472923808572097</v>
       </c>
       <c r="Y3" t="n">
         <v>2.425963998992027</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.450727607485942</v>
+        <v>2.450727607485941</v>
       </c>
       <c r="AA3" t="n">
         <v>2.519788622010043</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.11508908139519</v>
+        <v>2.115089081395191</v>
       </c>
       <c r="C4" t="n">
         <v>2.636290073385751</v>
@@ -7654,16 +7654,16 @@
         <v>2.578423580210357</v>
       </c>
       <c r="F4" t="n">
-        <v>2.683366872877498</v>
+        <v>2.683366872877499</v>
       </c>
       <c r="G4" t="n">
         <v>2.158924307227309</v>
       </c>
       <c r="H4" t="n">
-        <v>2.193370612673457</v>
+        <v>2.193370612673458</v>
       </c>
       <c r="I4" t="n">
-        <v>2.358616278550391</v>
+        <v>2.358616278550392</v>
       </c>
       <c r="J4" t="n">
         <v>2.212029990504045</v>
@@ -7681,10 +7681,10 @@
         <v>2.126535223267565</v>
       </c>
       <c r="O4" t="n">
-        <v>2.159288585890562</v>
+        <v>2.159288585890563</v>
       </c>
       <c r="P4" t="n">
-        <v>2.187774321360088</v>
+        <v>2.187774321360089</v>
       </c>
       <c r="Q4" t="n">
         <v>2.121516174716668</v>
@@ -7693,7 +7693,7 @@
         <v>2.282262038170921</v>
       </c>
       <c r="S4" t="n">
-        <v>2.289622516897267</v>
+        <v>2.289622516897268</v>
       </c>
       <c r="T4" t="n">
         <v>2.135824775731438</v>
@@ -7711,7 +7711,7 @@
         <v>2.232190043677788</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.158450150437275</v>
+        <v>2.158450150437276</v>
       </c>
       <c r="Z4" t="n">
         <v>2.147781757263533</v>
@@ -7736,13 +7736,13 @@
         <v>12.2834608692371</v>
       </c>
       <c r="D5" t="n">
-        <v>9.130628177965948</v>
+        <v>9.130628177965933</v>
       </c>
       <c r="E5" t="n">
-        <v>11.03573970372592</v>
+        <v>11.03573970372593</v>
       </c>
       <c r="F5" t="n">
-        <v>13.56576675361611</v>
+        <v>13.56576675361609</v>
       </c>
       <c r="G5" t="n">
         <v>3.081807098432753</v>
@@ -7751,64 +7751,64 @@
         <v>3.986382904568297</v>
       </c>
       <c r="I5" t="n">
-        <v>7.216327296331094</v>
+        <v>7.216327296331101</v>
       </c>
       <c r="J5" t="n">
-        <v>4.116877238390618</v>
+        <v>4.116877238390619</v>
       </c>
       <c r="K5" t="n">
-        <v>4.872782298840758</v>
+        <v>4.872782298840756</v>
       </c>
       <c r="L5" t="n">
-        <v>4.757107865707335</v>
+        <v>4.757107865707334</v>
       </c>
       <c r="M5" t="n">
-        <v>3.987327846767727</v>
+        <v>3.987327846767725</v>
       </c>
       <c r="N5" t="n">
-        <v>3.991046277802223</v>
+        <v>3.991046277802226</v>
       </c>
       <c r="O5" t="n">
         <v>3.070766291490418</v>
       </c>
       <c r="P5" t="n">
-        <v>3.616913281486902</v>
+        <v>3.616913281486901</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.467798417892463</v>
+        <v>2.467798417892464</v>
       </c>
       <c r="R5" t="n">
-        <v>5.784031747879793</v>
+        <v>5.7840317478798</v>
       </c>
       <c r="S5" t="n">
-        <v>5.249802261455214</v>
+        <v>5.249802261455213</v>
       </c>
       <c r="T5" t="n">
-        <v>2.766617328726183</v>
+        <v>2.766617328726184</v>
       </c>
       <c r="U5" t="n">
-        <v>4.074607530447704</v>
+        <v>4.074607530447708</v>
       </c>
       <c r="V5" t="n">
-        <v>4.160878050800131</v>
+        <v>4.160878050800129</v>
       </c>
       <c r="W5" t="n">
-        <v>3.856125420045134</v>
+        <v>3.856125420045135</v>
       </c>
       <c r="X5" t="n">
-        <v>4.641800946331678</v>
+        <v>4.641800946331679</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.150159171804166</v>
+        <v>3.150159171804165</v>
       </c>
       <c r="Z5" t="n">
         <v>2.899760379070254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.969242369405754</v>
+        <v>5.969242369405749</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.510563266538464</v>
+        <v>3.510563266538463</v>
       </c>
     </row>
     <row r="6">
@@ -7830,10 +7830,10 @@
         <v>17.05284685609555</v>
       </c>
       <c r="F6" t="n">
-        <v>17.15779014876267</v>
+        <v>17.15779014876269</v>
       </c>
       <c r="G6" t="n">
-        <v>3.336069838337948</v>
+        <v>3.336069838337949</v>
       </c>
       <c r="H6" t="n">
         <v>16.66779388855863</v>
@@ -7842,28 +7842,28 @@
         <v>3.535761809661032</v>
       </c>
       <c r="J6" t="n">
-        <v>16.68645326638923</v>
+        <v>3.389175521614685</v>
       </c>
       <c r="K6" t="n">
         <v>3.434292344967258</v>
       </c>
       <c r="L6" t="n">
-        <v>3.425503094875812</v>
+        <v>16.72278083965037</v>
       </c>
       <c r="M6" t="n">
-        <v>16.6774433479065</v>
+        <v>16.67744334790649</v>
       </c>
       <c r="N6" t="n">
-        <v>3.301520860807789</v>
+        <v>3.301520860807792</v>
       </c>
       <c r="O6" t="n">
-        <v>3.334274223430785</v>
+        <v>3.334274223430788</v>
       </c>
       <c r="P6" t="n">
-        <v>16.66127589708969</v>
+        <v>16.66127589708967</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.298661705827298</v>
+        <v>16.59593945060186</v>
       </c>
       <c r="R6" t="n">
         <v>16.75668531405611</v>
@@ -7872,25 +7872,25 @@
         <v>16.76404579278246</v>
       </c>
       <c r="T6" t="n">
-        <v>16.61024805161662</v>
+        <v>3.312970306842074</v>
       </c>
       <c r="U6" t="n">
         <v>16.68451975179823</v>
       </c>
       <c r="V6" t="n">
-        <v>3.40031909229804</v>
+        <v>16.6975968370726</v>
       </c>
       <c r="W6" t="n">
-        <v>3.372678946652573</v>
+        <v>3.372678946652572</v>
       </c>
       <c r="X6" t="n">
-        <v>16.70661331956298</v>
+        <v>3.409335574788425</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.352917743090944</v>
+        <v>3.352917743090948</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.324927288374175</v>
+        <v>3.324927288374176</v>
       </c>
       <c r="AA6" t="n">
         <v>16.78100944534641</v>
@@ -7909,7 +7909,7 @@
         <v>2.183399304858201</v>
       </c>
       <c r="C7" t="n">
-        <v>2.704600296848763</v>
+        <v>2.704600296848764</v>
       </c>
       <c r="D7" t="n">
         <v>2.522781969521996</v>
@@ -7930,13 +7930,13 @@
         <v>2.426926502013403</v>
       </c>
       <c r="J7" t="n">
-        <v>2.280340213967056</v>
+        <v>2.280340213967057</v>
       </c>
       <c r="K7" t="n">
         <v>2.325457037319628</v>
       </c>
       <c r="L7" t="n">
-        <v>2.316667787228182</v>
+        <v>2.316667787228181</v>
       </c>
       <c r="M7" t="n">
         <v>2.271330295484309</v>
@@ -7948,19 +7948,19 @@
         <v>2.227594000050065</v>
       </c>
       <c r="P7" t="n">
-        <v>2.256079735519591</v>
+        <v>2.25607973551959</v>
       </c>
       <c r="Q7" t="n">
         <v>2.189826398179679</v>
       </c>
       <c r="R7" t="n">
-        <v>2.350572261633933</v>
+        <v>2.350572261633934</v>
       </c>
       <c r="S7" t="n">
         <v>2.357932740360279</v>
       </c>
       <c r="T7" t="n">
-        <v>2.20413499919445</v>
+        <v>2.204134999194451</v>
       </c>
       <c r="U7" t="n">
         <v>2.278419883919697</v>
@@ -7978,7 +7978,7 @@
         <v>2.226439085270902</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.216091980726544</v>
+        <v>2.216091980726545</v>
       </c>
       <c r="AA7" t="n">
         <v>2.374896392924215</v>
@@ -7997,28 +7997,28 @@
         <v>2.194628695758277</v>
       </c>
       <c r="C8" t="n">
-        <v>2.772148421453179</v>
+        <v>2.77214842145318</v>
       </c>
       <c r="D8" t="n">
         <v>2.59033009412641</v>
       </c>
       <c r="E8" t="n">
-        <v>2.714281928277785</v>
+        <v>2.684293863880177</v>
       </c>
       <c r="F8" t="n">
-        <v>2.771680287740215</v>
+        <v>2.771680287740214</v>
       </c>
       <c r="G8" t="n">
-        <v>2.294782655294737</v>
+        <v>2.306460711610389</v>
       </c>
       <c r="H8" t="n">
         <v>2.329228960740885</v>
       </c>
       <c r="I8" t="n">
-        <v>2.494474626617818</v>
+        <v>2.49447462661782</v>
       </c>
       <c r="J8" t="n">
-        <v>2.347888338571472</v>
+        <v>2.347888338571473</v>
       </c>
       <c r="K8" t="n">
         <v>2.393005161924045</v>
@@ -8027,13 +8027,13 @@
         <v>2.384215911832597</v>
       </c>
       <c r="M8" t="n">
-        <v>2.338878420088724</v>
+        <v>2.338878420088719</v>
       </c>
       <c r="N8" t="n">
         <v>2.21873713079389</v>
       </c>
       <c r="O8" t="n">
-        <v>2.263487662337258</v>
+        <v>2.263487662337259</v>
       </c>
       <c r="P8" t="n">
         <v>2.289032601812468</v>
@@ -8045,28 +8045,28 @@
         <v>2.418120386238349</v>
       </c>
       <c r="S8" t="n">
-        <v>2.425480864964694</v>
+        <v>2.425480864964695</v>
       </c>
       <c r="T8" t="n">
-        <v>2.271683123798865</v>
+        <v>2.271683123798866</v>
       </c>
       <c r="U8" t="n">
-        <v>2.311312301616004</v>
+        <v>2.318480346523641</v>
       </c>
       <c r="V8" t="n">
-        <v>2.35903190925483</v>
+        <v>2.343654530841529</v>
       </c>
       <c r="W8" t="n">
         <v>2.330748906085494</v>
       </c>
       <c r="X8" t="n">
-        <v>2.305823465304862</v>
+        <v>2.305823465304863</v>
       </c>
       <c r="Y8" t="n">
         <v>2.350007500376796</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.283640105330961</v>
+        <v>2.226275222234583</v>
       </c>
       <c r="AA8" t="n">
         <v>2.442444517528631</v>
@@ -8082,22 +8082,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.624255263686314</v>
+        <v>2.624255263686315</v>
       </c>
       <c r="C9" t="n">
-        <v>3.288784588718021</v>
+        <v>3.288784588718022</v>
       </c>
       <c r="D9" t="n">
         <v>3.106966261391256</v>
       </c>
       <c r="E9" t="n">
-        <v>3.230918095542629</v>
+        <v>3.197838504439936</v>
       </c>
       <c r="F9" t="n">
-        <v>3.335861388209772</v>
+        <v>3.005450456533378</v>
       </c>
       <c r="G9" t="n">
-        <v>2.81141882255958</v>
+        <v>2.811418827158615</v>
       </c>
       <c r="H9" t="n">
         <v>2.84586512800573</v>
@@ -8106,13 +8106,13 @@
         <v>3.011110793882664</v>
       </c>
       <c r="J9" t="n">
-        <v>2.864524505836318</v>
+        <v>2.864524505836319</v>
       </c>
       <c r="K9" t="n">
-        <v>2.909641329188888</v>
+        <v>2.909641329188889</v>
       </c>
       <c r="L9" t="n">
-        <v>2.900852079097442</v>
+        <v>2.900852079097441</v>
       </c>
       <c r="M9" t="n">
         <v>2.855514587353567</v>
@@ -8121,19 +8121,19 @@
         <v>2.779029738599837</v>
       </c>
       <c r="O9" t="n">
-        <v>2.859281929243549</v>
+        <v>2.859281929243551</v>
       </c>
       <c r="P9" t="n">
-        <v>2.898097843864459</v>
+        <v>2.898097843864458</v>
       </c>
       <c r="Q9" t="n">
         <v>2.774010694647973</v>
       </c>
       <c r="R9" t="n">
-        <v>2.934756553503196</v>
+        <v>2.934756553503195</v>
       </c>
       <c r="S9" t="n">
-        <v>2.942117032229538</v>
+        <v>2.942117032229539</v>
       </c>
       <c r="T9" t="n">
         <v>2.788319291063709</v>
@@ -8142,7 +8142,7 @@
         <v>2.862590991245312</v>
       </c>
       <c r="V9" t="n">
-        <v>2.875668076519673</v>
+        <v>3.04106581741669</v>
       </c>
       <c r="W9" t="n">
         <v>2.847374005110994</v>
@@ -8154,13 +8154,13 @@
         <v>2.810623377140164</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.800276272595802</v>
+        <v>2.71386203485092</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.959080684793474</v>
+        <v>2.959080684793473</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.822562644630136</v>
+        <v>2.822562644630137</v>
       </c>
     </row>
   </sheetData>
@@ -8326,19 +8326,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.396544411750759</v>
+        <v>2.396544411750761</v>
       </c>
       <c r="C2" t="n">
-        <v>2.439622219529355</v>
+        <v>2.439622219529354</v>
       </c>
       <c r="D2" t="n">
         <v>2.41095398317314</v>
       </c>
       <c r="E2" t="n">
-        <v>2.427648288966812</v>
+        <v>2.427648288966813</v>
       </c>
       <c r="F2" t="n">
-        <v>2.444747402377157</v>
+        <v>2.444747402377159</v>
       </c>
       <c r="G2" t="n">
         <v>2.400095802425968</v>
@@ -8347,61 +8347,61 @@
         <v>2.403158530629909</v>
       </c>
       <c r="I2" t="n">
-        <v>2.410102393699347</v>
+        <v>2.410102393699346</v>
       </c>
       <c r="J2" t="n">
-        <v>2.405628299697293</v>
+        <v>2.405628299697292</v>
       </c>
       <c r="K2" t="n">
         <v>2.406892546200408</v>
       </c>
       <c r="L2" t="n">
-        <v>2.40799501255571</v>
+        <v>2.407995012555711</v>
       </c>
       <c r="M2" t="n">
         <v>2.415109339737249</v>
       </c>
       <c r="N2" t="n">
-        <v>2.397782995153934</v>
+        <v>2.397782995153935</v>
       </c>
       <c r="O2" t="n">
         <v>2.435984591565422</v>
       </c>
       <c r="P2" t="n">
-        <v>2.404161808561147</v>
+        <v>2.404161808561146</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.397319703200495</v>
+        <v>2.397319703200494</v>
       </c>
       <c r="R2" t="n">
-        <v>2.407700566856099</v>
+        <v>2.407700566856098</v>
       </c>
       <c r="S2" t="n">
-        <v>2.409925802070415</v>
+        <v>2.409925802070414</v>
       </c>
       <c r="T2" t="n">
-        <v>2.399209169793149</v>
+        <v>2.399209169793151</v>
       </c>
       <c r="U2" t="n">
-        <v>2.436903928950523</v>
+        <v>2.436903928950524</v>
       </c>
       <c r="V2" t="n">
-        <v>2.404892678023905</v>
+        <v>2.404892678023906</v>
       </c>
       <c r="W2" t="n">
-        <v>2.438905505321895</v>
+        <v>2.438905505321896</v>
       </c>
       <c r="X2" t="n">
-        <v>2.408360774176119</v>
+        <v>2.408360774176118</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.400015207479826</v>
+        <v>2.400015207479827</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.416972712491962</v>
+        <v>2.416972712491961</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.408083485316116</v>
+        <v>2.408083485316117</v>
       </c>
       <c r="AB2" t="n">
         <v>2.402224576704381</v>
@@ -8414,13 +8414,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.393535395188734</v>
+        <v>2.393535395188733</v>
       </c>
       <c r="C3" t="n">
-        <v>2.673588209672543</v>
+        <v>2.673588209672545</v>
       </c>
       <c r="D3" t="n">
-        <v>2.496500755811316</v>
+        <v>2.496500755811317</v>
       </c>
       <c r="E3" t="n">
         <v>2.61544732778891</v>
@@ -8429,7 +8429,7 @@
         <v>2.73793225654275</v>
       </c>
       <c r="G3" t="n">
-        <v>2.418718051771586</v>
+        <v>2.418718051771584</v>
       </c>
       <c r="H3" t="n">
         <v>2.441038915789822</v>
@@ -8438,16 +8438,16 @@
         <v>2.490629132332463</v>
       </c>
       <c r="J3" t="n">
-        <v>2.458219861967365</v>
+        <v>2.458219861967364</v>
       </c>
       <c r="K3" t="n">
-        <v>2.46707815718531</v>
+        <v>2.467078157185311</v>
       </c>
       <c r="L3" t="n">
         <v>2.474844655526827</v>
       </c>
       <c r="M3" t="n">
-        <v>2.525580564029858</v>
+        <v>2.525580564029857</v>
       </c>
       <c r="N3" t="n">
         <v>2.402400173234819</v>
@@ -8462,37 +8462,37 @@
         <v>2.399068081794416</v>
       </c>
       <c r="R3" t="n">
-        <v>2.473518830204503</v>
+        <v>2.473518830204505</v>
       </c>
       <c r="S3" t="n">
-        <v>2.488415323509077</v>
+        <v>2.488415323509078</v>
       </c>
       <c r="T3" t="n">
         <v>2.412619456165042</v>
       </c>
       <c r="U3" t="n">
-        <v>2.504883790174952</v>
+        <v>2.504883790174953</v>
       </c>
       <c r="V3" t="n">
         <v>2.452749143080958</v>
       </c>
       <c r="W3" t="n">
-        <v>2.495270127378077</v>
+        <v>2.495270127378078</v>
       </c>
       <c r="X3" t="n">
-        <v>2.477893782800634</v>
+        <v>2.477893782800633</v>
       </c>
       <c r="Y3" t="n">
         <v>2.4183123203445</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.438287753410433</v>
+        <v>2.438287753410432</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.475922454711123</v>
+        <v>2.475922454711124</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.4348722633075</v>
+        <v>2.434872263307499</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.107528750042462</v>
+        <v>2.107528750042464</v>
       </c>
       <c r="C4" t="n">
         <v>2.539045801846009</v>
       </c>
       <c r="D4" t="n">
-        <v>2.270291487988591</v>
+        <v>2.270291487988592</v>
       </c>
       <c r="E4" t="n">
-        <v>2.45886135168822</v>
+        <v>2.458861351688219</v>
       </c>
       <c r="F4" t="n">
         <v>2.652003703638862</v>
       </c>
       <c r="G4" t="n">
-        <v>2.147643341439353</v>
+        <v>2.147643341439349</v>
       </c>
       <c r="H4" t="n">
-        <v>2.182238265427458</v>
+        <v>2.182238265427455</v>
       </c>
       <c r="I4" t="n">
-        <v>2.260672393131573</v>
+        <v>2.260672393131571</v>
       </c>
       <c r="J4" t="n">
-        <v>2.210165752757861</v>
+        <v>2.210165752757862</v>
       </c>
       <c r="K4" t="n">
         <v>2.22441568902827</v>
       </c>
       <c r="L4" t="n">
-        <v>2.236868553670997</v>
+        <v>2.236868553670996</v>
       </c>
       <c r="M4" t="n">
-        <v>2.316886799404819</v>
+        <v>2.316886799404816</v>
       </c>
       <c r="N4" t="n">
-        <v>2.121519119357829</v>
+        <v>2.121519119357828</v>
       </c>
       <c r="O4" t="n">
-        <v>2.166169848523011</v>
+        <v>2.16616984852301</v>
       </c>
       <c r="P4" t="n">
-        <v>2.193570751191421</v>
+        <v>2.193570751191422</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.11628602361889</v>
+        <v>2.116286023618889</v>
       </c>
       <c r="R4" t="n">
-        <v>2.233542654042157</v>
+        <v>2.233542654042156</v>
       </c>
       <c r="S4" t="n">
-        <v>2.25867770944662</v>
+        <v>2.258677709446618</v>
       </c>
       <c r="T4" t="n">
         <v>2.137628417980526</v>
       </c>
       <c r="U4" t="n">
-        <v>2.200350432703338</v>
+        <v>2.200350432703337</v>
       </c>
       <c r="V4" t="n">
-        <v>2.201947748891033</v>
+        <v>2.201947748891032</v>
       </c>
       <c r="W4" t="n">
-        <v>2.172980573994032</v>
+        <v>2.172980573994031</v>
       </c>
       <c r="X4" t="n">
-        <v>2.24099999943215</v>
+        <v>2.240999999432149</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.146925090319083</v>
+        <v>2.146925090319084</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.130424694584125</v>
+        <v>2.130424694584124</v>
       </c>
       <c r="AA4" t="n">
         <v>2.237867894199256</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.172782849498602</v>
+        <v>2.172782849498601</v>
       </c>
     </row>
     <row r="5">
@@ -8593,55 +8593,55 @@
         <v>2.225985091008088</v>
       </c>
       <c r="C5" t="n">
-        <v>9.662642037742497</v>
+        <v>9.662642037742485</v>
       </c>
       <c r="D5" t="n">
         <v>5.168729522563424</v>
       </c>
       <c r="E5" t="n">
-        <v>8.399465719027337</v>
+        <v>8.399465719027349</v>
       </c>
       <c r="F5" t="n">
-        <v>12.04751814309068</v>
+        <v>12.04751814309069</v>
       </c>
       <c r="G5" t="n">
-        <v>2.850594855184929</v>
+        <v>2.850594855184879</v>
       </c>
       <c r="H5" t="n">
-        <v>3.701893412218903</v>
+        <v>3.701893412218899</v>
       </c>
       <c r="I5" t="n">
-        <v>5.105464648161771</v>
+        <v>5.105464648161773</v>
       </c>
       <c r="J5" t="n">
-        <v>3.964245228842085</v>
+        <v>3.964245228842081</v>
       </c>
       <c r="K5" t="n">
-        <v>4.131435566009857</v>
+        <v>4.13143556600986</v>
       </c>
       <c r="L5" t="n">
-        <v>4.298899180475225</v>
+        <v>4.298899180475227</v>
       </c>
       <c r="M5" t="n">
-        <v>5.789848083551346</v>
+        <v>5.789848083551343</v>
       </c>
       <c r="N5" t="n">
-        <v>3.649747961134746</v>
+        <v>3.649747961134753</v>
       </c>
       <c r="O5" t="n">
-        <v>3.140274617493406</v>
+        <v>3.140274617493409</v>
       </c>
       <c r="P5" t="n">
-        <v>3.617137657014559</v>
+        <v>3.617137657014561</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.380557299840433</v>
+        <v>2.38055729984043</v>
       </c>
       <c r="R5" t="n">
-        <v>4.642035255327691</v>
+        <v>4.642035255327686</v>
       </c>
       <c r="S5" t="n">
-        <v>4.576075990770094</v>
+        <v>4.576075990770099</v>
       </c>
       <c r="T5" t="n">
         <v>2.792317006411477</v>
@@ -8650,25 +8650,25 @@
         <v>3.728387168608365</v>
       </c>
       <c r="V5" t="n">
-        <v>3.703080134234316</v>
+        <v>3.703080134234321</v>
       </c>
       <c r="W5" t="n">
-        <v>3.39350849311029</v>
+        <v>3.393508493110291</v>
       </c>
       <c r="X5" t="n">
-        <v>4.599299383180987</v>
+        <v>4.599299383180983</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.922321745346988</v>
+        <v>2.922321745346986</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.584722222835874</v>
+        <v>2.58472222283587</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.547891360704742</v>
+        <v>4.547891360704745</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.485229708206366</v>
+        <v>3.485229708206364</v>
       </c>
     </row>
     <row r="6">
@@ -8678,82 +8678,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.5912481570624</v>
+        <v>3.20170684978325</v>
       </c>
       <c r="C6" t="n">
-        <v>16.02276520886594</v>
+        <v>16.02276520886593</v>
       </c>
       <c r="D6" t="n">
-        <v>3.364469587729383</v>
+        <v>3.364469587729381</v>
       </c>
       <c r="E6" t="n">
-        <v>3.553039451429011</v>
+        <v>15.94258075870814</v>
       </c>
       <c r="F6" t="n">
-        <v>3.746181803379649</v>
+        <v>16.13572311065879</v>
       </c>
       <c r="G6" t="n">
-        <v>15.63136274845928</v>
+        <v>3.241821441180133</v>
       </c>
       <c r="H6" t="n">
-        <v>3.276416365168242</v>
+        <v>15.66595767244737</v>
       </c>
       <c r="I6" t="n">
-        <v>3.354850492872353</v>
+        <v>15.74439180015151</v>
       </c>
       <c r="J6" t="n">
-        <v>15.69388515977779</v>
+        <v>3.30434385249865</v>
       </c>
       <c r="K6" t="n">
-        <v>3.318593788769052</v>
+        <v>15.7081350960482</v>
       </c>
       <c r="L6" t="n">
-        <v>15.72058796069091</v>
+        <v>3.331046653411782</v>
       </c>
       <c r="M6" t="n">
-        <v>3.411064899145606</v>
+        <v>15.80060620642475</v>
       </c>
       <c r="N6" t="n">
-        <v>3.214219205285816</v>
+        <v>3.214219205285815</v>
       </c>
       <c r="O6" t="n">
-        <v>15.64916059789164</v>
+        <v>3.25886993445099</v>
       </c>
       <c r="P6" t="n">
         <v>3.283312971888645</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.210464123359681</v>
+        <v>15.60000543063882</v>
       </c>
       <c r="R6" t="n">
-        <v>15.7172620610621</v>
+        <v>15.71726206106208</v>
       </c>
       <c r="S6" t="n">
-        <v>3.352855809187406</v>
+        <v>3.352855809187405</v>
       </c>
       <c r="T6" t="n">
         <v>3.231806517721314</v>
       </c>
       <c r="U6" t="n">
-        <v>15.68387773385136</v>
+        <v>3.294336426572231</v>
       </c>
       <c r="V6" t="n">
-        <v>15.68566715591097</v>
+        <v>15.68566715591096</v>
       </c>
       <c r="W6" t="n">
-        <v>3.268199176925095</v>
+        <v>3.268199176925096</v>
       </c>
       <c r="X6" t="n">
-        <v>15.72471940645209</v>
+        <v>3.335178099172935</v>
       </c>
       <c r="Y6" t="n">
         <v>3.257805376320409</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.224602794324912</v>
+        <v>3.22460279432491</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.72158730121921</v>
+        <v>15.72158730121919</v>
       </c>
       <c r="AB6" t="n">
         <v>3.265399927419061</v>
@@ -8766,31 +8766,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.170963615123656</v>
+        <v>2.170963615123661</v>
       </c>
       <c r="C7" t="n">
-        <v>2.602480666927204</v>
+        <v>2.602480666927205</v>
       </c>
       <c r="D7" t="n">
-        <v>2.333726353069791</v>
+        <v>2.333726353069789</v>
       </c>
       <c r="E7" t="n">
-        <v>2.522296216769421</v>
+        <v>2.522296216769416</v>
       </c>
       <c r="F7" t="n">
-        <v>2.715438568720066</v>
+        <v>2.71543856872006</v>
       </c>
       <c r="G7" t="n">
-        <v>2.211078206520549</v>
+        <v>2.211078206520545</v>
       </c>
       <c r="H7" t="n">
-        <v>2.245673130508656</v>
+        <v>2.245673130508653</v>
       </c>
       <c r="I7" t="n">
-        <v>2.324107258212763</v>
+        <v>2.324107258212769</v>
       </c>
       <c r="J7" t="n">
-        <v>2.273600617839067</v>
+        <v>2.273600617839059</v>
       </c>
       <c r="K7" t="n">
         <v>2.287850554109467</v>
@@ -8799,52 +8799,52 @@
         <v>2.300303418752193</v>
       </c>
       <c r="M7" t="n">
-        <v>2.380321664486012</v>
+        <v>2.380321664486014</v>
       </c>
       <c r="N7" t="n">
-        <v>2.184953984439018</v>
+        <v>2.184953984439026</v>
       </c>
       <c r="O7" t="n">
         <v>2.229600250674719</v>
       </c>
       <c r="P7" t="n">
-        <v>2.257001153343134</v>
+        <v>2.257001153343132</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.179720888700081</v>
+        <v>2.179720888700086</v>
       </c>
       <c r="R7" t="n">
-        <v>2.296977519123358</v>
+        <v>2.296977519123354</v>
       </c>
       <c r="S7" t="n">
-        <v>2.322112574527813</v>
+        <v>2.322112574527816</v>
       </c>
       <c r="T7" t="n">
         <v>2.201063283061722</v>
       </c>
       <c r="U7" t="n">
-        <v>2.263621210534886</v>
+        <v>2.263621210534889</v>
       </c>
       <c r="V7" t="n">
-        <v>2.265382613972227</v>
+        <v>2.265382613972231</v>
       </c>
       <c r="W7" t="n">
-        <v>2.236415439075227</v>
+        <v>2.236415439075228</v>
       </c>
       <c r="X7" t="n">
         <v>2.304434864513347</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.210167849528385</v>
+        <v>2.210167849528383</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.193859559665318</v>
+        <v>2.193859559665323</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.301302759280457</v>
+        <v>2.301302759280452</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.236217714579796</v>
+        <v>2.236217714579799</v>
       </c>
     </row>
     <row r="8">
@@ -8863,19 +8863,19 @@
         <v>2.396531127554251</v>
       </c>
       <c r="E8" t="n">
-        <v>2.585100991253879</v>
+        <v>2.557224961991823</v>
       </c>
       <c r="F8" t="n">
-        <v>2.734046961214152</v>
+        <v>2.734046961214149</v>
       </c>
       <c r="G8" t="n">
-        <v>2.273882981005011</v>
+        <v>2.28473856125395</v>
       </c>
       <c r="H8" t="n">
-        <v>2.308477904993113</v>
+        <v>2.308477904993115</v>
       </c>
       <c r="I8" t="n">
-        <v>2.386912032697228</v>
+        <v>2.38691203269723</v>
       </c>
       <c r="J8" t="n">
         <v>2.336405392323521</v>
@@ -8887,16 +8887,16 @@
         <v>2.363108193236654</v>
       </c>
       <c r="M8" t="n">
-        <v>2.443126438970475</v>
+        <v>2.443126438970473</v>
       </c>
       <c r="N8" t="n">
         <v>2.207177006201645</v>
       </c>
       <c r="O8" t="n">
-        <v>2.262979953377937</v>
+        <v>2.262979953377934</v>
       </c>
       <c r="P8" t="n">
-        <v>2.287647177936713</v>
+        <v>2.287647177936711</v>
       </c>
       <c r="Q8" t="n">
         <v>2.179885000206507</v>
@@ -8905,19 +8905,19 @@
         <v>2.359782293607815</v>
       </c>
       <c r="S8" t="n">
-        <v>2.384917349012281</v>
+        <v>2.384917349012278</v>
       </c>
       <c r="T8" t="n">
-        <v>2.263868057546182</v>
+        <v>2.263868057546185</v>
       </c>
       <c r="U8" t="n">
-        <v>2.294206753645574</v>
+        <v>2.30087070391555</v>
       </c>
       <c r="V8" t="n">
-        <v>2.328187388456694</v>
+        <v>2.313906493356763</v>
       </c>
       <c r="W8" t="n">
-        <v>2.299230502272516</v>
+        <v>2.299230502272519</v>
       </c>
       <c r="X8" t="n">
         <v>2.309397163829451</v>
@@ -8926,13 +8926,13 @@
         <v>2.325068338041977</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.256664334149787</v>
+        <v>2.203339613400864</v>
       </c>
       <c r="AA8" t="n">
         <v>2.364107533764914</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.353708792657936</v>
+        <v>2.353708792657935</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.525312311142659</v>
+        <v>2.525312311142658</v>
       </c>
       <c r="C9" t="n">
-        <v>3.074722131380716</v>
+        <v>3.074722131380712</v>
       </c>
       <c r="D9" t="n">
         <v>2.805967817523293</v>
       </c>
       <c r="E9" t="n">
-        <v>2.994537681222923</v>
+        <v>2.967328485983611</v>
       </c>
       <c r="F9" t="n">
-        <v>3.187680033173564</v>
+        <v>2.915905068637808</v>
       </c>
       <c r="G9" t="n">
-        <v>2.683319670974052</v>
+        <v>2.683319638264324</v>
       </c>
       <c r="H9" t="n">
-        <v>2.717914594962161</v>
+        <v>2.717914594962158</v>
       </c>
       <c r="I9" t="n">
         <v>2.796348722666277</v>
       </c>
       <c r="J9" t="n">
-        <v>2.745842082292564</v>
+        <v>2.745842082292567</v>
       </c>
       <c r="K9" t="n">
         <v>2.760092018562971</v>
       </c>
       <c r="L9" t="n">
-        <v>2.772544883205701</v>
+        <v>2.772544883205698</v>
       </c>
       <c r="M9" t="n">
-        <v>2.852563128939521</v>
+        <v>2.852563128939519</v>
       </c>
       <c r="N9" t="n">
         <v>2.657195448892531</v>
       </c>
       <c r="O9" t="n">
-        <v>2.740915643599981</v>
+        <v>2.740915643599975</v>
       </c>
       <c r="P9" t="n">
-        <v>2.776813491818242</v>
+        <v>2.776813491818241</v>
       </c>
       <c r="Q9" t="n">
         <v>2.651962320443866</v>
       </c>
       <c r="R9" t="n">
-        <v>2.769218983576861</v>
+        <v>2.769218983576859</v>
       </c>
       <c r="S9" t="n">
-        <v>2.79435403898132</v>
+        <v>2.794354038981321</v>
       </c>
       <c r="T9" t="n">
-        <v>2.673304747515226</v>
+        <v>2.673304747515227</v>
       </c>
       <c r="U9" t="n">
-        <v>2.735834656366142</v>
+        <v>2.73583465636614</v>
       </c>
       <c r="V9" t="n">
-        <v>2.737624078425736</v>
+        <v>2.873669659051335</v>
       </c>
       <c r="W9" t="n">
         <v>2.708656903528734</v>
       </c>
       <c r="X9" t="n">
-        <v>2.776676328966852</v>
+        <v>2.77667632896685</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.682409313981892</v>
+        <v>2.682409313981891</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.666101024118828</v>
+        <v>2.595022155198196</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.77354422373396</v>
+        <v>2.773544223733956</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.708459179033308</v>
+        <v>2.708459179033306</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia water use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia water use results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.398762762559154</v>
+        <v>2.400374429269666</v>
       </c>
       <c r="C2" t="n">
-        <v>2.448247051777014</v>
+        <v>2.448255974820209</v>
       </c>
       <c r="D2" t="n">
-        <v>2.443667367988472</v>
+        <v>2.444146209731753</v>
       </c>
       <c r="E2" t="n">
-        <v>2.439411279524754</v>
+        <v>2.43978725135039</v>
       </c>
       <c r="F2" t="n">
-        <v>2.440132061732939</v>
+        <v>2.440390868719063</v>
       </c>
       <c r="G2" t="n">
-        <v>2.402474827229611</v>
+        <v>2.402607904871429</v>
       </c>
       <c r="H2" t="n">
-        <v>2.402550824764571</v>
+        <v>2.402819549943506</v>
       </c>
       <c r="I2" t="n">
-        <v>2.418093629817522</v>
+        <v>2.418336904764316</v>
       </c>
       <c r="J2" t="n">
-        <v>2.406098952689786</v>
+        <v>2.406634773869031</v>
       </c>
       <c r="K2" t="n">
-        <v>2.407434198040655</v>
+        <v>2.407646893450392</v>
       </c>
       <c r="L2" t="n">
-        <v>2.405319443734015</v>
+        <v>2.407667404700605</v>
       </c>
       <c r="M2" t="n">
-        <v>2.405534098306803</v>
+        <v>2.406967763912201</v>
       </c>
       <c r="N2" t="n">
-        <v>2.399534619686747</v>
+        <v>2.399709288144359</v>
       </c>
       <c r="O2" t="n">
-        <v>2.432791516808024</v>
+        <v>2.432987340450447</v>
       </c>
       <c r="P2" t="n">
-        <v>2.404423063666184</v>
+        <v>2.405097355213073</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.399113142914567</v>
+        <v>2.399435278854961</v>
       </c>
       <c r="R2" t="n">
-        <v>2.415776032675753</v>
+        <v>2.415999805420799</v>
       </c>
       <c r="S2" t="n">
-        <v>2.40862122078162</v>
+        <v>2.409517120984688</v>
       </c>
       <c r="T2" t="n">
-        <v>2.400228899264484</v>
+        <v>2.40056788845723</v>
       </c>
       <c r="U2" t="n">
-        <v>2.440914429850308</v>
+        <v>2.44093212855968</v>
       </c>
       <c r="V2" t="n">
-        <v>2.406470625018433</v>
+        <v>2.406956801236386</v>
       </c>
       <c r="W2" t="n">
-        <v>2.440738665986523</v>
+        <v>2.44010710223335</v>
       </c>
       <c r="X2" t="n">
-        <v>2.407353944709033</v>
+        <v>2.408251176621422</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.402019164311196</v>
+        <v>2.402454977076856</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.419967251171326</v>
+        <v>2.420636174795936</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.416940555471567</v>
+        <v>2.417115566474453</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.39934693942697</v>
+        <v>2.400873245263099</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.400453214506557</v>
+        <v>2.411265517745634</v>
       </c>
       <c r="C3" t="n">
-        <v>2.723202633962577</v>
+        <v>2.723562531326078</v>
       </c>
       <c r="D3" t="n">
-        <v>2.721974310753083</v>
+        <v>2.724753522566105</v>
       </c>
       <c r="E3" t="n">
-        <v>2.690538290595501</v>
+        <v>2.692574785917628</v>
       </c>
       <c r="F3" t="n">
-        <v>2.697085717015383</v>
+        <v>2.698291208501121</v>
       </c>
       <c r="G3" t="n">
-        <v>2.426886279116287</v>
+        <v>2.427188836526554</v>
       </c>
       <c r="H3" t="n">
-        <v>2.427732218904315</v>
+        <v>2.429010112489429</v>
       </c>
       <c r="I3" t="n">
-        <v>2.539002782982618</v>
+        <v>2.540096348911874</v>
       </c>
       <c r="J3" t="n">
-        <v>2.452841880778343</v>
+        <v>2.456017170148726</v>
       </c>
       <c r="K3" t="n">
-        <v>2.462557676805835</v>
+        <v>2.463431248704039</v>
       </c>
       <c r="L3" t="n">
-        <v>2.447266857528136</v>
+        <v>2.463374787951338</v>
       </c>
       <c r="M3" t="n">
-        <v>2.449871077376991</v>
+        <v>2.459451473487251</v>
       </c>
       <c r="N3" t="n">
-        <v>2.406014994164035</v>
+        <v>2.406615763175858</v>
       </c>
       <c r="O3" t="n">
-        <v>2.468205838293971</v>
+        <v>2.471992345942413</v>
       </c>
       <c r="P3" t="n">
-        <v>2.440723612187166</v>
+        <v>2.444876878825272</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.403010096487618</v>
+        <v>2.40466542278282</v>
       </c>
       <c r="R3" t="n">
-        <v>2.52250438027234</v>
+        <v>2.523458929490867</v>
       </c>
       <c r="S3" t="n">
-        <v>2.470658912852711</v>
+        <v>2.476392835541885</v>
       </c>
       <c r="T3" t="n">
-        <v>2.411017467613465</v>
+        <v>2.412795918073654</v>
       </c>
       <c r="U3" t="n">
-        <v>2.526637669026701</v>
+        <v>2.528994023056435</v>
       </c>
       <c r="V3" t="n">
-        <v>2.45527856893704</v>
+        <v>2.458091257103928</v>
       </c>
       <c r="W3" t="n">
-        <v>2.502153930273403</v>
+        <v>2.500967750989907</v>
       </c>
       <c r="X3" t="n">
-        <v>2.46196322935347</v>
+        <v>2.467732877914438</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.423739733399767</v>
+        <v>2.426204063552926</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.448402230569882</v>
+        <v>2.453680607430978</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.530310365418609</v>
+        <v>2.530913286536242</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.405987316538388</v>
+        <v>2.41622410709707</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.118489376979914</v>
+        <v>2.122580202969871</v>
       </c>
       <c r="C4" t="n">
-        <v>2.613898021319005</v>
+        <v>2.601812501908985</v>
       </c>
       <c r="D4" t="n">
-        <v>2.625707552443139</v>
+        <v>2.617002599302984</v>
       </c>
       <c r="E4" t="n">
-        <v>2.577633075348012</v>
+        <v>2.567766159165569</v>
       </c>
       <c r="F4" t="n">
-        <v>2.585774641965674</v>
+        <v>2.57458429502244</v>
       </c>
       <c r="G4" t="n">
-        <v>2.160418855066833</v>
+        <v>2.147808337341329</v>
       </c>
       <c r="H4" t="n">
-        <v>2.161277282184813</v>
+        <v>2.150198965791973</v>
       </c>
       <c r="I4" t="n">
-        <v>2.336840415301463</v>
+        <v>2.325474626828922</v>
       </c>
       <c r="J4" t="n">
-        <v>2.201375412264218</v>
+        <v>2.19331540162813</v>
       </c>
       <c r="K4" t="n">
-        <v>2.216437229800872</v>
+        <v>2.204726031389983</v>
       </c>
       <c r="L4" t="n">
-        <v>2.192550107072324</v>
+        <v>2.204957715396772</v>
       </c>
       <c r="M4" t="n">
-        <v>2.196499846324494</v>
+        <v>2.198506060285256</v>
       </c>
       <c r="N4" t="n">
-        <v>2.127207858307911</v>
+        <v>2.651628247835907</v>
       </c>
       <c r="O4" t="n">
-        <v>2.142504886512028</v>
+        <v>2.136904563815196</v>
       </c>
       <c r="P4" t="n">
-        <v>2.182425081850977</v>
+        <v>2.175927824153935</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.122447084277234</v>
+        <v>2.111972067005243</v>
       </c>
       <c r="R4" t="n">
-        <v>2.310662089437832</v>
+        <v>2.299076014625077</v>
       </c>
       <c r="S4" t="n">
-        <v>2.229845197717515</v>
+        <v>2.225851111737021</v>
       </c>
       <c r="T4" t="n">
-        <v>2.135050065522829</v>
+        <v>2.124765413489031</v>
       </c>
       <c r="U4" t="n">
-        <v>2.235289456228167</v>
+        <v>2.227290726145028</v>
       </c>
       <c r="V4" t="n">
-        <v>2.205607843703008</v>
+        <v>2.196994821077154</v>
       </c>
       <c r="W4" t="n">
-        <v>2.185127753928624</v>
+        <v>2.172049394362677</v>
       </c>
       <c r="X4" t="n">
-        <v>2.215530731501841</v>
+        <v>2.211551687790759</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.155380535763236</v>
+        <v>2.146173500509866</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.145219504246259</v>
+        <v>2.141059878031945</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.323815910123495</v>
+        <v>2.311679049001543</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.127359621225507</v>
+        <v>2.130364596679949</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.439803203323066</v>
+        <v>2.745041224125755</v>
       </c>
       <c r="C5" t="n">
-        <v>12.84851129548315</v>
+        <v>12.85462616761466</v>
       </c>
       <c r="D5" t="n">
-        <v>13.26905319403547</v>
+        <v>13.34748039117923</v>
       </c>
       <c r="E5" t="n">
-        <v>11.67086375936637</v>
+        <v>11.72082245389331</v>
       </c>
       <c r="F5" t="n">
-        <v>12.66878981369109</v>
+        <v>12.69519251411143</v>
       </c>
       <c r="G5" t="n">
-        <v>3.248436834958488</v>
+        <v>3.242913491519423</v>
       </c>
       <c r="H5" t="n">
-        <v>3.446133567982946</v>
+        <v>3.475752472588586</v>
       </c>
       <c r="I5" t="n">
-        <v>7.184145627228222</v>
+        <v>7.206377802718711</v>
       </c>
       <c r="J5" t="n">
-        <v>4.126337335681396</v>
+        <v>4.211434078045261</v>
       </c>
       <c r="K5" t="n">
-        <v>4.540638831809181</v>
+        <v>4.55487725111555</v>
       </c>
       <c r="L5" t="n">
-        <v>3.942093272376534</v>
+        <v>4.438978692482667</v>
       </c>
       <c r="M5" t="n">
-        <v>4.166411815211916</v>
+        <v>4.476448811975223</v>
       </c>
       <c r="N5" t="n">
-        <v>4.639130811425069</v>
+        <v>2.651628247835907</v>
       </c>
       <c r="O5" t="n">
-        <v>2.874246323719088</v>
+        <v>2.995286672442975</v>
       </c>
       <c r="P5" t="n">
-        <v>3.651578827831759</v>
+        <v>3.762054141469441</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.552905320011268</v>
+        <v>2.592437096538006</v>
       </c>
       <c r="R5" t="n">
-        <v>6.682173036139442</v>
+        <v>6.7000710349051</v>
       </c>
       <c r="S5" t="n">
-        <v>4.590377829949591</v>
+        <v>4.750681566890085</v>
       </c>
       <c r="T5" t="n">
-        <v>2.832950183663244</v>
+        <v>2.87800444807127</v>
       </c>
       <c r="U5" t="n">
-        <v>4.747103806370143</v>
+        <v>4.832659811928045</v>
       </c>
       <c r="V5" t="n">
-        <v>4.082561220276288</v>
+        <v>4.151450374621873</v>
       </c>
       <c r="W5" t="n">
-        <v>3.808257708194636</v>
+        <v>3.793718024521738</v>
       </c>
       <c r="X5" t="n">
-        <v>4.509501124061793</v>
+        <v>4.685692459035249</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.20751848976664</v>
+        <v>3.271532993891267</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.956646264027963</v>
+        <v>3.113334554405597</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.64675436490961</v>
+        <v>6.651413257535824</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.696019428279663</v>
+        <v>3.038714318704859</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.58561142182269</v>
+        <v>3.380596962652827</v>
       </c>
       <c r="C6" t="n">
-        <v>18.08102006616178</v>
+        <v>18.06977135067768</v>
       </c>
       <c r="D6" t="n">
-        <v>3.883011860703629</v>
+        <v>18.08496144807169</v>
       </c>
       <c r="E6" t="n">
-        <v>3.834937383608501</v>
+        <v>18.03572500793429</v>
       </c>
       <c r="F6" t="n">
-        <v>18.05289668680844</v>
+        <v>3.832601054705397</v>
       </c>
       <c r="G6" t="n">
-        <v>17.62754089990963</v>
+        <v>17.61576718611004</v>
       </c>
       <c r="H6" t="n">
-        <v>17.6283993270276</v>
+        <v>17.61815781456068</v>
       </c>
       <c r="I6" t="n">
-        <v>3.594144723561956</v>
+        <v>3.583491386511883</v>
       </c>
       <c r="J6" t="n">
-        <v>17.66849745710701</v>
+        <v>3.451332161311081</v>
       </c>
       <c r="K6" t="n">
-        <v>3.473741538061365</v>
+        <v>17.67268488015867</v>
       </c>
       <c r="L6" t="n">
-        <v>3.449854415332819</v>
+        <v>17.67291656416547</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45380415458498</v>
+        <v>17.66646490905397</v>
       </c>
       <c r="N6" t="n">
-        <v>3.382200296829949</v>
+        <v>2.651628247835907</v>
       </c>
       <c r="O6" t="n">
-        <v>17.60875234395061</v>
+        <v>3.392622809302435</v>
       </c>
       <c r="P6" t="n">
-        <v>17.64867256943308</v>
+        <v>17.64299670650758</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.379751392537729</v>
+        <v>17.57993091577396</v>
       </c>
       <c r="R6" t="n">
-        <v>3.567966397698323</v>
+        <v>17.76703486339379</v>
       </c>
       <c r="S6" t="n">
-        <v>17.69696724256031</v>
+        <v>3.48386787141998</v>
       </c>
       <c r="T6" t="n">
-        <v>3.392354373783323</v>
+        <v>3.382782173171986</v>
       </c>
       <c r="U6" t="n">
-        <v>3.492485161513472</v>
+        <v>3.485214932869475</v>
       </c>
       <c r="V6" t="n">
-        <v>17.67272988854579</v>
+        <v>17.66495366984587</v>
       </c>
       <c r="W6" t="n">
-        <v>17.65137523522131</v>
+        <v>17.63911826865523</v>
       </c>
       <c r="X6" t="n">
-        <v>17.68265277634463</v>
+        <v>17.67951053655947</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.431336521533246</v>
+        <v>3.422885015844092</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.402523812506751</v>
+        <v>3.399076637714904</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.581120218383981</v>
+        <v>17.77963789777027</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.381841639762779</v>
+        <v>3.385640380843339</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.190412316825233</v>
+        <v>2.193208364635016</v>
       </c>
       <c r="C7" t="n">
-        <v>2.685820961164322</v>
+        <v>2.672440663574128</v>
       </c>
       <c r="D7" t="n">
-        <v>2.697630492288456</v>
+        <v>2.687630760968131</v>
       </c>
       <c r="E7" t="n">
-        <v>2.649556015193331</v>
+        <v>2.638394320830716</v>
       </c>
       <c r="F7" t="n">
-        <v>2.657697581810991</v>
+        <v>2.645212456687584</v>
       </c>
       <c r="G7" t="n">
-        <v>2.23234179491215</v>
+        <v>2.218436499006474</v>
       </c>
       <c r="H7" t="n">
-        <v>2.23320022203013</v>
+        <v>2.220827127457118</v>
       </c>
       <c r="I7" t="n">
-        <v>2.408763355146784</v>
+        <v>2.396102788494068</v>
       </c>
       <c r="J7" t="n">
-        <v>2.273298352109536</v>
+        <v>2.263943563293275</v>
       </c>
       <c r="K7" t="n">
-        <v>2.288360169646191</v>
+        <v>2.275354193055128</v>
       </c>
       <c r="L7" t="n">
-        <v>2.264473046917642</v>
+        <v>2.275585877061917</v>
       </c>
       <c r="M7" t="n">
-        <v>2.268422786169813</v>
+        <v>2.2691342219504</v>
       </c>
       <c r="N7" t="n">
-        <v>2.199130798153229</v>
+        <v>2.651628247835907</v>
       </c>
       <c r="O7" t="n">
-        <v>2.214422764048461</v>
+        <v>2.207527679598447</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25434295938741</v>
+        <v>2.246550939937186</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.194370024122552</v>
+        <v>2.182600228670388</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38258502928315</v>
+        <v>2.369704176290222</v>
       </c>
       <c r="S7" t="n">
-        <v>2.301768137562833</v>
+        <v>2.296479273402166</v>
       </c>
       <c r="T7" t="n">
-        <v>2.206973005368147</v>
+        <v>2.195393575154177</v>
       </c>
       <c r="U7" t="n">
-        <v>2.30709928938949</v>
+        <v>2.297814960728775</v>
       </c>
       <c r="V7" t="n">
-        <v>2.277530783548326</v>
+        <v>2.267622982742299</v>
       </c>
       <c r="W7" t="n">
-        <v>2.257050693773941</v>
+        <v>2.242677556027823</v>
       </c>
       <c r="X7" t="n">
-        <v>2.28745367134716</v>
+        <v>2.282179849455905</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.227194872633376</v>
+        <v>2.216709109216503</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.217142444091578</v>
+        <v>2.211688039697091</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.395738849968813</v>
+        <v>2.382307210666688</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.199282561070825</v>
+        <v>2.200992758345094</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.201351692158541</v>
+        <v>2.204133878360786</v>
       </c>
       <c r="C8" t="n">
-        <v>2.755421613224013</v>
+        <v>2.740902741711363</v>
       </c>
       <c r="D8" t="n">
-        <v>2.767231144348144</v>
+        <v>2.756092839105368</v>
       </c>
       <c r="E8" t="n">
-        <v>2.687921267796962</v>
+        <v>2.676219875642809</v>
       </c>
       <c r="F8" t="n">
-        <v>2.677775698468857</v>
+        <v>2.665101494703953</v>
       </c>
       <c r="G8" t="n">
-        <v>2.314106244843261</v>
+        <v>2.29882915858975</v>
       </c>
       <c r="H8" t="n">
-        <v>2.302800874089821</v>
+        <v>2.289289205594355</v>
       </c>
       <c r="I8" t="n">
-        <v>2.478364007206473</v>
+        <v>2.464564866631304</v>
       </c>
       <c r="J8" t="n">
-        <v>2.342899004169226</v>
+        <v>2.332405641430511</v>
       </c>
       <c r="K8" t="n">
-        <v>2.357960821705881</v>
+        <v>2.343816271192363</v>
       </c>
       <c r="L8" t="n">
-        <v>2.334073698977333</v>
+        <v>2.344047955199152</v>
       </c>
       <c r="M8" t="n">
-        <v>2.338023438229501</v>
+        <v>2.337596300087633</v>
       </c>
       <c r="N8" t="n">
-        <v>2.223259146930715</v>
+        <v>2.651628247835907</v>
       </c>
       <c r="O8" t="n">
-        <v>2.251052358903072</v>
+        <v>2.243650935049182</v>
       </c>
       <c r="P8" t="n">
-        <v>2.287909437650616</v>
+        <v>2.279669807913124</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.19378111970267</v>
+        <v>2.182218494283375</v>
       </c>
       <c r="R8" t="n">
-        <v>2.452185681342842</v>
+        <v>2.438166254427457</v>
       </c>
       <c r="S8" t="n">
-        <v>2.371368789622523</v>
+        <v>2.364941351539402</v>
       </c>
       <c r="T8" t="n">
-        <v>2.276573657427839</v>
+        <v>2.263855653291412</v>
       </c>
       <c r="U8" t="n">
-        <v>2.348073091828905</v>
+        <v>2.338200679596126</v>
       </c>
       <c r="V8" t="n">
-        <v>2.331098901647664</v>
+        <v>2.32035404105176</v>
       </c>
       <c r="W8" t="n">
-        <v>2.326662874449335</v>
+        <v>2.311150941741784</v>
       </c>
       <c r="X8" t="n">
-        <v>2.292241189497214</v>
+        <v>2.287071455519848</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.355121837491488</v>
+        <v>2.342370094015973</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.226992156093626</v>
+        <v>2.221544782200354</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.465339502028503</v>
+        <v>2.450769288803925</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.330159821841512</v>
+        <v>2.329556589132735</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.733058946855224</v>
+        <v>2.738061146542313</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4010464497313</v>
+        <v>3.389996726403786</v>
       </c>
       <c r="D9" t="n">
-        <v>3.412855980855432</v>
+        <v>3.40518682379779</v>
       </c>
       <c r="E9" t="n">
-        <v>3.324951015951839</v>
+        <v>3.316091178579199</v>
       </c>
       <c r="F9" t="n">
-        <v>2.975081685268604</v>
+        <v>2.964640308707352</v>
       </c>
       <c r="G9" t="n">
-        <v>2.947567294926722</v>
+        <v>2.935992571861911</v>
       </c>
       <c r="H9" t="n">
-        <v>2.948425710597105</v>
+        <v>2.938383190286774</v>
       </c>
       <c r="I9" t="n">
-        <v>3.123988843713758</v>
+        <v>3.113658851323726</v>
       </c>
       <c r="J9" t="n">
-        <v>2.988523840676506</v>
+        <v>2.981499626122934</v>
       </c>
       <c r="K9" t="n">
-        <v>3.003585658213165</v>
+        <v>2.992910255884787</v>
       </c>
       <c r="L9" t="n">
-        <v>2.97969853548462</v>
+        <v>2.993141939891574</v>
       </c>
       <c r="M9" t="n">
-        <v>2.983648274736788</v>
+        <v>2.986690284780059</v>
       </c>
       <c r="N9" t="n">
-        <v>2.914356286720204</v>
+        <v>2.651628247835907</v>
       </c>
       <c r="O9" t="n">
-        <v>2.986845737912234</v>
+        <v>2.982322442820503</v>
       </c>
       <c r="P9" t="n">
-        <v>3.03920430150439</v>
+        <v>3.033793038870421</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.909595524137124</v>
+        <v>2.900156301525828</v>
       </c>
       <c r="R9" t="n">
-        <v>3.097810517850125</v>
+        <v>3.087260239119877</v>
       </c>
       <c r="S9" t="n">
-        <v>3.016993626129806</v>
+        <v>3.014035336231823</v>
       </c>
       <c r="T9" t="n">
-        <v>2.922198493935122</v>
+        <v>2.912949637983838</v>
       </c>
       <c r="U9" t="n">
-        <v>3.022329281665281</v>
+        <v>3.015382397681323</v>
       </c>
       <c r="V9" t="n">
-        <v>3.191908501350334</v>
+        <v>3.18447485001274</v>
       </c>
       <c r="W9" t="n">
-        <v>2.972276182340917</v>
+        <v>2.960233618857482</v>
       </c>
       <c r="X9" t="n">
-        <v>3.002679159914133</v>
+        <v>2.999735912285565</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.942420361200353</v>
+        <v>2.93426517204616</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.82831823181738</v>
+        <v>2.82511938548668</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.110964338535785</v>
+        <v>3.099863273496345</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.914508049637803</v>
+        <v>2.918548821174752</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.391280928544738</v>
+        <v>2.391629213700597</v>
       </c>
       <c r="C2" t="n">
-        <v>2.433071272595621</v>
+        <v>2.433474677306433</v>
       </c>
       <c r="D2" t="n">
-        <v>2.399182350803846</v>
+        <v>2.399530484516952</v>
       </c>
       <c r="E2" t="n">
-        <v>2.417759209882345</v>
+        <v>2.418106724953188</v>
       </c>
       <c r="F2" t="n">
-        <v>2.436171733987306</v>
+        <v>2.436523124788455</v>
       </c>
       <c r="G2" t="n">
-        <v>2.393525434624902</v>
+        <v>2.393861434136306</v>
       </c>
       <c r="H2" t="n">
-        <v>2.397229327828334</v>
+        <v>2.397579734498809</v>
       </c>
       <c r="I2" t="n">
-        <v>2.398452535241633</v>
+        <v>2.398825376240441</v>
       </c>
       <c r="J2" t="n">
-        <v>2.398611500928109</v>
+        <v>2.39896389632799</v>
       </c>
       <c r="K2" t="n">
-        <v>2.400460609202907</v>
+        <v>2.400841895758792</v>
       </c>
       <c r="L2" t="n">
-        <v>2.404428344551239</v>
+        <v>2.404802203758543</v>
       </c>
       <c r="M2" t="n">
-        <v>2.402450456201667</v>
+        <v>2.402820921261532</v>
       </c>
       <c r="N2" t="n">
-        <v>2.392530005152984</v>
+        <v>2.392889415868782</v>
       </c>
       <c r="O2" t="n">
-        <v>2.428379752258873</v>
+        <v>2.4289698906931</v>
       </c>
       <c r="P2" t="n">
-        <v>2.399131274794038</v>
+        <v>2.39947900153186</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.391685848318817</v>
+        <v>2.392033897098119</v>
       </c>
       <c r="R2" t="n">
-        <v>2.399522495210288</v>
+        <v>2.399884612228977</v>
       </c>
       <c r="S2" t="n">
-        <v>2.403540885314018</v>
+        <v>2.403865962289795</v>
       </c>
       <c r="T2" t="n">
-        <v>2.394711132695927</v>
+        <v>2.395090493857476</v>
       </c>
       <c r="U2" t="n">
-        <v>2.428340086474766</v>
+        <v>2.429050294255111</v>
       </c>
       <c r="V2" t="n">
-        <v>2.397528546789443</v>
+        <v>2.397879896977531</v>
       </c>
       <c r="W2" t="n">
-        <v>2.430085084197405</v>
+        <v>2.43075295327561</v>
       </c>
       <c r="X2" t="n">
-        <v>2.402856833618326</v>
+        <v>2.403204766187488</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.393064339602457</v>
+        <v>2.393415436472297</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.409597747827681</v>
+        <v>2.410015106967889</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.397125652097347</v>
+        <v>2.397482113791853</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.394942429295534</v>
+        <v>2.395310989058629</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.388599100128378</v>
+        <v>2.388950925997256</v>
       </c>
       <c r="C3" t="n">
-        <v>2.658954072250728</v>
+        <v>2.659398364476564</v>
       </c>
       <c r="D3" t="n">
-        <v>2.444984272932358</v>
+        <v>2.44533518919915</v>
       </c>
       <c r="E3" t="n">
-        <v>2.576752273022413</v>
+        <v>2.577099045984045</v>
       </c>
       <c r="F3" t="n">
-        <v>2.709344705562101</v>
+        <v>2.709718871930274</v>
       </c>
       <c r="G3" t="n">
-        <v>2.404526382693799</v>
+        <v>2.404791199167071</v>
       </c>
       <c r="H3" t="n">
-        <v>2.431257373712197</v>
+        <v>2.431624593207775</v>
       </c>
       <c r="I3" t="n">
-        <v>2.439897750266267</v>
+        <v>2.440425284622143</v>
       </c>
       <c r="J3" t="n">
-        <v>2.440826447043817</v>
+        <v>2.441207830896325</v>
       </c>
       <c r="K3" t="n">
-        <v>2.453832009426869</v>
+        <v>2.454418469370801</v>
       </c>
       <c r="L3" t="n">
-        <v>2.481962357795526</v>
+        <v>2.482495886705472</v>
       </c>
       <c r="M3" t="n">
-        <v>2.468521513475856</v>
+        <v>2.469032154709305</v>
       </c>
       <c r="N3" t="n">
-        <v>2.397536219217789</v>
+        <v>2.397967609328091</v>
       </c>
       <c r="O3" t="n">
-        <v>2.476504623169029</v>
+        <v>2.477255130174679</v>
       </c>
       <c r="P3" t="n">
-        <v>2.444295794473843</v>
+        <v>2.444643663269848</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.391496855255022</v>
+        <v>2.391847088864577</v>
       </c>
       <c r="R3" t="n">
-        <v>2.447654368541342</v>
+        <v>2.448105402756303</v>
       </c>
       <c r="S3" t="n">
-        <v>2.475602781490173</v>
+        <v>2.475789956061033</v>
       </c>
       <c r="T3" t="n">
-        <v>2.413158442801489</v>
+        <v>2.413732699673109</v>
       </c>
       <c r="U3" t="n">
-        <v>2.485063588637577</v>
+        <v>2.486443450985509</v>
       </c>
       <c r="V3" t="n">
-        <v>2.432934349427993</v>
+        <v>2.433308003958032</v>
       </c>
       <c r="W3" t="n">
-        <v>2.475336776976368</v>
+        <v>2.476239059826369</v>
       </c>
       <c r="X3" t="n">
-        <v>2.471120823841586</v>
+        <v>2.47147025866794</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.401345349780474</v>
+        <v>2.401717285224548</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.425337264607395</v>
+        <v>2.425829920556866</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.430345509683733</v>
+        <v>2.430755747017422</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.415462776687407</v>
+        <v>2.415959410192045</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.096835778051888</v>
+        <v>2.088196985869412</v>
       </c>
       <c r="C4" t="n">
-        <v>2.512810580044558</v>
+        <v>2.504174517775781</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186085977302334</v>
+        <v>2.177445474504301</v>
       </c>
       <c r="E4" t="n">
-        <v>2.395920146371378</v>
+        <v>2.387272655724379</v>
       </c>
       <c r="F4" t="n">
-        <v>2.603898076316468</v>
+        <v>2.595294363826207</v>
       </c>
       <c r="G4" t="n">
-        <v>2.122188506751156</v>
+        <v>2.113410942562876</v>
       </c>
       <c r="H4" t="n">
-        <v>2.164025684358977</v>
+        <v>2.155410855660022</v>
       </c>
       <c r="I4" t="n">
-        <v>2.177842374795395</v>
+        <v>2.169480952155268</v>
       </c>
       <c r="J4" t="n">
-        <v>2.179666189579389</v>
+        <v>2.171073830333565</v>
       </c>
       <c r="K4" t="n">
-        <v>2.200524493947655</v>
+        <v>2.192258467759847</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2453418899555</v>
+        <v>2.236991968448732</v>
       </c>
       <c r="M4" t="n">
-        <v>2.223278724601687</v>
+        <v>2.214890945523725</v>
       </c>
       <c r="N4" t="n">
-        <v>2.461655237951347</v>
+        <v>2.455833555757122</v>
       </c>
       <c r="O4" t="n">
-        <v>2.152195927784768</v>
+        <v>2.143555868228461</v>
       </c>
       <c r="P4" t="n">
-        <v>2.185509050275431</v>
+        <v>2.17686395050434</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.101409533172412</v>
+        <v>2.092768071007985</v>
       </c>
       <c r="R4" t="n">
-        <v>2.189928064847266</v>
+        <v>2.181445509918415</v>
       </c>
       <c r="S4" t="n">
-        <v>2.235317629619658</v>
+        <v>2.226416690366868</v>
       </c>
       <c r="T4" t="n">
-        <v>2.135581511911443</v>
+        <v>2.127293737508894</v>
       </c>
       <c r="U4" t="n">
-        <v>2.170326363347652</v>
+        <v>2.162480333263688</v>
       </c>
       <c r="V4" t="n">
-        <v>2.167512228131783</v>
+        <v>2.158908225647412</v>
       </c>
       <c r="W4" t="n">
-        <v>2.143535549266991</v>
+        <v>2.134943914199154</v>
       </c>
       <c r="X4" t="n">
-        <v>2.227590951037498</v>
+        <v>2.218948176226077</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.117259224417912</v>
+        <v>2.108551464869568</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.110349984428961</v>
+        <v>2.10176687566124</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.162854619284287</v>
+        <v>2.15430818486721</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.139282924855844</v>
+        <v>2.130871924615892</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.200509437172228</v>
+        <v>2.192381894404154</v>
       </c>
       <c r="C5" t="n">
-        <v>9.354019532855384</v>
+        <v>9.346029782875126</v>
       </c>
       <c r="D5" t="n">
-        <v>3.775070789718172</v>
+        <v>3.76700173910479</v>
       </c>
       <c r="E5" t="n">
-        <v>7.063478923807874</v>
+        <v>7.055427225982791</v>
       </c>
       <c r="F5" t="n">
-        <v>11.35410621736746</v>
+        <v>11.34668998963254</v>
       </c>
       <c r="G5" t="n">
-        <v>2.601305381689869</v>
+        <v>2.59107263858255</v>
       </c>
       <c r="H5" t="n">
-        <v>3.494721896259027</v>
+        <v>3.487148920365581</v>
       </c>
       <c r="I5" t="n">
-        <v>3.692599958653714</v>
+        <v>3.689612501209998</v>
       </c>
       <c r="J5" t="n">
-        <v>3.617710002734397</v>
+        <v>3.61051915270409</v>
       </c>
       <c r="K5" t="n">
-        <v>3.887794592508185</v>
+        <v>3.88579437441225</v>
       </c>
       <c r="L5" t="n">
-        <v>4.58325736625218</v>
+        <v>4.57981390996351</v>
       </c>
       <c r="M5" t="n">
-        <v>4.46479298982733</v>
+        <v>4.461237180095863</v>
       </c>
       <c r="N5" t="n">
-        <v>2.461655237951347</v>
+        <v>2.455833555757122</v>
       </c>
       <c r="O5" t="n">
-        <v>3.064549852192891</v>
+        <v>3.056438038466271</v>
       </c>
       <c r="P5" t="n">
-        <v>3.596989848751395</v>
+        <v>3.588765455416251</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.285457663050181</v>
+        <v>2.277332010408535</v>
       </c>
       <c r="R5" t="n">
-        <v>3.968677361192239</v>
+        <v>3.963566881571212</v>
       </c>
       <c r="S5" t="n">
-        <v>4.392625016039456</v>
+        <v>4.380372271055424</v>
       </c>
       <c r="T5" t="n">
-        <v>2.926111962411771</v>
+        <v>2.924524412588211</v>
       </c>
       <c r="U5" t="n">
-        <v>3.357134736777416</v>
+        <v>3.363068264434046</v>
       </c>
       <c r="V5" t="n">
-        <v>3.316966582800007</v>
+        <v>3.309427374317957</v>
       </c>
       <c r="W5" t="n">
-        <v>3.027283513137324</v>
+        <v>3.020000554559964</v>
       </c>
       <c r="X5" t="n">
-        <v>4.463335324642946</v>
+        <v>4.455202320790822</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.566102502558523</v>
+        <v>2.558558566615912</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.407844828562325</v>
+        <v>2.400580144445538</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.384913813205773</v>
+        <v>3.378448324556244</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.023699941506062</v>
+        <v>3.019999841715599</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.189399630609591</v>
+        <v>3.180835854165581</v>
       </c>
       <c r="C6" t="n">
-        <v>3.605374432602262</v>
+        <v>15.98485009206703</v>
       </c>
       <c r="D6" t="n">
-        <v>15.66651279894139</v>
+        <v>3.270084342800468</v>
       </c>
       <c r="E6" t="n">
-        <v>3.488483998929081</v>
+        <v>15.86794823001562</v>
       </c>
       <c r="F6" t="n">
-        <v>3.696461928874174</v>
+        <v>16.07596993811747</v>
       </c>
       <c r="G6" t="n">
-        <v>15.6026153283902</v>
+        <v>3.206049810859039</v>
       </c>
       <c r="H6" t="n">
-        <v>15.64445250599805</v>
+        <v>3.248049723956188</v>
       </c>
       <c r="I6" t="n">
-        <v>15.65826919643444</v>
+        <v>3.262119820451435</v>
       </c>
       <c r="J6" t="n">
-        <v>15.66009301121846</v>
+        <v>15.6517494046248</v>
       </c>
       <c r="K6" t="n">
-        <v>3.293088346505364</v>
+        <v>3.284897336056012</v>
       </c>
       <c r="L6" t="n">
-        <v>15.72576871159455</v>
+        <v>15.71766754273997</v>
       </c>
       <c r="M6" t="n">
-        <v>15.70370554624076</v>
+        <v>3.307529813819885</v>
       </c>
       <c r="N6" t="n">
-        <v>2.461655237951347</v>
+        <v>2.455833555757122</v>
       </c>
       <c r="O6" t="n">
-        <v>15.63150574089236</v>
+        <v>15.62320126248977</v>
       </c>
       <c r="P6" t="n">
-        <v>15.66482164193153</v>
+        <v>3.265369354717851</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.58183635481148</v>
+        <v>3.18540693930415</v>
       </c>
       <c r="R6" t="n">
-        <v>15.67035488648634</v>
+        <v>3.274084378214579</v>
       </c>
       <c r="S6" t="n">
-        <v>15.71574445125873</v>
+        <v>15.70709226465812</v>
       </c>
       <c r="T6" t="n">
-        <v>3.22814536446915</v>
+        <v>3.21993260580506</v>
       </c>
       <c r="U6" t="n">
-        <v>15.65047418692726</v>
+        <v>15.64297763646422</v>
       </c>
       <c r="V6" t="n">
-        <v>15.64793904977086</v>
+        <v>3.251547093943577</v>
       </c>
       <c r="W6" t="n">
-        <v>3.237200971185964</v>
+        <v>3.228690503160967</v>
       </c>
       <c r="X6" t="n">
-        <v>3.320154803595199</v>
+        <v>15.69962375051731</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.226494648132481</v>
+        <v>3.217967269007588</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.202913836986667</v>
+        <v>3.194405743957403</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.255418471841994</v>
+        <v>15.63498375915847</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.230444668954727</v>
+        <v>3.222104083607249</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.156952283562072</v>
+        <v>2.14839575009032</v>
       </c>
       <c r="C7" t="n">
-        <v>2.572927085554741</v>
+        <v>2.564373281996692</v>
       </c>
       <c r="D7" t="n">
-        <v>2.246202482812519</v>
+        <v>2.237644238725209</v>
       </c>
       <c r="E7" t="n">
-        <v>2.456036651881561</v>
+        <v>2.447471419945285</v>
       </c>
       <c r="F7" t="n">
-        <v>2.664014581826652</v>
+        <v>2.655493128047115</v>
       </c>
       <c r="G7" t="n">
-        <v>2.18230501226134</v>
+        <v>2.173609706783784</v>
       </c>
       <c r="H7" t="n">
-        <v>2.224142189869161</v>
+        <v>2.21560961988093</v>
       </c>
       <c r="I7" t="n">
-        <v>2.237958880305579</v>
+        <v>2.229679716376177</v>
       </c>
       <c r="J7" t="n">
-        <v>2.239782695089573</v>
+        <v>2.231272594554474</v>
       </c>
       <c r="K7" t="n">
-        <v>2.26064099945784</v>
+        <v>2.252457231980755</v>
       </c>
       <c r="L7" t="n">
-        <v>2.305458395465683</v>
+        <v>2.297190732669641</v>
       </c>
       <c r="M7" t="n">
-        <v>2.283395230111871</v>
+        <v>2.275089709744634</v>
       </c>
       <c r="N7" t="n">
-        <v>2.461655237951347</v>
+        <v>2.455833555757122</v>
       </c>
       <c r="O7" t="n">
-        <v>2.212308020281305</v>
+        <v>2.203750234190684</v>
       </c>
       <c r="P7" t="n">
-        <v>2.245621142771967</v>
+        <v>2.237058316466563</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.161526038682597</v>
+        <v>2.152966835228894</v>
       </c>
       <c r="R7" t="n">
-        <v>2.250044570357451</v>
+        <v>2.241644274139323</v>
       </c>
       <c r="S7" t="n">
-        <v>2.295434135129843</v>
+        <v>2.286615454587776</v>
       </c>
       <c r="T7" t="n">
-        <v>2.195698017421627</v>
+        <v>2.187492501729802</v>
       </c>
       <c r="U7" t="n">
-        <v>2.230197202150519</v>
+        <v>2.222505454375558</v>
       </c>
       <c r="V7" t="n">
-        <v>2.227628733641967</v>
+        <v>2.21910698986832</v>
       </c>
       <c r="W7" t="n">
-        <v>2.203652054777176</v>
+        <v>2.195142678420063</v>
       </c>
       <c r="X7" t="n">
-        <v>2.287707456547682</v>
+        <v>2.279146940446986</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.177096731868629</v>
+        <v>2.168571957999749</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.170466489939145</v>
+        <v>2.161965639882149</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.222971124794471</v>
+        <v>2.214506949088119</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.199399430366028</v>
+        <v>2.191070688836801</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.165664103836845</v>
+        <v>2.157252678571397</v>
       </c>
       <c r="C8" t="n">
-        <v>2.630100112176044</v>
+        <v>2.621939122877326</v>
       </c>
       <c r="D8" t="n">
-        <v>2.30337550943382</v>
+        <v>2.295210079605843</v>
       </c>
       <c r="E8" t="n">
-        <v>2.487405515640562</v>
+        <v>2.479101201797747</v>
       </c>
       <c r="F8" t="n">
-        <v>2.680276091671722</v>
+        <v>2.671938335806309</v>
       </c>
       <c r="G8" t="n">
-        <v>2.249526785713652</v>
+        <v>2.241275657958985</v>
       </c>
       <c r="H8" t="n">
-        <v>2.281315216490463</v>
+        <v>2.273175460761565</v>
       </c>
       <c r="I8" t="n">
-        <v>2.295131906926881</v>
+        <v>2.287245557256811</v>
       </c>
       <c r="J8" t="n">
-        <v>2.296955721710875</v>
+        <v>2.288838435435109</v>
       </c>
       <c r="K8" t="n">
-        <v>2.317814026079141</v>
+        <v>2.310023072861389</v>
       </c>
       <c r="L8" t="n">
-        <v>2.362631422086986</v>
+        <v>2.354756573550275</v>
       </c>
       <c r="M8" t="n">
-        <v>2.340568256733186</v>
+        <v>2.33265555062527</v>
       </c>
       <c r="N8" t="n">
-        <v>2.461655237951347</v>
+        <v>2.455833555757122</v>
       </c>
       <c r="O8" t="n">
-        <v>2.242243254812063</v>
+        <v>2.233939021605889</v>
       </c>
       <c r="P8" t="n">
-        <v>2.273025877908792</v>
+        <v>2.264703670018275</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.160714125838591</v>
+        <v>2.152251350698836</v>
       </c>
       <c r="R8" t="n">
-        <v>2.307217596978752</v>
+        <v>2.299210115019957</v>
       </c>
       <c r="S8" t="n">
-        <v>2.352607161751144</v>
+        <v>2.34418129546841</v>
       </c>
       <c r="T8" t="n">
-        <v>2.252871044042929</v>
+        <v>2.245058342610437</v>
       </c>
       <c r="U8" t="n">
-        <v>2.263712880360678</v>
+        <v>2.256299492353508</v>
       </c>
       <c r="V8" t="n">
-        <v>2.271588844809025</v>
+        <v>2.26336766595145</v>
       </c>
       <c r="W8" t="n">
-        <v>2.260834605409608</v>
+        <v>2.252718091990812</v>
       </c>
       <c r="X8" t="n">
-        <v>2.291337109556429</v>
+        <v>2.28289572452019</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.282503672787383</v>
+        <v>2.274579928396684</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.178278118426508</v>
+        <v>2.169917775308946</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.280144151415772</v>
+        <v>2.272072789968752</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.30719423927207</v>
+        <v>2.299517061685131</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.465624935206608</v>
+        <v>2.458697854599865</v>
       </c>
       <c r="C9" t="n">
-        <v>2.985648360335675</v>
+        <v>2.979242327496936</v>
       </c>
       <c r="D9" t="n">
-        <v>2.658923757593452</v>
+        <v>2.652513284225456</v>
       </c>
       <c r="E9" t="n">
-        <v>2.844743913502074</v>
+        <v>2.838206826744014</v>
       </c>
       <c r="F9" t="n">
-        <v>2.836875408757331</v>
+        <v>2.829306861401563</v>
       </c>
       <c r="G9" t="n">
-        <v>2.595026267090311</v>
+        <v>2.588478732469218</v>
       </c>
       <c r="H9" t="n">
-        <v>2.636863464650095</v>
+        <v>2.630478665381178</v>
       </c>
       <c r="I9" t="n">
-        <v>2.650680155086513</v>
+        <v>2.644548761876422</v>
       </c>
       <c r="J9" t="n">
-        <v>2.652503969870509</v>
+        <v>2.646141640054721</v>
       </c>
       <c r="K9" t="n">
-        <v>2.673362274238773</v>
+        <v>2.667326277481001</v>
       </c>
       <c r="L9" t="n">
-        <v>2.718179670246614</v>
+        <v>2.712059778169885</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6961165048928</v>
+        <v>2.689958755244879</v>
       </c>
       <c r="N9" t="n">
-        <v>2.461655237951347</v>
+        <v>2.455833555757122</v>
       </c>
       <c r="O9" t="n">
-        <v>2.659515258979388</v>
+        <v>2.653276998893955</v>
       </c>
       <c r="P9" t="n">
-        <v>2.700327531526735</v>
+        <v>2.694121588233498</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.574247293511568</v>
+        <v>2.567835860914327</v>
       </c>
       <c r="R9" t="n">
-        <v>2.662765845138383</v>
+        <v>2.656513319639568</v>
       </c>
       <c r="S9" t="n">
-        <v>2.708155409910776</v>
+        <v>2.701484500088023</v>
       </c>
       <c r="T9" t="n">
-        <v>2.608419292202561</v>
+        <v>2.602361547230049</v>
       </c>
       <c r="U9" t="n">
-        <v>2.642885145579302</v>
+        <v>2.637369871894116</v>
       </c>
       <c r="V9" t="n">
-        <v>2.76041977407089</v>
+        <v>2.754643928962847</v>
       </c>
       <c r="W9" t="n">
-        <v>2.616373329558109</v>
+        <v>2.610011723920309</v>
       </c>
       <c r="X9" t="n">
-        <v>2.700428731328612</v>
+        <v>2.694015985947233</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.589818006649561</v>
+        <v>2.583441003499993</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.520455689410739</v>
+        <v>2.513790110551994</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.635692399575404</v>
+        <v>2.629375994588364</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.61212070514696</v>
+        <v>2.605939734337047</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.398869363292547</v>
+        <v>2.399905025709628</v>
       </c>
       <c r="C2" t="n">
-        <v>2.44713505950887</v>
+        <v>2.446788843352677</v>
       </c>
       <c r="D2" t="n">
-        <v>2.426132106396519</v>
+        <v>2.42665344934745</v>
       </c>
       <c r="E2" t="n">
-        <v>2.43818358583104</v>
+        <v>2.438216108530169</v>
       </c>
       <c r="F2" t="n">
-        <v>2.443984785554628</v>
+        <v>2.443825650983193</v>
       </c>
       <c r="G2" t="n">
-        <v>2.402608696465063</v>
+        <v>2.402400769988617</v>
       </c>
       <c r="H2" t="n">
-        <v>2.404839269708559</v>
+        <v>2.404663374949535</v>
       </c>
       <c r="I2" t="n">
-        <v>2.422065674666782</v>
+        <v>2.42198434104182</v>
       </c>
       <c r="J2" t="n">
-        <v>2.406633707000734</v>
+        <v>2.406821317345762</v>
       </c>
       <c r="K2" t="n">
-        <v>2.409509340811067</v>
+        <v>2.409461462067402</v>
       </c>
       <c r="L2" t="n">
-        <v>2.408164956656206</v>
+        <v>2.410181645404037</v>
       </c>
       <c r="M2" t="n">
-        <v>2.406017832708321</v>
+        <v>2.407057931686444</v>
       </c>
       <c r="N2" t="n">
-        <v>2.399709891560647</v>
+        <v>2.399691757147235</v>
       </c>
       <c r="O2" t="n">
-        <v>2.435530017344637</v>
+        <v>2.435373547595248</v>
       </c>
       <c r="P2" t="n">
-        <v>2.404556244199608</v>
+        <v>2.405117262765832</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.39950459852266</v>
+        <v>2.399504613913992</v>
       </c>
       <c r="R2" t="n">
-        <v>2.415380073938699</v>
+        <v>2.415299231874284</v>
       </c>
       <c r="S2" t="n">
-        <v>2.411833435561666</v>
+        <v>2.412439754889515</v>
       </c>
       <c r="T2" t="n">
-        <v>2.400372807290191</v>
+        <v>2.400510686421863</v>
       </c>
       <c r="U2" t="n">
-        <v>2.440614239225634</v>
+        <v>2.440034161760513</v>
       </c>
       <c r="V2" t="n">
-        <v>2.407791482191274</v>
+        <v>2.407805149847365</v>
       </c>
       <c r="W2" t="n">
-        <v>2.440664116977363</v>
+        <v>2.439234158094774</v>
       </c>
       <c r="X2" t="n">
-        <v>2.408078183957235</v>
+        <v>2.408695359304019</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.402374435368779</v>
+        <v>2.402454906782245</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.42058090191912</v>
+        <v>2.420565595965297</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.413479116794893</v>
+        <v>2.413572367190197</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.399683627378591</v>
+        <v>2.400857717531876</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.399201716227401</v>
+        <v>2.407800818759129</v>
       </c>
       <c r="C3" t="n">
-        <v>2.713756067604122</v>
+        <v>2.713514051165993</v>
       </c>
       <c r="D3" t="n">
-        <v>2.594419329677087</v>
+        <v>2.599401887703394</v>
       </c>
       <c r="E3" t="n">
-        <v>2.679706251627306</v>
+        <v>2.68118387175308</v>
       </c>
       <c r="F3" t="n">
-        <v>2.722243705587065</v>
+        <v>2.722354705039877</v>
       </c>
       <c r="G3" t="n">
-        <v>2.425814507068225</v>
+        <v>2.425576672456037</v>
       </c>
       <c r="H3" t="n">
-        <v>2.442110958723986</v>
+        <v>2.442102411607931</v>
       </c>
       <c r="I3" t="n">
-        <v>2.565429372011464</v>
+        <v>2.566098132309003</v>
       </c>
       <c r="J3" t="n">
-        <v>2.454614099127701</v>
+        <v>2.45719812128096</v>
       </c>
       <c r="K3" t="n">
-        <v>2.475083757987526</v>
+        <v>2.475985843356527</v>
       </c>
       <c r="L3" t="n">
-        <v>2.46555399613972</v>
+        <v>2.481190321801019</v>
       </c>
       <c r="M3" t="n">
-        <v>2.451210826923119</v>
+        <v>2.459865369182648</v>
       </c>
       <c r="N3" t="n">
-        <v>2.405245969296818</v>
+        <v>2.406364316538772</v>
       </c>
       <c r="O3" t="n">
-        <v>2.478241928980586</v>
+        <v>2.481606274206298</v>
       </c>
       <c r="P3" t="n">
-        <v>2.439655164017573</v>
+        <v>2.444887805314341</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.403783696990968</v>
+        <v>2.4050319105061</v>
       </c>
       <c r="R3" t="n">
-        <v>2.517636208413662</v>
+        <v>2.518309140404439</v>
       </c>
       <c r="S3" t="n">
-        <v>2.491469277230065</v>
+        <v>2.49702600425951</v>
       </c>
       <c r="T3" t="n">
-        <v>2.410018062474595</v>
+        <v>2.41225521019758</v>
       </c>
       <c r="U3" t="n">
-        <v>2.519342503552898</v>
+        <v>2.521673785307906</v>
       </c>
       <c r="V3" t="n">
-        <v>2.462539128407272</v>
+        <v>2.463873376507516</v>
       </c>
       <c r="W3" t="n">
-        <v>2.496004282029384</v>
+        <v>2.493819107103987</v>
       </c>
       <c r="X3" t="n">
-        <v>2.465100053346037</v>
+        <v>2.470762161302913</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.424241687983221</v>
+        <v>2.426061175615828</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.449159504094738</v>
+        <v>2.452754463808905</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.503520088234175</v>
+        <v>2.505432027698827</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.406294049503472</v>
+        <v>2.415903392066709</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.11595887212932</v>
+        <v>2.116692478437603</v>
       </c>
       <c r="C4" t="n">
-        <v>2.59964232168672</v>
+        <v>2.586780841014647</v>
       </c>
       <c r="D4" t="n">
-        <v>2.423904096970123</v>
+        <v>2.418828228309597</v>
       </c>
       <c r="E4" t="n">
-        <v>2.560031101137481</v>
+        <v>2.549433782864438</v>
       </c>
       <c r="F4" t="n">
-        <v>2.625558320699131</v>
+        <v>2.612796145388358</v>
       </c>
       <c r="G4" t="n">
-        <v>2.158196360491135</v>
+        <v>2.144883058167873</v>
       </c>
       <c r="H4" t="n">
-        <v>2.183391711390805</v>
+        <v>2.170440222051149</v>
       </c>
       <c r="I4" t="n">
-        <v>2.377971879931735</v>
+        <v>2.366088502101579</v>
       </c>
       <c r="J4" t="n">
-        <v>2.203690853853928</v>
+        <v>2.194846025144578</v>
       </c>
       <c r="K4" t="n">
-        <v>2.236142312832489</v>
+        <v>2.224636823276584</v>
       </c>
       <c r="L4" t="n">
-        <v>2.22095687535607</v>
+        <v>2.23277162536457</v>
       </c>
       <c r="M4" t="n">
-        <v>2.198080622964368</v>
+        <v>2.198782508957231</v>
       </c>
       <c r="N4" t="n">
-        <v>2.12545302557962</v>
+        <v>2.600155173142274</v>
       </c>
       <c r="O4" t="n">
-        <v>2.154387570488869</v>
+        <v>2.14837048759219</v>
       </c>
       <c r="P4" t="n">
-        <v>2.180194808069037</v>
+        <v>2.175567093734932</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.123134146276091</v>
+        <v>2.112169643007368</v>
       </c>
       <c r="R4" t="n">
-        <v>2.302454944179753</v>
+        <v>2.290577118752108</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2623940321769</v>
+        <v>2.258278010784729</v>
       </c>
       <c r="T4" t="n">
-        <v>2.132940963701119</v>
+        <v>2.123533694799985</v>
       </c>
       <c r="U4" t="n">
-        <v>2.221922781395227</v>
+        <v>2.215108698421299</v>
       </c>
       <c r="V4" t="n">
-        <v>2.216859103072633</v>
+        <v>2.206053650382273</v>
       </c>
       <c r="W4" t="n">
-        <v>2.173144160560683</v>
+        <v>2.159974668098564</v>
       </c>
       <c r="X4" t="n">
-        <v>2.219976737803774</v>
+        <v>2.215983340139485</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.155876362679044</v>
+        <v>2.14575357791525</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.145129543933184</v>
+        <v>2.139080129241677</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.280982758756982</v>
+        <v>2.271071387748338</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.127286393081889</v>
+        <v>2.129453326895117</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.368959748903621</v>
+        <v>2.598093633823609</v>
       </c>
       <c r="C5" t="n">
-        <v>11.64691047607934</v>
+        <v>11.6403000722266</v>
       </c>
       <c r="D5" t="n">
-        <v>8.548639997264093</v>
+        <v>8.698060748477648</v>
       </c>
       <c r="E5" t="n">
-        <v>10.71925731150388</v>
+        <v>10.75526746620946</v>
       </c>
       <c r="F5" t="n">
-        <v>12.58891767169357</v>
+        <v>12.58468833887212</v>
       </c>
       <c r="G5" t="n">
-        <v>3.125861592047955</v>
+        <v>3.110875793924029</v>
       </c>
       <c r="H5" t="n">
-        <v>3.811777245578803</v>
+        <v>3.804008271465176</v>
       </c>
       <c r="I5" t="n">
-        <v>7.698159731700859</v>
+        <v>7.711932332913304</v>
       </c>
       <c r="J5" t="n">
-        <v>4.026065856365781</v>
+        <v>4.094940026115967</v>
       </c>
       <c r="K5" t="n">
-        <v>4.610227675095381</v>
+        <v>4.628117612056675</v>
       </c>
       <c r="L5" t="n">
-        <v>4.359350032793905</v>
+        <v>4.817798194477158</v>
       </c>
       <c r="M5" t="n">
-        <v>4.056436681620546</v>
+        <v>4.322921213304491</v>
       </c>
       <c r="N5" t="n">
-        <v>4.228537814053319</v>
+        <v>2.600155173142274</v>
       </c>
       <c r="O5" t="n">
-        <v>3.017550176114054</v>
+        <v>3.125706242224059</v>
       </c>
       <c r="P5" t="n">
-        <v>3.508944035279381</v>
+        <v>3.648438941639363</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.531477541018647</v>
+        <v>2.561990806803994</v>
       </c>
       <c r="R5" t="n">
-        <v>6.227080853587307</v>
+        <v>6.241327391114021</v>
       </c>
       <c r="S5" t="n">
-        <v>4.994438540020091</v>
+        <v>5.144037803068742</v>
       </c>
       <c r="T5" t="n">
-        <v>2.737991103906233</v>
+        <v>2.800725732797912</v>
       </c>
       <c r="U5" t="n">
-        <v>4.324681480833065</v>
+        <v>4.430557665077101</v>
       </c>
       <c r="V5" t="n">
-        <v>4.085408201531059</v>
+        <v>4.112500651115875</v>
       </c>
       <c r="W5" t="n">
-        <v>3.47076883039917</v>
+        <v>3.458500718529085</v>
       </c>
       <c r="X5" t="n">
-        <v>4.432782067920497</v>
+        <v>4.600217081060605</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.130952129778045</v>
+        <v>3.177011064843009</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.892878240150349</v>
+        <v>3.007820815267599</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.51581803351219</v>
+        <v>5.565300076638735</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.651879847365034</v>
+        <v>2.959868661974347</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.292054924412529</v>
+        <v>3.293462403457499</v>
       </c>
       <c r="C6" t="n">
-        <v>17.07260792703803</v>
+        <v>17.0605111204118</v>
       </c>
       <c r="D6" t="n">
-        <v>16.89686970232144</v>
+        <v>3.595598153329492</v>
       </c>
       <c r="E6" t="n">
-        <v>3.736127153420687</v>
+        <v>17.02316406226158</v>
       </c>
       <c r="F6" t="n">
-        <v>3.801654372982334</v>
+        <v>3.789566070408247</v>
       </c>
       <c r="G6" t="n">
-        <v>3.334292412774348</v>
+        <v>16.61861333756503</v>
       </c>
       <c r="H6" t="n">
-        <v>16.65635731674212</v>
+        <v>16.64417050144831</v>
       </c>
       <c r="I6" t="n">
-        <v>3.554067932214943</v>
+        <v>16.83981878149874</v>
       </c>
       <c r="J6" t="n">
-        <v>16.67665645920524</v>
+        <v>16.66857630454174</v>
       </c>
       <c r="K6" t="n">
-        <v>16.70910791818381</v>
+        <v>3.401406748296481</v>
       </c>
       <c r="L6" t="n">
-        <v>3.397052927639286</v>
+        <v>16.70650190476173</v>
       </c>
       <c r="M6" t="n">
-        <v>3.37417667524758</v>
+        <v>16.67251278835439</v>
       </c>
       <c r="N6" t="n">
-        <v>3.299487353152404</v>
+        <v>2.600155173142274</v>
       </c>
       <c r="O6" t="n">
-        <v>16.62647643186902</v>
+        <v>3.32308656800073</v>
       </c>
       <c r="P6" t="n">
-        <v>16.65228493839375</v>
+        <v>16.64838105282156</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.59609975162741</v>
+        <v>3.288939568027263</v>
       </c>
       <c r="R6" t="n">
-        <v>16.77542054953106</v>
+        <v>16.76430739814927</v>
       </c>
       <c r="S6" t="n">
-        <v>16.73535963752823</v>
+        <v>3.435047935804626</v>
       </c>
       <c r="T6" t="n">
-        <v>3.309037015984329</v>
+        <v>3.300303619819877</v>
       </c>
       <c r="U6" t="n">
-        <v>3.39769274464257</v>
+        <v>3.391619603682002</v>
       </c>
       <c r="V6" t="n">
-        <v>16.68982470842395</v>
+        <v>3.382823575402163</v>
       </c>
       <c r="W6" t="n">
-        <v>16.64523120920316</v>
+        <v>3.337316728437194</v>
       </c>
       <c r="X6" t="n">
-        <v>16.69294234315509</v>
+        <v>16.68971361953664</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.349346321250126</v>
+        <v>3.339977657065713</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.61809514928452</v>
+        <v>3.315850054261567</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.45707881104019</v>
+        <v>16.7448016671455</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.300844094155423</v>
+        <v>3.303757902212259</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.183938182506699</v>
+        <v>2.183055617283713</v>
       </c>
       <c r="C7" t="n">
-        <v>2.667621632064097</v>
+        <v>2.653143979860755</v>
       </c>
       <c r="D7" t="n">
-        <v>2.491883407347502</v>
+        <v>2.485191367155708</v>
       </c>
       <c r="E7" t="n">
-        <v>2.628010411514861</v>
+        <v>2.615796921710547</v>
       </c>
       <c r="F7" t="n">
-        <v>2.693537631076512</v>
+        <v>2.679159284234466</v>
       </c>
       <c r="G7" t="n">
-        <v>2.226175670868514</v>
+        <v>2.211246197013983</v>
       </c>
       <c r="H7" t="n">
-        <v>2.251371021768185</v>
+        <v>2.236803360897259</v>
       </c>
       <c r="I7" t="n">
-        <v>2.445951190309115</v>
+        <v>2.432451640947687</v>
       </c>
       <c r="J7" t="n">
-        <v>2.271670164231307</v>
+        <v>2.261209163990688</v>
       </c>
       <c r="K7" t="n">
-        <v>2.304121623209868</v>
+        <v>2.290999962122693</v>
       </c>
       <c r="L7" t="n">
-        <v>2.28893618573345</v>
+        <v>2.299134764210681</v>
       </c>
       <c r="M7" t="n">
-        <v>2.266059933341747</v>
+        <v>2.265145647803342</v>
       </c>
       <c r="N7" t="n">
-        <v>2.193432335956999</v>
+        <v>2.600155173142274</v>
       </c>
       <c r="O7" t="n">
-        <v>2.222362085113682</v>
+        <v>2.214728860409421</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24816932269385</v>
+        <v>2.241925466552163</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.19111345665347</v>
+        <v>2.178532781853478</v>
       </c>
       <c r="R7" t="n">
-        <v>2.370434254557131</v>
+        <v>2.356940257598218</v>
       </c>
       <c r="S7" t="n">
-        <v>2.330373342554279</v>
+        <v>2.324641149630839</v>
       </c>
       <c r="T7" t="n">
-        <v>2.200920274078498</v>
+        <v>2.189896833646095</v>
       </c>
       <c r="U7" t="n">
-        <v>2.289582007513801</v>
+        <v>2.281201687012492</v>
       </c>
       <c r="V7" t="n">
-        <v>2.284838413450012</v>
+        <v>2.272416789228382</v>
       </c>
       <c r="W7" t="n">
-        <v>2.241123470938062</v>
+        <v>2.226337806944673</v>
       </c>
       <c r="X7" t="n">
-        <v>2.287956048181153</v>
+        <v>2.282346478985595</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.223529584020558</v>
+        <v>2.211857697002169</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.213108854310563</v>
+        <v>2.205443268087787</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.348962069134361</v>
+        <v>2.337434526594449</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.195265703459268</v>
+        <v>2.195816465741227</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.194733422239518</v>
+        <v>2.193648084736354</v>
       </c>
       <c r="C8" t="n">
-        <v>2.734198479749906</v>
+        <v>2.718043119677115</v>
       </c>
       <c r="D8" t="n">
-        <v>2.558460255033309</v>
+        <v>2.550090506972067</v>
       </c>
       <c r="E8" t="n">
-        <v>2.664885198421373</v>
+        <v>2.651779360441461</v>
       </c>
       <c r="F8" t="n">
-        <v>2.713022993394445</v>
+        <v>2.698212096545177</v>
       </c>
       <c r="G8" t="n">
-        <v>2.304319198346396</v>
+        <v>2.287406179119505</v>
       </c>
       <c r="H8" t="n">
-        <v>2.317947869453991</v>
+        <v>2.301702500713619</v>
       </c>
       <c r="I8" t="n">
-        <v>2.512528037994922</v>
+        <v>2.49735078076405</v>
       </c>
       <c r="J8" t="n">
-        <v>2.338247011917114</v>
+        <v>2.326108303807047</v>
       </c>
       <c r="K8" t="n">
-        <v>2.370698470895675</v>
+        <v>2.355899101939054</v>
       </c>
       <c r="L8" t="n">
-        <v>2.355513033419257</v>
+        <v>2.364033904027041</v>
       </c>
       <c r="M8" t="n">
-        <v>2.332636781027547</v>
+        <v>2.330044787619685</v>
       </c>
       <c r="N8" t="n">
-        <v>2.216769105418243</v>
+        <v>2.600155173142274</v>
       </c>
       <c r="O8" t="n">
-        <v>2.257586399268194</v>
+        <v>2.24910456403562</v>
       </c>
       <c r="P8" t="n">
-        <v>2.280480887955826</v>
+        <v>2.27346543801552</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.190946337272063</v>
+        <v>2.178452748699443</v>
       </c>
       <c r="R8" t="n">
-        <v>2.437011102242938</v>
+        <v>2.421839397414579</v>
       </c>
       <c r="S8" t="n">
-        <v>2.396950190240088</v>
+        <v>2.389540289447199</v>
       </c>
       <c r="T8" t="n">
-        <v>2.267497121764305</v>
+        <v>2.254795973462456</v>
       </c>
       <c r="U8" t="n">
-        <v>2.328934962231667</v>
+        <v>2.319600663057176</v>
       </c>
       <c r="V8" t="n">
-        <v>2.336178538619646</v>
+        <v>2.32246765644943</v>
       </c>
       <c r="W8" t="n">
-        <v>2.30771128130286</v>
+        <v>2.291247619571216</v>
       </c>
       <c r="X8" t="n">
-        <v>2.292901424005083</v>
+        <v>2.287243760258353</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.345583133704299</v>
+        <v>2.330744287308033</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.222867922037912</v>
+        <v>2.215026961220941</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.415538916820168</v>
+        <v>2.402333666410808</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.320111105029011</v>
+        <v>2.317443465884763</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.622304608230426</v>
+        <v>2.622795268792752</v>
       </c>
       <c r="C9" t="n">
-        <v>3.248514178566553</v>
+        <v>3.235203632827641</v>
       </c>
       <c r="D9" t="n">
-        <v>3.072775953849955</v>
+        <v>3.067251020122597</v>
       </c>
       <c r="E9" t="n">
-        <v>3.176008514278129</v>
+        <v>3.16500970137881</v>
       </c>
       <c r="F9" t="n">
-        <v>2.945868564034739</v>
+        <v>2.933132486742303</v>
       </c>
       <c r="G9" t="n">
-        <v>2.807068222029157</v>
+        <v>2.793305853263675</v>
       </c>
       <c r="H9" t="n">
-        <v>2.832263568270639</v>
+        <v>2.818863013864143</v>
       </c>
       <c r="I9" t="n">
-        <v>3.026843736811565</v>
+        <v>3.014511293914574</v>
       </c>
       <c r="J9" t="n">
-        <v>2.852562710733758</v>
+        <v>2.843268816957574</v>
       </c>
       <c r="K9" t="n">
-        <v>2.885014169712321</v>
+        <v>2.873059615089578</v>
       </c>
       <c r="L9" t="n">
-        <v>2.869828732235903</v>
+        <v>2.881194417177566</v>
       </c>
       <c r="M9" t="n">
-        <v>2.846952479844201</v>
+        <v>2.847205300770227</v>
       </c>
       <c r="N9" t="n">
-        <v>2.77432488245945</v>
+        <v>2.600155173142274</v>
       </c>
       <c r="O9" t="n">
-        <v>2.850492403374817</v>
+        <v>2.843957945907068</v>
       </c>
       <c r="P9" t="n">
-        <v>2.886572001841578</v>
+        <v>2.88141205709035</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.772006007814113</v>
+        <v>2.760592438103173</v>
       </c>
       <c r="R9" t="n">
-        <v>2.951326801059583</v>
+        <v>2.938999910565105</v>
       </c>
       <c r="S9" t="n">
-        <v>2.911265889056732</v>
+        <v>2.906700802597725</v>
       </c>
       <c r="T9" t="n">
-        <v>2.781812820580948</v>
+        <v>2.771956486612978</v>
       </c>
       <c r="U9" t="n">
-        <v>2.870468549239193</v>
+        <v>2.863272470475103</v>
       </c>
       <c r="V9" t="n">
-        <v>3.030202969594644</v>
+        <v>3.018710589621241</v>
       </c>
       <c r="W9" t="n">
-        <v>2.822016017440514</v>
+        <v>2.808397459911562</v>
       </c>
       <c r="X9" t="n">
-        <v>2.868848594683605</v>
+        <v>2.864406131952482</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.804422130523009</v>
+        <v>2.793917349969054</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.708070825750363</v>
+        <v>2.701696617067519</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.929854615636814</v>
+        <v>2.919494179561336</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.776158249961722</v>
+        <v>2.777876118708111</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.396372432914894</v>
+        <v>2.397247055861032</v>
       </c>
       <c r="C2" t="n">
-        <v>2.435597003197286</v>
+        <v>2.43546149459064</v>
       </c>
       <c r="D2" t="n">
-        <v>2.412842999675997</v>
+        <v>2.413534985399381</v>
       </c>
       <c r="E2" t="n">
-        <v>2.424766871225271</v>
+        <v>2.424845519604841</v>
       </c>
       <c r="F2" t="n">
-        <v>2.438363136631224</v>
+        <v>2.438554804394502</v>
       </c>
       <c r="G2" t="n">
-        <v>2.399868376831045</v>
+        <v>2.399733661320383</v>
       </c>
       <c r="H2" t="n">
-        <v>2.401763841166303</v>
+        <v>2.401671162915952</v>
       </c>
       <c r="I2" t="n">
-        <v>2.407181714659363</v>
+        <v>2.407501194832627</v>
       </c>
       <c r="J2" t="n">
-        <v>2.403007547495728</v>
+        <v>2.403310074476366</v>
       </c>
       <c r="K2" t="n">
-        <v>2.404597643892147</v>
+        <v>2.405062389380008</v>
       </c>
       <c r="L2" t="n">
-        <v>2.405370401487377</v>
+        <v>2.407157619928722</v>
       </c>
       <c r="M2" t="n">
-        <v>2.401623401824076</v>
+        <v>2.402585058641602</v>
       </c>
       <c r="N2" t="n">
-        <v>2.396992422906925</v>
+        <v>2.397064021629306</v>
       </c>
       <c r="O2" t="n">
-        <v>2.434095913918474</v>
+        <v>2.434218953226643</v>
       </c>
       <c r="P2" t="n">
-        <v>2.401686455280143</v>
+        <v>2.402369192417578</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.397217742651493</v>
+        <v>2.397313029297482</v>
       </c>
       <c r="R2" t="n">
-        <v>2.412517911314897</v>
+        <v>2.412555963486852</v>
       </c>
       <c r="S2" t="n">
-        <v>2.406084036410856</v>
+        <v>2.406729142261837</v>
       </c>
       <c r="T2" t="n">
-        <v>2.398754399662094</v>
+        <v>2.399034084364677</v>
       </c>
       <c r="U2" t="n">
-        <v>2.434085168554694</v>
+        <v>2.434138686278785</v>
       </c>
       <c r="V2" t="n">
-        <v>2.404466640662644</v>
+        <v>2.404711985485004</v>
       </c>
       <c r="W2" t="n">
-        <v>2.437948751936239</v>
+        <v>2.436934061634882</v>
       </c>
       <c r="X2" t="n">
-        <v>2.405946657808733</v>
+        <v>2.406666905606225</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.399312603977031</v>
+        <v>2.39967322311466</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.417772554614865</v>
+        <v>2.417838277235574</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.40600539012937</v>
+        <v>2.40643637669329</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.39807934524726</v>
+        <v>2.399249723716486</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.39687235811205</v>
+        <v>2.403689563504609</v>
       </c>
       <c r="C3" t="n">
-        <v>2.650168125412215</v>
+        <v>2.650092319902357</v>
       </c>
       <c r="D3" t="n">
-        <v>2.514761663255849</v>
+        <v>2.520312940472506</v>
       </c>
       <c r="E3" t="n">
-        <v>2.599505057544745</v>
+        <v>2.600664868468874</v>
       </c>
       <c r="F3" t="n">
-        <v>2.697277134854179</v>
+        <v>2.699248321616718</v>
       </c>
       <c r="G3" t="n">
-        <v>2.421731303774957</v>
+        <v>2.421369795038072</v>
       </c>
       <c r="H3" t="n">
-        <v>2.435643289352186</v>
+        <v>2.435580608119342</v>
       </c>
       <c r="I3" t="n">
-        <v>2.474341891344105</v>
+        <v>2.477231017217742</v>
       </c>
       <c r="J3" t="n">
-        <v>2.444206668163113</v>
+        <v>2.446962925914248</v>
       </c>
       <c r="K3" t="n">
-        <v>2.455391312427664</v>
+        <v>2.459291633873065</v>
       </c>
       <c r="L3" t="n">
-        <v>2.461081237999127</v>
+        <v>2.474429107368338</v>
       </c>
       <c r="M3" t="n">
-        <v>2.435235731887647</v>
+        <v>2.442692821954232</v>
       </c>
       <c r="N3" t="n">
-        <v>2.401339289643508</v>
+        <v>2.402450725645688</v>
       </c>
       <c r="O3" t="n">
-        <v>2.481823578762151</v>
+        <v>2.485151876473562</v>
       </c>
       <c r="P3" t="n">
-        <v>2.434648109175586</v>
+        <v>2.440098221081247</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.402941616688353</v>
+        <v>2.404220805546674</v>
       </c>
       <c r="R3" t="n">
-        <v>2.512684940431384</v>
+        <v>2.513559496054764</v>
       </c>
       <c r="S3" t="n">
-        <v>2.465959133876298</v>
+        <v>2.471144540746644</v>
       </c>
       <c r="T3" t="n">
-        <v>2.413976402959335</v>
+        <v>2.416579467100198</v>
       </c>
       <c r="U3" t="n">
-        <v>2.487172127256854</v>
+        <v>2.493171417240879</v>
       </c>
       <c r="V3" t="n">
-        <v>2.454289980545444</v>
+        <v>2.456624588552204</v>
       </c>
       <c r="W3" t="n">
-        <v>2.490290004851808</v>
+        <v>2.49009317857182</v>
       </c>
       <c r="X3" t="n">
-        <v>2.465360991864171</v>
+        <v>2.471109848841537</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.417882747745082</v>
+        <v>2.421054678886681</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.443913269242273</v>
+        <v>2.447490481478993</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.465673885563492</v>
+        <v>2.469349882551319</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.410093422879107</v>
+        <v>2.419037585862625</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.111285110163974</v>
+        <v>2.110982984032178</v>
       </c>
       <c r="C4" t="n">
-        <v>2.500483439900913</v>
+        <v>2.489363285760985</v>
       </c>
       <c r="D4" t="n">
-        <v>2.297327738565679</v>
+        <v>2.294962640985586</v>
       </c>
       <c r="E4" t="n">
-        <v>2.432013352966645</v>
+        <v>2.422720327939068</v>
       </c>
       <c r="F4" t="n">
-        <v>2.58558942531798</v>
+        <v>2.57757300622086</v>
       </c>
       <c r="G4" t="n">
-        <v>2.150773404910559</v>
+        <v>2.139070336590566</v>
       </c>
       <c r="H4" t="n">
-        <v>2.172183546533974</v>
+        <v>2.160955308407288</v>
       </c>
       <c r="I4" t="n">
-        <v>2.233380919983022</v>
+        <v>2.226808200853314</v>
       </c>
       <c r="J4" t="n">
-        <v>2.186263946990783</v>
+        <v>2.179501196613962</v>
       </c>
       <c r="K4" t="n">
-        <v>2.20419265193605</v>
+        <v>2.19926077136005</v>
       </c>
       <c r="L4" t="n">
-        <v>2.21292130446022</v>
+        <v>2.222927364261451</v>
       </c>
       <c r="M4" t="n">
-        <v>2.171869194850822</v>
+        <v>2.172492524322839</v>
       </c>
       <c r="N4" t="n">
-        <v>2.118288182333465</v>
+        <v>2.503742816802815</v>
       </c>
       <c r="O4" t="n">
-        <v>2.158371669923439</v>
+        <v>2.153442690341442</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17130943735053</v>
+        <v>2.168839872737583</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.120833272500553</v>
+        <v>2.111728184346152</v>
       </c>
       <c r="R4" t="n">
-        <v>2.293655715979032</v>
+        <v>2.283904138111256</v>
       </c>
       <c r="S4" t="n">
-        <v>2.220982139209199</v>
+        <v>2.218087511904518</v>
       </c>
       <c r="T4" t="n">
-        <v>2.138190520332451</v>
+        <v>2.131168293054568</v>
       </c>
       <c r="U4" t="n">
-        <v>2.169505972080808</v>
+        <v>2.170305290930953</v>
       </c>
       <c r="V4" t="n">
-        <v>2.202846522114238</v>
+        <v>2.195446417697783</v>
       </c>
       <c r="W4" t="n">
-        <v>2.162247953569897</v>
+        <v>2.153875830232443</v>
       </c>
       <c r="X4" t="n">
-        <v>2.219430384700942</v>
+        <v>2.217384520249099</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.144847453108814</v>
+        <v>2.138751189352242</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.135607967716957</v>
+        <v>2.131390874619777</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.220093793280741</v>
+        <v>2.21478059012896</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.132189043762875</v>
+        <v>2.135117318838134</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.335404985892862</v>
+        <v>2.505335975131925</v>
       </c>
       <c r="C5" t="n">
-        <v>9.095151522829909</v>
+        <v>9.086053435871651</v>
       </c>
       <c r="D5" t="n">
-        <v>5.801061239321728</v>
+        <v>5.953971137896853</v>
       </c>
       <c r="E5" t="n">
-        <v>7.997740794802306</v>
+        <v>8.020839313891447</v>
       </c>
       <c r="F5" t="n">
-        <v>11.09480617309458</v>
+        <v>11.14294558890016</v>
       </c>
       <c r="G5" t="n">
-        <v>2.986257798924969</v>
+        <v>2.96749202874195</v>
       </c>
       <c r="H5" t="n">
-        <v>3.56391013104429</v>
+        <v>3.552923487429543</v>
       </c>
       <c r="I5" t="n">
-        <v>4.662335450376659</v>
+        <v>4.738981395964899</v>
       </c>
       <c r="J5" t="n">
-        <v>3.650196281925235</v>
+        <v>3.717304260670474</v>
       </c>
       <c r="K5" t="n">
-        <v>3.882867261821818</v>
+        <v>3.975283025667557</v>
       </c>
       <c r="L5" t="n">
-        <v>4.127790075026628</v>
+        <v>4.489068113363536</v>
       </c>
       <c r="M5" t="n">
-        <v>3.508432543098824</v>
+        <v>3.720659673942277</v>
       </c>
       <c r="N5" t="n">
-        <v>3.277881117971717</v>
+        <v>2.503742816802815</v>
       </c>
       <c r="O5" t="n">
-        <v>3.070311941405291</v>
+        <v>3.157915899107183</v>
       </c>
       <c r="P5" t="n">
-        <v>3.318942220800471</v>
+        <v>3.451784863892904</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.523060893197423</v>
+        <v>2.549809762519272</v>
       </c>
       <c r="R5" t="n">
-        <v>5.862276747940213</v>
+        <v>5.879587612177379</v>
       </c>
       <c r="S5" t="n">
-        <v>4.158758441564095</v>
+        <v>4.28608936937137</v>
       </c>
       <c r="T5" t="n">
-        <v>2.865078533427645</v>
+        <v>2.932717279582491</v>
       </c>
       <c r="U5" t="n">
-        <v>3.328747149466573</v>
+        <v>3.522194173887785</v>
       </c>
       <c r="V5" t="n">
-        <v>3.770619776218922</v>
+        <v>3.819296876269218</v>
       </c>
       <c r="W5" t="n">
-        <v>3.254872465380091</v>
+        <v>3.294685304890314</v>
       </c>
       <c r="X5" t="n">
-        <v>4.329449011387246</v>
+        <v>4.485865806284</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.936388328064778</v>
+        <v>3.015653254777986</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.714877305096775</v>
+        <v>2.813907566920798</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.286104634747328</v>
+        <v>4.380386209306149</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.786293151101757</v>
+        <v>3.052775460180265</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.205123562599156</v>
+        <v>15.59522945686913</v>
       </c>
       <c r="C6" t="n">
-        <v>3.594321892336104</v>
+        <v>3.583985029240174</v>
       </c>
       <c r="D6" t="n">
-        <v>15.78059842370808</v>
+        <v>15.77920911382249</v>
       </c>
       <c r="E6" t="n">
-        <v>3.525851805401837</v>
+        <v>15.906966800776</v>
       </c>
       <c r="F6" t="n">
-        <v>16.06886011046039</v>
+        <v>3.672194749700046</v>
       </c>
       <c r="G6" t="n">
-        <v>3.244611857345745</v>
+        <v>3.233692080069751</v>
       </c>
       <c r="H6" t="n">
-        <v>3.266021998969165</v>
+        <v>3.255577051886481</v>
       </c>
       <c r="I6" t="n">
-        <v>3.327219372418213</v>
+        <v>3.321429944332499</v>
       </c>
       <c r="J6" t="n">
-        <v>15.66953463213319</v>
+        <v>15.6637476694509</v>
       </c>
       <c r="K6" t="n">
-        <v>15.68746333707845</v>
+        <v>15.68350724419699</v>
       </c>
       <c r="L6" t="n">
-        <v>3.306759756895406</v>
+        <v>15.70717383709838</v>
       </c>
       <c r="M6" t="n">
-        <v>15.65513987999323</v>
+        <v>3.267114267802031</v>
       </c>
       <c r="N6" t="n">
-        <v>3.210769053414966</v>
+        <v>2.503742816802815</v>
       </c>
       <c r="O6" t="n">
-        <v>3.250852541004938</v>
+        <v>15.63687495287758</v>
       </c>
       <c r="P6" t="n">
-        <v>15.65387214022694</v>
+        <v>15.65227493556479</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.60410395764295</v>
+        <v>15.59597465718307</v>
       </c>
       <c r="R6" t="n">
-        <v>15.77692640112145</v>
+        <v>3.378525881590444</v>
       </c>
       <c r="S6" t="n">
-        <v>3.314820591644389</v>
+        <v>15.70233398474146</v>
       </c>
       <c r="T6" t="n">
-        <v>3.232028972767642</v>
+        <v>3.225790036533759</v>
       </c>
       <c r="U6" t="n">
-        <v>3.262992666263511</v>
+        <v>3.264563504311874</v>
       </c>
       <c r="V6" t="n">
-        <v>15.68611720725664</v>
+        <v>15.6796928905347</v>
       </c>
       <c r="W6" t="n">
-        <v>3.257195685271112</v>
+        <v>15.63730682034379</v>
       </c>
       <c r="X6" t="n">
-        <v>3.313268837136133</v>
+        <v>3.312006263728294</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.255339689216644</v>
+        <v>3.250048806481626</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.229446420152145</v>
+        <v>15.6156373474567</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.70336447842316</v>
+        <v>15.69902706296589</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.224389390493549</v>
+        <v>3.228163242158662</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.17408792836578</v>
+        <v>2.172224912529056</v>
       </c>
       <c r="C7" t="n">
-        <v>2.563286258102719</v>
+        <v>2.550605214257863</v>
       </c>
       <c r="D7" t="n">
-        <v>2.360130556767486</v>
+        <v>2.356204569482463</v>
       </c>
       <c r="E7" t="n">
-        <v>2.494816171168451</v>
+        <v>2.483962256435946</v>
       </c>
       <c r="F7" t="n">
-        <v>2.648392243519786</v>
+        <v>2.638814934717738</v>
       </c>
       <c r="G7" t="n">
-        <v>2.213576223112365</v>
+        <v>2.200312265087446</v>
       </c>
       <c r="H7" t="n">
-        <v>2.23498636473578</v>
+        <v>2.222197236904166</v>
       </c>
       <c r="I7" t="n">
-        <v>2.296183738184828</v>
+        <v>2.288050129350193</v>
       </c>
       <c r="J7" t="n">
-        <v>2.249066765192589</v>
+        <v>2.24074312511084</v>
       </c>
       <c r="K7" t="n">
-        <v>2.266995470137855</v>
+        <v>2.260502699856928</v>
       </c>
       <c r="L7" t="n">
-        <v>2.275724122662026</v>
+        <v>2.28416929275833</v>
       </c>
       <c r="M7" t="n">
-        <v>2.234672013052629</v>
+        <v>2.233734452819718</v>
       </c>
       <c r="N7" t="n">
-        <v>2.181091000535271</v>
+        <v>2.503742816802815</v>
       </c>
       <c r="O7" t="n">
-        <v>2.221170002126745</v>
+        <v>2.214680157680946</v>
       </c>
       <c r="P7" t="n">
-        <v>2.234107769553836</v>
+        <v>2.230077340077087</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18363609070236</v>
+        <v>2.172970112843031</v>
       </c>
       <c r="R7" t="n">
-        <v>2.356458534180838</v>
+        <v>2.345146066608135</v>
       </c>
       <c r="S7" t="n">
-        <v>2.283784957411005</v>
+        <v>2.279329440401396</v>
       </c>
       <c r="T7" t="n">
-        <v>2.200993338534257</v>
+        <v>2.192410221551446</v>
       </c>
       <c r="U7" t="n">
-        <v>2.231984106991707</v>
+        <v>2.231194603589926</v>
       </c>
       <c r="V7" t="n">
-        <v>2.265649340316043</v>
+        <v>2.256688346194661</v>
       </c>
       <c r="W7" t="n">
-        <v>2.225050771771702</v>
+        <v>2.215117758729321</v>
       </c>
       <c r="X7" t="n">
-        <v>2.282233202902747</v>
+        <v>2.278626448745977</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.207298513058134</v>
+        <v>2.199629587750856</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.198410785918762</v>
+        <v>2.192632803116656</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.282896611482547</v>
+        <v>2.276022518625838</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.19499186196468</v>
+        <v>2.196359247335013</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.183581757670391</v>
+        <v>2.181492563281421</v>
       </c>
       <c r="C8" t="n">
-        <v>2.624011306029988</v>
+        <v>2.609691583868428</v>
       </c>
       <c r="D8" t="n">
-        <v>2.420855604694753</v>
+        <v>2.415290939093029</v>
       </c>
       <c r="E8" t="n">
-        <v>2.528262106406588</v>
+        <v>2.516521627816436</v>
       </c>
       <c r="F8" t="n">
-        <v>2.66586729793342</v>
+        <v>2.655843759623817</v>
       </c>
       <c r="G8" t="n">
-        <v>2.284924397961084</v>
+        <v>2.269728870591483</v>
       </c>
       <c r="H8" t="n">
-        <v>2.295711412663047</v>
+        <v>2.28128360651473</v>
       </c>
       <c r="I8" t="n">
-        <v>2.356908786112096</v>
+        <v>2.347136498960758</v>
       </c>
       <c r="J8" t="n">
-        <v>2.309791813119857</v>
+        <v>2.299829494721405</v>
       </c>
       <c r="K8" t="n">
-        <v>2.327720518065122</v>
+        <v>2.319589069467494</v>
       </c>
       <c r="L8" t="n">
-        <v>2.336449170589293</v>
+        <v>2.343255662368894</v>
       </c>
       <c r="M8" t="n">
-        <v>2.295397060979889</v>
+        <v>2.292820822430264</v>
       </c>
       <c r="N8" t="n">
-        <v>2.202103283232673</v>
+        <v>2.503742816802815</v>
       </c>
       <c r="O8" t="n">
-        <v>2.253100183525606</v>
+        <v>2.245765665024911</v>
       </c>
       <c r="P8" t="n">
-        <v>2.263362809794445</v>
+        <v>2.258561462780418</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.183061816253506</v>
+        <v>2.17244724828513</v>
       </c>
       <c r="R8" t="n">
-        <v>2.417183582108106</v>
+        <v>2.4042324362187</v>
       </c>
       <c r="S8" t="n">
-        <v>2.344510005338273</v>
+        <v>2.338415810011961</v>
       </c>
       <c r="T8" t="n">
-        <v>2.261718386461525</v>
+        <v>2.251496591162011</v>
       </c>
       <c r="U8" t="n">
-        <v>2.26770126488963</v>
+        <v>2.265966122755482</v>
       </c>
       <c r="V8" t="n">
-        <v>2.312399101245055</v>
+        <v>2.302171651288138</v>
       </c>
       <c r="W8" t="n">
-        <v>2.285785888096736</v>
+        <v>2.274213919138427</v>
       </c>
       <c r="X8" t="n">
-        <v>2.28635437143575</v>
+        <v>2.282669568758279</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.319003437742807</v>
+        <v>2.30826995964828</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.206952969035794</v>
+        <v>2.200975045590019</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.343621659409814</v>
+        <v>2.335108888236402</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.309232201623662</v>
+        <v>2.30748543455952</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.529654914256165</v>
+        <v>2.528997510187523</v>
       </c>
       <c r="C9" t="n">
-        <v>3.036860098819963</v>
+        <v>3.025165840970808</v>
       </c>
       <c r="D9" t="n">
-        <v>2.833704397484729</v>
+        <v>2.830765196195411</v>
       </c>
       <c r="E9" t="n">
-        <v>2.941154513973026</v>
+        <v>2.93133788864489</v>
       </c>
       <c r="F9" t="n">
-        <v>2.849928071915104</v>
+        <v>2.841842003403121</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68715006752198</v>
+        <v>2.674872894599603</v>
       </c>
       <c r="H9" t="n">
-        <v>2.708560205453025</v>
+        <v>2.696757863617113</v>
       </c>
       <c r="I9" t="n">
-        <v>2.769757578902072</v>
+        <v>2.762610756063139</v>
       </c>
       <c r="J9" t="n">
-        <v>2.722640605909834</v>
+        <v>2.715303751823786</v>
       </c>
       <c r="K9" t="n">
-        <v>2.740569310855098</v>
+        <v>2.735063326569875</v>
       </c>
       <c r="L9" t="n">
-        <v>2.749297963379269</v>
+        <v>2.758729919471277</v>
       </c>
       <c r="M9" t="n">
-        <v>2.708245853769872</v>
+        <v>2.708295079532665</v>
       </c>
       <c r="N9" t="n">
-        <v>2.654664841252513</v>
+        <v>2.503742816802815</v>
       </c>
       <c r="O9" t="n">
-        <v>2.733855650931495</v>
+        <v>2.728280047876684</v>
       </c>
       <c r="P9" t="n">
-        <v>2.755298589141018</v>
+        <v>2.752166629445153</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.657209935111977</v>
+        <v>2.647530742355189</v>
       </c>
       <c r="R9" t="n">
-        <v>2.830032374898084</v>
+        <v>2.819706693321083</v>
       </c>
       <c r="S9" t="n">
-        <v>2.757358798128248</v>
+        <v>2.753890067114343</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6745671792515</v>
+        <v>2.666970848264394</v>
       </c>
       <c r="U9" t="n">
-        <v>2.705530872747371</v>
+        <v>2.705744316042515</v>
       </c>
       <c r="V9" t="n">
-        <v>2.875400494777086</v>
+        <v>2.867173763060099</v>
       </c>
       <c r="W9" t="n">
-        <v>2.698624612488947</v>
+        <v>2.689678385442268</v>
       </c>
       <c r="X9" t="n">
-        <v>2.755807043619989</v>
+        <v>2.753187075458925</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.680872353775379</v>
+        <v>2.674190214463803</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.600836988220614</v>
+        <v>2.596177723541542</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.756470452199788</v>
+        <v>2.750583145338784</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.668565702681921</v>
+        <v>2.670919874047959</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.394013149042772</v>
+        <v>2.394789628463498</v>
       </c>
       <c r="C2" t="n">
-        <v>2.434390983828913</v>
+        <v>2.434470573125203</v>
       </c>
       <c r="D2" t="n">
-        <v>2.406835265592563</v>
+        <v>2.407427896218863</v>
       </c>
       <c r="E2" t="n">
-        <v>2.419721496553547</v>
+        <v>2.419828259852877</v>
       </c>
       <c r="F2" t="n">
-        <v>2.430871095140024</v>
+        <v>2.431153532610379</v>
       </c>
       <c r="G2" t="n">
-        <v>2.397037890930552</v>
+        <v>2.396980920355948</v>
       </c>
       <c r="H2" t="n">
-        <v>2.39835554309487</v>
+        <v>2.398337671609773</v>
       </c>
       <c r="I2" t="n">
-        <v>2.400663529732786</v>
+        <v>2.401069069010921</v>
       </c>
       <c r="J2" t="n">
-        <v>2.400184989038867</v>
+        <v>2.400564901043356</v>
       </c>
       <c r="K2" t="n">
-        <v>2.400202534624392</v>
+        <v>2.400883098245199</v>
       </c>
       <c r="L2" t="n">
-        <v>2.403264647554887</v>
+        <v>2.40473453567795</v>
       </c>
       <c r="M2" t="n">
-        <v>2.400945884705354</v>
+        <v>2.4017989787279</v>
       </c>
       <c r="N2" t="n">
-        <v>2.39439370930593</v>
+        <v>2.394521995760762</v>
       </c>
       <c r="O2" t="n">
-        <v>2.430559650566173</v>
+        <v>2.430540615560898</v>
       </c>
       <c r="P2" t="n">
-        <v>2.39807740271504</v>
+        <v>2.398763709603612</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.394990511422387</v>
+        <v>2.395224891143825</v>
       </c>
       <c r="R2" t="n">
-        <v>2.406248208811539</v>
+        <v>2.406412844311231</v>
       </c>
       <c r="S2" t="n">
-        <v>2.402515725377528</v>
+        <v>2.403174547329807</v>
       </c>
       <c r="T2" t="n">
-        <v>2.39673545732091</v>
+        <v>2.397099884147507</v>
       </c>
       <c r="U2" t="n">
-        <v>2.429079514274896</v>
+        <v>2.429423601308343</v>
       </c>
       <c r="V2" t="n">
-        <v>2.400465116900695</v>
+        <v>2.401045591220076</v>
       </c>
       <c r="W2" t="n">
-        <v>2.434391097031224</v>
+        <v>2.433525962587049</v>
       </c>
       <c r="X2" t="n">
-        <v>2.403881600097762</v>
+        <v>2.404666089746624</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.395670094149189</v>
+        <v>2.396468891713773</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.414171076772126</v>
+        <v>2.414253027972946</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.401285782095883</v>
+        <v>2.401838472573483</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.39578016315303</v>
+        <v>2.396895376527622</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.395214292179797</v>
+        <v>2.400862902573528</v>
       </c>
       <c r="C3" t="n">
-        <v>2.655201024871143</v>
+        <v>2.655620814773071</v>
       </c>
       <c r="D3" t="n">
-        <v>2.486782369281612</v>
+        <v>2.491147935899102</v>
       </c>
       <c r="E3" t="n">
-        <v>2.578059449866423</v>
+        <v>2.578953958633321</v>
       </c>
       <c r="F3" t="n">
-        <v>2.658781588938879</v>
+        <v>2.660936608216037</v>
       </c>
       <c r="G3" t="n">
-        <v>2.416688201062831</v>
+        <v>2.416419088906568</v>
       </c>
       <c r="H3" t="n">
-        <v>2.426469622268807</v>
+        <v>2.42647735170578</v>
       </c>
       <c r="I3" t="n">
-        <v>2.442851978794924</v>
+        <v>2.445889043724379</v>
       </c>
       <c r="J3" t="n">
-        <v>2.439218328297426</v>
+        <v>2.442059485892805</v>
       </c>
       <c r="K3" t="n">
-        <v>2.439263633139162</v>
+        <v>2.444238167144781</v>
       </c>
       <c r="L3" t="n">
-        <v>2.461093373459369</v>
+        <v>2.471692010515997</v>
       </c>
       <c r="M3" t="n">
-        <v>2.445241492609473</v>
+        <v>2.451450444594914</v>
       </c>
       <c r="N3" t="n">
-        <v>2.397977320113392</v>
+        <v>2.399029935973688</v>
       </c>
       <c r="O3" t="n">
-        <v>2.47522367768725</v>
+        <v>2.476842417978635</v>
       </c>
       <c r="P3" t="n">
-        <v>2.424055219813029</v>
+        <v>2.429060886917906</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.402215325206414</v>
+        <v>2.404021680577986</v>
       </c>
       <c r="R3" t="n">
-        <v>2.482999128389823</v>
+        <v>2.484315317851925</v>
       </c>
       <c r="S3" t="n">
-        <v>2.455659906311094</v>
+        <v>2.460478187982983</v>
       </c>
       <c r="T3" t="n">
-        <v>2.414762689585126</v>
+        <v>2.417507563880266</v>
       </c>
       <c r="U3" t="n">
-        <v>2.467478425886205</v>
+        <v>2.475202457933928</v>
       </c>
       <c r="V3" t="n">
-        <v>2.440963222670697</v>
+        <v>2.445213391992988</v>
       </c>
       <c r="W3" t="n">
-        <v>2.480852021741385</v>
+        <v>2.481272952434419</v>
       </c>
       <c r="X3" t="n">
-        <v>2.46568274827268</v>
+        <v>2.471416824516286</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.407087625247443</v>
+        <v>2.412929464210303</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.435333200533971</v>
+        <v>2.438692910484866</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.447187518712332</v>
+        <v>2.451270170009389</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.408701530614461</v>
+        <v>2.416784755220898</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.109192688875723</v>
+        <v>2.107351232378809</v>
       </c>
       <c r="C4" t="n">
-        <v>2.508510167350149</v>
+        <v>2.49820377428373</v>
       </c>
       <c r="D4" t="n">
-        <v>2.254024393770657</v>
+        <v>2.250106280566058</v>
       </c>
       <c r="E4" t="n">
-        <v>2.399580300434077</v>
+        <v>2.390174092261345</v>
       </c>
       <c r="F4" t="n">
-        <v>2.525520145537085</v>
+        <v>2.518098257940194</v>
       </c>
       <c r="G4" t="n">
-        <v>2.143358539948224</v>
+        <v>2.132102882348098</v>
       </c>
       <c r="H4" t="n">
-        <v>2.158242027294146</v>
+        <v>2.147428011896443</v>
       </c>
       <c r="I4" t="n">
-        <v>2.184311798095703</v>
+        <v>2.17828040204731</v>
       </c>
       <c r="J4" t="n">
-        <v>2.178935769656634</v>
+        <v>2.172617940222277</v>
       </c>
       <c r="K4" t="n">
-        <v>2.179104646278174</v>
+        <v>2.176179776697711</v>
       </c>
       <c r="L4" t="n">
-        <v>2.21369262046965</v>
+        <v>2.219683534249383</v>
       </c>
       <c r="M4" t="n">
-        <v>2.188297371320381</v>
+        <v>2.187281239816168</v>
       </c>
       <c r="N4" t="n">
-        <v>2.11349129211447</v>
+        <v>2.454300934083968</v>
       </c>
       <c r="O4" t="n">
-        <v>2.150044266840952</v>
+        <v>2.142576381266148</v>
       </c>
       <c r="P4" t="n">
-        <v>2.155100303753059</v>
+        <v>2.152240307024035</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.120232446562386</v>
+        <v>2.112267724583825</v>
       </c>
       <c r="R4" t="n">
-        <v>2.247393317369518</v>
+        <v>2.238640802322381</v>
       </c>
       <c r="S4" t="n">
-        <v>2.205233199955159</v>
+        <v>2.202062748226999</v>
       </c>
       <c r="T4" t="n">
-        <v>2.139942413200975</v>
+        <v>2.133446633099813</v>
       </c>
       <c r="U4" t="n">
-        <v>2.139180286128999</v>
+        <v>2.143202243760133</v>
       </c>
       <c r="V4" t="n">
-        <v>2.182184492056261</v>
+        <v>2.178149812267535</v>
       </c>
       <c r="W4" t="n">
-        <v>2.148197899431994</v>
+        <v>2.141111838835089</v>
       </c>
       <c r="X4" t="n">
-        <v>2.220661383253614</v>
+        <v>2.218910405968357</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.128171367305734</v>
+        <v>2.126687103650241</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.12346842693988</v>
+        <v>2.119290015784704</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.191340424787114</v>
+        <v>2.186971169229558</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.130490084246132</v>
+        <v>2.132380119834213</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.334989303752998</v>
+        <v>2.467791740616281</v>
       </c>
       <c r="C5" t="n">
-        <v>9.218087797069041</v>
+        <v>9.215963638568827</v>
       </c>
       <c r="D5" t="n">
-        <v>4.925593472815544</v>
+        <v>5.036744159512149</v>
       </c>
       <c r="E5" t="n">
-        <v>7.141071505097034</v>
+        <v>7.153394981052301</v>
       </c>
       <c r="F5" t="n">
-        <v>9.96287639770981</v>
+        <v>10.01377583665909</v>
       </c>
       <c r="G5" t="n">
-        <v>2.88028195882886</v>
+        <v>2.862463138246397</v>
       </c>
       <c r="H5" t="n">
-        <v>3.339032664166067</v>
+        <v>3.327879449136619</v>
       </c>
       <c r="I5" t="n">
-        <v>3.75355234178985</v>
+        <v>3.83083896717647</v>
       </c>
       <c r="J5" t="n">
-        <v>3.544860373122416</v>
+        <v>3.610291150038885</v>
       </c>
       <c r="K5" t="n">
-        <v>3.50692036696407</v>
+        <v>3.625991569163492</v>
       </c>
       <c r="L5" t="n">
-        <v>4.105859232670298</v>
+        <v>4.377777825765715</v>
       </c>
       <c r="M5" t="n">
-        <v>3.793840100760383</v>
+        <v>3.959538999201417</v>
       </c>
       <c r="N5" t="n">
-        <v>2.806535578604489</v>
+        <v>2.454300934083968</v>
       </c>
       <c r="O5" t="n">
-        <v>2.97485869128379</v>
+        <v>3.016496690125778</v>
       </c>
       <c r="P5" t="n">
-        <v>3.060991882579812</v>
+        <v>3.176102385030362</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.543485757714992</v>
+        <v>2.581844201897621</v>
       </c>
       <c r="R5" t="n">
-        <v>5.019028638716709</v>
+        <v>5.047393246961107</v>
       </c>
       <c r="S5" t="n">
-        <v>3.910443749621916</v>
+        <v>4.024611245333947</v>
       </c>
       <c r="T5" t="n">
-        <v>2.940594100464804</v>
+        <v>3.010305252750704</v>
       </c>
       <c r="U5" t="n">
-        <v>2.831961851398408</v>
+        <v>3.062593914742752</v>
       </c>
       <c r="V5" t="n">
-        <v>3.469076258805698</v>
+        <v>3.562978651221024</v>
       </c>
       <c r="W5" t="n">
-        <v>3.046183043758903</v>
+        <v>3.101505273498696</v>
       </c>
       <c r="X5" t="n">
-        <v>4.325582773425107</v>
+        <v>4.474649404358031</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.690696611844587</v>
+        <v>2.84554777148638</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.541164405987972</v>
+        <v>2.628818718623662</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.823189276872244</v>
+        <v>3.927469514500179</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.788844201870317</v>
+        <v>3.023135270505751</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.59026396630406</v>
+        <v>3.200425500401615</v>
       </c>
       <c r="C6" t="n">
-        <v>3.600640426421414</v>
+        <v>3.591278042306548</v>
       </c>
       <c r="D6" t="n">
-        <v>3.346154652841924</v>
+        <v>15.7323698071585</v>
       </c>
       <c r="E6" t="n">
-        <v>15.88065157786243</v>
+        <v>15.87243761885379</v>
       </c>
       <c r="F6" t="n">
-        <v>3.61765040460835</v>
+        <v>3.611172525963007</v>
       </c>
       <c r="G6" t="n">
-        <v>15.62442981737656</v>
+        <v>3.225177150370919</v>
       </c>
       <c r="H6" t="n">
-        <v>3.250372286365413</v>
+        <v>15.62969153848887</v>
       </c>
       <c r="I6" t="n">
-        <v>3.276442057166971</v>
+        <v>3.271354670070123</v>
       </c>
       <c r="J6" t="n">
-        <v>15.66000704708498</v>
+        <v>15.6548814668147</v>
       </c>
       <c r="K6" t="n">
-        <v>15.66017592370651</v>
+        <v>15.65844330329016</v>
       </c>
       <c r="L6" t="n">
-        <v>15.694763897898</v>
+        <v>3.312757802272202</v>
       </c>
       <c r="M6" t="n">
-        <v>3.280427630391647</v>
+        <v>3.28035550783898</v>
       </c>
       <c r="N6" t="n">
-        <v>3.204325492348059</v>
+        <v>2.454300934083968</v>
       </c>
       <c r="O6" t="n">
-        <v>15.63036068059225</v>
+        <v>3.234383972970493</v>
       </c>
       <c r="P6" t="n">
-        <v>3.24309179183546</v>
+        <v>15.633572712292</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.60130372399073</v>
+        <v>15.59453125117626</v>
       </c>
       <c r="R6" t="n">
-        <v>15.72846459479785</v>
+        <v>15.72090432891482</v>
       </c>
       <c r="S6" t="n">
-        <v>15.6863044773835</v>
+        <v>3.295137016249814</v>
       </c>
       <c r="T6" t="n">
-        <v>15.62101369062931</v>
+        <v>15.61571015969225</v>
       </c>
       <c r="U6" t="n">
-        <v>3.231047823979658</v>
+        <v>15.62509794999225</v>
       </c>
       <c r="V6" t="n">
-        <v>3.274314751127525</v>
+        <v>3.271224080290354</v>
       </c>
       <c r="W6" t="n">
-        <v>15.62851372963509</v>
+        <v>3.235344468864863</v>
       </c>
       <c r="X6" t="n">
-        <v>3.312791642324886</v>
+        <v>3.311984673991173</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.237021782014884</v>
+        <v>3.236436054715604</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.60453970436823</v>
+        <v>3.212364283807521</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.67241170221545</v>
+        <v>15.66923469582201</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.221150574456776</v>
+        <v>3.224040516291701</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.171586772127861</v>
+        <v>2.168158656587956</v>
       </c>
       <c r="C7" t="n">
-        <v>2.570904250602286</v>
+        <v>2.559011198492876</v>
       </c>
       <c r="D7" t="n">
-        <v>2.316418477022796</v>
+        <v>2.310913704775206</v>
       </c>
       <c r="E7" t="n">
-        <v>2.461974383686216</v>
+        <v>2.450981516470493</v>
       </c>
       <c r="F7" t="n">
-        <v>2.587914228789225</v>
+        <v>2.578905682149341</v>
       </c>
       <c r="G7" t="n">
-        <v>2.205752623200362</v>
+        <v>2.192910306557246</v>
       </c>
       <c r="H7" t="n">
-        <v>2.220636110546284</v>
+        <v>2.20823543610559</v>
       </c>
       <c r="I7" t="n">
-        <v>2.246705881347841</v>
+        <v>2.239087826256456</v>
       </c>
       <c r="J7" t="n">
-        <v>2.241329852908771</v>
+        <v>2.233425364431425</v>
       </c>
       <c r="K7" t="n">
-        <v>2.241498729530313</v>
+        <v>2.23698720090686</v>
       </c>
       <c r="L7" t="n">
-        <v>2.276086703721789</v>
+        <v>2.28049095845853</v>
       </c>
       <c r="M7" t="n">
-        <v>2.250691454572519</v>
+        <v>2.248088664025314</v>
       </c>
       <c r="N7" t="n">
-        <v>2.175885375366608</v>
+        <v>2.454300934083968</v>
       </c>
       <c r="O7" t="n">
-        <v>2.212433883708908</v>
+        <v>2.203379363652584</v>
       </c>
       <c r="P7" t="n">
-        <v>2.217489920621015</v>
+        <v>2.213043289410471</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.182626529814525</v>
+        <v>2.173075148792972</v>
       </c>
       <c r="R7" t="n">
-        <v>2.309787400621656</v>
+        <v>2.299448226531529</v>
       </c>
       <c r="S7" t="n">
-        <v>2.267627283207299</v>
+        <v>2.262870172436146</v>
       </c>
       <c r="T7" t="n">
-        <v>2.202336496453113</v>
+        <v>2.19425405730896</v>
       </c>
       <c r="U7" t="n">
-        <v>2.201363744366061</v>
+        <v>2.203668718774239</v>
       </c>
       <c r="V7" t="n">
-        <v>2.244578575308399</v>
+        <v>2.238957236476683</v>
       </c>
       <c r="W7" t="n">
-        <v>2.210591982684133</v>
+        <v>2.201919263044237</v>
       </c>
       <c r="X7" t="n">
-        <v>2.283055466505751</v>
+        <v>2.279717830177505</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.190302729337265</v>
+        <v>2.187126707499055</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.185862510192017</v>
+        <v>2.180097439993851</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.253734508039252</v>
+        <v>2.247778593438706</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.19288416749827</v>
+        <v>2.193187544043361</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.18068889303772</v>
+        <v>2.177048021120553</v>
       </c>
       <c r="C8" t="n">
-        <v>2.630684875622958</v>
+        <v>2.617147122034081</v>
       </c>
       <c r="D8" t="n">
-        <v>2.376199102043469</v>
+        <v>2.36904962831641</v>
       </c>
       <c r="E8" t="n">
-        <v>2.494770200191172</v>
+        <v>2.482895100023871</v>
       </c>
       <c r="F8" t="n">
-        <v>2.604911468346912</v>
+        <v>2.595467085018069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.276041766187878</v>
+        <v>2.261257824919826</v>
       </c>
       <c r="H8" t="n">
-        <v>2.280416735566956</v>
+        <v>2.266371359646796</v>
       </c>
       <c r="I8" t="n">
-        <v>2.306486506368513</v>
+        <v>2.297223749797662</v>
       </c>
       <c r="J8" t="n">
-        <v>2.301110477929444</v>
+        <v>2.291561287972629</v>
       </c>
       <c r="K8" t="n">
-        <v>2.301279354550984</v>
+        <v>2.295123124448064</v>
       </c>
       <c r="L8" t="n">
-        <v>2.335867328742462</v>
+        <v>2.338626881999735</v>
       </c>
       <c r="M8" t="n">
-        <v>2.310472079593191</v>
+        <v>2.30622458756651</v>
       </c>
       <c r="N8" t="n">
-        <v>2.196381681371303</v>
+        <v>2.454300934083968</v>
       </c>
       <c r="O8" t="n">
-        <v>2.243730328061226</v>
+        <v>2.233836042158078</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24614008491533</v>
+        <v>2.24092845975308</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.181769167987482</v>
+        <v>2.172286440484669</v>
       </c>
       <c r="R8" t="n">
-        <v>2.36956802564233</v>
+        <v>2.357584150072733</v>
       </c>
       <c r="S8" t="n">
-        <v>2.327407908227971</v>
+        <v>2.32100609597735</v>
       </c>
       <c r="T8" t="n">
-        <v>2.262117121473785</v>
+        <v>2.252389980850164</v>
       </c>
       <c r="U8" t="n">
-        <v>2.236400606339106</v>
+        <v>2.237765449777247</v>
       </c>
       <c r="V8" t="n">
-        <v>2.290556349315086</v>
+        <v>2.283660098455293</v>
       </c>
       <c r="W8" t="n">
-        <v>2.270382567478706</v>
+        <v>2.260064864938142</v>
       </c>
       <c r="X8" t="n">
-        <v>2.28684289027752</v>
+        <v>2.283442666852268</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.300546825755481</v>
+        <v>2.294268877165525</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.194023251870082</v>
+        <v>2.188072024410404</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.313515133059924</v>
+        <v>2.30591451697991</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.305602727726157</v>
+        <v>2.30276561639234</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.484450818421983</v>
+        <v>2.48230617188513</v>
       </c>
       <c r="C9" t="n">
-        <v>2.989833205647962</v>
+        <v>2.979014152892809</v>
       </c>
       <c r="D9" t="n">
-        <v>2.735347432068472</v>
+        <v>2.730916659175139</v>
       </c>
       <c r="E9" t="n">
-        <v>2.856423985053226</v>
+        <v>2.84655346129673</v>
       </c>
       <c r="F9" t="n">
-        <v>2.762334630414284</v>
+        <v>2.754882968917314</v>
       </c>
       <c r="G9" t="n">
-        <v>2.624681571265214</v>
+        <v>2.612913253150099</v>
       </c>
       <c r="H9" t="n">
-        <v>2.639565065591959</v>
+        <v>2.628238390505524</v>
       </c>
       <c r="I9" t="n">
-        <v>2.665634836393516</v>
+        <v>2.659090780656388</v>
       </c>
       <c r="J9" t="n">
-        <v>2.660258807954448</v>
+        <v>2.653428318831357</v>
       </c>
       <c r="K9" t="n">
-        <v>2.660427684575989</v>
+        <v>2.656990155306795</v>
       </c>
       <c r="L9" t="n">
-        <v>2.695015658767464</v>
+        <v>2.700493912858463</v>
       </c>
       <c r="M9" t="n">
-        <v>2.669620409618194</v>
+        <v>2.668091618425248</v>
       </c>
       <c r="N9" t="n">
-        <v>2.594814330412284</v>
+        <v>2.454300934083968</v>
       </c>
       <c r="O9" t="n">
-        <v>2.666517067724786</v>
+        <v>2.65846710339384</v>
       </c>
       <c r="P9" t="n">
-        <v>2.679217576448947</v>
+        <v>2.675760403687346</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.601555477879378</v>
+        <v>2.593078095385827</v>
       </c>
       <c r="R9" t="n">
-        <v>2.728716355667332</v>
+        <v>2.719451180931459</v>
       </c>
       <c r="S9" t="n">
-        <v>2.686556238252974</v>
+        <v>2.682873126836077</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62126545149879</v>
+        <v>2.614257011708893</v>
       </c>
       <c r="U9" t="n">
-        <v>2.620240603206207</v>
+        <v>2.623644802008878</v>
       </c>
       <c r="V9" t="n">
-        <v>2.785904073843589</v>
+        <v>2.781115008675865</v>
       </c>
       <c r="W9" t="n">
-        <v>2.62952093772981</v>
+        <v>2.621922217444168</v>
       </c>
       <c r="X9" t="n">
-        <v>2.701984421551427</v>
+        <v>2.699720784577437</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.60923168438294</v>
+        <v>2.607129661898988</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.540843754148223</v>
+        <v>2.536278974547673</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.672663463084928</v>
+        <v>2.667781547838636</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.611813122543946</v>
+        <v>2.613190498443292</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.399249649647783</v>
+        <v>2.39867499041809</v>
       </c>
       <c r="C2" t="n">
-        <v>2.453103058309987</v>
+        <v>2.452504126082418</v>
       </c>
       <c r="D2" t="n">
-        <v>2.41590727147702</v>
+        <v>2.415279491217256</v>
       </c>
       <c r="E2" t="n">
-        <v>2.442901932875979</v>
+        <v>2.442298675715666</v>
       </c>
       <c r="F2" t="n">
-        <v>2.454158011861055</v>
+        <v>2.453460097201012</v>
       </c>
       <c r="G2" t="n">
-        <v>2.401795102213242</v>
+        <v>2.401101269768827</v>
       </c>
       <c r="H2" t="n">
-        <v>2.407583540121621</v>
+        <v>2.406920681447952</v>
       </c>
       <c r="I2" t="n">
-        <v>2.42488412190932</v>
+        <v>2.424282948680796</v>
       </c>
       <c r="J2" t="n">
-        <v>2.409515988771772</v>
+        <v>2.408910760303996</v>
       </c>
       <c r="K2" t="n">
-        <v>2.413567521901798</v>
+        <v>2.412901765464472</v>
       </c>
       <c r="L2" t="n">
-        <v>2.416255385962423</v>
+        <v>2.416071217499356</v>
       </c>
       <c r="M2" t="n">
-        <v>2.419278226655535</v>
+        <v>2.41899263915991</v>
       </c>
       <c r="N2" t="n">
-        <v>2.401157551047771</v>
+        <v>2.400467615267978</v>
       </c>
       <c r="O2" t="n">
-        <v>2.439358944397934</v>
+        <v>2.438069652145243</v>
       </c>
       <c r="P2" t="n">
-        <v>2.409352663931954</v>
+        <v>2.40880992637861</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.40038030030938</v>
+        <v>2.399712381358891</v>
       </c>
       <c r="R2" t="n">
-        <v>2.416027352822243</v>
+        <v>2.41541678887265</v>
       </c>
       <c r="S2" t="n">
-        <v>2.422139209592621</v>
+        <v>2.421499096310511</v>
       </c>
       <c r="T2" t="n">
-        <v>2.403096507631809</v>
+        <v>2.402454361327776</v>
       </c>
       <c r="U2" t="n">
-        <v>2.439244908506299</v>
+        <v>2.43856872030646</v>
       </c>
       <c r="V2" t="n">
-        <v>2.409376202552697</v>
+        <v>2.408725936381352</v>
       </c>
       <c r="W2" t="n">
-        <v>2.443858473437397</v>
+        <v>2.442664757495297</v>
       </c>
       <c r="X2" t="n">
-        <v>2.411079256386697</v>
+        <v>2.410471442353677</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.403703448149393</v>
+        <v>2.403047752993953</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.42159461119273</v>
+        <v>2.420269260040117</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.417209232573351</v>
+        <v>2.416698207915214</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.411364514434541</v>
+        <v>2.410983803101824</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.395694419688065</v>
+        <v>2.395856166765058</v>
       </c>
       <c r="C3" t="n">
-        <v>2.749021266309682</v>
+        <v>2.748657515080791</v>
       </c>
       <c r="D3" t="n">
-        <v>2.514847682211703</v>
+        <v>2.514634593799272</v>
       </c>
       <c r="E3" t="n">
-        <v>2.707119426380299</v>
+        <v>2.707080744328392</v>
       </c>
       <c r="F3" t="n">
-        <v>2.788309960756174</v>
+        <v>2.787595155521675</v>
       </c>
       <c r="G3" t="n">
-        <v>2.413745250256628</v>
+        <v>2.413060121059136</v>
       </c>
       <c r="H3" t="n">
-        <v>2.455501803832772</v>
+        <v>2.455038024634851</v>
       </c>
       <c r="I3" t="n">
-        <v>2.579211648072867</v>
+        <v>2.579189326497566</v>
       </c>
       <c r="J3" t="n">
-        <v>2.468807936186607</v>
+        <v>2.468753157035257</v>
       </c>
       <c r="K3" t="n">
-        <v>2.497595628549564</v>
+        <v>2.497109753239583</v>
       </c>
       <c r="L3" t="n">
-        <v>2.516286868133541</v>
+        <v>2.519214755021272</v>
       </c>
       <c r="M3" t="n">
-        <v>2.538286027700488</v>
+        <v>2.540479987298073</v>
       </c>
       <c r="N3" t="n">
-        <v>2.409314868557934</v>
+        <v>2.408657548996564</v>
       </c>
       <c r="O3" t="n">
-        <v>2.491673790344925</v>
+        <v>2.490267073288447</v>
       </c>
       <c r="P3" t="n">
-        <v>2.467519702278372</v>
+        <v>2.467909437022442</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.403769216730124</v>
+        <v>2.403268760501493</v>
       </c>
       <c r="R3" t="n">
-        <v>2.515997932811822</v>
+        <v>2.515909209990748</v>
       </c>
       <c r="S3" t="n">
-        <v>2.557499631173188</v>
+        <v>2.557194710485524</v>
       </c>
       <c r="T3" t="n">
-        <v>2.423178023788534</v>
+        <v>2.422861221219704</v>
       </c>
       <c r="U3" t="n">
-        <v>2.50570082421712</v>
+        <v>2.507481493368223</v>
       </c>
       <c r="V3" t="n">
-        <v>2.467566721249349</v>
+        <v>2.467190805885726</v>
       </c>
       <c r="W3" t="n">
-        <v>2.513982521173943</v>
+        <v>2.512999918586183</v>
       </c>
       <c r="X3" t="n">
-        <v>2.480250793613695</v>
+        <v>2.480180161931621</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.427477830330388</v>
+        <v>2.427064711471524</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.451275916641919</v>
+        <v>2.450040397866841</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.52389170958038</v>
+        <v>2.524511455585242</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.482735615459239</v>
+        <v>2.484272583707952</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.111570100588293</v>
+        <v>2.096693147054328</v>
       </c>
       <c r="C4" t="n">
-        <v>2.656393427844347</v>
+        <v>2.640508729045212</v>
       </c>
       <c r="D4" t="n">
-        <v>2.299725602034156</v>
+        <v>2.28424862202865</v>
       </c>
       <c r="E4" t="n">
-        <v>2.604642720693169</v>
+        <v>2.589442740377147</v>
       </c>
       <c r="F4" t="n">
-        <v>2.731785310881756</v>
+        <v>2.715516130561684</v>
       </c>
       <c r="G4" t="n">
-        <v>2.140322158281184</v>
+        <v>2.124099088464543</v>
       </c>
       <c r="H4" t="n">
-        <v>2.205705227269316</v>
+        <v>2.189832020441894</v>
       </c>
       <c r="I4" t="n">
-        <v>2.401123257222201</v>
+        <v>2.385946815874392</v>
       </c>
       <c r="J4" t="n">
-        <v>2.227570882057433</v>
+        <v>2.21234980489076</v>
       </c>
       <c r="K4" t="n">
-        <v>2.273297054244047</v>
+        <v>2.257391115843077</v>
       </c>
       <c r="L4" t="n">
-        <v>2.303657715287357</v>
+        <v>2.293191534597061</v>
       </c>
       <c r="M4" t="n">
-        <v>2.337686509939046</v>
+        <v>2.326025449846589</v>
       </c>
       <c r="N4" t="n">
-        <v>2.133120724579161</v>
+        <v>2.630435288418834</v>
       </c>
       <c r="O4" t="n">
-        <v>2.173378627224226</v>
+        <v>2.157697330492536</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2256882945442</v>
+        <v>2.211171911029284</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.124341319936036</v>
+        <v>2.108410954954085</v>
       </c>
       <c r="R4" t="n">
-        <v>2.301081976068591</v>
+        <v>2.285799462206376</v>
       </c>
       <c r="S4" t="n">
-        <v>2.370118209883036</v>
+        <v>2.354501922716677</v>
       </c>
       <c r="T4" t="n">
-        <v>2.155022131159968</v>
+        <v>2.139382880075749</v>
       </c>
       <c r="U4" t="n">
-        <v>2.202889876357307</v>
+        <v>2.191711161070128</v>
       </c>
       <c r="V4" t="n">
-        <v>2.226127263121045</v>
+        <v>2.210404224242082</v>
       </c>
       <c r="W4" t="n">
-        <v>2.203468263337288</v>
+        <v>2.188331035510443</v>
       </c>
       <c r="X4" t="n">
-        <v>2.245190950592283</v>
+        <v>2.229939498302784</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.16231109966556</v>
+        <v>2.146527813118119</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.150366961933487</v>
+        <v>2.135164367436696</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.314431851548906</v>
+        <v>2.300273679774022</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.248896445825951</v>
+        <v>2.236175236944186</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.240524336508799</v>
+        <v>2.243501948472979</v>
       </c>
       <c r="C5" t="n">
-        <v>12.60761199754195</v>
+        <v>12.59341393597399</v>
       </c>
       <c r="D5" t="n">
-        <v>5.946634962247173</v>
+        <v>5.940654308856484</v>
       </c>
       <c r="E5" t="n">
-        <v>11.49480128532114</v>
+        <v>11.4937154019193</v>
       </c>
       <c r="F5" t="n">
-        <v>14.37449912816199</v>
+        <v>14.35289220395061</v>
       </c>
       <c r="G5" t="n">
-        <v>2.719545451885995</v>
+        <v>2.699111292721892</v>
       </c>
       <c r="H5" t="n">
-        <v>4.202836018887528</v>
+        <v>4.189177571092249</v>
       </c>
       <c r="I5" t="n">
-        <v>8.028326837843967</v>
+        <v>8.028513220913759</v>
       </c>
       <c r="J5" t="n">
-        <v>4.345386988530619</v>
+        <v>4.342753501802332</v>
       </c>
       <c r="K5" t="n">
-        <v>5.139294054870828</v>
+        <v>5.124229972851181</v>
       </c>
       <c r="L5" t="n">
-        <v>5.439623401457952</v>
+        <v>5.514424701331864</v>
       </c>
       <c r="M5" t="n">
-        <v>6.354323565231363</v>
+        <v>6.415816423523887</v>
       </c>
       <c r="N5" t="n">
-        <v>3.802732113697948</v>
+        <v>2.630435288418834</v>
       </c>
       <c r="O5" t="n">
-        <v>3.270350558201499</v>
+        <v>3.259148337815348</v>
       </c>
       <c r="P5" t="n">
-        <v>4.242296243695077</v>
+        <v>4.252181059492901</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.484941656542493</v>
+        <v>2.469890142292755</v>
       </c>
       <c r="R5" t="n">
-        <v>6.13535837030962</v>
+        <v>6.133884402964029</v>
       </c>
       <c r="S5" t="n">
-        <v>6.262242254328265</v>
+        <v>6.251508164987208</v>
       </c>
       <c r="T5" t="n">
-        <v>3.077898616803052</v>
+        <v>3.068191839091424</v>
       </c>
       <c r="U5" t="n">
-        <v>3.872067969323045</v>
+        <v>3.941791346348984</v>
       </c>
       <c r="V5" t="n">
-        <v>4.1802147384879</v>
+        <v>4.168136066833825</v>
       </c>
       <c r="W5" t="n">
-        <v>3.987478755453574</v>
+        <v>3.987723987278667</v>
       </c>
       <c r="X5" t="n">
-        <v>4.838135859529175</v>
+        <v>4.836395422820266</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.189751396022425</v>
+        <v>3.177363692284663</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.892257090502551</v>
+        <v>2.889109258034909</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.086699106980214</v>
+        <v>6.10540067482567</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.011806814489113</v>
+        <v>5.061114344965587</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.288797081224149</v>
+        <v>3.274492332132383</v>
       </c>
       <c r="C6" t="n">
-        <v>17.13077971157247</v>
+        <v>3.818307914123272</v>
       </c>
       <c r="D6" t="n">
-        <v>3.476952582670011</v>
+        <v>16.75920941431827</v>
       </c>
       <c r="E6" t="n">
-        <v>3.78186970132902</v>
+        <v>17.06440353266677</v>
       </c>
       <c r="F6" t="n">
-        <v>17.20617159460988</v>
+        <v>3.893315315639745</v>
       </c>
       <c r="G6" t="n">
-        <v>16.61470844200931</v>
+        <v>3.301898273542594</v>
       </c>
       <c r="H6" t="n">
-        <v>3.382932207905171</v>
+        <v>16.66479281273152</v>
       </c>
       <c r="I6" t="n">
-        <v>3.578350237858061</v>
+        <v>16.86090760816401</v>
       </c>
       <c r="J6" t="n">
-        <v>3.404797862693291</v>
+        <v>3.390148989968818</v>
       </c>
       <c r="K6" t="n">
-        <v>3.450524034879906</v>
+        <v>16.7323519081327</v>
       </c>
       <c r="L6" t="n">
-        <v>3.480884695923209</v>
+        <v>3.47099071967512</v>
       </c>
       <c r="M6" t="n">
-        <v>16.81207279366718</v>
+        <v>16.80098624213623</v>
       </c>
       <c r="N6" t="n">
-        <v>3.308024091480914</v>
+        <v>2.630435288418834</v>
       </c>
       <c r="O6" t="n">
-        <v>16.64671124461569</v>
+        <v>16.63145970732298</v>
       </c>
       <c r="P6" t="n">
-        <v>3.397300227885636</v>
+        <v>16.68493715879482</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.59872760366415</v>
+        <v>16.5833717472437</v>
       </c>
       <c r="R6" t="n">
-        <v>3.478308956704447</v>
+        <v>16.760760254496</v>
       </c>
       <c r="S6" t="n">
-        <v>3.547345190518891</v>
+        <v>3.532301107794731</v>
       </c>
       <c r="T6" t="n">
-        <v>16.62940841488808</v>
+        <v>3.317182065153806</v>
       </c>
       <c r="U6" t="n">
-        <v>3.379683560840121</v>
+        <v>3.369068044948938</v>
       </c>
       <c r="V6" t="n">
-        <v>16.70051354684916</v>
+        <v>16.6853650165317</v>
       </c>
       <c r="W6" t="n">
-        <v>3.381238575609607</v>
+        <v>16.6620916235924</v>
       </c>
       <c r="X6" t="n">
-        <v>3.422417931228139</v>
+        <v>3.407738683380836</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.356620231981223</v>
+        <v>3.341398044482535</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.62475324566159</v>
+        <v>3.312963552514751</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.78881813527703</v>
+        <v>16.77523447206364</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.424043899934438</v>
+        <v>3.411903865318831</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.180240081690417</v>
+        <v>2.163583354886262</v>
       </c>
       <c r="C7" t="n">
-        <v>2.725063408946472</v>
+        <v>2.707398936877147</v>
       </c>
       <c r="D7" t="n">
-        <v>2.368395583136281</v>
+        <v>2.351138829860585</v>
       </c>
       <c r="E7" t="n">
-        <v>2.673312701795294</v>
+        <v>2.656332948209083</v>
       </c>
       <c r="F7" t="n">
-        <v>2.800455291983878</v>
+        <v>2.78240633839362</v>
       </c>
       <c r="G7" t="n">
-        <v>2.208992139383309</v>
+        <v>2.190989296296478</v>
       </c>
       <c r="H7" t="n">
-        <v>2.27437520837144</v>
+        <v>2.25672222827383</v>
       </c>
       <c r="I7" t="n">
-        <v>2.469793238324326</v>
+        <v>2.452837023706329</v>
       </c>
       <c r="J7" t="n">
-        <v>2.296240863159556</v>
+        <v>2.279240012722695</v>
       </c>
       <c r="K7" t="n">
-        <v>2.34196703534617</v>
+        <v>2.324281323675013</v>
       </c>
       <c r="L7" t="n">
-        <v>2.37232769638948</v>
+        <v>2.360081742428995</v>
       </c>
       <c r="M7" t="n">
-        <v>2.40635649104117</v>
+        <v>2.392915657678524</v>
       </c>
       <c r="N7" t="n">
-        <v>2.201790705681285</v>
+        <v>2.630435288418834</v>
       </c>
       <c r="O7" t="n">
-        <v>2.242043805871095</v>
+        <v>2.224582759550136</v>
       </c>
       <c r="P7" t="n">
-        <v>2.294353473191069</v>
+        <v>2.278057340086883</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.19301130103816</v>
+        <v>2.175301162786019</v>
       </c>
       <c r="R7" t="n">
-        <v>2.369751957170715</v>
+        <v>2.352689670038311</v>
       </c>
       <c r="S7" t="n">
-        <v>2.438788190985159</v>
+        <v>2.421392130548613</v>
       </c>
       <c r="T7" t="n">
-        <v>2.223692112262092</v>
+        <v>2.206273087907683</v>
       </c>
       <c r="U7" t="n">
-        <v>2.271162786600727</v>
+        <v>2.258173411432769</v>
       </c>
       <c r="V7" t="n">
-        <v>2.294797244223169</v>
+        <v>2.277294432074018</v>
       </c>
       <c r="W7" t="n">
-        <v>2.272138244439411</v>
+        <v>2.255221243342378</v>
       </c>
       <c r="X7" t="n">
-        <v>2.313860931694407</v>
+        <v>2.296829706134718</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.230547784614638</v>
+        <v>2.212975719750809</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.21903694303561</v>
+        <v>2.202054575268632</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.383101832651031</v>
+        <v>2.367163887605957</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.317566426928074</v>
+        <v>2.303065444776121</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.192109092566989</v>
+        <v>2.175119750331866</v>
       </c>
       <c r="C8" t="n">
-        <v>2.793837664507977</v>
+        <v>2.774164310351534</v>
       </c>
       <c r="D8" t="n">
-        <v>2.437169838697786</v>
+        <v>2.417904203334972</v>
       </c>
       <c r="E8" t="n">
-        <v>2.711786593162925</v>
+        <v>2.693690520037887</v>
       </c>
       <c r="F8" t="n">
-        <v>2.821189474916212</v>
+        <v>2.802546763140627</v>
       </c>
       <c r="G8" t="n">
-        <v>2.289566068133097</v>
+        <v>2.269206758147855</v>
       </c>
       <c r="H8" t="n">
-        <v>2.343149463932946</v>
+        <v>2.323487601748214</v>
       </c>
       <c r="I8" t="n">
-        <v>2.538567493885833</v>
+        <v>2.519602397180713</v>
       </c>
       <c r="J8" t="n">
-        <v>2.365015118721063</v>
+        <v>2.34600538619708</v>
       </c>
       <c r="K8" t="n">
-        <v>2.410741290907677</v>
+        <v>2.391046697149397</v>
       </c>
       <c r="L8" t="n">
-        <v>2.441101951950986</v>
+        <v>2.426847115903383</v>
       </c>
       <c r="M8" t="n">
-        <v>2.475130746602673</v>
+        <v>2.459681031152895</v>
       </c>
       <c r="N8" t="n">
-        <v>2.226453876570699</v>
+        <v>2.630435288418834</v>
       </c>
       <c r="O8" t="n">
-        <v>2.278833888291182</v>
+        <v>2.260306240436872</v>
       </c>
       <c r="P8" t="n">
-        <v>2.328172133765834</v>
+        <v>2.310896928764908</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.193697132536873</v>
+        <v>2.175983803511404</v>
       </c>
       <c r="R8" t="n">
-        <v>2.438526212732223</v>
+        <v>2.419455043512694</v>
       </c>
       <c r="S8" t="n">
-        <v>2.507562446546666</v>
+        <v>2.488157504022997</v>
       </c>
       <c r="T8" t="n">
-        <v>2.292466367823599</v>
+        <v>2.273038461382068</v>
       </c>
       <c r="U8" t="n">
-        <v>2.312157921938736</v>
+        <v>2.297982733601045</v>
       </c>
       <c r="V8" t="n">
-        <v>2.348053507886693</v>
+        <v>2.328981238539618</v>
       </c>
       <c r="W8" t="n">
-        <v>2.340923683506941</v>
+        <v>2.32199747088563</v>
       </c>
       <c r="X8" t="n">
-        <v>2.319762241937767</v>
+        <v>2.302574192433255</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.355956022565331</v>
+        <v>2.334679360787861</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.229848909777524</v>
+        <v>2.212565064093594</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.451876088212536</v>
+        <v>2.433929261080344</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.445782968897213</v>
+        <v>2.42752210396601</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.616127213739273</v>
+        <v>2.599897920836224</v>
       </c>
       <c r="C9" t="n">
-        <v>3.302983151523256</v>
+        <v>3.285226708743663</v>
       </c>
       <c r="D9" t="n">
-        <v>2.946315325713066</v>
+        <v>2.928966601727101</v>
       </c>
       <c r="E9" t="n">
-        <v>3.218451869265313</v>
+        <v>3.201500020732532</v>
       </c>
       <c r="F9" t="n">
-        <v>3.050951150323763</v>
+        <v>3.034007596602642</v>
       </c>
       <c r="G9" t="n">
-        <v>2.786911845640255</v>
+        <v>2.768817030930528</v>
       </c>
       <c r="H9" t="n">
-        <v>2.852294950948226</v>
+        <v>2.834550000140341</v>
       </c>
       <c r="I9" t="n">
-        <v>3.04771298090111</v>
+        <v>3.030664795572844</v>
       </c>
       <c r="J9" t="n">
-        <v>2.87416060573634</v>
+        <v>2.857067784589211</v>
       </c>
       <c r="K9" t="n">
-        <v>2.919886777922955</v>
+        <v>2.902109095541527</v>
       </c>
       <c r="L9" t="n">
-        <v>2.950247438966262</v>
+        <v>2.93790951429551</v>
       </c>
       <c r="M9" t="n">
-        <v>2.984276233617954</v>
+        <v>2.970743429545041</v>
       </c>
       <c r="N9" t="n">
-        <v>2.77971044825807</v>
+        <v>2.630435288418834</v>
       </c>
       <c r="O9" t="n">
-        <v>2.867037723700237</v>
+        <v>2.849312551764913</v>
       </c>
       <c r="P9" t="n">
-        <v>2.92958417992782</v>
+        <v>2.912986485819985</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.770931007295103</v>
+        <v>2.75312889742007</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9476716997475</v>
+        <v>2.930517441904829</v>
       </c>
       <c r="S9" t="n">
-        <v>3.016707933561944</v>
+        <v>2.999219902415128</v>
       </c>
       <c r="T9" t="n">
-        <v>2.801611854838877</v>
+        <v>2.7841008597742</v>
       </c>
       <c r="U9" t="n">
-        <v>2.849046303883171</v>
+        <v>2.835986839569335</v>
       </c>
       <c r="V9" t="n">
-        <v>3.036619407257195</v>
+        <v>3.018425241085491</v>
       </c>
       <c r="W9" t="n">
-        <v>2.850057987016196</v>
+        <v>2.833049015208893</v>
       </c>
       <c r="X9" t="n">
-        <v>2.891780674271192</v>
+        <v>2.874657478001233</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.808467527191423</v>
+        <v>2.790803491617326</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.711323637074408</v>
+        <v>2.694562453028162</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.961021575227814</v>
+        <v>2.944991659472471</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.895486169504858</v>
+        <v>2.880893216642638</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.393946904007541</v>
+        <v>2.392994666761364</v>
       </c>
       <c r="C2" t="n">
-        <v>2.437024840396869</v>
+        <v>2.436133605672671</v>
       </c>
       <c r="D2" t="n">
-        <v>2.402833122741637</v>
+        <v>2.401887889804848</v>
       </c>
       <c r="E2" t="n">
-        <v>2.419920467322823</v>
+        <v>2.419108345779788</v>
       </c>
       <c r="F2" t="n">
-        <v>2.437009485476385</v>
+        <v>2.436212705762627</v>
       </c>
       <c r="G2" t="n">
-        <v>2.395647294897497</v>
+        <v>2.394692237645622</v>
       </c>
       <c r="H2" t="n">
-        <v>2.400024919331525</v>
+        <v>2.399094524801902</v>
       </c>
       <c r="I2" t="n">
-        <v>2.404913047501798</v>
+        <v>2.404015401308486</v>
       </c>
       <c r="J2" t="n">
-        <v>2.401477784952245</v>
+        <v>2.400545783728759</v>
       </c>
       <c r="K2" t="n">
-        <v>2.401471149942931</v>
+        <v>2.400537422184499</v>
       </c>
       <c r="L2" t="n">
-        <v>2.402682812610894</v>
+        <v>2.401748761633706</v>
       </c>
       <c r="M2" t="n">
-        <v>2.406165827872074</v>
+        <v>2.405237546350028</v>
       </c>
       <c r="N2" t="n">
-        <v>2.395631636600878</v>
+        <v>2.39468935802886</v>
       </c>
       <c r="O2" t="n">
-        <v>2.43344248996677</v>
+        <v>2.431562618381026</v>
       </c>
       <c r="P2" t="n">
-        <v>2.403320572559379</v>
+        <v>2.40240405185382</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.394339500758179</v>
+        <v>2.393397311144202</v>
       </c>
       <c r="R2" t="n">
-        <v>2.404298425676036</v>
+        <v>2.403397701374354</v>
       </c>
       <c r="S2" t="n">
-        <v>2.408789180754695</v>
+        <v>2.407861221116392</v>
       </c>
       <c r="T2" t="n">
-        <v>2.396689940289664</v>
+        <v>2.395766817995331</v>
       </c>
       <c r="U2" t="n">
-        <v>2.433372593247965</v>
+        <v>2.431605690001691</v>
       </c>
       <c r="V2" t="n">
-        <v>2.402086726144977</v>
+        <v>2.401161660928755</v>
       </c>
       <c r="W2" t="n">
-        <v>2.435790549339984</v>
+        <v>2.433778612366674</v>
       </c>
       <c r="X2" t="n">
-        <v>2.404098570796534</v>
+        <v>2.403176446932317</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.397068509691871</v>
+        <v>2.39613305288292</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.414026497208085</v>
+        <v>2.412216495057383</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.400965903504269</v>
+        <v>2.400029953974842</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.402043260253626</v>
+        <v>2.401112489812887</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.39247266594607</v>
+        <v>2.391500735382837</v>
       </c>
       <c r="C3" t="n">
-        <v>2.671801234697973</v>
+        <v>2.671274235270132</v>
       </c>
       <c r="D3" t="n">
-        <v>2.455836793116688</v>
+        <v>2.454913424102697</v>
       </c>
       <c r="E3" t="n">
-        <v>2.577717960747926</v>
+        <v>2.577744795005074</v>
       </c>
       <c r="F3" t="n">
-        <v>2.699938981668902</v>
+        <v>2.700075527032632</v>
       </c>
       <c r="G3" t="n">
-        <v>2.404520671217626</v>
+        <v>2.403528338999614</v>
       </c>
       <c r="H3" t="n">
-        <v>2.436078091034101</v>
+        <v>2.435260680179947</v>
       </c>
       <c r="I3" t="n">
-        <v>2.470870983001037</v>
+        <v>2.470287634531326</v>
       </c>
       <c r="J3" t="n">
-        <v>2.446033839238289</v>
+        <v>2.44520529302014</v>
       </c>
       <c r="K3" t="n">
-        <v>2.445970501859845</v>
+        <v>2.445128810627193</v>
       </c>
       <c r="L3" t="n">
-        <v>2.454151526008678</v>
+        <v>2.453307219769471</v>
       </c>
       <c r="M3" t="n">
-        <v>2.479314026342677</v>
+        <v>2.478504591340397</v>
       </c>
       <c r="N3" t="n">
-        <v>2.40449435344672</v>
+        <v>2.403592703929947</v>
       </c>
       <c r="O3" t="n">
-        <v>2.488198814485624</v>
+        <v>2.485811310877656</v>
       </c>
       <c r="P3" t="n">
-        <v>2.459059888866415</v>
+        <v>2.458341710564173</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.395277857230511</v>
+        <v>2.394376812442784</v>
       </c>
       <c r="R3" t="n">
-        <v>2.466583061303305</v>
+        <v>2.46597803718885</v>
       </c>
       <c r="S3" t="n">
-        <v>2.497450143169754</v>
+        <v>2.49665006528146</v>
       </c>
       <c r="T3" t="n">
-        <v>2.41205975396988</v>
+        <v>2.411293869425605</v>
       </c>
       <c r="U3" t="n">
-        <v>2.497255232913287</v>
+        <v>2.495091415708906</v>
       </c>
       <c r="V3" t="n">
-        <v>2.450175018989079</v>
+        <v>2.449395179416743</v>
       </c>
       <c r="W3" t="n">
-        <v>2.490879703789658</v>
+        <v>2.488173504516686</v>
       </c>
       <c r="X3" t="n">
-        <v>2.464811842073144</v>
+        <v>2.46405347013769</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.41477311617456</v>
+        <v>2.413920133132809</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.43420572990988</v>
+        <v>2.431847783499503</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.442586123696638</v>
+        <v>2.441729675326958</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.450549868816112</v>
+        <v>2.449732005687201</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.104912158210644</v>
+        <v>2.092315257632959</v>
       </c>
       <c r="C4" t="n">
-        <v>2.534989713846242</v>
+        <v>2.523105218013931</v>
       </c>
       <c r="D4" t="n">
-        <v>2.205286086674831</v>
+        <v>2.192768302993838</v>
       </c>
       <c r="E4" t="n">
-        <v>2.398295504286203</v>
+        <v>2.387281275031917</v>
       </c>
       <c r="F4" t="n">
-        <v>2.591323825667421</v>
+        <v>2.580482889432424</v>
       </c>
       <c r="G4" t="n">
-        <v>2.124118855531141</v>
+        <v>2.111490101691841</v>
       </c>
       <c r="H4" t="n">
-        <v>2.173566137320225</v>
+        <v>2.16121596027417</v>
       </c>
       <c r="I4" t="n">
-        <v>2.228779793653507</v>
+        <v>2.216799524131072</v>
       </c>
       <c r="J4" t="n">
-        <v>2.190018865391091</v>
+        <v>2.177651613846193</v>
       </c>
       <c r="K4" t="n">
-        <v>2.189901977375007</v>
+        <v>2.177514149976203</v>
       </c>
       <c r="L4" t="n">
-        <v>2.203588264602022</v>
+        <v>2.191196786298667</v>
       </c>
       <c r="M4" t="n">
-        <v>2.243106274649899</v>
+        <v>2.230769260571412</v>
       </c>
       <c r="N4" t="n">
-        <v>2.123941987867656</v>
+        <v>2.566766782647715</v>
       </c>
       <c r="O4" t="n">
-        <v>2.168319266999168</v>
+        <v>2.155962484184635</v>
       </c>
       <c r="P4" t="n">
-        <v>2.210792056604227</v>
+        <v>2.198598590783241</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.109346719112533</v>
+        <v>2.096863311162684</v>
       </c>
       <c r="R4" t="n">
-        <v>2.221837357391519</v>
+        <v>2.209822319219042</v>
       </c>
       <c r="S4" t="n">
-        <v>2.272562501854387</v>
+        <v>2.260239828025886</v>
       </c>
       <c r="T4" t="n">
-        <v>2.135896014876252</v>
+        <v>2.123627981073181</v>
       </c>
       <c r="U4" t="n">
-        <v>2.188010317432326</v>
+        <v>2.175756036368576</v>
       </c>
       <c r="V4" t="n">
-        <v>2.197055135434374</v>
+        <v>2.18477240689915</v>
       </c>
       <c r="W4" t="n">
-        <v>2.165509273866759</v>
+        <v>2.152944815147938</v>
       </c>
       <c r="X4" t="n">
-        <v>2.219579904589764</v>
+        <v>2.207323148514163</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.140634167678189</v>
+        <v>2.128249954585968</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.12274345730974</v>
+        <v>2.110208599696772</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.184194986425481</v>
+        <v>2.171782063101212</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.19674694094144</v>
+        <v>2.18439690574498</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.24794173637769</v>
+        <v>2.229824065247112</v>
       </c>
       <c r="C5" t="n">
-        <v>9.65388740915518</v>
+        <v>9.647356187492923</v>
       </c>
       <c r="D5" t="n">
-        <v>3.993547300794976</v>
+        <v>3.976088629539057</v>
       </c>
       <c r="E5" t="n">
-        <v>7.369892785341383</v>
+        <v>7.379120555917693</v>
       </c>
       <c r="F5" t="n">
-        <v>10.91650310884392</v>
+        <v>10.92890763670037</v>
       </c>
       <c r="G5" t="n">
-        <v>2.542159666297153</v>
+        <v>2.523336036685596</v>
       </c>
       <c r="H5" t="n">
-        <v>3.579488736435257</v>
+        <v>3.565023334441089</v>
       </c>
       <c r="I5" t="n">
-        <v>4.507360418196137</v>
+        <v>4.499611500187205</v>
       </c>
       <c r="J5" t="n">
-        <v>3.655534863004857</v>
+        <v>3.640921441453488</v>
       </c>
       <c r="K5" t="n">
-        <v>3.645884608066343</v>
+        <v>3.630498870734936</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6461078638071</v>
+        <v>3.630497848670789</v>
       </c>
       <c r="M5" t="n">
-        <v>4.453129015320437</v>
+        <v>4.438228503152976</v>
       </c>
       <c r="N5" t="n">
-        <v>3.421665269874386</v>
+        <v>2.566766782647715</v>
       </c>
       <c r="O5" t="n">
-        <v>3.231404164794385</v>
+        <v>3.217029977688017</v>
       </c>
       <c r="P5" t="n">
-        <v>3.958337586836553</v>
+        <v>3.946754977387684</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.328037092827724</v>
+        <v>2.311499358437499</v>
       </c>
       <c r="R5" t="n">
-        <v>4.43570256964927</v>
+        <v>4.427490534013718</v>
       </c>
       <c r="S5" t="n">
-        <v>4.719458110618162</v>
+        <v>4.705455841324375</v>
       </c>
       <c r="T5" t="n">
-        <v>2.801073483803516</v>
+        <v>2.787866070246442</v>
       </c>
       <c r="U5" t="n">
-        <v>3.485271562185585</v>
+        <v>3.471602584617553</v>
       </c>
       <c r="V5" t="n">
-        <v>3.671180905098007</v>
+        <v>3.65754683026904</v>
       </c>
       <c r="W5" t="n">
-        <v>3.269720792370946</v>
+        <v>3.251763476359177</v>
       </c>
       <c r="X5" t="n">
-        <v>4.217068606849211</v>
+        <v>4.204261088801076</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.882659863269563</v>
+        <v>2.867472062316005</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.525540113221016</v>
+        <v>2.508388664414357</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.659780906362348</v>
+        <v>3.644521225493043</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.91632772560771</v>
+        <v>3.901785319498171</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.19821147700188</v>
+        <v>15.57442485238239</v>
       </c>
       <c r="C6" t="n">
-        <v>3.628289032637476</v>
+        <v>3.616928583613872</v>
       </c>
       <c r="D6" t="n">
-        <v>3.298585405466066</v>
+        <v>3.286591668593778</v>
       </c>
       <c r="E6" t="n">
-        <v>15.88000926266128</v>
+        <v>3.481104640631858</v>
       </c>
       <c r="F6" t="n">
-        <v>16.07303758404252</v>
+        <v>16.06259248418184</v>
       </c>
       <c r="G6" t="n">
-        <v>3.217418174322374</v>
+        <v>15.59359969644128</v>
       </c>
       <c r="H6" t="n">
-        <v>3.266865456111455</v>
+        <v>15.64332555502362</v>
       </c>
       <c r="I6" t="n">
-        <v>3.322079112444737</v>
+        <v>15.69890911888049</v>
       </c>
       <c r="J6" t="n">
-        <v>3.28331818418232</v>
+        <v>15.65976120859563</v>
       </c>
       <c r="K6" t="n">
-        <v>3.28320129616624</v>
+        <v>15.65962374472565</v>
       </c>
       <c r="L6" t="n">
-        <v>15.68530202297712</v>
+        <v>3.28502015189861</v>
       </c>
       <c r="M6" t="n">
-        <v>15.72482003302498</v>
+        <v>15.71287885532085</v>
       </c>
       <c r="N6" t="n">
-        <v>3.216045163513274</v>
+        <v>2.566766782647715</v>
       </c>
       <c r="O6" t="n">
-        <v>3.260422442644785</v>
+        <v>15.63708890348497</v>
       </c>
       <c r="P6" t="n">
-        <v>3.29999464721414</v>
+        <v>3.288321159965977</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.202646037903766</v>
+        <v>15.57897290591213</v>
       </c>
       <c r="R6" t="n">
-        <v>15.70355111576661</v>
+        <v>3.303645684818982</v>
       </c>
       <c r="S6" t="n">
-        <v>3.365861820645624</v>
+        <v>15.74234942277531</v>
       </c>
       <c r="T6" t="n">
-        <v>15.61760977325133</v>
+        <v>3.217451346673117</v>
       </c>
       <c r="U6" t="n">
-        <v>3.28084759897009</v>
+        <v>3.269094219987429</v>
       </c>
       <c r="V6" t="n">
-        <v>15.67876889380947</v>
+        <v>3.278595772499092</v>
       </c>
       <c r="W6" t="n">
-        <v>3.260088974569234</v>
+        <v>3.248030761877773</v>
       </c>
       <c r="X6" t="n">
-        <v>3.312879223381</v>
+        <v>15.6894327432636</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.250656349822597</v>
+        <v>3.238756191632721</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.60445721568483</v>
+        <v>3.204031965296721</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.66590874480056</v>
+        <v>15.65389165785065</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.288949240237654</v>
+        <v>3.277109589338555</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.167221347359566</v>
+        <v>2.152737291977064</v>
       </c>
       <c r="C7" t="n">
-        <v>2.597298902995166</v>
+        <v>2.583527252358035</v>
       </c>
       <c r="D7" t="n">
-        <v>2.267595275823754</v>
+        <v>2.253190337337942</v>
       </c>
       <c r="E7" t="n">
-        <v>2.460604693435126</v>
+        <v>2.447703309376022</v>
       </c>
       <c r="F7" t="n">
-        <v>2.653633014816345</v>
+        <v>2.640904923776528</v>
       </c>
       <c r="G7" t="n">
-        <v>2.186428044680063</v>
+        <v>2.171912136035946</v>
       </c>
       <c r="H7" t="n">
-        <v>2.235875326469147</v>
+        <v>2.221637994618275</v>
       </c>
       <c r="I7" t="n">
-        <v>2.29108898280243</v>
+        <v>2.277221558475177</v>
       </c>
       <c r="J7" t="n">
-        <v>2.252328054540013</v>
+        <v>2.238073648190298</v>
       </c>
       <c r="K7" t="n">
-        <v>2.252211166523929</v>
+        <v>2.237936184320308</v>
       </c>
       <c r="L7" t="n">
-        <v>2.265897453750943</v>
+        <v>2.251618820642772</v>
       </c>
       <c r="M7" t="n">
-        <v>2.305415463798821</v>
+        <v>2.291191294915517</v>
       </c>
       <c r="N7" t="n">
-        <v>2.186251177016579</v>
+        <v>2.566766782647715</v>
       </c>
       <c r="O7" t="n">
-        <v>2.23062399727295</v>
+        <v>2.216380084083682</v>
       </c>
       <c r="P7" t="n">
-        <v>2.273096786878009</v>
+        <v>2.259016190682289</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.171655908261456</v>
+        <v>2.15728534550679</v>
       </c>
       <c r="R7" t="n">
-        <v>2.284146546540442</v>
+        <v>2.270244353563147</v>
       </c>
       <c r="S7" t="n">
-        <v>2.334871691003309</v>
+        <v>2.320661862369991</v>
       </c>
       <c r="T7" t="n">
-        <v>2.198205204025174</v>
+        <v>2.184050015417287</v>
       </c>
       <c r="U7" t="n">
-        <v>2.249897799376972</v>
+        <v>2.235710168623578</v>
       </c>
       <c r="V7" t="n">
-        <v>2.259364324583296</v>
+        <v>2.245194441243254</v>
       </c>
       <c r="W7" t="n">
-        <v>2.22781846301568</v>
+        <v>2.213366849492043</v>
       </c>
       <c r="X7" t="n">
-        <v>2.281889093738685</v>
+        <v>2.267745182858267</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.202481319573641</v>
+        <v>2.188186806948986</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.185052646458662</v>
+        <v>2.170630634040877</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.246504175574404</v>
+        <v>2.232204097445317</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.259056130090362</v>
+        <v>2.244818940089085</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.176620982121344</v>
+        <v>2.161601070819474</v>
       </c>
       <c r="C8" t="n">
-        <v>2.657397126279549</v>
+        <v>2.641189974906062</v>
       </c>
       <c r="D8" t="n">
-        <v>2.327693499108136</v>
+        <v>2.310853059885969</v>
       </c>
       <c r="E8" t="n">
-        <v>2.493707413847042</v>
+        <v>2.479382033881176</v>
       </c>
       <c r="F8" t="n">
-        <v>2.670930897142545</v>
+        <v>2.657371007722298</v>
       </c>
       <c r="G8" t="n">
-        <v>2.257038950564884</v>
+        <v>2.239693637456343</v>
       </c>
       <c r="H8" t="n">
-        <v>2.295973549753528</v>
+        <v>2.279300717166301</v>
       </c>
       <c r="I8" t="n">
-        <v>2.35118720608681</v>
+        <v>2.334884281023203</v>
       </c>
       <c r="J8" t="n">
-        <v>2.312426277824394</v>
+        <v>2.295736370738323</v>
       </c>
       <c r="K8" t="n">
-        <v>2.31230938980831</v>
+        <v>2.295598906868334</v>
       </c>
       <c r="L8" t="n">
-        <v>2.325995677035323</v>
+        <v>2.309281543190797</v>
       </c>
       <c r="M8" t="n">
-        <v>2.365513687083203</v>
+        <v>2.348854017463542</v>
       </c>
       <c r="N8" t="n">
-        <v>2.207049512505724</v>
+        <v>2.566766782647715</v>
       </c>
       <c r="O8" t="n">
-        <v>2.262226742036229</v>
+        <v>2.246615178740711</v>
       </c>
       <c r="P8" t="n">
-        <v>2.302052202835361</v>
+        <v>2.286703150310052</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.171092113241103</v>
+        <v>2.156559018131584</v>
       </c>
       <c r="R8" t="n">
-        <v>2.344244769824824</v>
+        <v>2.327907076111172</v>
       </c>
       <c r="S8" t="n">
-        <v>2.394969914287691</v>
+        <v>2.378324584918016</v>
       </c>
       <c r="T8" t="n">
-        <v>2.258303427309556</v>
+        <v>2.241712737965312</v>
       </c>
       <c r="U8" t="n">
-        <v>2.285245098534895</v>
+        <v>2.269554326243159</v>
       </c>
       <c r="V8" t="n">
-        <v>2.305644143643244</v>
+        <v>2.289538237551176</v>
       </c>
       <c r="W8" t="n">
-        <v>2.287926650020803</v>
+        <v>2.271039162423814</v>
       </c>
       <c r="X8" t="n">
-        <v>2.285971925093202</v>
+        <v>2.271491375634358</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.31304737470351</v>
+        <v>2.294397996431255</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.193510528910424</v>
+        <v>2.178587947451282</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.306602398858785</v>
+        <v>2.289866819993343</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.37211326842919</v>
+        <v>2.353456239832205</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.516261016951801</v>
+        <v>2.502000737482523</v>
       </c>
       <c r="C9" t="n">
-        <v>3.062334514839456</v>
+        <v>3.048169893158228</v>
       </c>
       <c r="D9" t="n">
-        <v>2.732630887668042</v>
+        <v>2.717832978138132</v>
       </c>
       <c r="E9" t="n">
-        <v>2.898868895440077</v>
+        <v>2.88571688289022</v>
       </c>
       <c r="F9" t="n">
-        <v>2.851266354573941</v>
+        <v>2.839567062771328</v>
       </c>
       <c r="G9" t="n">
-        <v>2.651463631165174</v>
+        <v>2.636554751309593</v>
       </c>
       <c r="H9" t="n">
-        <v>2.700910938313433</v>
+        <v>2.686280635418467</v>
       </c>
       <c r="I9" t="n">
-        <v>2.756124594646717</v>
+        <v>2.741864199275368</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7173636663843</v>
+        <v>2.70271628899049</v>
       </c>
       <c r="K9" t="n">
-        <v>2.717246778368215</v>
+        <v>2.702578825120499</v>
       </c>
       <c r="L9" t="n">
-        <v>2.730933065595231</v>
+        <v>2.716261461442961</v>
       </c>
       <c r="M9" t="n">
-        <v>2.770451075643106</v>
+        <v>2.755833935715709</v>
       </c>
       <c r="N9" t="n">
-        <v>2.651286788860865</v>
+        <v>2.566766782647715</v>
       </c>
       <c r="O9" t="n">
-        <v>2.734104937607966</v>
+        <v>2.719263639587593</v>
       </c>
       <c r="P9" t="n">
-        <v>2.784937962335097</v>
+        <v>2.77021553016627</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.636691494746566</v>
+        <v>2.621927960780435</v>
       </c>
       <c r="R9" t="n">
-        <v>2.749182158384731</v>
+        <v>2.734886994363336</v>
       </c>
       <c r="S9" t="n">
-        <v>2.799907302847597</v>
+        <v>2.785304503170184</v>
       </c>
       <c r="T9" t="n">
-        <v>2.663240815869462</v>
+        <v>2.648692656217476</v>
       </c>
       <c r="U9" t="n">
-        <v>2.714893081172065</v>
+        <v>2.700335529531784</v>
       </c>
       <c r="V9" t="n">
-        <v>2.858256646666222</v>
+        <v>2.8429820800119</v>
       </c>
       <c r="W9" t="n">
-        <v>2.692854074859969</v>
+        <v>2.678009490292234</v>
       </c>
       <c r="X9" t="n">
-        <v>2.746924705582969</v>
+        <v>2.732387823658458</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.667516931417928</v>
+        <v>2.652829447749176</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.580153009816793</v>
+        <v>2.565709869860436</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.711539787418693</v>
+        <v>2.696846738245508</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.72409174193465</v>
+        <v>2.709461580889275</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.389682119776527</v>
+        <v>2.388592647785057</v>
       </c>
       <c r="C2" t="n">
-        <v>2.428297860628664</v>
+        <v>2.427284894164103</v>
       </c>
       <c r="D2" t="n">
-        <v>2.396651209166582</v>
+        <v>2.395585724985056</v>
       </c>
       <c r="E2" t="n">
-        <v>2.400639535542123</v>
+        <v>2.399617950438288</v>
       </c>
       <c r="F2" t="n">
-        <v>2.425941249772477</v>
+        <v>2.424980201278661</v>
       </c>
       <c r="G2" t="n">
-        <v>2.390308544757525</v>
+        <v>2.389232245394572</v>
       </c>
       <c r="H2" t="n">
-        <v>2.394227884962982</v>
+        <v>2.393157187218496</v>
       </c>
       <c r="I2" t="n">
-        <v>2.394516045220629</v>
+        <v>2.393451902210811</v>
       </c>
       <c r="J2" t="n">
-        <v>2.395116119213768</v>
+        <v>2.394048659843483</v>
       </c>
       <c r="K2" t="n">
-        <v>2.394149684728235</v>
+        <v>2.393073703991619</v>
       </c>
       <c r="L2" t="n">
-        <v>2.397279919924815</v>
+        <v>2.396221702564189</v>
       </c>
       <c r="M2" t="n">
-        <v>2.398206249682967</v>
+        <v>2.397133883004428</v>
       </c>
       <c r="N2" t="n">
-        <v>2.390423578373515</v>
+        <v>2.389347891231623</v>
       </c>
       <c r="O2" t="n">
-        <v>2.426626745873999</v>
+        <v>2.424518273979581</v>
       </c>
       <c r="P2" t="n">
-        <v>2.398061501905873</v>
+        <v>2.397017729203362</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.389594234980989</v>
+        <v>2.38851943284325</v>
       </c>
       <c r="R2" t="n">
-        <v>2.396224405866904</v>
+        <v>2.395173716769923</v>
       </c>
       <c r="S2" t="n">
-        <v>2.400720181703127</v>
+        <v>2.399673722659565</v>
       </c>
       <c r="T2" t="n">
-        <v>2.391784694573607</v>
+        <v>2.390718534059106</v>
       </c>
       <c r="U2" t="n">
-        <v>2.427227936443144</v>
+        <v>2.424859841412913</v>
       </c>
       <c r="V2" t="n">
-        <v>2.395155130558781</v>
+        <v>2.39408822686025</v>
       </c>
       <c r="W2" t="n">
-        <v>2.428511479847756</v>
+        <v>2.42582683615824</v>
       </c>
       <c r="X2" t="n">
-        <v>2.397587577339094</v>
+        <v>2.396529931080176</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.391695522242911</v>
+        <v>2.390622317612847</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.408077700357538</v>
+        <v>2.406071023236945</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.392197993951685</v>
+        <v>2.391116461137397</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.393884276027314</v>
+        <v>2.39282155271073</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.389897658001733</v>
+        <v>2.388779985354412</v>
       </c>
       <c r="C3" t="n">
-        <v>2.638137123063468</v>
+        <v>2.637647545748767</v>
       </c>
       <c r="D3" t="n">
-        <v>2.439660748545026</v>
+        <v>2.4387128034635</v>
       </c>
       <c r="E3" t="n">
-        <v>2.467793110752786</v>
+        <v>2.467157528930707</v>
       </c>
       <c r="F3" t="n">
-        <v>2.649184329543241</v>
+        <v>2.648983174989455</v>
       </c>
       <c r="G3" t="n">
-        <v>2.394347761048433</v>
+        <v>2.393323299864142</v>
       </c>
       <c r="H3" t="n">
-        <v>2.422512700771601</v>
+        <v>2.421527272071342</v>
       </c>
       <c r="I3" t="n">
-        <v>2.424506615998572</v>
+        <v>2.423568373808191</v>
       </c>
       <c r="J3" t="n">
-        <v>2.428629199864573</v>
+        <v>2.427667545803387</v>
       </c>
       <c r="K3" t="n">
-        <v>2.421746019487498</v>
+        <v>2.420723197456427</v>
       </c>
       <c r="L3" t="n">
-        <v>2.443703846359452</v>
+        <v>2.442807063879219</v>
       </c>
       <c r="M3" t="n">
-        <v>2.450822533729553</v>
+        <v>2.449818571568446</v>
       </c>
       <c r="N3" t="n">
-        <v>2.395210056247218</v>
+        <v>2.394189777096645</v>
       </c>
       <c r="O3" t="n">
-        <v>2.475666734324332</v>
+        <v>2.472996963846885</v>
       </c>
       <c r="P3" t="n">
-        <v>2.449339186397482</v>
+        <v>2.448545775895623</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.389292803520196</v>
+        <v>2.388278828956764</v>
       </c>
       <c r="R3" t="n">
-        <v>2.436791703481189</v>
+        <v>2.435949806819071</v>
       </c>
       <c r="S3" t="n">
-        <v>2.46820424325549</v>
+        <v>2.467391751102494</v>
       </c>
       <c r="T3" t="n">
-        <v>2.404951979557563</v>
+        <v>2.403999252407788</v>
       </c>
       <c r="U3" t="n">
-        <v>2.482308699286245</v>
+        <v>2.479240076609146</v>
       </c>
       <c r="V3" t="n">
-        <v>2.428743527023522</v>
+        <v>2.427785623305987</v>
       </c>
       <c r="W3" t="n">
-        <v>2.468461127233638</v>
+        <v>2.464508883005823</v>
       </c>
       <c r="X3" t="n">
-        <v>2.446191968167395</v>
+        <v>2.445299924555049</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.404303007039526</v>
+        <v>2.403300487202289</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.421961250156035</v>
+        <v>2.419359231879</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.407879496785526</v>
+        <v>2.406817538218212</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.42032507183703</v>
+        <v>2.419398345944749</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.100896341790532</v>
+        <v>2.090060955874822</v>
       </c>
       <c r="C4" t="n">
-        <v>2.481689050299104</v>
+        <v>2.471890726514805</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179615412390708</v>
+        <v>2.169050979823256</v>
       </c>
       <c r="E4" t="n">
-        <v>2.224665393523221</v>
+        <v>2.214596821232865</v>
       </c>
       <c r="F4" t="n">
-        <v>2.510459895118666</v>
+        <v>2.501075111686674</v>
       </c>
       <c r="G4" t="n">
-        <v>2.107972100120631</v>
+        <v>2.097285505103729</v>
       </c>
       <c r="H4" t="n">
-        <v>2.152242850726841</v>
+        <v>2.141619528567395</v>
       </c>
       <c r="I4" t="n">
-        <v>2.155497753397225</v>
+        <v>2.144948469981178</v>
       </c>
       <c r="J4" t="n">
-        <v>2.162312629720689</v>
+        <v>2.151726425552898</v>
       </c>
       <c r="K4" t="n">
-        <v>2.151359543101481</v>
+        <v>2.140676547115633</v>
       </c>
       <c r="L4" t="n">
-        <v>2.18671698962619</v>
+        <v>2.176234639143704</v>
       </c>
       <c r="M4" t="n">
-        <v>2.197378505726233</v>
+        <v>2.186724209373637</v>
       </c>
       <c r="N4" t="n">
-        <v>2.109271457731314</v>
+        <v>2.413112687863385</v>
       </c>
       <c r="O4" t="n">
-        <v>2.152357316381387</v>
+        <v>2.141791443596902</v>
       </c>
       <c r="P4" t="n">
-        <v>2.195545317647714</v>
+        <v>2.185226126223506</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.099903642595929</v>
+        <v>2.089233959426566</v>
       </c>
       <c r="R4" t="n">
-        <v>2.174794472781624</v>
+        <v>2.164397157500185</v>
       </c>
       <c r="S4" t="n">
-        <v>2.225576329010837</v>
+        <v>2.215226794128681</v>
       </c>
       <c r="T4" t="n">
-        <v>2.124645891355734</v>
+        <v>2.114073819296213</v>
       </c>
       <c r="U4" t="n">
-        <v>2.164461735357583</v>
+        <v>2.153936658203811</v>
       </c>
       <c r="V4" t="n">
-        <v>2.162880211223769</v>
+        <v>2.152303384338526</v>
       </c>
       <c r="W4" t="n">
-        <v>2.130721969044455</v>
+        <v>2.119472331732764</v>
       </c>
       <c r="X4" t="n">
-        <v>2.190192121649865</v>
+        <v>2.179716222023892</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.124008364134629</v>
+        <v>2.113334705738148</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.104432725951224</v>
+        <v>2.093658562314137</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.129314297958237</v>
+        <v>2.11856858870099</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.148892146226812</v>
+        <v>2.138361691765464</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.268960927685448</v>
+        <v>2.252083345558275</v>
       </c>
       <c r="C5" t="n">
-        <v>8.912578589692437</v>
+        <v>8.913066318287189</v>
       </c>
       <c r="D5" t="n">
-        <v>3.673857469839385</v>
+        <v>3.661007955325526</v>
       </c>
       <c r="E5" t="n">
-        <v>4.298319638719938</v>
+        <v>4.293749655869026</v>
       </c>
       <c r="F5" t="n">
-        <v>9.773670059464797</v>
+        <v>9.782424517134491</v>
       </c>
       <c r="G5" t="n">
-        <v>2.383368079140309</v>
+        <v>2.368706367266729</v>
       </c>
       <c r="H5" t="n">
-        <v>3.266082671389222</v>
+        <v>3.252049520798748</v>
       </c>
       <c r="I5" t="n">
-        <v>3.291158880320139</v>
+        <v>3.278645129730962</v>
       </c>
       <c r="J5" t="n">
-        <v>3.328071545779328</v>
+        <v>3.315029061804666</v>
       </c>
       <c r="K5" t="n">
-        <v>3.142377782395708</v>
+        <v>3.127450705082228</v>
       </c>
       <c r="L5" t="n">
-        <v>3.569346950758144</v>
+        <v>3.557585885872454</v>
       </c>
       <c r="M5" t="n">
-        <v>3.965069729150113</v>
+        <v>3.950470286172633</v>
       </c>
       <c r="N5" t="n">
-        <v>3.19781031537218</v>
+        <v>2.413112687863385</v>
       </c>
       <c r="O5" t="n">
-        <v>3.070241100834594</v>
+        <v>3.057633672085279</v>
       </c>
       <c r="P5" t="n">
-        <v>3.755107286642191</v>
+        <v>3.746376923641908</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.263003182526381</v>
+        <v>2.248537380073234</v>
       </c>
       <c r="R5" t="n">
-        <v>3.680353947702267</v>
+        <v>3.67069605508746</v>
       </c>
       <c r="S5" t="n">
-        <v>4.229212527818206</v>
+        <v>4.219992596726855</v>
       </c>
       <c r="T5" t="n">
-        <v>2.713958450904939</v>
+        <v>2.700997115589991</v>
       </c>
       <c r="U5" t="n">
-        <v>3.252630877723059</v>
+        <v>3.240711509800616</v>
       </c>
       <c r="V5" t="n">
-        <v>3.250952093228308</v>
+        <v>3.237912037102858</v>
       </c>
       <c r="W5" t="n">
-        <v>2.787027791173518</v>
+        <v>2.762698687525914</v>
       </c>
       <c r="X5" t="n">
-        <v>3.78231623238884</v>
+        <v>3.7710127857012</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.689642499756872</v>
+        <v>2.67552343286575</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.321478135387426</v>
+        <v>2.30564855112497</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.785011435323648</v>
+        <v>2.769228540155101</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.194633839511685</v>
+        <v>3.18238390443864</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.5779646539429</v>
+        <v>15.5674216317523</v>
       </c>
       <c r="C6" t="n">
-        <v>15.95875736245147</v>
+        <v>15.94925140239225</v>
       </c>
       <c r="D6" t="n">
-        <v>15.65668372454305</v>
+        <v>15.64641165570074</v>
       </c>
       <c r="E6" t="n">
-        <v>15.70173370567557</v>
+        <v>3.30531658831003</v>
       </c>
       <c r="F6" t="n">
-        <v>15.98752820727101</v>
+        <v>15.97843578756416</v>
       </c>
       <c r="G6" t="n">
-        <v>15.585040412273</v>
+        <v>15.5746461809812</v>
       </c>
       <c r="H6" t="n">
-        <v>3.242499976037679</v>
+        <v>15.61898020444486</v>
       </c>
       <c r="I6" t="n">
-        <v>3.24575487870806</v>
+        <v>15.62230914585864</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25256975503153</v>
+        <v>3.242446192630061</v>
       </c>
       <c r="K6" t="n">
-        <v>15.62842785525383</v>
+        <v>3.231396314192793</v>
       </c>
       <c r="L6" t="n">
-        <v>15.66378530177853</v>
+        <v>15.65359531502117</v>
       </c>
       <c r="M6" t="n">
-        <v>15.67444681787859</v>
+        <v>15.66408488525109</v>
       </c>
       <c r="N6" t="n">
-        <v>3.199135545364193</v>
+        <v>2.413112687863385</v>
       </c>
       <c r="O6" t="n">
-        <v>15.6286253356743</v>
+        <v>3.232111949234068</v>
       </c>
       <c r="P6" t="n">
-        <v>15.67181382122084</v>
+        <v>15.66158023787241</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.57697195474829</v>
+        <v>15.56659463530405</v>
       </c>
       <c r="R6" t="n">
-        <v>3.265051598092469</v>
+        <v>15.64175783337765</v>
       </c>
       <c r="S6" t="n">
-        <v>3.315833454321672</v>
+        <v>15.69258747000618</v>
       </c>
       <c r="T6" t="n">
-        <v>15.60171420350809</v>
+        <v>3.204793586373376</v>
       </c>
       <c r="U6" t="n">
-        <v>15.64116033223455</v>
+        <v>15.63094963861709</v>
       </c>
       <c r="V6" t="n">
-        <v>3.253137336534613</v>
+        <v>3.24302315141569</v>
       </c>
       <c r="W6" t="n">
-        <v>15.60698930046567</v>
+        <v>15.59582280844969</v>
       </c>
       <c r="X6" t="n">
-        <v>3.280449246960701</v>
+        <v>3.270435989101057</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.23175748713626</v>
+        <v>3.221552143297163</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.194689851262066</v>
+        <v>3.184378329391294</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.219571423269074</v>
+        <v>15.59592926457845</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.238737309079043</v>
+        <v>3.228661247631275</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.161854472474956</v>
+        <v>2.149039554704811</v>
       </c>
       <c r="C7" t="n">
-        <v>2.54264718098353</v>
+        <v>2.530869325344793</v>
       </c>
       <c r="D7" t="n">
-        <v>2.240573543075132</v>
+        <v>2.228029578653246</v>
       </c>
       <c r="E7" t="n">
-        <v>2.285623524207645</v>
+        <v>2.273575420062854</v>
       </c>
       <c r="F7" t="n">
-        <v>2.571418025803088</v>
+        <v>2.560053710516663</v>
       </c>
       <c r="G7" t="n">
-        <v>2.168930230805055</v>
+        <v>2.156264103933718</v>
       </c>
       <c r="H7" t="n">
-        <v>2.213200981411264</v>
+        <v>2.200598127397384</v>
       </c>
       <c r="I7" t="n">
-        <v>2.21645588408165</v>
+        <v>2.203927068811166</v>
       </c>
       <c r="J7" t="n">
-        <v>2.223270760405113</v>
+        <v>2.210705024382888</v>
       </c>
       <c r="K7" t="n">
-        <v>2.212317673785904</v>
+        <v>2.199655145945622</v>
       </c>
       <c r="L7" t="n">
-        <v>2.247675120310614</v>
+        <v>2.235213237973693</v>
       </c>
       <c r="M7" t="n">
-        <v>2.258336636410657</v>
+        <v>2.245702808203626</v>
       </c>
       <c r="N7" t="n">
-        <v>2.170229588415738</v>
+        <v>2.413112687863385</v>
       </c>
       <c r="O7" t="n">
-        <v>2.2133110356498</v>
+        <v>2.200765658808405</v>
       </c>
       <c r="P7" t="n">
-        <v>2.256499036916126</v>
+        <v>2.244200341435009</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.160861773280352</v>
+        <v>2.148212558256554</v>
       </c>
       <c r="R7" t="n">
-        <v>2.235752603466048</v>
+        <v>2.223375756330173</v>
       </c>
       <c r="S7" t="n">
-        <v>2.28653445969526</v>
+        <v>2.274205392958671</v>
       </c>
       <c r="T7" t="n">
-        <v>2.185604022040158</v>
+        <v>2.173052418126202</v>
       </c>
       <c r="U7" t="n">
-        <v>2.225077226493251</v>
+        <v>2.212576268850723</v>
       </c>
       <c r="V7" t="n">
-        <v>2.223838341908194</v>
+        <v>2.211281983168514</v>
       </c>
       <c r="W7" t="n">
-        <v>2.191680099728879</v>
+        <v>2.178450930562752</v>
       </c>
       <c r="X7" t="n">
-        <v>2.251150252334289</v>
+        <v>2.238694820853881</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.184596779543661</v>
+        <v>2.171965609103944</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.165390856635647</v>
+        <v>2.152637161144126</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.190272428642661</v>
+        <v>2.177547187530978</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.209850276911236</v>
+        <v>2.197340290595453</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.169890137867076</v>
+        <v>2.156531347103623</v>
       </c>
       <c r="C8" t="n">
-        <v>2.599473499559658</v>
+        <v>2.585163884250809</v>
       </c>
       <c r="D8" t="n">
-        <v>2.297399861651262</v>
+        <v>2.282324137559261</v>
       </c>
       <c r="E8" t="n">
-        <v>2.31647025919852</v>
+        <v>2.302948886400404</v>
       </c>
       <c r="F8" t="n">
-        <v>2.587054704732403</v>
+        <v>2.574836826941236</v>
       </c>
       <c r="G8" t="n">
-        <v>2.235873609160108</v>
+        <v>2.22026352136618</v>
       </c>
       <c r="H8" t="n">
-        <v>2.270027299987395</v>
+        <v>2.254892686303401</v>
       </c>
       <c r="I8" t="n">
-        <v>2.273282202657779</v>
+        <v>2.258221627717182</v>
       </c>
       <c r="J8" t="n">
-        <v>2.280097078981242</v>
+        <v>2.264999583288903</v>
       </c>
       <c r="K8" t="n">
-        <v>2.269143992362034</v>
+        <v>2.253949704851638</v>
       </c>
       <c r="L8" t="n">
-        <v>2.304501438886744</v>
+        <v>2.289507796879708</v>
       </c>
       <c r="M8" t="n">
-        <v>2.315162954986793</v>
+        <v>2.299997367109652</v>
       </c>
       <c r="N8" t="n">
-        <v>2.189234988274684</v>
+        <v>2.413112687863385</v>
       </c>
       <c r="O8" t="n">
-        <v>2.242714363779452</v>
+        <v>2.228754679215432</v>
       </c>
       <c r="P8" t="n">
-        <v>2.283354662922365</v>
+        <v>2.269745461221424</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.159308961730864</v>
+        <v>2.146506538817548</v>
       </c>
       <c r="R8" t="n">
-        <v>2.292578922042178</v>
+        <v>2.27767031523619</v>
       </c>
       <c r="S8" t="n">
-        <v>2.343360778271389</v>
+        <v>2.328499951864686</v>
       </c>
       <c r="T8" t="n">
-        <v>2.242430340616287</v>
+        <v>2.227346977032218</v>
       </c>
       <c r="U8" t="n">
-        <v>2.258086804485079</v>
+        <v>2.244028459935142</v>
       </c>
       <c r="V8" t="n">
-        <v>2.267356353722464</v>
+        <v>2.252795830061059</v>
       </c>
       <c r="W8" t="n">
-        <v>2.24851600706184</v>
+        <v>2.23275468754724</v>
       </c>
       <c r="X8" t="n">
-        <v>2.254069201094789</v>
+        <v>2.241278367959924</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.289976278348412</v>
+        <v>2.272812448804924</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1725202105962</v>
+        <v>2.159259568127159</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.24709874721879</v>
+        <v>2.231841746436994</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.317642512541731</v>
+        <v>2.300524252695901</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.466966389457021</v>
+        <v>2.45436900089019</v>
       </c>
       <c r="C9" t="n">
-        <v>2.951153371868824</v>
+        <v>2.938938380463757</v>
       </c>
       <c r="D9" t="n">
-        <v>2.649079733960428</v>
+        <v>2.636098633772206</v>
       </c>
       <c r="E9" t="n">
-        <v>2.670266720727196</v>
+        <v>2.657932574716751</v>
       </c>
       <c r="F9" t="n">
-        <v>2.741572226379013</v>
+        <v>2.731279956932774</v>
       </c>
       <c r="G9" t="n">
-        <v>2.577436398697198</v>
+        <v>2.564333135924342</v>
       </c>
       <c r="H9" t="n">
-        <v>2.621707172296557</v>
+        <v>2.608667182516343</v>
       </c>
       <c r="I9" t="n">
-        <v>2.624962074966943</v>
+        <v>2.611996123930127</v>
       </c>
       <c r="J9" t="n">
-        <v>2.631776951290405</v>
+        <v>2.618774079501849</v>
       </c>
       <c r="K9" t="n">
-        <v>2.620823864671199</v>
+        <v>2.607724201064582</v>
       </c>
       <c r="L9" t="n">
-        <v>2.656181311195908</v>
+        <v>2.643282293092655</v>
       </c>
       <c r="M9" t="n">
-        <v>2.666842827295951</v>
+        <v>2.653771863322587</v>
       </c>
       <c r="N9" t="n">
-        <v>2.578735779301032</v>
+        <v>2.413112687863385</v>
       </c>
       <c r="O9" t="n">
-        <v>2.656086334326497</v>
+        <v>2.642886838627526</v>
       </c>
       <c r="P9" t="n">
-        <v>2.70672632417165</v>
+        <v>2.693726325808299</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.569367941172497</v>
+        <v>2.556281590247178</v>
       </c>
       <c r="R9" t="n">
-        <v>2.64425879435134</v>
+        <v>2.631444811449136</v>
       </c>
       <c r="S9" t="n">
-        <v>2.695040650580554</v>
+        <v>2.682274448077632</v>
       </c>
       <c r="T9" t="n">
-        <v>2.594110212925451</v>
+        <v>2.581121473245163</v>
       </c>
       <c r="U9" t="n">
-        <v>2.633556341651908</v>
+        <v>2.620636616688569</v>
       </c>
       <c r="V9" t="n">
-        <v>2.751659199456386</v>
+        <v>2.737910236282036</v>
       </c>
       <c r="W9" t="n">
-        <v>2.600186290614174</v>
+        <v>2.586519985681712</v>
       </c>
       <c r="X9" t="n">
-        <v>2.659656443219582</v>
+        <v>2.646763875972841</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.593102970428956</v>
+        <v>2.580034664222905</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.511559485404576</v>
+        <v>2.498763358854657</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.598778619527954</v>
+        <v>2.58561624264994</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.61835646779653</v>
+        <v>2.605409345714413</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.399860144523656</v>
+        <v>2.400139210731762</v>
       </c>
       <c r="C2" t="n">
-        <v>2.451667880151802</v>
+        <v>2.451155470962896</v>
       </c>
       <c r="D2" t="n">
-        <v>2.42990608014566</v>
+        <v>2.429825854941701</v>
       </c>
       <c r="E2" t="n">
-        <v>2.440879677847919</v>
+        <v>2.440686816564016</v>
       </c>
       <c r="F2" t="n">
-        <v>2.450170427623138</v>
+        <v>2.449806527997118</v>
       </c>
       <c r="G2" t="n">
-        <v>2.403740927222538</v>
+        <v>2.403354993244746</v>
       </c>
       <c r="H2" t="n">
-        <v>2.406790498056912</v>
+        <v>2.406425700587746</v>
       </c>
       <c r="I2" t="n">
-        <v>2.421419885929955</v>
+        <v>2.421137275119836</v>
       </c>
       <c r="J2" t="n">
-        <v>2.408439838142775</v>
+        <v>2.408340753814069</v>
       </c>
       <c r="K2" t="n">
-        <v>2.41243667811995</v>
+        <v>2.412105325025206</v>
       </c>
       <c r="L2" t="n">
-        <v>2.411658555752754</v>
+        <v>2.413205361138126</v>
       </c>
       <c r="M2" t="n">
-        <v>2.407513492804671</v>
+        <v>2.408326963266235</v>
       </c>
       <c r="N2" t="n">
-        <v>2.400873484560215</v>
+        <v>2.400486803946755</v>
       </c>
       <c r="O2" t="n">
-        <v>2.437425139740939</v>
+        <v>2.436384056184433</v>
       </c>
       <c r="P2" t="n">
-        <v>2.406295051983702</v>
+        <v>2.406416872939385</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.400429142449243</v>
+        <v>2.400118557879228</v>
       </c>
       <c r="R2" t="n">
-        <v>2.414660157665163</v>
+        <v>2.414388996774198</v>
       </c>
       <c r="S2" t="n">
-        <v>2.415311789268615</v>
+        <v>2.415341026968841</v>
       </c>
       <c r="T2" t="n">
-        <v>2.401695899268883</v>
+        <v>2.401423166786549</v>
       </c>
       <c r="U2" t="n">
-        <v>2.440454579154299</v>
+        <v>2.440200961689088</v>
       </c>
       <c r="V2" t="n">
-        <v>2.409418765136607</v>
+        <v>2.409179519438776</v>
       </c>
       <c r="W2" t="n">
-        <v>2.443574316731982</v>
+        <v>2.442450324560924</v>
       </c>
       <c r="X2" t="n">
-        <v>2.410227226700652</v>
+        <v>2.410478455489613</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.403670505529415</v>
+        <v>2.40351686644665</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.421776829109974</v>
+        <v>2.421261082482792</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.416813600839796</v>
+        <v>2.416698100730482</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.404577986089464</v>
+        <v>2.405397732987713</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.398756639740654</v>
+        <v>2.403133100611286</v>
       </c>
       <c r="C3" t="n">
-        <v>2.737308371297231</v>
+        <v>2.736942741323777</v>
       </c>
       <c r="D3" t="n">
-        <v>2.61388691726625</v>
+        <v>2.615727900190767</v>
       </c>
       <c r="E3" t="n">
-        <v>2.691417473823047</v>
+        <v>2.692447624593673</v>
       </c>
       <c r="F3" t="n">
-        <v>2.758707348857717</v>
+        <v>2.758517266046126</v>
       </c>
       <c r="G3" t="n">
-        <v>2.42631665707256</v>
+        <v>2.425968966407595</v>
       </c>
       <c r="H3" t="n">
-        <v>2.44853699006112</v>
+        <v>2.448340890300947</v>
       </c>
       <c r="I3" t="n">
-        <v>2.553137348098347</v>
+        <v>2.553529367803363</v>
       </c>
       <c r="J3" t="n">
-        <v>2.459909618280998</v>
+        <v>2.461604671205945</v>
       </c>
       <c r="K3" t="n">
-        <v>2.488259620751509</v>
+        <v>2.488299708495691</v>
       </c>
       <c r="L3" t="n">
-        <v>2.482796946439209</v>
+        <v>2.496213100081024</v>
       </c>
       <c r="M3" t="n">
-        <v>2.454176369023366</v>
+        <v>2.462318875449238</v>
       </c>
       <c r="N3" t="n">
-        <v>2.406026618166018</v>
+        <v>2.405673862318016</v>
       </c>
       <c r="O3" t="n">
-        <v>2.482063314998018</v>
+        <v>2.48180298610749</v>
       </c>
       <c r="P3" t="n">
-        <v>2.44452689604841</v>
+        <v>2.447791633771558</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.402848045152385</v>
+        <v>2.403038296490298</v>
       </c>
       <c r="R3" t="n">
-        <v>2.504913334112052</v>
+        <v>2.505388593105514</v>
       </c>
       <c r="S3" t="n">
-        <v>2.508353240549448</v>
+        <v>2.510950293245214</v>
       </c>
       <c r="T3" t="n">
-        <v>2.411939788971156</v>
+        <v>2.4124024835777</v>
       </c>
       <c r="U3" t="n">
-        <v>2.511818041284539</v>
+        <v>2.515562874540892</v>
       </c>
       <c r="V3" t="n">
-        <v>2.466599303285227</v>
+        <v>2.467292296303885</v>
       </c>
       <c r="W3" t="n">
-        <v>2.509702789742063</v>
+        <v>2.508491755935033</v>
       </c>
       <c r="X3" t="n">
-        <v>2.472923808572097</v>
+        <v>2.477132304249448</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.425963998992027</v>
+        <v>2.427273463681332</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.450727607485941</v>
+        <v>2.452447265800893</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.519788622010043</v>
+        <v>2.521371476142068</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.433600446470023</v>
+        <v>2.4418299174226</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.115089081395191</v>
+        <v>2.108608976631343</v>
       </c>
       <c r="C4" t="n">
-        <v>2.636290073385751</v>
+        <v>2.622684758614499</v>
       </c>
       <c r="D4" t="n">
-        <v>2.454471746058984</v>
+        <v>2.443933279513649</v>
       </c>
       <c r="E4" t="n">
-        <v>2.578423580210357</v>
+        <v>2.56661283732689</v>
       </c>
       <c r="F4" t="n">
-        <v>2.683366872877499</v>
+        <v>2.669624173238305</v>
       </c>
       <c r="G4" t="n">
-        <v>2.158924307227309</v>
+        <v>2.144932719448536</v>
       </c>
       <c r="H4" t="n">
-        <v>2.193370612673458</v>
+        <v>2.179617771482894</v>
       </c>
       <c r="I4" t="n">
-        <v>2.358616278550392</v>
+        <v>2.345791773481496</v>
       </c>
       <c r="J4" t="n">
-        <v>2.212029990504045</v>
+        <v>2.201279553030734</v>
       </c>
       <c r="K4" t="n">
-        <v>2.257146813856618</v>
+        <v>2.243771742260328</v>
       </c>
       <c r="L4" t="n">
-        <v>2.24835756376517</v>
+        <v>2.256197156197378</v>
       </c>
       <c r="M4" t="n">
-        <v>2.203020072021298</v>
+        <v>2.202468151893692</v>
       </c>
       <c r="N4" t="n">
-        <v>2.126535223267565</v>
+        <v>2.55144311233155</v>
       </c>
       <c r="O4" t="n">
-        <v>2.159288585890563</v>
+        <v>2.147722405317159</v>
       </c>
       <c r="P4" t="n">
-        <v>2.187774321360089</v>
+        <v>2.179518059133748</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.121516174716668</v>
+        <v>2.108375693161187</v>
       </c>
       <c r="R4" t="n">
-        <v>2.282262038170921</v>
+        <v>2.269566865206103</v>
       </c>
       <c r="S4" t="n">
-        <v>2.289622516897268</v>
+        <v>2.280320484210123</v>
       </c>
       <c r="T4" t="n">
-        <v>2.135824775731438</v>
+        <v>2.123111850919138</v>
       </c>
       <c r="U4" t="n">
-        <v>2.210417764542426</v>
+        <v>2.204372183774381</v>
       </c>
       <c r="V4" t="n">
-        <v>2.223173561187403</v>
+        <v>2.210846023278775</v>
       </c>
       <c r="W4" t="n">
-        <v>2.194879489778724</v>
+        <v>2.181617776892622</v>
       </c>
       <c r="X4" t="n">
-        <v>2.232190043677788</v>
+        <v>2.225395502458848</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.158450150437276</v>
+        <v>2.147034300156727</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.147781757263533</v>
+        <v>2.138513054324449</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.306586169461203</v>
+        <v>2.295649256632633</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.170068129297865</v>
+        <v>2.169559693596572</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.329346915498973</v>
+        <v>2.443853077843693</v>
       </c>
       <c r="C5" t="n">
-        <v>12.2834608692371</v>
+        <v>12.2755169757183</v>
       </c>
       <c r="D5" t="n">
-        <v>9.130628177965933</v>
+        <v>9.184417950449363</v>
       </c>
       <c r="E5" t="n">
-        <v>11.03573970372593</v>
+        <v>11.06161212271707</v>
       </c>
       <c r="F5" t="n">
-        <v>13.56576675361609</v>
+        <v>13.55537442035458</v>
       </c>
       <c r="G5" t="n">
-        <v>3.081807098432753</v>
+        <v>3.066515501084314</v>
       </c>
       <c r="H5" t="n">
-        <v>3.986382904568297</v>
+        <v>3.976016272862462</v>
       </c>
       <c r="I5" t="n">
-        <v>7.216327296331101</v>
+        <v>7.224375136646273</v>
       </c>
       <c r="J5" t="n">
-        <v>4.116877238390619</v>
+        <v>4.160338222041089</v>
       </c>
       <c r="K5" t="n">
-        <v>4.872782298840756</v>
+        <v>4.868164412185051</v>
       </c>
       <c r="L5" t="n">
-        <v>4.757107865707334</v>
+        <v>5.1377951783873</v>
       </c>
       <c r="M5" t="n">
-        <v>3.987327846767725</v>
+        <v>4.219896497758999</v>
       </c>
       <c r="N5" t="n">
-        <v>3.991046277802226</v>
+        <v>2.55144311233155</v>
       </c>
       <c r="O5" t="n">
-        <v>3.070766291490418</v>
+        <v>3.096190243072295</v>
       </c>
       <c r="P5" t="n">
-        <v>3.616913281486901</v>
+        <v>3.703700129759095</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.467798417892464</v>
+        <v>2.468693736476749</v>
       </c>
       <c r="R5" t="n">
-        <v>5.7840317478798</v>
+        <v>5.795370697208032</v>
       </c>
       <c r="S5" t="n">
-        <v>5.249802261455213</v>
+        <v>5.312970702041082</v>
       </c>
       <c r="T5" t="n">
-        <v>2.766617328726184</v>
+        <v>2.776871011903646</v>
       </c>
       <c r="U5" t="n">
-        <v>4.074607530447708</v>
+        <v>4.205592433763509</v>
       </c>
       <c r="V5" t="n">
-        <v>4.160878050800129</v>
+        <v>4.173453105306329</v>
       </c>
       <c r="W5" t="n">
-        <v>3.856125420045135</v>
+        <v>3.85488245419825</v>
       </c>
       <c r="X5" t="n">
-        <v>4.641800946331679</v>
+        <v>4.767442241474583</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.150159171804165</v>
+        <v>3.184065330137293</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.899760379070254</v>
+        <v>2.966903317707278</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.969242369405749</v>
+        <v>6.011955648608946</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.510563266538463</v>
+        <v>3.775689348747144</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.58951235728037</v>
+        <v>3.286356174077273</v>
       </c>
       <c r="C6" t="n">
-        <v>3.813435604496384</v>
+        <v>3.800431956060429</v>
       </c>
       <c r="D6" t="n">
-        <v>16.92889502194419</v>
+        <v>3.62168047695958</v>
       </c>
       <c r="E6" t="n">
-        <v>17.05284685609555</v>
+        <v>17.04167380859619</v>
       </c>
       <c r="F6" t="n">
-        <v>17.15779014876269</v>
+        <v>3.847371370684233</v>
       </c>
       <c r="G6" t="n">
-        <v>3.336069838337949</v>
+        <v>16.61999369071781</v>
       </c>
       <c r="H6" t="n">
-        <v>16.66779388855863</v>
+        <v>3.35736496892883</v>
       </c>
       <c r="I6" t="n">
-        <v>3.535761809661032</v>
+        <v>3.523538970927423</v>
       </c>
       <c r="J6" t="n">
-        <v>3.389175521614685</v>
+        <v>3.379026750476662</v>
       </c>
       <c r="K6" t="n">
-        <v>3.434292344967258</v>
+        <v>16.71883271352961</v>
       </c>
       <c r="L6" t="n">
-        <v>16.72278083965037</v>
+        <v>16.73125812746664</v>
       </c>
       <c r="M6" t="n">
-        <v>16.67744334790649</v>
+        <v>3.380215349339618</v>
       </c>
       <c r="N6" t="n">
-        <v>3.301520860807792</v>
+        <v>2.55144311233155</v>
       </c>
       <c r="O6" t="n">
-        <v>3.334274223430788</v>
+        <v>16.62180330135958</v>
       </c>
       <c r="P6" t="n">
-        <v>16.66127589708967</v>
+        <v>16.65360112487786</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.59593945060186</v>
+        <v>3.286122890607111</v>
       </c>
       <c r="R6" t="n">
-        <v>16.75668531405611</v>
+        <v>16.74462783647538</v>
       </c>
       <c r="S6" t="n">
-        <v>16.76404579278246</v>
+        <v>3.45806768165605</v>
       </c>
       <c r="T6" t="n">
-        <v>3.312970306842074</v>
+        <v>3.300859048365067</v>
       </c>
       <c r="U6" t="n">
-        <v>16.68451975179823</v>
+        <v>16.67916000661633</v>
       </c>
       <c r="V6" t="n">
-        <v>16.6975968370726</v>
+        <v>3.388593220724707</v>
       </c>
       <c r="W6" t="n">
-        <v>3.372678946652572</v>
+        <v>3.360011832403319</v>
       </c>
       <c r="X6" t="n">
-        <v>3.409335574788425</v>
+        <v>16.70045647372812</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.352917743090948</v>
+        <v>3.342159577172019</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.324927288374176</v>
+        <v>16.61357402559373</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.78100944534641</v>
+        <v>16.77071022790192</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.344820755450228</v>
+        <v>3.3449777081442</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.183399304858201</v>
+        <v>2.175239516366381</v>
       </c>
       <c r="C7" t="n">
-        <v>2.704600296848764</v>
+        <v>2.689315298349538</v>
       </c>
       <c r="D7" t="n">
-        <v>2.522781969521996</v>
+        <v>2.510563819248688</v>
       </c>
       <c r="E7" t="n">
-        <v>2.646733803673369</v>
+        <v>2.633243377061929</v>
       </c>
       <c r="F7" t="n">
-        <v>2.751677096340509</v>
+        <v>2.736254712973344</v>
       </c>
       <c r="G7" t="n">
-        <v>2.227234530690321</v>
+        <v>2.211563259183574</v>
       </c>
       <c r="H7" t="n">
-        <v>2.261680836136469</v>
+        <v>2.246248311217932</v>
       </c>
       <c r="I7" t="n">
-        <v>2.426926502013403</v>
+        <v>2.412422313216533</v>
       </c>
       <c r="J7" t="n">
-        <v>2.280340213967057</v>
+        <v>2.267910092765772</v>
       </c>
       <c r="K7" t="n">
-        <v>2.325457037319628</v>
+        <v>2.310402281995366</v>
       </c>
       <c r="L7" t="n">
-        <v>2.316667787228181</v>
+        <v>2.322827695932416</v>
       </c>
       <c r="M7" t="n">
-        <v>2.271330295484309</v>
+        <v>2.26909869162873</v>
       </c>
       <c r="N7" t="n">
-        <v>2.194845446730576</v>
+        <v>2.55144311233155</v>
       </c>
       <c r="O7" t="n">
-        <v>2.227594000050065</v>
+        <v>2.214348162787982</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25607973551959</v>
+        <v>2.246143816604572</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.189826398179679</v>
+        <v>2.175006232896224</v>
       </c>
       <c r="R7" t="n">
-        <v>2.350572261633934</v>
+        <v>2.336197404941139</v>
       </c>
       <c r="S7" t="n">
-        <v>2.357932740360279</v>
+        <v>2.346951023945161</v>
       </c>
       <c r="T7" t="n">
-        <v>2.204134999194451</v>
+        <v>2.189742390654175</v>
       </c>
       <c r="U7" t="n">
-        <v>2.278419883919697</v>
+        <v>2.27072884002011</v>
       </c>
       <c r="V7" t="n">
-        <v>2.291483784650413</v>
+        <v>2.277476563013813</v>
       </c>
       <c r="W7" t="n">
-        <v>2.263189713241735</v>
+        <v>2.24824831662766</v>
       </c>
       <c r="X7" t="n">
-        <v>2.300500267140798</v>
+        <v>2.292026042193887</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.226439085270902</v>
+        <v>2.213391691464443</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.216091980726545</v>
+        <v>2.205143594059488</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.374896392924215</v>
+        <v>2.362279796367668</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.238378352760877</v>
+        <v>2.23619023333161</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.194628695758277</v>
+        <v>2.186226167885127</v>
       </c>
       <c r="C8" t="n">
-        <v>2.77214842145318</v>
+        <v>2.755086590855391</v>
       </c>
       <c r="D8" t="n">
-        <v>2.59033009412641</v>
+        <v>2.576335111754541</v>
       </c>
       <c r="E8" t="n">
-        <v>2.684293863880177</v>
+        <v>2.669843464289694</v>
       </c>
       <c r="F8" t="n">
-        <v>2.771680287740214</v>
+        <v>2.7557761712755</v>
       </c>
       <c r="G8" t="n">
-        <v>2.306460711610389</v>
+        <v>2.288694503886289</v>
       </c>
       <c r="H8" t="n">
-        <v>2.329228960740885</v>
+        <v>2.312019603723785</v>
       </c>
       <c r="I8" t="n">
-        <v>2.49447462661782</v>
+        <v>2.478193605722389</v>
       </c>
       <c r="J8" t="n">
-        <v>2.347888338571473</v>
+        <v>2.333681385271626</v>
       </c>
       <c r="K8" t="n">
-        <v>2.393005161924045</v>
+        <v>2.37617357450122</v>
       </c>
       <c r="L8" t="n">
-        <v>2.384215911832597</v>
+        <v>2.388598988438268</v>
       </c>
       <c r="M8" t="n">
-        <v>2.338878420088719</v>
+        <v>2.334869984134567</v>
       </c>
       <c r="N8" t="n">
-        <v>2.21873713079389</v>
+        <v>2.55144311233155</v>
       </c>
       <c r="O8" t="n">
-        <v>2.263487662337259</v>
+        <v>2.249327347861612</v>
       </c>
       <c r="P8" t="n">
-        <v>2.289032601812468</v>
+        <v>2.278262311422073</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.189987872496161</v>
+        <v>2.175226452064824</v>
       </c>
       <c r="R8" t="n">
-        <v>2.418120386238349</v>
+        <v>2.401968697446993</v>
       </c>
       <c r="S8" t="n">
-        <v>2.425480864964695</v>
+        <v>2.412722316451014</v>
       </c>
       <c r="T8" t="n">
-        <v>2.271683123798866</v>
+        <v>2.25551368316003</v>
       </c>
       <c r="U8" t="n">
-        <v>2.318480346523641</v>
+        <v>2.30976435200253</v>
       </c>
       <c r="V8" t="n">
-        <v>2.343654530841529</v>
+        <v>2.328277846529395</v>
       </c>
       <c r="W8" t="n">
-        <v>2.330748906085494</v>
+        <v>2.314030375877789</v>
       </c>
       <c r="X8" t="n">
-        <v>2.305823465304863</v>
+        <v>2.297267382563084</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.350007500376796</v>
+        <v>2.333639471131224</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.226275222234583</v>
+        <v>2.215112592746222</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.442444517528631</v>
+        <v>2.428051088873524</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.364756104010004</v>
+        <v>2.359188664358439</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.624255263686315</v>
+        <v>2.617085579704216</v>
       </c>
       <c r="C9" t="n">
-        <v>3.288784588718022</v>
+        <v>3.274162926824509</v>
       </c>
       <c r="D9" t="n">
-        <v>3.106966261391256</v>
+        <v>3.095411447723652</v>
       </c>
       <c r="E9" t="n">
-        <v>3.197838504439936</v>
+        <v>3.185086829463117</v>
       </c>
       <c r="F9" t="n">
-        <v>3.005450456533378</v>
+        <v>2.991444701808744</v>
       </c>
       <c r="G9" t="n">
-        <v>2.811418827158615</v>
+        <v>2.796410890085885</v>
       </c>
       <c r="H9" t="n">
-        <v>2.84586512800573</v>
+        <v>2.831095939692903</v>
       </c>
       <c r="I9" t="n">
-        <v>3.011110793882664</v>
+        <v>2.997269941691502</v>
       </c>
       <c r="J9" t="n">
-        <v>2.864524505836319</v>
+        <v>2.85275772124074</v>
       </c>
       <c r="K9" t="n">
-        <v>2.909641329188889</v>
+        <v>2.895249910470333</v>
       </c>
       <c r="L9" t="n">
-        <v>2.900852079097441</v>
+        <v>2.907675324407384</v>
       </c>
       <c r="M9" t="n">
-        <v>2.855514587353567</v>
+        <v>2.853946320103698</v>
       </c>
       <c r="N9" t="n">
-        <v>2.779029738599837</v>
+        <v>2.55144311233155</v>
       </c>
       <c r="O9" t="n">
-        <v>2.859281929243551</v>
+        <v>2.84659110820097</v>
       </c>
       <c r="P9" t="n">
-        <v>2.898097843864458</v>
+        <v>2.888693389696294</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.774010694647973</v>
+        <v>2.759853863798538</v>
       </c>
       <c r="R9" t="n">
-        <v>2.934756553503195</v>
+        <v>2.921045033416106</v>
       </c>
       <c r="S9" t="n">
-        <v>2.942117032229539</v>
+        <v>2.931798652420126</v>
       </c>
       <c r="T9" t="n">
-        <v>2.788319291063709</v>
+        <v>2.774590019129144</v>
       </c>
       <c r="U9" t="n">
-        <v>2.862590991245312</v>
+        <v>2.855577203557066</v>
       </c>
       <c r="V9" t="n">
-        <v>3.04106581741669</v>
+        <v>3.027344843616931</v>
       </c>
       <c r="W9" t="n">
-        <v>2.847374005110994</v>
+        <v>2.833095945102627</v>
       </c>
       <c r="X9" t="n">
-        <v>2.884684559010058</v>
+        <v>2.876873670668854</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.810623377140164</v>
+        <v>2.798239319939409</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.71386203485092</v>
+        <v>2.703773995916004</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.959080684793473</v>
+        <v>2.947127424842638</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.822562644630137</v>
+        <v>2.821037861806576</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.396544411750761</v>
+        <v>2.395660550246153</v>
       </c>
       <c r="C2" t="n">
-        <v>2.439622219529354</v>
+        <v>2.438852044624189</v>
       </c>
       <c r="D2" t="n">
-        <v>2.41095398317314</v>
+        <v>2.410118898304301</v>
       </c>
       <c r="E2" t="n">
-        <v>2.427648288966813</v>
+        <v>2.426841467204258</v>
       </c>
       <c r="F2" t="n">
-        <v>2.444747402377159</v>
+        <v>2.444013362847081</v>
       </c>
       <c r="G2" t="n">
-        <v>2.400095802425968</v>
+        <v>2.399183035731398</v>
       </c>
       <c r="H2" t="n">
-        <v>2.403158530629909</v>
+        <v>2.402287111571559</v>
       </c>
       <c r="I2" t="n">
-        <v>2.410102393699346</v>
+        <v>2.409270967942358</v>
       </c>
       <c r="J2" t="n">
-        <v>2.405628299697292</v>
+        <v>2.404797564377407</v>
       </c>
       <c r="K2" t="n">
-        <v>2.406892546200408</v>
+        <v>2.406073454464221</v>
       </c>
       <c r="L2" t="n">
-        <v>2.407995012555711</v>
+        <v>2.407711807874861</v>
       </c>
       <c r="M2" t="n">
-        <v>2.415109339737249</v>
+        <v>2.414339700386105</v>
       </c>
       <c r="N2" t="n">
-        <v>2.397782995153935</v>
+        <v>2.396915652287754</v>
       </c>
       <c r="O2" t="n">
-        <v>2.435984591565422</v>
+        <v>2.434330037122911</v>
       </c>
       <c r="P2" t="n">
-        <v>2.404161808561146</v>
+        <v>2.403497764377979</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.397319703200494</v>
+        <v>2.396432966958185</v>
       </c>
       <c r="R2" t="n">
-        <v>2.407700566856098</v>
+        <v>2.406877682859171</v>
       </c>
       <c r="S2" t="n">
-        <v>2.409925802070414</v>
+        <v>2.409085978819795</v>
       </c>
       <c r="T2" t="n">
-        <v>2.399209169793151</v>
+        <v>2.398356493337613</v>
       </c>
       <c r="U2" t="n">
-        <v>2.436903928950524</v>
+        <v>2.435277252673192</v>
       </c>
       <c r="V2" t="n">
-        <v>2.404892678023906</v>
+        <v>2.404035807843974</v>
       </c>
       <c r="W2" t="n">
-        <v>2.438905505321896</v>
+        <v>2.437013600742415</v>
       </c>
       <c r="X2" t="n">
-        <v>2.408360774176118</v>
+        <v>2.407612254657903</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.400015207479827</v>
+        <v>2.399312329961633</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.416972712491961</v>
+        <v>2.415299866709014</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.408083485316117</v>
+        <v>2.407280692254555</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.402224576704381</v>
+        <v>2.402002976791292</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.393535395188733</v>
+        <v>2.392680501811385</v>
       </c>
       <c r="C3" t="n">
-        <v>2.673588209672545</v>
+        <v>2.673256041899937</v>
       </c>
       <c r="D3" t="n">
-        <v>2.496500755811317</v>
+        <v>2.495993316583704</v>
       </c>
       <c r="E3" t="n">
-        <v>2.61544732778891</v>
+        <v>2.615141742057572</v>
       </c>
       <c r="F3" t="n">
-        <v>2.73793225654275</v>
+        <v>2.738146642941604</v>
       </c>
       <c r="G3" t="n">
-        <v>2.418718051771584</v>
+        <v>2.417657966211087</v>
       </c>
       <c r="H3" t="n">
-        <v>2.441038915789822</v>
+        <v>2.440271907585328</v>
       </c>
       <c r="I3" t="n">
-        <v>2.490629132332463</v>
+        <v>2.490148599648367</v>
       </c>
       <c r="J3" t="n">
-        <v>2.458219861967364</v>
+        <v>2.457742822731366</v>
       </c>
       <c r="K3" t="n">
-        <v>2.467078157185311</v>
+        <v>2.466682167537921</v>
       </c>
       <c r="L3" t="n">
-        <v>2.474844655526827</v>
+        <v>2.478252936546266</v>
       </c>
       <c r="M3" t="n">
-        <v>2.525580564029857</v>
+        <v>2.525527434229362</v>
       </c>
       <c r="N3" t="n">
-        <v>2.402400173234819</v>
+        <v>2.401662684066677</v>
       </c>
       <c r="O3" t="n">
-        <v>2.486884346359777</v>
+        <v>2.485014220743336</v>
       </c>
       <c r="P3" t="n">
-        <v>2.447649040282185</v>
+        <v>2.448355751358362</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.399068081794416</v>
+        <v>2.398192252287022</v>
       </c>
       <c r="R3" t="n">
-        <v>2.473518830204505</v>
+        <v>2.47309977923641</v>
       </c>
       <c r="S3" t="n">
-        <v>2.488415323509078</v>
+        <v>2.487872568506718</v>
       </c>
       <c r="T3" t="n">
-        <v>2.412619456165042</v>
+        <v>2.411986605673406</v>
       </c>
       <c r="U3" t="n">
-        <v>2.504883790174953</v>
+        <v>2.503329592689425</v>
       </c>
       <c r="V3" t="n">
-        <v>2.452749143080958</v>
+        <v>2.452085110336989</v>
       </c>
       <c r="W3" t="n">
-        <v>2.495270127378078</v>
+        <v>2.492948608972596</v>
       </c>
       <c r="X3" t="n">
-        <v>2.477893782800633</v>
+        <v>2.478004063665532</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4183123203445</v>
+        <v>2.418748011640627</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.438287753410432</v>
+        <v>2.436367797261255</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.475922454711124</v>
+        <v>2.47564578839666</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.434872263307499</v>
+        <v>2.438709591339993</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.107528750042464</v>
+        <v>2.09243504949362</v>
       </c>
       <c r="C4" t="n">
-        <v>2.539045801846009</v>
+        <v>2.524644669529281</v>
       </c>
       <c r="D4" t="n">
-        <v>2.270291487988592</v>
+        <v>2.255748741979107</v>
       </c>
       <c r="E4" t="n">
-        <v>2.458861351688219</v>
+        <v>2.444637850465889</v>
       </c>
       <c r="F4" t="n">
-        <v>2.652003703638862</v>
+        <v>2.63860231121385</v>
       </c>
       <c r="G4" t="n">
-        <v>2.147643341439349</v>
+        <v>2.132223143472847</v>
       </c>
       <c r="H4" t="n">
-        <v>2.182238265427455</v>
+        <v>2.167285108032911</v>
       </c>
       <c r="I4" t="n">
-        <v>2.260672393131571</v>
+        <v>2.246170978473728</v>
       </c>
       <c r="J4" t="n">
-        <v>2.210165752757862</v>
+        <v>2.195673070104653</v>
       </c>
       <c r="K4" t="n">
-        <v>2.22441568902827</v>
+        <v>2.210053592809296</v>
       </c>
       <c r="L4" t="n">
-        <v>2.236868553670996</v>
+        <v>2.228559548262293</v>
       </c>
       <c r="M4" t="n">
-        <v>2.316886799404816</v>
+        <v>2.303064690971287</v>
       </c>
       <c r="N4" t="n">
-        <v>2.121519119357828</v>
+        <v>2.470460842603512</v>
       </c>
       <c r="O4" t="n">
-        <v>2.16616984852301</v>
+        <v>2.151609806044521</v>
       </c>
       <c r="P4" t="n">
-        <v>2.193570751191422</v>
+        <v>2.180959988409215</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.116286023618889</v>
+        <v>2.101159851585256</v>
       </c>
       <c r="R4" t="n">
-        <v>2.233542654042156</v>
+        <v>2.219137722493605</v>
       </c>
       <c r="S4" t="n">
-        <v>2.258677709446618</v>
+        <v>2.244081441235182</v>
       </c>
       <c r="T4" t="n">
-        <v>2.137628417980526</v>
+        <v>2.122886966906754</v>
       </c>
       <c r="U4" t="n">
-        <v>2.200350432703337</v>
+        <v>2.186396307131262</v>
       </c>
       <c r="V4" t="n">
-        <v>2.201947748891032</v>
+        <v>2.18716526825427</v>
       </c>
       <c r="W4" t="n">
-        <v>2.172980573994031</v>
+        <v>2.158293947527775</v>
       </c>
       <c r="X4" t="n">
-        <v>2.240999999432149</v>
+        <v>2.227435048879998</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.146925090319084</v>
+        <v>2.13392275027475</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.130424694584124</v>
+        <v>2.115823981972088</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.237867894199256</v>
+        <v>2.223689899007954</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.172782849498601</v>
+        <v>2.165074806433037</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.225985091008088</v>
+        <v>2.207044082907968</v>
       </c>
       <c r="C5" t="n">
-        <v>9.662642037742485</v>
+        <v>9.655093690701239</v>
       </c>
       <c r="D5" t="n">
-        <v>5.168729522563424</v>
+        <v>5.159187330708686</v>
       </c>
       <c r="E5" t="n">
-        <v>8.399465719027349</v>
+        <v>8.39564156733751</v>
       </c>
       <c r="F5" t="n">
-        <v>12.04751814309069</v>
+        <v>12.05850470437159</v>
       </c>
       <c r="G5" t="n">
-        <v>2.850594855184879</v>
+        <v>2.826452149960718</v>
       </c>
       <c r="H5" t="n">
-        <v>3.701893412218899</v>
+        <v>3.684962833104509</v>
       </c>
       <c r="I5" t="n">
-        <v>5.105464648161773</v>
+        <v>5.097063530192061</v>
       </c>
       <c r="J5" t="n">
-        <v>3.964245228842081</v>
+        <v>3.955239722352926</v>
       </c>
       <c r="K5" t="n">
-        <v>4.13143556600986</v>
+        <v>4.123692260379839</v>
       </c>
       <c r="L5" t="n">
-        <v>4.298899180475227</v>
+        <v>4.387652338450336</v>
       </c>
       <c r="M5" t="n">
-        <v>5.789848083551343</v>
+        <v>5.791666377548317</v>
       </c>
       <c r="N5" t="n">
-        <v>3.649747961134753</v>
+        <v>2.470460842603512</v>
       </c>
       <c r="O5" t="n">
-        <v>3.140274617493409</v>
+        <v>3.129596989728045</v>
       </c>
       <c r="P5" t="n">
-        <v>3.617137657014561</v>
+        <v>3.638358140145077</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38055729984043</v>
+        <v>2.360824852228133</v>
       </c>
       <c r="R5" t="n">
-        <v>4.642035255327686</v>
+        <v>4.635609428693595</v>
       </c>
       <c r="S5" t="n">
-        <v>4.576075990770099</v>
+        <v>4.564811021326125</v>
       </c>
       <c r="T5" t="n">
-        <v>2.792317006411477</v>
+        <v>2.779333336651753</v>
       </c>
       <c r="U5" t="n">
-        <v>3.728387168608365</v>
+        <v>3.726795484617806</v>
       </c>
       <c r="V5" t="n">
-        <v>3.703080134234321</v>
+        <v>3.688616464439599</v>
       </c>
       <c r="W5" t="n">
-        <v>3.393508493110291</v>
+        <v>3.381566654345418</v>
       </c>
       <c r="X5" t="n">
-        <v>4.599299383180983</v>
+        <v>4.606998709237943</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.922321745346986</v>
+        <v>2.938963804035737</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.58472222283587</v>
+        <v>2.573385774127106</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.547891360704745</v>
+        <v>4.544958278951004</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.485229708206364</v>
+        <v>3.605821443678938</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.20170684978325</v>
+        <v>15.57669822648971</v>
       </c>
       <c r="C6" t="n">
-        <v>16.02276520886593</v>
+        <v>16.00890784652535</v>
       </c>
       <c r="D6" t="n">
-        <v>3.364469587729381</v>
+        <v>15.74001191897516</v>
       </c>
       <c r="E6" t="n">
-        <v>15.94258075870814</v>
+        <v>3.539401159802792</v>
       </c>
       <c r="F6" t="n">
-        <v>16.13572311065879</v>
+        <v>3.73336562055075</v>
       </c>
       <c r="G6" t="n">
-        <v>3.241821441180133</v>
+        <v>3.226986452809746</v>
       </c>
       <c r="H6" t="n">
-        <v>15.66595767244737</v>
+        <v>3.262048417369808</v>
       </c>
       <c r="I6" t="n">
-        <v>15.74439180015151</v>
+        <v>15.7304341554698</v>
       </c>
       <c r="J6" t="n">
-        <v>3.30434385249865</v>
+        <v>15.67993624710073</v>
       </c>
       <c r="K6" t="n">
-        <v>15.7081350960482</v>
+        <v>3.304816902146198</v>
       </c>
       <c r="L6" t="n">
-        <v>3.331046653411782</v>
+        <v>15.71282272525836</v>
       </c>
       <c r="M6" t="n">
-        <v>15.80060620642475</v>
+        <v>3.397828000308187</v>
       </c>
       <c r="N6" t="n">
-        <v>3.214219205285815</v>
+        <v>2.470460842603512</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25886993445099</v>
+        <v>15.6349519263031</v>
       </c>
       <c r="P6" t="n">
-        <v>3.283312971888645</v>
+        <v>3.27128797722856</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.60000543063882</v>
+        <v>3.195923160922152</v>
       </c>
       <c r="R6" t="n">
-        <v>15.71726206106208</v>
+        <v>15.70340089948969</v>
       </c>
       <c r="S6" t="n">
-        <v>3.352855809187405</v>
+        <v>3.338844750572085</v>
       </c>
       <c r="T6" t="n">
-        <v>3.231806517721314</v>
+        <v>3.217650276243655</v>
       </c>
       <c r="U6" t="n">
-        <v>3.294336426572231</v>
+        <v>15.67042031513422</v>
       </c>
       <c r="V6" t="n">
-        <v>15.68566715591096</v>
+        <v>3.281928577591173</v>
       </c>
       <c r="W6" t="n">
-        <v>3.268199176925096</v>
+        <v>3.254088367472959</v>
       </c>
       <c r="X6" t="n">
-        <v>3.335178099172935</v>
+        <v>15.71169822587606</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.257805376320409</v>
+        <v>3.245332257595233</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.22460279432491</v>
+        <v>15.60008715896816</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.72158730121919</v>
+        <v>3.318453208344856</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.265399927419061</v>
+        <v>3.258307194329665</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.170963615123661</v>
+        <v>2.153971023914886</v>
       </c>
       <c r="C7" t="n">
-        <v>2.602480666927205</v>
+        <v>2.586180643950545</v>
       </c>
       <c r="D7" t="n">
-        <v>2.333726353069789</v>
+        <v>2.317284716400374</v>
       </c>
       <c r="E7" t="n">
-        <v>2.522296216769416</v>
+        <v>2.506173824887155</v>
       </c>
       <c r="F7" t="n">
-        <v>2.71543856872006</v>
+        <v>2.700138285635115</v>
       </c>
       <c r="G7" t="n">
-        <v>2.211078206520545</v>
+        <v>2.193759117894112</v>
       </c>
       <c r="H7" t="n">
-        <v>2.245673130508653</v>
+        <v>2.228821082454176</v>
       </c>
       <c r="I7" t="n">
-        <v>2.324107258212769</v>
+        <v>2.307706952894994</v>
       </c>
       <c r="J7" t="n">
-        <v>2.273600617839059</v>
+        <v>2.257209044525919</v>
       </c>
       <c r="K7" t="n">
-        <v>2.287850554109467</v>
+        <v>2.271589567230562</v>
       </c>
       <c r="L7" t="n">
-        <v>2.300303418752193</v>
+        <v>2.29009552268356</v>
       </c>
       <c r="M7" t="n">
-        <v>2.380321664486014</v>
+        <v>2.364600665392554</v>
       </c>
       <c r="N7" t="n">
-        <v>2.184953984439026</v>
+        <v>2.470460842603512</v>
       </c>
       <c r="O7" t="n">
-        <v>2.229600250674719</v>
+        <v>2.213141340225525</v>
       </c>
       <c r="P7" t="n">
-        <v>2.257001153343132</v>
+        <v>2.24249152259022</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.179720888700086</v>
+        <v>2.162695826006521</v>
       </c>
       <c r="R7" t="n">
-        <v>2.296977519123354</v>
+        <v>2.28067369691487</v>
       </c>
       <c r="S7" t="n">
-        <v>2.322112574527816</v>
+        <v>2.305617415656447</v>
       </c>
       <c r="T7" t="n">
-        <v>2.201063283061722</v>
+        <v>2.184422941328021</v>
       </c>
       <c r="U7" t="n">
-        <v>2.263621210534889</v>
+        <v>2.247699046998261</v>
       </c>
       <c r="V7" t="n">
-        <v>2.265382613972231</v>
+        <v>2.248701242675536</v>
       </c>
       <c r="W7" t="n">
-        <v>2.236415439075228</v>
+        <v>2.21982992194904</v>
       </c>
       <c r="X7" t="n">
-        <v>2.304434864513347</v>
+        <v>2.288971023301264</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.210167849528383</v>
+        <v>2.195219555702892</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.193859559665323</v>
+        <v>2.177359956393354</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.301302759280452</v>
+        <v>2.285225873429219</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.236217714579799</v>
+        <v>2.226610780854303</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.181416138795261</v>
+        <v>2.163935063076468</v>
       </c>
       <c r="C8" t="n">
-        <v>2.665285441411668</v>
+        <v>2.646603143456967</v>
       </c>
       <c r="D8" t="n">
-        <v>2.396531127554251</v>
+        <v>2.377707215906796</v>
       </c>
       <c r="E8" t="n">
-        <v>2.557224961991823</v>
+        <v>2.539728682693057</v>
       </c>
       <c r="F8" t="n">
-        <v>2.734046961214149</v>
+        <v>2.717963163197226</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28473856125395</v>
+        <v>2.264644507858784</v>
       </c>
       <c r="H8" t="n">
-        <v>2.308477904993115</v>
+        <v>2.2892435819606</v>
       </c>
       <c r="I8" t="n">
-        <v>2.38691203269723</v>
+        <v>2.368129452401415</v>
       </c>
       <c r="J8" t="n">
-        <v>2.336405392323521</v>
+        <v>2.317631544032341</v>
       </c>
       <c r="K8" t="n">
-        <v>2.35065532859393</v>
+        <v>2.332012066736984</v>
       </c>
       <c r="L8" t="n">
-        <v>2.363108193236654</v>
+        <v>2.350518022189981</v>
       </c>
       <c r="M8" t="n">
-        <v>2.443126438970473</v>
+        <v>2.425023164898977</v>
       </c>
       <c r="N8" t="n">
-        <v>2.207177006201645</v>
+        <v>2.470460842603512</v>
       </c>
       <c r="O8" t="n">
-        <v>2.262979953377934</v>
+        <v>2.245203329330831</v>
       </c>
       <c r="P8" t="n">
-        <v>2.287647177936711</v>
+        <v>2.27191872166599</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.179885000206507</v>
+        <v>2.162743626054335</v>
       </c>
       <c r="R8" t="n">
-        <v>2.359782293607815</v>
+        <v>2.341096196421292</v>
       </c>
       <c r="S8" t="n">
-        <v>2.384917349012278</v>
+        <v>2.366039915162869</v>
       </c>
       <c r="T8" t="n">
-        <v>2.263868057546185</v>
+        <v>2.244845440834442</v>
       </c>
       <c r="U8" t="n">
-        <v>2.30087070391555</v>
+        <v>2.283495551150422</v>
       </c>
       <c r="V8" t="n">
-        <v>2.313906493356763</v>
+        <v>2.295341552162875</v>
       </c>
       <c r="W8" t="n">
-        <v>2.299230502272519</v>
+        <v>2.28026233798154</v>
       </c>
       <c r="X8" t="n">
-        <v>2.309397163829451</v>
+        <v>2.293643441497719</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.325068338041977</v>
+        <v>2.305825508128033</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.203339613400864</v>
+        <v>2.186386703749386</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.364107533764914</v>
+        <v>2.345648372935643</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.353708792657935</v>
+        <v>2.339741361451773</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.525312311142658</v>
+        <v>2.50861825468246</v>
       </c>
       <c r="C9" t="n">
-        <v>3.074722131380712</v>
+        <v>3.058114018740125</v>
       </c>
       <c r="D9" t="n">
-        <v>2.805967817523293</v>
+        <v>2.789218091189948</v>
       </c>
       <c r="E9" t="n">
-        <v>2.967328485983611</v>
+        <v>2.951038010528004</v>
       </c>
       <c r="F9" t="n">
-        <v>2.915905068637808</v>
+        <v>2.90169513131626</v>
       </c>
       <c r="G9" t="n">
-        <v>2.683319638264324</v>
+        <v>2.665692459519664</v>
       </c>
       <c r="H9" t="n">
-        <v>2.717914594962158</v>
+        <v>2.700754457243753</v>
       </c>
       <c r="I9" t="n">
-        <v>2.796348722666277</v>
+        <v>2.77964032768457</v>
       </c>
       <c r="J9" t="n">
-        <v>2.745842082292567</v>
+        <v>2.729142419315493</v>
       </c>
       <c r="K9" t="n">
-        <v>2.760092018562971</v>
+        <v>2.743522942020139</v>
       </c>
       <c r="L9" t="n">
-        <v>2.772544883205698</v>
+        <v>2.762028897473136</v>
       </c>
       <c r="M9" t="n">
-        <v>2.852563128939519</v>
+        <v>2.836534040182131</v>
       </c>
       <c r="N9" t="n">
-        <v>2.657195448892531</v>
+        <v>2.470460842603512</v>
       </c>
       <c r="O9" t="n">
-        <v>2.740915643599975</v>
+        <v>2.723947585656769</v>
       </c>
       <c r="P9" t="n">
-        <v>2.776813491818241</v>
+        <v>2.761750991976167</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.651962320443866</v>
+        <v>2.634629167632071</v>
       </c>
       <c r="R9" t="n">
-        <v>2.769218983576859</v>
+        <v>2.752607071704447</v>
       </c>
       <c r="S9" t="n">
-        <v>2.794354038981321</v>
+        <v>2.777550790446023</v>
       </c>
       <c r="T9" t="n">
-        <v>2.673304747515227</v>
+        <v>2.656356316117598</v>
       </c>
       <c r="U9" t="n">
-        <v>2.73583465636614</v>
+        <v>2.71962648734898</v>
       </c>
       <c r="V9" t="n">
-        <v>2.873669659051335</v>
+        <v>2.855980166249304</v>
       </c>
       <c r="W9" t="n">
-        <v>2.708656903528734</v>
+        <v>2.691763296738619</v>
       </c>
       <c r="X9" t="n">
-        <v>2.77667632896685</v>
+        <v>2.760904398090839</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.682409313981891</v>
+        <v>2.66715293049247</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.595022155198196</v>
+        <v>2.578580202659492</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.773544223733956</v>
+        <v>2.757159248218798</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.708459179033306</v>
+        <v>2.698544155643879</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia water use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia water use results.xlsx
@@ -798,7 +798,7 @@
         <v>2.198506060285256</v>
       </c>
       <c r="N4" t="n">
-        <v>2.651628247835907</v>
+        <v>2.115067127979503</v>
       </c>
       <c r="O4" t="n">
         <v>2.136904563815196</v>
@@ -974,7 +974,7 @@
         <v>17.66646490905397</v>
       </c>
       <c r="N6" t="n">
-        <v>2.651628247835907</v>
+        <v>3.370785312917368</v>
       </c>
       <c r="O6" t="n">
         <v>3.392622809302435</v>
@@ -1062,7 +1062,7 @@
         <v>2.2691342219504</v>
       </c>
       <c r="N7" t="n">
-        <v>2.651628247835907</v>
+        <v>2.185695289644649</v>
       </c>
       <c r="O7" t="n">
         <v>2.207527679598447</v>
@@ -1150,7 +1150,7 @@
         <v>2.337596300087633</v>
       </c>
       <c r="N8" t="n">
-        <v>2.651628247835907</v>
+        <v>2.209556904703817</v>
       </c>
       <c r="O8" t="n">
         <v>2.243650935049182</v>
@@ -1238,7 +1238,7 @@
         <v>2.986690284780059</v>
       </c>
       <c r="N9" t="n">
-        <v>2.651628247835907</v>
+        <v>2.903251352474305</v>
       </c>
       <c r="O9" t="n">
         <v>2.982322442820503</v>
@@ -1658,7 +1658,7 @@
         <v>2.214890945523725</v>
       </c>
       <c r="N4" t="n">
-        <v>2.455833555757122</v>
+        <v>2.102431549080699</v>
       </c>
       <c r="O4" t="n">
         <v>2.143555868228461</v>
@@ -1834,7 +1834,7 @@
         <v>3.307529813819885</v>
       </c>
       <c r="N6" t="n">
-        <v>2.455833555757122</v>
+        <v>3.193764807008485</v>
       </c>
       <c r="O6" t="n">
         <v>15.62320126248977</v>
@@ -1922,7 +1922,7 @@
         <v>2.275089709744634</v>
       </c>
       <c r="N7" t="n">
-        <v>2.455833555757122</v>
+        <v>2.162630313301608</v>
       </c>
       <c r="O7" t="n">
         <v>2.203750234190684</v>
@@ -2010,7 +2010,7 @@
         <v>2.33265555062527</v>
       </c>
       <c r="N8" t="n">
-        <v>2.455833555757122</v>
+        <v>2.182438598247387</v>
       </c>
       <c r="O8" t="n">
         <v>2.233939021605889</v>
@@ -2098,7 +2098,7 @@
         <v>2.689958755244879</v>
       </c>
       <c r="N9" t="n">
-        <v>2.455833555757122</v>
+        <v>2.577499358801854</v>
       </c>
       <c r="O9" t="n">
         <v>2.653276998893955</v>
@@ -2518,7 +2518,7 @@
         <v>2.198782508957231</v>
       </c>
       <c r="N4" t="n">
-        <v>2.600155173142274</v>
+        <v>2.114283511916984</v>
       </c>
       <c r="O4" t="n">
         <v>2.14837048759219</v>
@@ -2694,7 +2694,7 @@
         <v>16.67251278835439</v>
       </c>
       <c r="N6" t="n">
-        <v>2.600155173142274</v>
+        <v>3.289001344644499</v>
       </c>
       <c r="O6" t="n">
         <v>3.32308656800073</v>
@@ -2782,7 +2782,7 @@
         <v>2.265145647803342</v>
       </c>
       <c r="N7" t="n">
-        <v>2.600155173142274</v>
+        <v>2.180646650763095</v>
       </c>
       <c r="O7" t="n">
         <v>2.214728860409421</v>
@@ -2870,7 +2870,7 @@
         <v>2.330044787619685</v>
       </c>
       <c r="N8" t="n">
-        <v>2.600155173142274</v>
+        <v>2.203449034187501</v>
       </c>
       <c r="O8" t="n">
         <v>2.24910456403562</v>
@@ -2958,7 +2958,7 @@
         <v>2.847205300770227</v>
       </c>
       <c r="N9" t="n">
-        <v>2.600155173142274</v>
+        <v>2.76270630372998</v>
       </c>
       <c r="O9" t="n">
         <v>2.843957945907068</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.397247055861032</v>
+        <v>2.397247055861033</v>
       </c>
       <c r="C2" t="n">
         <v>2.43546149459064</v>
@@ -3175,16 +3175,16 @@
         <v>2.413534985399381</v>
       </c>
       <c r="E2" t="n">
-        <v>2.424845519604841</v>
+        <v>2.424845519604842</v>
       </c>
       <c r="F2" t="n">
         <v>2.438554804394502</v>
       </c>
       <c r="G2" t="n">
-        <v>2.399733661320383</v>
+        <v>2.399733661320384</v>
       </c>
       <c r="H2" t="n">
-        <v>2.401671162915952</v>
+        <v>2.401671162915953</v>
       </c>
       <c r="I2" t="n">
         <v>2.407501194832627</v>
@@ -3193,10 +3193,10 @@
         <v>2.403310074476366</v>
       </c>
       <c r="K2" t="n">
-        <v>2.405062389380008</v>
+        <v>2.405062389380009</v>
       </c>
       <c r="L2" t="n">
-        <v>2.407157619928722</v>
+        <v>2.407157619928723</v>
       </c>
       <c r="M2" t="n">
         <v>2.402585058641602</v>
@@ -3205,7 +3205,7 @@
         <v>2.397064021629306</v>
       </c>
       <c r="O2" t="n">
-        <v>2.434218953226643</v>
+        <v>2.434218953226642</v>
       </c>
       <c r="P2" t="n">
         <v>2.402369192417578</v>
@@ -3214,10 +3214,10 @@
         <v>2.397313029297482</v>
       </c>
       <c r="R2" t="n">
-        <v>2.412555963486852</v>
+        <v>2.412555963486853</v>
       </c>
       <c r="S2" t="n">
-        <v>2.406729142261837</v>
+        <v>2.406729142261838</v>
       </c>
       <c r="T2" t="n">
         <v>2.399034084364677</v>
@@ -3226,13 +3226,13 @@
         <v>2.434138686278785</v>
       </c>
       <c r="V2" t="n">
-        <v>2.404711985485004</v>
+        <v>2.404711985485005</v>
       </c>
       <c r="W2" t="n">
         <v>2.436934061634882</v>
       </c>
       <c r="X2" t="n">
-        <v>2.406666905606225</v>
+        <v>2.406666905606226</v>
       </c>
       <c r="Y2" t="n">
         <v>2.39967322311466</v>
@@ -3241,7 +3241,7 @@
         <v>2.417838277235574</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.40643637669329</v>
+        <v>2.406436376693291</v>
       </c>
       <c r="AB2" t="n">
         <v>2.399249723716486</v>
@@ -3257,7 +3257,7 @@
         <v>2.403689563504609</v>
       </c>
       <c r="C3" t="n">
-        <v>2.650092319902357</v>
+        <v>2.650092319902356</v>
       </c>
       <c r="D3" t="n">
         <v>2.520312940472506</v>
@@ -3308,19 +3308,19 @@
         <v>2.471144540746644</v>
       </c>
       <c r="T3" t="n">
-        <v>2.416579467100198</v>
+        <v>2.416579467100197</v>
       </c>
       <c r="U3" t="n">
         <v>2.493171417240879</v>
       </c>
       <c r="V3" t="n">
-        <v>2.456624588552204</v>
+        <v>2.456624588552203</v>
       </c>
       <c r="W3" t="n">
         <v>2.49009317857182</v>
       </c>
       <c r="X3" t="n">
-        <v>2.471109848841537</v>
+        <v>2.471109848841536</v>
       </c>
       <c r="Y3" t="n">
         <v>2.421054678886681</v>
@@ -3329,7 +3329,7 @@
         <v>2.447490481478993</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.469349882551319</v>
+        <v>2.469349882551318</v>
       </c>
       <c r="AB3" t="n">
         <v>2.419037585862625</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.110982984032178</v>
+        <v>2.110982984032177</v>
       </c>
       <c r="C4" t="n">
         <v>2.489363285760985</v>
@@ -3354,7 +3354,7 @@
         <v>2.422720327939068</v>
       </c>
       <c r="F4" t="n">
-        <v>2.57757300622086</v>
+        <v>2.577573006220859</v>
       </c>
       <c r="G4" t="n">
         <v>2.139070336590566</v>
@@ -3366,7 +3366,7 @@
         <v>2.226808200853314</v>
       </c>
       <c r="J4" t="n">
-        <v>2.179501196613962</v>
+        <v>2.179501196613961</v>
       </c>
       <c r="K4" t="n">
         <v>2.19926077136005</v>
@@ -3378,7 +3378,7 @@
         <v>2.172492524322839</v>
       </c>
       <c r="N4" t="n">
-        <v>2.503742816802815</v>
+        <v>2.108915528184919</v>
       </c>
       <c r="O4" t="n">
         <v>2.153442690341442</v>
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.505335975131925</v>
+        <v>2.505335975131922</v>
       </c>
       <c r="C5" t="n">
-        <v>9.086053435871651</v>
+        <v>9.086053435871642</v>
       </c>
       <c r="D5" t="n">
-        <v>5.953971137896853</v>
+        <v>5.953971137896854</v>
       </c>
       <c r="E5" t="n">
-        <v>8.020839313891447</v>
+        <v>8.020839313891445</v>
       </c>
       <c r="F5" t="n">
-        <v>11.14294558890016</v>
+        <v>11.14294558890015</v>
       </c>
       <c r="G5" t="n">
-        <v>2.96749202874195</v>
+        <v>2.967492028741962</v>
       </c>
       <c r="H5" t="n">
-        <v>3.552923487429543</v>
+        <v>3.552923487429547</v>
       </c>
       <c r="I5" t="n">
-        <v>4.738981395964899</v>
+        <v>4.738981395964896</v>
       </c>
       <c r="J5" t="n">
-        <v>3.717304260670474</v>
+        <v>3.717304260670476</v>
       </c>
       <c r="K5" t="n">
         <v>3.975283025667557</v>
       </c>
       <c r="L5" t="n">
-        <v>4.489068113363536</v>
+        <v>4.489068113363531</v>
       </c>
       <c r="M5" t="n">
-        <v>3.720659673942277</v>
+        <v>3.72065967394227</v>
       </c>
       <c r="N5" t="n">
         <v>2.503742816802815</v>
       </c>
       <c r="O5" t="n">
-        <v>3.157915899107183</v>
+        <v>3.157915899107184</v>
       </c>
       <c r="P5" t="n">
-        <v>3.451784863892904</v>
+        <v>3.451784863892906</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.549809762519272</v>
+        <v>2.549809762519271</v>
       </c>
       <c r="R5" t="n">
-        <v>5.879587612177379</v>
+        <v>5.879587612177378</v>
       </c>
       <c r="S5" t="n">
-        <v>4.28608936937137</v>
+        <v>4.286089369371368</v>
       </c>
       <c r="T5" t="n">
         <v>2.932717279582491</v>
       </c>
       <c r="U5" t="n">
-        <v>3.522194173887785</v>
+        <v>3.522194173887806</v>
       </c>
       <c r="V5" t="n">
-        <v>3.819296876269218</v>
+        <v>3.819296876269221</v>
       </c>
       <c r="W5" t="n">
-        <v>3.294685304890314</v>
+        <v>3.294685304890309</v>
       </c>
       <c r="X5" t="n">
-        <v>4.485865806284</v>
+        <v>4.485865806284004</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.015653254777986</v>
+        <v>3.015653254777988</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.813907566920798</v>
+        <v>2.813907566920795</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.380386209306149</v>
+        <v>4.380386209306148</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.052775460180265</v>
+        <v>3.052775460180263</v>
       </c>
     </row>
     <row r="6">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.59522945686913</v>
+        <v>15.59522945686912</v>
       </c>
       <c r="C6" t="n">
         <v>3.583985029240174</v>
@@ -3527,64 +3527,64 @@
         <v>15.77920911382249</v>
       </c>
       <c r="E6" t="n">
-        <v>15.906966800776</v>
+        <v>15.90696680077599</v>
       </c>
       <c r="F6" t="n">
-        <v>3.672194749700046</v>
+        <v>3.672194749700047</v>
       </c>
       <c r="G6" t="n">
-        <v>3.233692080069751</v>
+        <v>3.233692080069752</v>
       </c>
       <c r="H6" t="n">
-        <v>3.255577051886481</v>
+        <v>3.255577051886482</v>
       </c>
       <c r="I6" t="n">
         <v>3.321429944332499</v>
       </c>
       <c r="J6" t="n">
-        <v>15.6637476694509</v>
+        <v>15.66374766945088</v>
       </c>
       <c r="K6" t="n">
         <v>15.68350724419699</v>
       </c>
       <c r="L6" t="n">
-        <v>15.70717383709838</v>
+        <v>15.70717383709837</v>
       </c>
       <c r="M6" t="n">
-        <v>3.267114267802031</v>
+        <v>3.267114267802032</v>
       </c>
       <c r="N6" t="n">
-        <v>2.503742816802815</v>
+        <v>3.202198665227223</v>
       </c>
       <c r="O6" t="n">
         <v>15.63687495287758</v>
       </c>
       <c r="P6" t="n">
-        <v>15.65227493556479</v>
+        <v>15.6522749355648</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.59597465718307</v>
+        <v>15.59597465718306</v>
       </c>
       <c r="R6" t="n">
         <v>3.378525881590444</v>
       </c>
       <c r="S6" t="n">
-        <v>15.70233398474146</v>
+        <v>15.70233398474145</v>
       </c>
       <c r="T6" t="n">
-        <v>3.225790036533759</v>
+        <v>3.22579003653376</v>
       </c>
       <c r="U6" t="n">
-        <v>3.264563504311874</v>
+        <v>3.264563504311875</v>
       </c>
       <c r="V6" t="n">
         <v>15.6796928905347</v>
       </c>
       <c r="W6" t="n">
-        <v>15.63730682034379</v>
+        <v>15.6373068203438</v>
       </c>
       <c r="X6" t="n">
-        <v>3.312006263728294</v>
+        <v>3.312006263728295</v>
       </c>
       <c r="Y6" t="n">
         <v>3.250048806481626</v>
@@ -3593,7 +3593,7 @@
         <v>15.6156373474567</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.69902706296589</v>
+        <v>15.69902706296588</v>
       </c>
       <c r="AB6" t="n">
         <v>3.228163242158662</v>
@@ -3606,22 +3606,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.172224912529056</v>
+        <v>2.172224912529055</v>
       </c>
       <c r="C7" t="n">
-        <v>2.550605214257863</v>
+        <v>2.550605214257862</v>
       </c>
       <c r="D7" t="n">
-        <v>2.356204569482463</v>
+        <v>2.356204569482464</v>
       </c>
       <c r="E7" t="n">
         <v>2.483962256435946</v>
       </c>
       <c r="F7" t="n">
-        <v>2.638814934717738</v>
+        <v>2.638814934717737</v>
       </c>
       <c r="G7" t="n">
-        <v>2.200312265087446</v>
+        <v>2.200312265087445</v>
       </c>
       <c r="H7" t="n">
         <v>2.222197236904166</v>
@@ -3636,13 +3636,13 @@
         <v>2.260502699856928</v>
       </c>
       <c r="L7" t="n">
-        <v>2.28416929275833</v>
+        <v>2.284169292758329</v>
       </c>
       <c r="M7" t="n">
         <v>2.233734452819718</v>
       </c>
       <c r="N7" t="n">
-        <v>2.503742816802815</v>
+        <v>2.170157456681798</v>
       </c>
       <c r="O7" t="n">
         <v>2.214680157680946</v>
@@ -3654,7 +3654,7 @@
         <v>2.172970112843031</v>
       </c>
       <c r="R7" t="n">
-        <v>2.345146066608135</v>
+        <v>2.345146066608134</v>
       </c>
       <c r="S7" t="n">
         <v>2.279329440401396</v>
@@ -3663,7 +3663,7 @@
         <v>2.192410221551446</v>
       </c>
       <c r="U7" t="n">
-        <v>2.231194603589926</v>
+        <v>2.231194603589928</v>
       </c>
       <c r="V7" t="n">
         <v>2.256688346194661</v>
@@ -3678,7 +3678,7 @@
         <v>2.199629587750856</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.192632803116656</v>
+        <v>2.192632803116655</v>
       </c>
       <c r="AA7" t="n">
         <v>2.276022518625838</v>
@@ -3715,7 +3715,7 @@
         <v>2.28128360651473</v>
       </c>
       <c r="I8" t="n">
-        <v>2.347136498960758</v>
+        <v>2.347136498960757</v>
       </c>
       <c r="J8" t="n">
         <v>2.299829494721405</v>
@@ -3727,22 +3727,22 @@
         <v>2.343255662368894</v>
       </c>
       <c r="M8" t="n">
-        <v>2.292820822430264</v>
+        <v>2.292820822430263</v>
       </c>
       <c r="N8" t="n">
-        <v>2.503742816802815</v>
+        <v>2.190625984685393</v>
       </c>
       <c r="O8" t="n">
         <v>2.245765665024911</v>
       </c>
       <c r="P8" t="n">
-        <v>2.258561462780418</v>
+        <v>2.258561462780417</v>
       </c>
       <c r="Q8" t="n">
         <v>2.17244724828513</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4042324362187</v>
+        <v>2.404232436218699</v>
       </c>
       <c r="S8" t="n">
         <v>2.338415810011961</v>
@@ -3751,10 +3751,10 @@
         <v>2.251496591162011</v>
       </c>
       <c r="U8" t="n">
-        <v>2.265966122755482</v>
+        <v>2.265966122755481</v>
       </c>
       <c r="V8" t="n">
-        <v>2.302171651288138</v>
+        <v>2.302171651288139</v>
       </c>
       <c r="W8" t="n">
         <v>2.274213919138427</v>
@@ -3763,7 +3763,7 @@
         <v>2.282669568758279</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.30826995964828</v>
+        <v>2.308269959648279</v>
       </c>
       <c r="Z8" t="n">
         <v>2.200975045590019</v>
@@ -3797,7 +3797,7 @@
         <v>2.841842003403121</v>
       </c>
       <c r="G9" t="n">
-        <v>2.674872894599603</v>
+        <v>2.674872894599602</v>
       </c>
       <c r="H9" t="n">
         <v>2.696757863617113</v>
@@ -3818,10 +3818,10 @@
         <v>2.708295079532665</v>
       </c>
       <c r="N9" t="n">
-        <v>2.503742816802815</v>
+        <v>2.644718083394745</v>
       </c>
       <c r="O9" t="n">
-        <v>2.728280047876684</v>
+        <v>2.728280047876685</v>
       </c>
       <c r="P9" t="n">
         <v>2.752166629445153</v>
@@ -3845,13 +3845,13 @@
         <v>2.867173763060099</v>
       </c>
       <c r="W9" t="n">
-        <v>2.689678385442268</v>
+        <v>2.689678385442267</v>
       </c>
       <c r="X9" t="n">
         <v>2.753187075458925</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.674190214463803</v>
+        <v>2.674190214463802</v>
       </c>
       <c r="Z9" t="n">
         <v>2.596177723541542</v>
@@ -4026,13 +4026,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.394789628463498</v>
+        <v>2.394789628463499</v>
       </c>
       <c r="C2" t="n">
         <v>2.434470573125203</v>
       </c>
       <c r="D2" t="n">
-        <v>2.407427896218863</v>
+        <v>2.407427896218864</v>
       </c>
       <c r="E2" t="n">
         <v>2.419828259852877</v>
@@ -4041,67 +4041,67 @@
         <v>2.431153532610379</v>
       </c>
       <c r="G2" t="n">
-        <v>2.396980920355948</v>
+        <v>2.396980920355949</v>
       </c>
       <c r="H2" t="n">
-        <v>2.398337671609773</v>
+        <v>2.398337671609772</v>
       </c>
       <c r="I2" t="n">
-        <v>2.401069069010921</v>
+        <v>2.401069069010922</v>
       </c>
       <c r="J2" t="n">
-        <v>2.400564901043356</v>
+        <v>2.400564901043357</v>
       </c>
       <c r="K2" t="n">
-        <v>2.400883098245199</v>
+        <v>2.4008830982452</v>
       </c>
       <c r="L2" t="n">
-        <v>2.40473453567795</v>
+        <v>2.404734535677951</v>
       </c>
       <c r="M2" t="n">
         <v>2.4017989787279</v>
       </c>
       <c r="N2" t="n">
-        <v>2.394521995760762</v>
+        <v>2.394521995760763</v>
       </c>
       <c r="O2" t="n">
-        <v>2.430540615560898</v>
+        <v>2.430540615560899</v>
       </c>
       <c r="P2" t="n">
-        <v>2.398763709603612</v>
+        <v>2.398763709603613</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.395224891143825</v>
+        <v>2.395224891143826</v>
       </c>
       <c r="R2" t="n">
-        <v>2.406412844311231</v>
+        <v>2.406412844311229</v>
       </c>
       <c r="S2" t="n">
         <v>2.403174547329807</v>
       </c>
       <c r="T2" t="n">
-        <v>2.397099884147507</v>
+        <v>2.397099884147508</v>
       </c>
       <c r="U2" t="n">
         <v>2.429423601308343</v>
       </c>
       <c r="V2" t="n">
-        <v>2.401045591220076</v>
+        <v>2.401045591220077</v>
       </c>
       <c r="W2" t="n">
-        <v>2.433525962587049</v>
+        <v>2.43352596258705</v>
       </c>
       <c r="X2" t="n">
         <v>2.404666089746624</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.396468891713773</v>
+        <v>2.396468891713772</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.414253027972946</v>
+        <v>2.414253027972945</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.401838472573483</v>
+        <v>2.401838472573482</v>
       </c>
       <c r="AB2" t="n">
         <v>2.396895376527622</v>
@@ -4114,31 +4114,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.400862902573528</v>
+        <v>2.400862902573529</v>
       </c>
       <c r="C3" t="n">
         <v>2.655620814773071</v>
       </c>
       <c r="D3" t="n">
-        <v>2.491147935899102</v>
+        <v>2.491147935899101</v>
       </c>
       <c r="E3" t="n">
-        <v>2.578953958633321</v>
+        <v>2.578953958633322</v>
       </c>
       <c r="F3" t="n">
         <v>2.660936608216037</v>
       </c>
       <c r="G3" t="n">
-        <v>2.416419088906568</v>
+        <v>2.416419088906569</v>
       </c>
       <c r="H3" t="n">
-        <v>2.42647735170578</v>
+        <v>2.426477351705781</v>
       </c>
       <c r="I3" t="n">
         <v>2.445889043724379</v>
       </c>
       <c r="J3" t="n">
-        <v>2.442059485892805</v>
+        <v>2.442059485892804</v>
       </c>
       <c r="K3" t="n">
         <v>2.444238167144781</v>
@@ -4150,10 +4150,10 @@
         <v>2.451450444594914</v>
       </c>
       <c r="N3" t="n">
-        <v>2.399029935973688</v>
+        <v>2.399029935973689</v>
       </c>
       <c r="O3" t="n">
-        <v>2.476842417978635</v>
+        <v>2.476842417978636</v>
       </c>
       <c r="P3" t="n">
         <v>2.429060886917906</v>
@@ -4162,7 +4162,7 @@
         <v>2.404021680577986</v>
       </c>
       <c r="R3" t="n">
-        <v>2.484315317851925</v>
+        <v>2.484315317851926</v>
       </c>
       <c r="S3" t="n">
         <v>2.460478187982983</v>
@@ -4174,7 +4174,7 @@
         <v>2.475202457933928</v>
       </c>
       <c r="V3" t="n">
-        <v>2.445213391992988</v>
+        <v>2.445213391992989</v>
       </c>
       <c r="W3" t="n">
         <v>2.481272952434419</v>
@@ -4183,16 +4183,16 @@
         <v>2.471416824516286</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.412929464210303</v>
+        <v>2.412929464210301</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.438692910484866</v>
+        <v>2.438692910484865</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.451270170009389</v>
+        <v>2.451270170009388</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.416784755220898</v>
+        <v>2.416784755220897</v>
       </c>
     </row>
     <row r="4">
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.107351232378809</v>
+        <v>2.10735123237881</v>
       </c>
       <c r="C4" t="n">
         <v>2.49820377428373</v>
@@ -4217,7 +4217,7 @@
         <v>2.518098257940194</v>
       </c>
       <c r="G4" t="n">
-        <v>2.132102882348098</v>
+        <v>2.132102882348097</v>
       </c>
       <c r="H4" t="n">
         <v>2.147428011896443</v>
@@ -4226,10 +4226,10 @@
         <v>2.17828040204731</v>
       </c>
       <c r="J4" t="n">
-        <v>2.172617940222277</v>
+        <v>2.172617940222276</v>
       </c>
       <c r="K4" t="n">
-        <v>2.176179776697711</v>
+        <v>2.176179776697712</v>
       </c>
       <c r="L4" t="n">
         <v>2.219683534249383</v>
@@ -4238,7 +4238,7 @@
         <v>2.187281239816168</v>
       </c>
       <c r="N4" t="n">
-        <v>2.454300934083968</v>
+        <v>2.104328197884277</v>
       </c>
       <c r="O4" t="n">
         <v>2.142576381266148</v>
@@ -4268,7 +4268,7 @@
         <v>2.141111838835089</v>
       </c>
       <c r="X4" t="n">
-        <v>2.218910405968357</v>
+        <v>2.218910405968356</v>
       </c>
       <c r="Y4" t="n">
         <v>2.126687103650241</v>
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.467791740616281</v>
+        <v>2.467791740616282</v>
       </c>
       <c r="C5" t="n">
-        <v>9.215963638568827</v>
+        <v>9.215963638568821</v>
       </c>
       <c r="D5" t="n">
-        <v>5.036744159512149</v>
+        <v>5.03674415951213</v>
       </c>
       <c r="E5" t="n">
-        <v>7.153394981052301</v>
+        <v>7.153394981052307</v>
       </c>
       <c r="F5" t="n">
         <v>10.01377583665909</v>
       </c>
       <c r="G5" t="n">
-        <v>2.862463138246397</v>
+        <v>2.862463138246377</v>
       </c>
       <c r="H5" t="n">
-        <v>3.327879449136619</v>
+        <v>3.32787944913662</v>
       </c>
       <c r="I5" t="n">
         <v>3.83083896717647</v>
       </c>
       <c r="J5" t="n">
-        <v>3.610291150038885</v>
+        <v>3.610291150038875</v>
       </c>
       <c r="K5" t="n">
-        <v>3.625991569163492</v>
+        <v>3.625991569163491</v>
       </c>
       <c r="L5" t="n">
-        <v>4.377777825765715</v>
+        <v>4.377777825765712</v>
       </c>
       <c r="M5" t="n">
-        <v>3.959538999201417</v>
+        <v>3.959538999201414</v>
       </c>
       <c r="N5" t="n">
         <v>2.454300934083968</v>
       </c>
       <c r="O5" t="n">
-        <v>3.016496690125778</v>
+        <v>3.016496690125764</v>
       </c>
       <c r="P5" t="n">
-        <v>3.176102385030362</v>
+        <v>3.176102385030336</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.581844201897621</v>
+        <v>2.581844201897618</v>
       </c>
       <c r="R5" t="n">
-        <v>5.047393246961107</v>
+        <v>5.047393246961103</v>
       </c>
       <c r="S5" t="n">
-        <v>4.024611245333947</v>
+        <v>4.024611245333944</v>
       </c>
       <c r="T5" t="n">
-        <v>3.010305252750704</v>
+        <v>3.010305252750705</v>
       </c>
       <c r="U5" t="n">
-        <v>3.062593914742752</v>
+        <v>3.062593914742755</v>
       </c>
       <c r="V5" t="n">
-        <v>3.562978651221024</v>
+        <v>3.562978651221031</v>
       </c>
       <c r="W5" t="n">
-        <v>3.101505273498696</v>
+        <v>3.101505273498695</v>
       </c>
       <c r="X5" t="n">
-        <v>4.474649404358031</v>
+        <v>4.474649404358018</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.84554777148638</v>
+        <v>2.845547771486353</v>
       </c>
       <c r="Z5" t="n">
         <v>2.628818718623662</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.927469514500179</v>
+        <v>3.927469514500177</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.023135270505751</v>
+        <v>3.023135270505748</v>
       </c>
     </row>
     <row r="6">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.200425500401615</v>
+        <v>3.200425500401616</v>
       </c>
       <c r="C6" t="n">
         <v>3.591278042306548</v>
@@ -4387,22 +4387,22 @@
         <v>15.7323698071585</v>
       </c>
       <c r="E6" t="n">
-        <v>15.87243761885379</v>
+        <v>15.87243761885378</v>
       </c>
       <c r="F6" t="n">
-        <v>3.611172525963007</v>
+        <v>3.611172525963006</v>
       </c>
       <c r="G6" t="n">
-        <v>3.225177150370919</v>
+        <v>3.225177150370917</v>
       </c>
       <c r="H6" t="n">
-        <v>15.62969153848887</v>
+        <v>15.62969153848888</v>
       </c>
       <c r="I6" t="n">
         <v>3.271354670070123</v>
       </c>
       <c r="J6" t="n">
-        <v>15.6548814668147</v>
+        <v>15.65488146681471</v>
       </c>
       <c r="K6" t="n">
         <v>15.65844330329016</v>
@@ -4414,22 +4414,22 @@
         <v>3.28035550783898</v>
       </c>
       <c r="N6" t="n">
-        <v>2.454300934083968</v>
+        <v>3.19613647831618</v>
       </c>
       <c r="O6" t="n">
-        <v>3.234383972970493</v>
+        <v>3.234383972970497</v>
       </c>
       <c r="P6" t="n">
         <v>15.633572712292</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.59453125117626</v>
+        <v>15.59453125117625</v>
       </c>
       <c r="R6" t="n">
         <v>15.72090432891482</v>
       </c>
       <c r="S6" t="n">
-        <v>3.295137016249814</v>
+        <v>3.295137016249813</v>
       </c>
       <c r="T6" t="n">
         <v>15.61571015969225</v>
@@ -4438,25 +4438,25 @@
         <v>15.62509794999225</v>
       </c>
       <c r="V6" t="n">
-        <v>3.271224080290354</v>
+        <v>3.271224080290352</v>
       </c>
       <c r="W6" t="n">
-        <v>3.235344468864863</v>
+        <v>3.235344468864865</v>
       </c>
       <c r="X6" t="n">
-        <v>3.311984673991173</v>
+        <v>3.311984673991172</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.236436054715604</v>
+        <v>3.236436054715602</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.212364283807521</v>
+        <v>3.212364283807522</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.66923469582201</v>
+        <v>15.669234695822</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.224040516291701</v>
+        <v>3.224040516291702</v>
       </c>
     </row>
     <row r="7">
@@ -4469,7 +4469,7 @@
         <v>2.168158656587956</v>
       </c>
       <c r="C7" t="n">
-        <v>2.559011198492876</v>
+        <v>2.559011198492877</v>
       </c>
       <c r="D7" t="n">
         <v>2.310913704775206</v>
@@ -4481,19 +4481,19 @@
         <v>2.578905682149341</v>
       </c>
       <c r="G7" t="n">
-        <v>2.192910306557246</v>
+        <v>2.192910306557244</v>
       </c>
       <c r="H7" t="n">
         <v>2.20823543610559</v>
       </c>
       <c r="I7" t="n">
-        <v>2.239087826256456</v>
+        <v>2.239087826256457</v>
       </c>
       <c r="J7" t="n">
-        <v>2.233425364431425</v>
+        <v>2.233425364431424</v>
       </c>
       <c r="K7" t="n">
-        <v>2.23698720090686</v>
+        <v>2.236987200906859</v>
       </c>
       <c r="L7" t="n">
         <v>2.28049095845853</v>
@@ -4502,13 +4502,13 @@
         <v>2.248088664025314</v>
       </c>
       <c r="N7" t="n">
-        <v>2.454300934083968</v>
+        <v>2.165135622093425</v>
       </c>
       <c r="O7" t="n">
         <v>2.203379363652584</v>
       </c>
       <c r="P7" t="n">
-        <v>2.213043289410471</v>
+        <v>2.21304328941047</v>
       </c>
       <c r="Q7" t="n">
         <v>2.173075148792972</v>
@@ -4517,31 +4517,31 @@
         <v>2.299448226531529</v>
       </c>
       <c r="S7" t="n">
-        <v>2.262870172436146</v>
+        <v>2.262870172436145</v>
       </c>
       <c r="T7" t="n">
         <v>2.19425405730896</v>
       </c>
       <c r="U7" t="n">
-        <v>2.203668718774239</v>
+        <v>2.203668718774238</v>
       </c>
       <c r="V7" t="n">
-        <v>2.238957236476683</v>
+        <v>2.238957236476682</v>
       </c>
       <c r="W7" t="n">
-        <v>2.201919263044237</v>
+        <v>2.201919263044236</v>
       </c>
       <c r="X7" t="n">
-        <v>2.279717830177505</v>
+        <v>2.279717830177504</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.187126707499055</v>
+        <v>2.187126707499052</v>
       </c>
       <c r="Z7" t="n">
         <v>2.180097439993851</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.247778593438706</v>
+        <v>2.247778593438705</v>
       </c>
       <c r="AB7" t="n">
         <v>2.193187544043361</v>
@@ -4557,43 +4557,43 @@
         <v>2.177048021120553</v>
       </c>
       <c r="C8" t="n">
-        <v>2.617147122034081</v>
+        <v>2.61714712203408</v>
       </c>
       <c r="D8" t="n">
         <v>2.36904962831641</v>
       </c>
       <c r="E8" t="n">
-        <v>2.482895100023871</v>
+        <v>2.48289510002387</v>
       </c>
       <c r="F8" t="n">
         <v>2.595467085018069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.261257824919826</v>
+        <v>2.261257824919825</v>
       </c>
       <c r="H8" t="n">
-        <v>2.266371359646796</v>
+        <v>2.266371359646795</v>
       </c>
       <c r="I8" t="n">
-        <v>2.297223749797662</v>
+        <v>2.297223749797661</v>
       </c>
       <c r="J8" t="n">
-        <v>2.291561287972629</v>
+        <v>2.291561287972628</v>
       </c>
       <c r="K8" t="n">
-        <v>2.295123124448064</v>
+        <v>2.295123124448063</v>
       </c>
       <c r="L8" t="n">
         <v>2.338626881999735</v>
       </c>
       <c r="M8" t="n">
-        <v>2.30622458756651</v>
+        <v>2.306224587566509</v>
       </c>
       <c r="N8" t="n">
-        <v>2.454300934083968</v>
+        <v>2.185097223631339</v>
       </c>
       <c r="O8" t="n">
-        <v>2.233836042158078</v>
+        <v>2.233836042158077</v>
       </c>
       <c r="P8" t="n">
         <v>2.24092845975308</v>
@@ -4620,16 +4620,16 @@
         <v>2.260064864938142</v>
       </c>
       <c r="X8" t="n">
-        <v>2.283442666852268</v>
+        <v>2.283442666852267</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.294268877165525</v>
+        <v>2.294268877165522</v>
       </c>
       <c r="Z8" t="n">
         <v>2.188072024410404</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.30591451697991</v>
+        <v>2.305914516979909</v>
       </c>
       <c r="AB8" t="n">
         <v>2.30276561639234</v>
@@ -4651,7 +4651,7 @@
         <v>2.730916659175139</v>
       </c>
       <c r="E9" t="n">
-        <v>2.84655346129673</v>
+        <v>2.846553461296729</v>
       </c>
       <c r="F9" t="n">
         <v>2.754882968917314</v>
@@ -4663,25 +4663,25 @@
         <v>2.628238390505524</v>
       </c>
       <c r="I9" t="n">
-        <v>2.659090780656388</v>
+        <v>2.659090780656387</v>
       </c>
       <c r="J9" t="n">
-        <v>2.653428318831357</v>
+        <v>2.653428318831356</v>
       </c>
       <c r="K9" t="n">
-        <v>2.656990155306795</v>
+        <v>2.656990155306794</v>
       </c>
       <c r="L9" t="n">
-        <v>2.700493912858463</v>
+        <v>2.700493912858462</v>
       </c>
       <c r="M9" t="n">
-        <v>2.668091618425248</v>
+        <v>2.668091618425247</v>
       </c>
       <c r="N9" t="n">
-        <v>2.454300934083968</v>
+        <v>2.585138576493355</v>
       </c>
       <c r="O9" t="n">
-        <v>2.65846710339384</v>
+        <v>2.658467103393838</v>
       </c>
       <c r="P9" t="n">
         <v>2.675760403687346</v>
@@ -4696,28 +4696,28 @@
         <v>2.682873126836077</v>
       </c>
       <c r="T9" t="n">
-        <v>2.614257011708893</v>
+        <v>2.614257011708894</v>
       </c>
       <c r="U9" t="n">
-        <v>2.623644802008878</v>
+        <v>2.623644802008879</v>
       </c>
       <c r="V9" t="n">
-        <v>2.781115008675865</v>
+        <v>2.781115008675864</v>
       </c>
       <c r="W9" t="n">
         <v>2.621922217444168</v>
       </c>
       <c r="X9" t="n">
-        <v>2.699720784577437</v>
+        <v>2.699720784577436</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.607129661898988</v>
+        <v>2.607129661898989</v>
       </c>
       <c r="Z9" t="n">
         <v>2.536278974547673</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.667781547838636</v>
+        <v>2.667781547838635</v>
       </c>
       <c r="AB9" t="n">
         <v>2.613190498443292</v>
@@ -5098,7 +5098,7 @@
         <v>2.326025449846589</v>
       </c>
       <c r="N4" t="n">
-        <v>2.630435288418834</v>
+        <v>2.116941669381987</v>
       </c>
       <c r="O4" t="n">
         <v>2.157697330492536</v>
@@ -5274,7 +5274,7 @@
         <v>16.80098624213623</v>
       </c>
       <c r="N6" t="n">
-        <v>2.630435288418834</v>
+        <v>3.292418033535595</v>
       </c>
       <c r="O6" t="n">
         <v>16.63145970732298</v>
@@ -5362,7 +5362,7 @@
         <v>2.392915657678524</v>
       </c>
       <c r="N7" t="n">
-        <v>2.630435288418834</v>
+        <v>2.183831877213922</v>
       </c>
       <c r="O7" t="n">
         <v>2.224582759550136</v>
@@ -5450,7 +5450,7 @@
         <v>2.459681031152895</v>
       </c>
       <c r="N8" t="n">
-        <v>2.630435288418834</v>
+        <v>2.207785553107362</v>
       </c>
       <c r="O8" t="n">
         <v>2.260306240436872</v>
@@ -5538,7 +5538,7 @@
         <v>2.970743429545041</v>
       </c>
       <c r="N9" t="n">
-        <v>2.630435288418834</v>
+        <v>2.761659649080436</v>
       </c>
       <c r="O9" t="n">
         <v>2.849312551764913</v>
@@ -5958,7 +5958,7 @@
         <v>2.230769260571412</v>
       </c>
       <c r="N4" t="n">
-        <v>2.566766782647715</v>
+        <v>2.111457575095829</v>
       </c>
       <c r="O4" t="n">
         <v>2.155962484184635</v>
@@ -6134,7 +6134,7 @@
         <v>15.71287885532085</v>
       </c>
       <c r="N6" t="n">
-        <v>2.566766782647715</v>
+        <v>3.204074920929994</v>
       </c>
       <c r="O6" t="n">
         <v>15.63708890348497</v>
@@ -6222,7 +6222,7 @@
         <v>2.291191294915517</v>
       </c>
       <c r="N7" t="n">
-        <v>2.566766782647715</v>
+        <v>2.171879609439933</v>
       </c>
       <c r="O7" t="n">
         <v>2.216380084083682</v>
@@ -6310,7 +6310,7 @@
         <v>2.348854017463542</v>
       </c>
       <c r="N8" t="n">
-        <v>2.566766782647715</v>
+        <v>2.191714986728974</v>
       </c>
       <c r="O8" t="n">
         <v>2.246615178740711</v>
@@ -6398,7 +6398,7 @@
         <v>2.755833935715709</v>
       </c>
       <c r="N9" t="n">
-        <v>2.566766782647715</v>
+        <v>2.636522250240126</v>
       </c>
       <c r="O9" t="n">
         <v>2.719263639587593</v>
@@ -6818,7 +6818,7 @@
         <v>2.186724209373637</v>
       </c>
       <c r="N4" t="n">
-        <v>2.413112687863385</v>
+        <v>2.098591778032932</v>
       </c>
       <c r="O4" t="n">
         <v>2.141791443596902</v>
@@ -6994,7 +6994,7 @@
         <v>15.66408488525109</v>
       </c>
       <c r="N6" t="n">
-        <v>2.413112687863385</v>
+        <v>3.18891252044968</v>
       </c>
       <c r="O6" t="n">
         <v>3.232111949234068</v>
@@ -7082,7 +7082,7 @@
         <v>2.245702808203626</v>
       </c>
       <c r="N7" t="n">
-        <v>2.413112687863385</v>
+        <v>2.157570376862921</v>
       </c>
       <c r="O7" t="n">
         <v>2.200765658808405</v>
@@ -7170,7 +7170,7 @@
         <v>2.299997367109652</v>
       </c>
       <c r="N8" t="n">
-        <v>2.413112687863385</v>
+        <v>2.175584961792073</v>
       </c>
       <c r="O8" t="n">
         <v>2.228754679215432</v>
@@ -7258,7 +7258,7 @@
         <v>2.653771863322587</v>
       </c>
       <c r="N9" t="n">
-        <v>2.413112687863385</v>
+        <v>2.565639431981882</v>
       </c>
       <c r="O9" t="n">
         <v>2.642886838627526</v>
@@ -7678,7 +7678,7 @@
         <v>2.202468151893692</v>
       </c>
       <c r="N4" t="n">
-        <v>2.55144311233155</v>
+        <v>2.112535201895464</v>
       </c>
       <c r="O4" t="n">
         <v>2.147722405317159</v>
@@ -7854,7 +7854,7 @@
         <v>3.380215349339618</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55144311233155</v>
+        <v>3.288128825213758</v>
       </c>
       <c r="O6" t="n">
         <v>16.62180330135958</v>
@@ -7942,7 +7942,7 @@
         <v>2.26909869162873</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55144311233155</v>
+        <v>2.179165741630503</v>
       </c>
       <c r="O7" t="n">
         <v>2.214348162787982</v>
@@ -8030,7 +8030,7 @@
         <v>2.334869984134567</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55144311233155</v>
+        <v>2.202469772098759</v>
       </c>
       <c r="O8" t="n">
         <v>2.249327347861612</v>
@@ -8118,7 +8118,7 @@
         <v>2.853946320103698</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55144311233155</v>
+        <v>2.76401337010547</v>
       </c>
       <c r="O9" t="n">
         <v>2.84659110820097</v>
@@ -8538,7 +8538,7 @@
         <v>2.303064690971287</v>
       </c>
       <c r="N4" t="n">
-        <v>2.470460842603512</v>
+        <v>2.106612004428962</v>
       </c>
       <c r="O4" t="n">
         <v>2.151609806044521</v>
@@ -8714,7 +8714,7 @@
         <v>3.397828000308187</v>
       </c>
       <c r="N6" t="n">
-        <v>2.470460842603512</v>
+        <v>3.19989259713342</v>
       </c>
       <c r="O6" t="n">
         <v>15.6349519263031</v>
@@ -8802,7 +8802,7 @@
         <v>2.364600665392554</v>
       </c>
       <c r="N7" t="n">
-        <v>2.470460842603512</v>
+        <v>2.168147978850227</v>
       </c>
       <c r="O7" t="n">
         <v>2.213141340225525</v>
@@ -8890,7 +8890,7 @@
         <v>2.425023164898977</v>
       </c>
       <c r="N8" t="n">
-        <v>2.470460842603512</v>
+        <v>2.189456730071121</v>
       </c>
       <c r="O8" t="n">
         <v>2.245203329330831</v>
@@ -8978,7 +8978,7 @@
         <v>2.836534040182131</v>
       </c>
       <c r="N9" t="n">
-        <v>2.470460842603512</v>
+        <v>2.640081353639803</v>
       </c>
       <c r="O9" t="n">
         <v>2.723947585656769</v>

--- a/Results/Phase 2/Ammonia/ammonia water use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia water use results.xlsx
@@ -610,10 +610,10 @@
         <v>2.418336904764316</v>
       </c>
       <c r="J2" t="n">
-        <v>2.406634773869031</v>
+        <v>2.406634773869032</v>
       </c>
       <c r="K2" t="n">
-        <v>2.407646893450392</v>
+        <v>2.407646893450393</v>
       </c>
       <c r="L2" t="n">
         <v>2.407667404700605</v>
@@ -622,7 +622,7 @@
         <v>2.406967763912201</v>
       </c>
       <c r="N2" t="n">
-        <v>2.399709288144359</v>
+        <v>2.39970928814436</v>
       </c>
       <c r="O2" t="n">
         <v>2.432987340450447</v>
@@ -643,7 +643,7 @@
         <v>2.40056788845723</v>
       </c>
       <c r="U2" t="n">
-        <v>2.44093212855968</v>
+        <v>2.440932128559681</v>
       </c>
       <c r="V2" t="n">
         <v>2.406956801236386</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.411265517745634</v>
+        <v>2.412101596226728</v>
       </c>
       <c r="C3" t="n">
-        <v>2.723562531326078</v>
+        <v>2.735171015229424</v>
       </c>
       <c r="D3" t="n">
-        <v>2.724753522566105</v>
+        <v>2.736716879806352</v>
       </c>
       <c r="E3" t="n">
-        <v>2.692574785917628</v>
+        <v>2.703330791523858</v>
       </c>
       <c r="F3" t="n">
-        <v>2.698291208501121</v>
+        <v>2.709354568005101</v>
       </c>
       <c r="G3" t="n">
-        <v>2.427188836526554</v>
+        <v>2.428584078979918</v>
       </c>
       <c r="H3" t="n">
-        <v>2.429010112489429</v>
+        <v>2.430488510606487</v>
       </c>
       <c r="I3" t="n">
-        <v>2.540096348911874</v>
+        <v>2.545515734292622</v>
       </c>
       <c r="J3" t="n">
-        <v>2.456017170148726</v>
+        <v>2.458437313564676</v>
       </c>
       <c r="K3" t="n">
-        <v>2.463431248704039</v>
+        <v>2.466122308832424</v>
       </c>
       <c r="L3" t="n">
-        <v>2.463374787951338</v>
+        <v>2.466050638796578</v>
       </c>
       <c r="M3" t="n">
-        <v>2.459451473487251</v>
+        <v>2.462015864067499</v>
       </c>
       <c r="N3" t="n">
-        <v>2.406615763175858</v>
+        <v>2.407292317993035</v>
       </c>
       <c r="O3" t="n">
-        <v>2.471992345942413</v>
+        <v>2.473144321944413</v>
       </c>
       <c r="P3" t="n">
-        <v>2.444876878825272</v>
+        <v>2.446889978589665</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.40466542278282</v>
+        <v>2.405273580410939</v>
       </c>
       <c r="R3" t="n">
-        <v>2.523458929490867</v>
+        <v>2.528293588721885</v>
       </c>
       <c r="S3" t="n">
-        <v>2.476392835541885</v>
+        <v>2.479524274764859</v>
       </c>
       <c r="T3" t="n">
-        <v>2.412795918073654</v>
+        <v>2.413693580076024</v>
       </c>
       <c r="U3" t="n">
-        <v>2.528994023056435</v>
+        <v>2.532162189474346</v>
       </c>
       <c r="V3" t="n">
-        <v>2.458091257103928</v>
+        <v>2.46057714399352</v>
       </c>
       <c r="W3" t="n">
-        <v>2.500967750989907</v>
+        <v>2.502913694809315</v>
       </c>
       <c r="X3" t="n">
-        <v>2.467732877914438</v>
+        <v>2.470578432645065</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.426204063552926</v>
+        <v>2.427572686289329</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.453680607430978</v>
+        <v>2.454927036215009</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.530913286536242</v>
+        <v>2.53597873026593</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.41622410709707</v>
+        <v>2.417247339848215</v>
       </c>
     </row>
     <row r="4">
@@ -765,13 +765,13 @@
         <v>2.122580202969871</v>
       </c>
       <c r="C4" t="n">
-        <v>2.601812501908985</v>
+        <v>2.601812501908984</v>
       </c>
       <c r="D4" t="n">
         <v>2.617002599302984</v>
       </c>
       <c r="E4" t="n">
-        <v>2.567766159165569</v>
+        <v>2.56776615916557</v>
       </c>
       <c r="F4" t="n">
         <v>2.57458429502244</v>
@@ -792,10 +792,10 @@
         <v>2.204726031389983</v>
       </c>
       <c r="L4" t="n">
-        <v>2.204957715396772</v>
+        <v>2.204957715396774</v>
       </c>
       <c r="M4" t="n">
-        <v>2.198506060285256</v>
+        <v>2.198506060285255</v>
       </c>
       <c r="N4" t="n">
         <v>2.115067127979503</v>
@@ -819,7 +819,7 @@
         <v>2.124765413489031</v>
       </c>
       <c r="U4" t="n">
-        <v>2.227290726145028</v>
+        <v>2.227290726145027</v>
       </c>
       <c r="V4" t="n">
         <v>2.196994821077154</v>
@@ -828,16 +828,16 @@
         <v>2.172049394362677</v>
       </c>
       <c r="X4" t="n">
-        <v>2.211551687790759</v>
+        <v>2.21155168779076</v>
       </c>
       <c r="Y4" t="n">
         <v>2.146173500509866</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.141059878031945</v>
+        <v>2.141059878031946</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.311679049001543</v>
+        <v>2.311679049001544</v>
       </c>
       <c r="AB4" t="n">
         <v>2.130364596679949</v>
@@ -856,13 +856,13 @@
         <v>12.85462616761466</v>
       </c>
       <c r="D5" t="n">
-        <v>13.34748039117923</v>
+        <v>13.3474803911792</v>
       </c>
       <c r="E5" t="n">
-        <v>11.72082245389331</v>
+        <v>11.7208224538933</v>
       </c>
       <c r="F5" t="n">
-        <v>12.69519251411143</v>
+        <v>12.69519251411145</v>
       </c>
       <c r="G5" t="n">
         <v>3.242913491519423</v>
@@ -871,64 +871,64 @@
         <v>3.475752472588586</v>
       </c>
       <c r="I5" t="n">
-        <v>7.206377802718711</v>
+        <v>7.206377802718714</v>
       </c>
       <c r="J5" t="n">
-        <v>4.211434078045261</v>
+        <v>4.211434078045266</v>
       </c>
       <c r="K5" t="n">
-        <v>4.55487725111555</v>
+        <v>4.554877251115548</v>
       </c>
       <c r="L5" t="n">
-        <v>4.438978692482667</v>
+        <v>4.438978692482594</v>
       </c>
       <c r="M5" t="n">
-        <v>4.476448811975223</v>
+        <v>4.476448811975215</v>
       </c>
       <c r="N5" t="n">
-        <v>2.651628247835907</v>
+        <v>2.651628247835906</v>
       </c>
       <c r="O5" t="n">
-        <v>2.995286672442975</v>
+        <v>2.995286672442971</v>
       </c>
       <c r="P5" t="n">
-        <v>3.762054141469441</v>
+        <v>3.762054141469446</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.592437096538006</v>
+        <v>2.592437096538004</v>
       </c>
       <c r="R5" t="n">
-        <v>6.7000710349051</v>
+        <v>6.700071034905103</v>
       </c>
       <c r="S5" t="n">
-        <v>4.750681566890085</v>
+        <v>4.750681566890094</v>
       </c>
       <c r="T5" t="n">
         <v>2.87800444807127</v>
       </c>
       <c r="U5" t="n">
-        <v>4.832659811928045</v>
+        <v>4.83265981192805</v>
       </c>
       <c r="V5" t="n">
-        <v>4.151450374621873</v>
+        <v>4.151450374621875</v>
       </c>
       <c r="W5" t="n">
         <v>3.793718024521738</v>
       </c>
       <c r="X5" t="n">
-        <v>4.685692459035249</v>
+        <v>4.685692459035246</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.271532993891267</v>
+        <v>3.271532993891271</v>
       </c>
       <c r="Z5" t="n">
         <v>3.113334554405597</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.651413257535824</v>
+        <v>6.65141325753583</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.038714318704859</v>
+        <v>3.03871431870486</v>
       </c>
     </row>
     <row r="6">
@@ -938,22 +938,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.380596962652827</v>
+        <v>3.38059696265283</v>
       </c>
       <c r="C6" t="n">
-        <v>18.06977135067768</v>
+        <v>18.06977135067769</v>
       </c>
       <c r="D6" t="n">
-        <v>18.08496144807169</v>
+        <v>18.0849614480717</v>
       </c>
       <c r="E6" t="n">
-        <v>18.03572500793429</v>
+        <v>18.0357250079343</v>
       </c>
       <c r="F6" t="n">
-        <v>3.832601054705397</v>
+        <v>3.832601054705398</v>
       </c>
       <c r="G6" t="n">
-        <v>17.61576718611004</v>
+        <v>17.61576718611005</v>
       </c>
       <c r="H6" t="n">
         <v>17.61815781456068</v>
@@ -962,43 +962,43 @@
         <v>3.583491386511883</v>
       </c>
       <c r="J6" t="n">
-        <v>3.451332161311081</v>
+        <v>3.451332161311082</v>
       </c>
       <c r="K6" t="n">
-        <v>17.67268488015867</v>
+        <v>17.67268488015869</v>
       </c>
       <c r="L6" t="n">
-        <v>17.67291656416547</v>
+        <v>17.67291656416549</v>
       </c>
       <c r="M6" t="n">
         <v>17.66646490905397</v>
       </c>
       <c r="N6" t="n">
-        <v>3.370785312917368</v>
+        <v>3.370785312917365</v>
       </c>
       <c r="O6" t="n">
-        <v>3.392622809302435</v>
+        <v>3.392622809302434</v>
       </c>
       <c r="P6" t="n">
-        <v>17.64299670650758</v>
+        <v>17.64299670650759</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.57993091577396</v>
+        <v>17.57993091577395</v>
       </c>
       <c r="R6" t="n">
-        <v>17.76703486339379</v>
+        <v>17.76703486339381</v>
       </c>
       <c r="S6" t="n">
-        <v>3.48386787141998</v>
+        <v>3.483867871419982</v>
       </c>
       <c r="T6" t="n">
-        <v>3.382782173171986</v>
+        <v>3.382782173171988</v>
       </c>
       <c r="U6" t="n">
-        <v>3.485214932869475</v>
+        <v>3.485214932869476</v>
       </c>
       <c r="V6" t="n">
-        <v>17.66495366984587</v>
+        <v>17.66495366984589</v>
       </c>
       <c r="W6" t="n">
         <v>17.63911826865523</v>
@@ -1007,13 +1007,13 @@
         <v>17.67951053655947</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.422885015844092</v>
+        <v>3.422885015844093</v>
       </c>
       <c r="Z6" t="n">
         <v>3.399076637714904</v>
       </c>
       <c r="AA6" t="n">
-        <v>17.77963789777027</v>
+        <v>17.77963789777026</v>
       </c>
       <c r="AB6" t="n">
         <v>3.385640380843339</v>
@@ -1056,7 +1056,7 @@
         <v>2.275354193055128</v>
       </c>
       <c r="L7" t="n">
-        <v>2.275585877061917</v>
+        <v>2.275585877061919</v>
       </c>
       <c r="M7" t="n">
         <v>2.2691342219504</v>
@@ -1065,13 +1065,13 @@
         <v>2.185695289644649</v>
       </c>
       <c r="O7" t="n">
-        <v>2.207527679598447</v>
+        <v>2.207527679598446</v>
       </c>
       <c r="P7" t="n">
         <v>2.246550939937186</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.182600228670388</v>
+        <v>2.182600228670389</v>
       </c>
       <c r="R7" t="n">
         <v>2.369704176290222</v>
@@ -1086,13 +1086,13 @@
         <v>2.297814960728775</v>
       </c>
       <c r="V7" t="n">
-        <v>2.267622982742299</v>
+        <v>2.2676229827423</v>
       </c>
       <c r="W7" t="n">
         <v>2.242677556027823</v>
       </c>
       <c r="X7" t="n">
-        <v>2.282179849455905</v>
+        <v>2.282179849455904</v>
       </c>
       <c r="Y7" t="n">
         <v>2.216709109216503</v>
@@ -1129,7 +1129,7 @@
         <v>2.665101494703953</v>
       </c>
       <c r="G8" t="n">
-        <v>2.29882915858975</v>
+        <v>2.298829158589751</v>
       </c>
       <c r="H8" t="n">
         <v>2.289289205594355</v>
@@ -1141,19 +1141,19 @@
         <v>2.332405641430511</v>
       </c>
       <c r="K8" t="n">
-        <v>2.343816271192363</v>
+        <v>2.343816271192364</v>
       </c>
       <c r="L8" t="n">
-        <v>2.344047955199152</v>
+        <v>2.344047955199157</v>
       </c>
       <c r="M8" t="n">
-        <v>2.337596300087633</v>
+        <v>2.337596300087632</v>
       </c>
       <c r="N8" t="n">
         <v>2.209556904703817</v>
       </c>
       <c r="O8" t="n">
-        <v>2.243650935049182</v>
+        <v>2.243650935049181</v>
       </c>
       <c r="P8" t="n">
         <v>2.279669807913124</v>
@@ -1168,10 +1168,10 @@
         <v>2.364941351539402</v>
       </c>
       <c r="T8" t="n">
-        <v>2.263855653291412</v>
+        <v>2.263855653291413</v>
       </c>
       <c r="U8" t="n">
-        <v>2.338200679596126</v>
+        <v>2.338200679596127</v>
       </c>
       <c r="V8" t="n">
         <v>2.32035404105176</v>
@@ -1192,7 +1192,7 @@
         <v>2.450769288803925</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.329556589132735</v>
+        <v>2.329556589132736</v>
       </c>
     </row>
     <row r="9">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.738061146542313</v>
+        <v>2.738061146542315</v>
       </c>
       <c r="C9" t="n">
         <v>3.389996726403786</v>
@@ -1211,10 +1211,10 @@
         <v>3.40518682379779</v>
       </c>
       <c r="E9" t="n">
-        <v>3.316091178579199</v>
+        <v>3.3160911785792</v>
       </c>
       <c r="F9" t="n">
-        <v>2.964640308707352</v>
+        <v>2.964640308707353</v>
       </c>
       <c r="G9" t="n">
         <v>2.935992571861911</v>
@@ -1226,7 +1226,7 @@
         <v>3.113658851323726</v>
       </c>
       <c r="J9" t="n">
-        <v>2.981499626122934</v>
+        <v>2.981499626122935</v>
       </c>
       <c r="K9" t="n">
         <v>2.992910255884787</v>
@@ -1238,13 +1238,13 @@
         <v>2.986690284780059</v>
       </c>
       <c r="N9" t="n">
-        <v>2.903251352474305</v>
+        <v>2.903251352474306</v>
       </c>
       <c r="O9" t="n">
         <v>2.982322442820503</v>
       </c>
       <c r="P9" t="n">
-        <v>3.033793038870421</v>
+        <v>3.033793038870422</v>
       </c>
       <c r="Q9" t="n">
         <v>2.900156301525828</v>
@@ -1253,16 +1253,16 @@
         <v>3.087260239119877</v>
       </c>
       <c r="S9" t="n">
-        <v>3.014035336231823</v>
+        <v>3.014035336231824</v>
       </c>
       <c r="T9" t="n">
         <v>2.912949637983838</v>
       </c>
       <c r="U9" t="n">
-        <v>3.015382397681323</v>
+        <v>3.015382397681322</v>
       </c>
       <c r="V9" t="n">
-        <v>3.18447485001274</v>
+        <v>3.184474850012741</v>
       </c>
       <c r="W9" t="n">
         <v>2.960233618857482</v>
@@ -1271,7 +1271,7 @@
         <v>2.999735912285565</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.93426517204616</v>
+        <v>2.934265172046161</v>
       </c>
       <c r="Z9" t="n">
         <v>2.82511938548668</v>
@@ -1280,7 +1280,7 @@
         <v>3.099863273496345</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.918548821174752</v>
+        <v>2.918548821174753</v>
       </c>
     </row>
   </sheetData>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.391629213700597</v>
+        <v>2.391629213700598</v>
       </c>
       <c r="C2" t="n">
         <v>2.433474677306433</v>
@@ -1455,13 +1455,13 @@
         <v>2.399530484516952</v>
       </c>
       <c r="E2" t="n">
-        <v>2.418106724953188</v>
+        <v>2.418106724953189</v>
       </c>
       <c r="F2" t="n">
         <v>2.436523124788455</v>
       </c>
       <c r="G2" t="n">
-        <v>2.393861434136306</v>
+        <v>2.393861434136307</v>
       </c>
       <c r="H2" t="n">
         <v>2.397579734498809</v>
@@ -1473,7 +1473,7 @@
         <v>2.39896389632799</v>
       </c>
       <c r="K2" t="n">
-        <v>2.400841895758792</v>
+        <v>2.400841895758791</v>
       </c>
       <c r="L2" t="n">
         <v>2.404802203758543</v>
@@ -1497,31 +1497,31 @@
         <v>2.399884612228977</v>
       </c>
       <c r="S2" t="n">
-        <v>2.403865962289795</v>
+        <v>2.403865962289797</v>
       </c>
       <c r="T2" t="n">
-        <v>2.395090493857476</v>
+        <v>2.395090493857477</v>
       </c>
       <c r="U2" t="n">
-        <v>2.429050294255111</v>
+        <v>2.429050294255112</v>
       </c>
       <c r="V2" t="n">
         <v>2.397879896977531</v>
       </c>
       <c r="W2" t="n">
-        <v>2.43075295327561</v>
+        <v>2.430752953275611</v>
       </c>
       <c r="X2" t="n">
-        <v>2.403204766187488</v>
+        <v>2.40320476618749</v>
       </c>
       <c r="Y2" t="n">
         <v>2.393415436472297</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.410015106967889</v>
+        <v>2.410015106967891</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.397482113791853</v>
+        <v>2.397482113791852</v>
       </c>
       <c r="AB2" t="n">
         <v>2.395310989058629</v>
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.388950925997256</v>
+        <v>2.389157644950207</v>
       </c>
       <c r="C3" t="n">
-        <v>2.659398364476564</v>
+        <v>2.668947961494856</v>
       </c>
       <c r="D3" t="n">
-        <v>2.44533518919915</v>
+        <v>2.447550424071393</v>
       </c>
       <c r="E3" t="n">
-        <v>2.577099045984045</v>
+        <v>2.583966477335498</v>
       </c>
       <c r="F3" t="n">
-        <v>2.709718871930274</v>
+        <v>2.721384531406736</v>
       </c>
       <c r="G3" t="n">
-        <v>2.404791199167071</v>
+        <v>2.405556417721848</v>
       </c>
       <c r="H3" t="n">
-        <v>2.431624593207775</v>
+        <v>2.433355632938521</v>
       </c>
       <c r="I3" t="n">
-        <v>2.440425284622143</v>
+        <v>2.442465145403367</v>
       </c>
       <c r="J3" t="n">
-        <v>2.441207830896325</v>
+        <v>2.443271621295268</v>
       </c>
       <c r="K3" t="n">
-        <v>2.454418469370801</v>
+        <v>2.456963219236439</v>
       </c>
       <c r="L3" t="n">
-        <v>2.482495886705472</v>
+        <v>2.486017846200365</v>
       </c>
       <c r="M3" t="n">
-        <v>2.469032154709305</v>
+        <v>2.47210058310705</v>
       </c>
       <c r="N3" t="n">
-        <v>2.397967609328091</v>
+        <v>2.398494503966642</v>
       </c>
       <c r="O3" t="n">
-        <v>2.477255130174679</v>
+        <v>2.478685749908501</v>
       </c>
       <c r="P3" t="n">
-        <v>2.444643663269848</v>
+        <v>2.446808903276113</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.391847088864577</v>
+        <v>2.392158044443411</v>
       </c>
       <c r="R3" t="n">
-        <v>2.448105402756303</v>
+        <v>2.450419390980112</v>
       </c>
       <c r="S3" t="n">
-        <v>2.475789956061033</v>
+        <v>2.479066078213374</v>
       </c>
       <c r="T3" t="n">
-        <v>2.413732699673109</v>
+        <v>2.414821093622534</v>
       </c>
       <c r="U3" t="n">
-        <v>2.486443450985509</v>
+        <v>2.488299916512541</v>
       </c>
       <c r="V3" t="n">
-        <v>2.433308003958032</v>
+        <v>2.435080412177307</v>
       </c>
       <c r="W3" t="n">
-        <v>2.476239059826369</v>
+        <v>2.477489866988241</v>
       </c>
       <c r="X3" t="n">
-        <v>2.47147025866794</v>
+        <v>2.474615580261185</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.401717285224548</v>
+        <v>2.402376186273511</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.425829920556866</v>
+        <v>2.426337491798092</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.430755747017422</v>
+        <v>2.432439922262189</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.415959410192045</v>
+        <v>2.417127852270461</v>
       </c>
     </row>
     <row r="4">
@@ -1634,10 +1634,10 @@
         <v>2.387272655724379</v>
       </c>
       <c r="F4" t="n">
-        <v>2.595294363826207</v>
+        <v>2.595294363826206</v>
       </c>
       <c r="G4" t="n">
-        <v>2.113410942562876</v>
+        <v>2.113410942562875</v>
       </c>
       <c r="H4" t="n">
         <v>2.155410855660022</v>
@@ -1673,13 +1673,13 @@
         <v>2.181445509918415</v>
       </c>
       <c r="S4" t="n">
-        <v>2.226416690366868</v>
+        <v>2.226416690366867</v>
       </c>
       <c r="T4" t="n">
         <v>2.127293737508894</v>
       </c>
       <c r="U4" t="n">
-        <v>2.162480333263688</v>
+        <v>2.162480333263687</v>
       </c>
       <c r="V4" t="n">
         <v>2.158908225647412</v>
@@ -1688,10 +1688,10 @@
         <v>2.134943914199154</v>
       </c>
       <c r="X4" t="n">
-        <v>2.218948176226077</v>
+        <v>2.218948176226078</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.108551464869568</v>
+        <v>2.108551464869567</v>
       </c>
       <c r="Z4" t="n">
         <v>2.10176687566124</v>
@@ -1700,7 +1700,7 @@
         <v>2.15430818486721</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.130871924615892</v>
+        <v>2.130871924615893</v>
       </c>
     </row>
     <row r="5">
@@ -1710,49 +1710,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.192381894404154</v>
+        <v>2.192381894404153</v>
       </c>
       <c r="C5" t="n">
-        <v>9.346029782875126</v>
+        <v>9.346029782875146</v>
       </c>
       <c r="D5" t="n">
-        <v>3.76700173910479</v>
+        <v>3.767001739104789</v>
       </c>
       <c r="E5" t="n">
-        <v>7.055427225982791</v>
+        <v>7.055427225982794</v>
       </c>
       <c r="F5" t="n">
         <v>11.34668998963254</v>
       </c>
       <c r="G5" t="n">
-        <v>2.59107263858255</v>
+        <v>2.591072638582565</v>
       </c>
       <c r="H5" t="n">
-        <v>3.487148920365581</v>
+        <v>3.487148920365578</v>
       </c>
       <c r="I5" t="n">
-        <v>3.689612501209998</v>
+        <v>3.689612501209997</v>
       </c>
       <c r="J5" t="n">
-        <v>3.61051915270409</v>
+        <v>3.610519152704096</v>
       </c>
       <c r="K5" t="n">
-        <v>3.88579437441225</v>
+        <v>3.885794374412249</v>
       </c>
       <c r="L5" t="n">
         <v>4.57981390996351</v>
       </c>
       <c r="M5" t="n">
-        <v>4.461237180095863</v>
+        <v>4.461237180095861</v>
       </c>
       <c r="N5" t="n">
-        <v>2.455833555757122</v>
+        <v>2.455833555757121</v>
       </c>
       <c r="O5" t="n">
         <v>3.056438038466271</v>
       </c>
       <c r="P5" t="n">
-        <v>3.588765455416251</v>
+        <v>3.588765455416249</v>
       </c>
       <c r="Q5" t="n">
         <v>2.277332010408535</v>
@@ -1761,34 +1761,34 @@
         <v>3.963566881571212</v>
       </c>
       <c r="S5" t="n">
-        <v>4.380372271055424</v>
+        <v>4.380372271055422</v>
       </c>
       <c r="T5" t="n">
         <v>2.924524412588211</v>
       </c>
       <c r="U5" t="n">
-        <v>3.363068264434046</v>
+        <v>3.363068264434047</v>
       </c>
       <c r="V5" t="n">
-        <v>3.309427374317957</v>
+        <v>3.309427374317956</v>
       </c>
       <c r="W5" t="n">
-        <v>3.020000554559964</v>
+        <v>3.020000554559961</v>
       </c>
       <c r="X5" t="n">
-        <v>4.455202320790822</v>
+        <v>4.455202320790825</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.558558566615912</v>
+        <v>2.558558566615913</v>
       </c>
       <c r="Z5" t="n">
         <v>2.400580144445538</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.378448324556244</v>
+        <v>3.378448324556246</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.019999841715599</v>
+        <v>3.019999841715601</v>
       </c>
     </row>
     <row r="6">
@@ -1798,28 +1798,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.180835854165581</v>
+        <v>3.18083585416558</v>
       </c>
       <c r="C6" t="n">
-        <v>15.98485009206703</v>
+        <v>15.98485009206704</v>
       </c>
       <c r="D6" t="n">
-        <v>3.270084342800468</v>
+        <v>3.270084342800466</v>
       </c>
       <c r="E6" t="n">
-        <v>15.86794823001562</v>
+        <v>15.86794823001564</v>
       </c>
       <c r="F6" t="n">
-        <v>16.07596993811747</v>
+        <v>16.07596993811746</v>
       </c>
       <c r="G6" t="n">
-        <v>3.206049810859039</v>
+        <v>3.206049810859037</v>
       </c>
       <c r="H6" t="n">
-        <v>3.248049723956188</v>
+        <v>3.248049723956187</v>
       </c>
       <c r="I6" t="n">
-        <v>3.262119820451435</v>
+        <v>3.262119820451434</v>
       </c>
       <c r="J6" t="n">
         <v>15.6517494046248</v>
@@ -1837,7 +1837,7 @@
         <v>3.193764807008485</v>
       </c>
       <c r="O6" t="n">
-        <v>15.62320126248977</v>
+        <v>15.62320126248976</v>
       </c>
       <c r="P6" t="n">
         <v>3.265369354717851</v>
@@ -1846,10 +1846,10 @@
         <v>3.18540693930415</v>
       </c>
       <c r="R6" t="n">
-        <v>3.274084378214579</v>
+        <v>3.274084378214578</v>
       </c>
       <c r="S6" t="n">
-        <v>15.70709226465812</v>
+        <v>15.70709226465811</v>
       </c>
       <c r="T6" t="n">
         <v>3.21993260580506</v>
@@ -1858,22 +1858,22 @@
         <v>15.64297763646422</v>
       </c>
       <c r="V6" t="n">
-        <v>3.251547093943577</v>
+        <v>3.251547093943576</v>
       </c>
       <c r="W6" t="n">
-        <v>3.228690503160967</v>
+        <v>3.228690503160965</v>
       </c>
       <c r="X6" t="n">
         <v>15.69962375051731</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.217967269007588</v>
+        <v>3.217967269007587</v>
       </c>
       <c r="Z6" t="n">
         <v>3.194405743957403</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.63498375915847</v>
+        <v>15.63498375915848</v>
       </c>
       <c r="AB6" t="n">
         <v>3.222104083607249</v>
@@ -1889,10 +1889,10 @@
         <v>2.14839575009032</v>
       </c>
       <c r="C7" t="n">
-        <v>2.564373281996692</v>
+        <v>2.564373281996693</v>
       </c>
       <c r="D7" t="n">
-        <v>2.237644238725209</v>
+        <v>2.23764423872521</v>
       </c>
       <c r="E7" t="n">
         <v>2.447471419945285</v>
@@ -1904,10 +1904,10 @@
         <v>2.173609706783784</v>
       </c>
       <c r="H7" t="n">
-        <v>2.21560961988093</v>
+        <v>2.215609619880931</v>
       </c>
       <c r="I7" t="n">
-        <v>2.229679716376177</v>
+        <v>2.229679716376176</v>
       </c>
       <c r="J7" t="n">
         <v>2.231272594554474</v>
@@ -1919,10 +1919,10 @@
         <v>2.297190732669641</v>
       </c>
       <c r="M7" t="n">
-        <v>2.275089709744634</v>
+        <v>2.275089709744633</v>
       </c>
       <c r="N7" t="n">
-        <v>2.162630313301608</v>
+        <v>2.162630313301607</v>
       </c>
       <c r="O7" t="n">
         <v>2.203750234190684</v>
@@ -1940,7 +1940,7 @@
         <v>2.286615454587776</v>
       </c>
       <c r="T7" t="n">
-        <v>2.187492501729802</v>
+        <v>2.187492501729803</v>
       </c>
       <c r="U7" t="n">
         <v>2.222505454375558</v>
@@ -1952,7 +1952,7 @@
         <v>2.195142678420063</v>
       </c>
       <c r="X7" t="n">
-        <v>2.279146940446986</v>
+        <v>2.279146940446985</v>
       </c>
       <c r="Y7" t="n">
         <v>2.168571957999749</v>
@@ -1961,7 +1961,7 @@
         <v>2.161965639882149</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.214506949088119</v>
+        <v>2.21450694908812</v>
       </c>
       <c r="AB7" t="n">
         <v>2.191070688836801</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.157252678571397</v>
+        <v>2.157252678571398</v>
       </c>
       <c r="C8" t="n">
-        <v>2.621939122877326</v>
+        <v>2.621939122877324</v>
       </c>
       <c r="D8" t="n">
         <v>2.295210079605843</v>
@@ -1989,7 +1989,7 @@
         <v>2.671938335806309</v>
       </c>
       <c r="G8" t="n">
-        <v>2.241275657958985</v>
+        <v>2.241275657958984</v>
       </c>
       <c r="H8" t="n">
         <v>2.273175460761565</v>
@@ -2028,7 +2028,7 @@
         <v>2.34418129546841</v>
       </c>
       <c r="T8" t="n">
-        <v>2.245058342610437</v>
+        <v>2.245058342610436</v>
       </c>
       <c r="U8" t="n">
         <v>2.256299492353508</v>
@@ -2049,7 +2049,7 @@
         <v>2.169917775308946</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.272072789968752</v>
+        <v>2.272072789968753</v>
       </c>
       <c r="AB8" t="n">
         <v>2.299517061685131</v>
@@ -2065,7 +2065,7 @@
         <v>2.458697854599865</v>
       </c>
       <c r="C9" t="n">
-        <v>2.979242327496936</v>
+        <v>2.979242327496935</v>
       </c>
       <c r="D9" t="n">
         <v>2.652513284225456</v>
@@ -2095,7 +2095,7 @@
         <v>2.712059778169885</v>
       </c>
       <c r="M9" t="n">
-        <v>2.689958755244879</v>
+        <v>2.68995875524488</v>
       </c>
       <c r="N9" t="n">
         <v>2.577499358801854</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.399905025709628</v>
+        <v>2.399905025709629</v>
       </c>
       <c r="C2" t="n">
         <v>2.446788843352677</v>
@@ -2342,7 +2342,7 @@
         <v>2.407057931686444</v>
       </c>
       <c r="N2" t="n">
-        <v>2.399691757147235</v>
+        <v>2.399691757147234</v>
       </c>
       <c r="O2" t="n">
         <v>2.435373547595248</v>
@@ -2384,7 +2384,7 @@
         <v>2.413572367190197</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.400857717531876</v>
+        <v>2.400857717531878</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.407800818759129</v>
+        <v>2.408504766712097</v>
       </c>
       <c r="C3" t="n">
-        <v>2.713514051165993</v>
+        <v>2.724783159560804</v>
       </c>
       <c r="D3" t="n">
-        <v>2.599401887703394</v>
+        <v>2.606908157165606</v>
       </c>
       <c r="E3" t="n">
-        <v>2.68118387175308</v>
+        <v>2.69152961551497</v>
       </c>
       <c r="F3" t="n">
-        <v>2.722354705039877</v>
+        <v>2.734279490796021</v>
       </c>
       <c r="G3" t="n">
-        <v>2.425576672456037</v>
+        <v>2.426905321506965</v>
       </c>
       <c r="H3" t="n">
-        <v>2.442102411607931</v>
+        <v>2.444037103735769</v>
       </c>
       <c r="I3" t="n">
-        <v>2.566098132309003</v>
+        <v>2.572430450882587</v>
       </c>
       <c r="J3" t="n">
-        <v>2.45719812128096</v>
+        <v>2.459652208056072</v>
       </c>
       <c r="K3" t="n">
-        <v>2.475985843356527</v>
+        <v>2.479122061234802</v>
       </c>
       <c r="L3" t="n">
-        <v>2.481190321801019</v>
+        <v>2.484483909175937</v>
       </c>
       <c r="M3" t="n">
-        <v>2.459865369182648</v>
+        <v>2.462434155511017</v>
       </c>
       <c r="N3" t="n">
-        <v>2.406364316538772</v>
+        <v>2.407021501754723</v>
       </c>
       <c r="O3" t="n">
-        <v>2.481606274206298</v>
+        <v>2.483009971678601</v>
       </c>
       <c r="P3" t="n">
-        <v>2.444887805314341</v>
+        <v>2.446891135122612</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4050319105061</v>
+        <v>2.405642668332064</v>
       </c>
       <c r="R3" t="n">
-        <v>2.518309140404439</v>
+        <v>2.522950132879658</v>
       </c>
       <c r="S3" t="n">
-        <v>2.49702600425951</v>
+        <v>2.500875630512838</v>
       </c>
       <c r="T3" t="n">
-        <v>2.41225521019758</v>
+        <v>2.413123327153825</v>
       </c>
       <c r="U3" t="n">
-        <v>2.521673785307906</v>
+        <v>2.524565348745467</v>
       </c>
       <c r="V3" t="n">
-        <v>2.463873376507516</v>
+        <v>2.466556931180061</v>
       </c>
       <c r="W3" t="n">
-        <v>2.493819107103987</v>
+        <v>2.495493817019611</v>
       </c>
       <c r="X3" t="n">
-        <v>2.470762161302913</v>
+        <v>2.473705416926478</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.426061175615828</v>
+        <v>2.427414869988495</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.452754463808905</v>
+        <v>2.453955215002251</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.505432027698827</v>
+        <v>2.509588866878292</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.415903392066709</v>
+        <v>2.416904297650593</v>
       </c>
     </row>
     <row r="4">
@@ -2491,7 +2491,7 @@
         <v>2.418828228309597</v>
       </c>
       <c r="E4" t="n">
-        <v>2.549433782864438</v>
+        <v>2.549433782864437</v>
       </c>
       <c r="F4" t="n">
         <v>2.612796145388358</v>
@@ -2512,7 +2512,7 @@
         <v>2.224636823276584</v>
       </c>
       <c r="L4" t="n">
-        <v>2.23277162536457</v>
+        <v>2.232771625364576</v>
       </c>
       <c r="M4" t="n">
         <v>2.198782508957231</v>
@@ -2521,19 +2521,19 @@
         <v>2.114283511916984</v>
       </c>
       <c r="O4" t="n">
-        <v>2.14837048759219</v>
+        <v>2.148370487592189</v>
       </c>
       <c r="P4" t="n">
         <v>2.175567093734932</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.112169643007368</v>
+        <v>2.112169643007369</v>
       </c>
       <c r="R4" t="n">
         <v>2.290577118752108</v>
       </c>
       <c r="S4" t="n">
-        <v>2.258278010784729</v>
+        <v>2.258278010784728</v>
       </c>
       <c r="T4" t="n">
         <v>2.123533694799985</v>
@@ -2548,7 +2548,7 @@
         <v>2.159974668098564</v>
       </c>
       <c r="X4" t="n">
-        <v>2.215983340139485</v>
+        <v>2.215983340139489</v>
       </c>
       <c r="Y4" t="n">
         <v>2.14575357791525</v>
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.598093633823609</v>
+        <v>2.598093633823761</v>
       </c>
       <c r="C5" t="n">
-        <v>11.6403000722266</v>
+        <v>11.64030007222658</v>
       </c>
       <c r="D5" t="n">
         <v>8.698060748477648</v>
       </c>
       <c r="E5" t="n">
-        <v>10.75526746620946</v>
+        <v>10.75526746620949</v>
       </c>
       <c r="F5" t="n">
         <v>12.58468833887212</v>
       </c>
       <c r="G5" t="n">
-        <v>3.110875793924029</v>
+        <v>3.110875793924017</v>
       </c>
       <c r="H5" t="n">
-        <v>3.804008271465176</v>
+        <v>3.804008271465175</v>
       </c>
       <c r="I5" t="n">
-        <v>7.711932332913304</v>
+        <v>7.711932332913316</v>
       </c>
       <c r="J5" t="n">
-        <v>4.094940026115967</v>
+        <v>4.094940026115988</v>
       </c>
       <c r="K5" t="n">
-        <v>4.628117612056675</v>
+        <v>4.628117612056673</v>
       </c>
       <c r="L5" t="n">
-        <v>4.817798194477158</v>
+        <v>4.817798194477361</v>
       </c>
       <c r="M5" t="n">
-        <v>4.322921213304491</v>
+        <v>4.322921213304485</v>
       </c>
       <c r="N5" t="n">
-        <v>2.600155173142274</v>
+        <v>2.600155173142277</v>
       </c>
       <c r="O5" t="n">
-        <v>3.125706242224059</v>
+        <v>3.125706242224052</v>
       </c>
       <c r="P5" t="n">
         <v>3.648438941639363</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.561990806803994</v>
+        <v>2.561990806804008</v>
       </c>
       <c r="R5" t="n">
-        <v>6.241327391114021</v>
+        <v>6.24132739111402</v>
       </c>
       <c r="S5" t="n">
-        <v>5.144037803068742</v>
+        <v>5.144037803068699</v>
       </c>
       <c r="T5" t="n">
-        <v>2.800725732797912</v>
+        <v>2.80072573279791</v>
       </c>
       <c r="U5" t="n">
-        <v>4.430557665077101</v>
+        <v>4.4305576650771</v>
       </c>
       <c r="V5" t="n">
-        <v>4.112500651115875</v>
+        <v>4.112500651115878</v>
       </c>
       <c r="W5" t="n">
-        <v>3.458500718529085</v>
+        <v>3.458500718529092</v>
       </c>
       <c r="X5" t="n">
-        <v>4.600217081060605</v>
+        <v>4.600217081060656</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.177011064843009</v>
+        <v>3.177011064843013</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.007820815267599</v>
+        <v>3.007820815267646</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.565300076638735</v>
+        <v>5.565300076638745</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.959868661974347</v>
+        <v>2.959868661974344</v>
       </c>
     </row>
     <row r="6">
@@ -2658,61 +2658,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.293462403457499</v>
+        <v>3.293462403457502</v>
       </c>
       <c r="C6" t="n">
         <v>17.0605111204118</v>
       </c>
       <c r="D6" t="n">
-        <v>3.595598153329492</v>
+        <v>3.595598153329491</v>
       </c>
       <c r="E6" t="n">
-        <v>17.02316406226158</v>
+        <v>17.02316406226159</v>
       </c>
       <c r="F6" t="n">
-        <v>3.789566070408247</v>
+        <v>3.789566070408246</v>
       </c>
       <c r="G6" t="n">
-        <v>16.61861333756503</v>
+        <v>16.61861333756505</v>
       </c>
       <c r="H6" t="n">
-        <v>16.64417050144831</v>
+        <v>16.64417050144832</v>
       </c>
       <c r="I6" t="n">
         <v>16.83981878149874</v>
       </c>
       <c r="J6" t="n">
-        <v>16.66857630454174</v>
+        <v>16.66857630454176</v>
       </c>
       <c r="K6" t="n">
-        <v>3.401406748296481</v>
+        <v>3.40140674829648</v>
       </c>
       <c r="L6" t="n">
-        <v>16.70650190476173</v>
+        <v>16.70650190476174</v>
       </c>
       <c r="M6" t="n">
-        <v>16.67251278835439</v>
+        <v>16.6725127883544</v>
       </c>
       <c r="N6" t="n">
-        <v>3.289001344644499</v>
+        <v>3.289001344644498</v>
       </c>
       <c r="O6" t="n">
-        <v>3.32308656800073</v>
+        <v>3.323086568000729</v>
       </c>
       <c r="P6" t="n">
-        <v>16.64838105282156</v>
+        <v>16.64838105282155</v>
       </c>
       <c r="Q6" t="n">
         <v>3.288939568027263</v>
       </c>
       <c r="R6" t="n">
-        <v>16.76430739814927</v>
+        <v>16.76430739814929</v>
       </c>
       <c r="S6" t="n">
-        <v>3.435047935804626</v>
+        <v>3.435047935804627</v>
       </c>
       <c r="T6" t="n">
-        <v>3.300303619819877</v>
+        <v>3.300303619819878</v>
       </c>
       <c r="U6" t="n">
         <v>3.391619603682002</v>
@@ -2721,22 +2721,22 @@
         <v>3.382823575402163</v>
       </c>
       <c r="W6" t="n">
-        <v>3.337316728437194</v>
+        <v>3.337316728437193</v>
       </c>
       <c r="X6" t="n">
         <v>16.68971361953664</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.339977657065713</v>
+        <v>3.339977657065711</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.315850054261567</v>
+        <v>3.315850054261568</v>
       </c>
       <c r="AA6" t="n">
         <v>16.7448016671455</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.303757902212259</v>
+        <v>3.303757902212258</v>
       </c>
     </row>
     <row r="7">
@@ -2755,10 +2755,10 @@
         <v>2.485191367155708</v>
       </c>
       <c r="E7" t="n">
-        <v>2.615796921710547</v>
+        <v>2.615796921710548</v>
       </c>
       <c r="F7" t="n">
-        <v>2.679159284234466</v>
+        <v>2.679159284234465</v>
       </c>
       <c r="G7" t="n">
         <v>2.211246197013983</v>
@@ -2770,13 +2770,13 @@
         <v>2.432451640947687</v>
       </c>
       <c r="J7" t="n">
-        <v>2.261209163990688</v>
+        <v>2.261209163990689</v>
       </c>
       <c r="K7" t="n">
         <v>2.290999962122693</v>
       </c>
       <c r="L7" t="n">
-        <v>2.299134764210681</v>
+        <v>2.299134764210676</v>
       </c>
       <c r="M7" t="n">
         <v>2.265145647803342</v>
@@ -2785,22 +2785,22 @@
         <v>2.180646650763095</v>
       </c>
       <c r="O7" t="n">
-        <v>2.214728860409421</v>
+        <v>2.21472886040942</v>
       </c>
       <c r="P7" t="n">
-        <v>2.241925466552163</v>
+        <v>2.241925466552164</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.178532781853478</v>
+        <v>2.178532781853479</v>
       </c>
       <c r="R7" t="n">
         <v>2.356940257598218</v>
       </c>
       <c r="S7" t="n">
-        <v>2.324641149630839</v>
+        <v>2.32464114963084</v>
       </c>
       <c r="T7" t="n">
-        <v>2.189896833646095</v>
+        <v>2.189896833646094</v>
       </c>
       <c r="U7" t="n">
         <v>2.281201687012492</v>
@@ -2809,10 +2809,10 @@
         <v>2.272416789228382</v>
       </c>
       <c r="W7" t="n">
-        <v>2.226337806944673</v>
+        <v>2.226337806944674</v>
       </c>
       <c r="X7" t="n">
-        <v>2.282346478985595</v>
+        <v>2.282346478985597</v>
       </c>
       <c r="Y7" t="n">
         <v>2.211857697002169</v>
@@ -2834,16 +2834,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.193648084736354</v>
+        <v>2.193648084736356</v>
       </c>
       <c r="C8" t="n">
-        <v>2.718043119677115</v>
+        <v>2.718043119677114</v>
       </c>
       <c r="D8" t="n">
         <v>2.550090506972067</v>
       </c>
       <c r="E8" t="n">
-        <v>2.651779360441461</v>
+        <v>2.651779360441462</v>
       </c>
       <c r="F8" t="n">
         <v>2.698212096545177</v>
@@ -2858,16 +2858,16 @@
         <v>2.49735078076405</v>
       </c>
       <c r="J8" t="n">
-        <v>2.326108303807047</v>
+        <v>2.326108303807048</v>
       </c>
       <c r="K8" t="n">
         <v>2.355899101939054</v>
       </c>
       <c r="L8" t="n">
-        <v>2.364033904027041</v>
+        <v>2.364033904027043</v>
       </c>
       <c r="M8" t="n">
-        <v>2.330044787619685</v>
+        <v>2.330044787619686</v>
       </c>
       <c r="N8" t="n">
         <v>2.203449034187501</v>
@@ -2879,28 +2879,28 @@
         <v>2.27346543801552</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.178452748699443</v>
+        <v>2.178452748699444</v>
       </c>
       <c r="R8" t="n">
         <v>2.421839397414579</v>
       </c>
       <c r="S8" t="n">
-        <v>2.389540289447199</v>
+        <v>2.3895402894472</v>
       </c>
       <c r="T8" t="n">
         <v>2.254795973462456</v>
       </c>
       <c r="U8" t="n">
-        <v>2.319600663057176</v>
+        <v>2.319600663057177</v>
       </c>
       <c r="V8" t="n">
         <v>2.32246765644943</v>
       </c>
       <c r="W8" t="n">
-        <v>2.291247619571216</v>
+        <v>2.291247619571217</v>
       </c>
       <c r="X8" t="n">
-        <v>2.287243760258353</v>
+        <v>2.287243760258356</v>
       </c>
       <c r="Y8" t="n">
         <v>2.330744287308033</v>
@@ -2909,10 +2909,10 @@
         <v>2.215026961220941</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.402333666410808</v>
+        <v>2.402333666410809</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.317443465884763</v>
+        <v>2.317443465884764</v>
       </c>
     </row>
     <row r="9">
@@ -2922,82 +2922,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.622795268792752</v>
+        <v>2.622795268792754</v>
       </c>
       <c r="C9" t="n">
-        <v>3.235203632827641</v>
+        <v>3.235203632827643</v>
       </c>
       <c r="D9" t="n">
         <v>3.067251020122597</v>
       </c>
       <c r="E9" t="n">
-        <v>3.16500970137881</v>
+        <v>3.165009701378811</v>
       </c>
       <c r="F9" t="n">
-        <v>2.933132486742303</v>
+        <v>2.933132486742304</v>
       </c>
       <c r="G9" t="n">
-        <v>2.793305853263675</v>
+        <v>2.793305853263676</v>
       </c>
       <c r="H9" t="n">
-        <v>2.818863013864143</v>
+        <v>2.818863013864145</v>
       </c>
       <c r="I9" t="n">
-        <v>3.014511293914574</v>
+        <v>3.014511293914575</v>
       </c>
       <c r="J9" t="n">
-        <v>2.843268816957574</v>
+        <v>2.843268816957575</v>
       </c>
       <c r="K9" t="n">
         <v>2.873059615089578</v>
       </c>
       <c r="L9" t="n">
-        <v>2.881194417177566</v>
+        <v>2.881194417177565</v>
       </c>
       <c r="M9" t="n">
         <v>2.847205300770227</v>
       </c>
       <c r="N9" t="n">
-        <v>2.76270630372998</v>
+        <v>2.762706303729981</v>
       </c>
       <c r="O9" t="n">
         <v>2.843957945907068</v>
       </c>
       <c r="P9" t="n">
-        <v>2.88141205709035</v>
+        <v>2.881412057090351</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.760592438103173</v>
+        <v>2.760592438103174</v>
       </c>
       <c r="R9" t="n">
         <v>2.938999910565105</v>
       </c>
       <c r="S9" t="n">
-        <v>2.906700802597725</v>
+        <v>2.906700802597729</v>
       </c>
       <c r="T9" t="n">
-        <v>2.771956486612978</v>
+        <v>2.77195648661298</v>
       </c>
       <c r="U9" t="n">
         <v>2.863272470475103</v>
       </c>
       <c r="V9" t="n">
-        <v>3.018710589621241</v>
+        <v>3.018710589621243</v>
       </c>
       <c r="W9" t="n">
-        <v>2.808397459911562</v>
+        <v>2.808397459911563</v>
       </c>
       <c r="X9" t="n">
-        <v>2.864406131952482</v>
+        <v>2.864406131952483</v>
       </c>
       <c r="Y9" t="n">
         <v>2.793917349969054</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.701696617067519</v>
+        <v>2.70169661706752</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.919494179561336</v>
+        <v>2.919494179561337</v>
       </c>
       <c r="AB9" t="n">
         <v>2.777876118708111</v>
@@ -3166,13 +3166,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.397247055861033</v>
+        <v>2.397247055861032</v>
       </c>
       <c r="C2" t="n">
         <v>2.43546149459064</v>
       </c>
       <c r="D2" t="n">
-        <v>2.413534985399381</v>
+        <v>2.41353498539938</v>
       </c>
       <c r="E2" t="n">
         <v>2.424845519604842</v>
@@ -3181,10 +3181,10 @@
         <v>2.438554804394502</v>
       </c>
       <c r="G2" t="n">
-        <v>2.399733661320384</v>
+        <v>2.399733661320383</v>
       </c>
       <c r="H2" t="n">
-        <v>2.401671162915953</v>
+        <v>2.401671162915952</v>
       </c>
       <c r="I2" t="n">
         <v>2.407501194832627</v>
@@ -3193,10 +3193,10 @@
         <v>2.403310074476366</v>
       </c>
       <c r="K2" t="n">
-        <v>2.405062389380009</v>
+        <v>2.405062389380008</v>
       </c>
       <c r="L2" t="n">
-        <v>2.407157619928723</v>
+        <v>2.407157619928722</v>
       </c>
       <c r="M2" t="n">
         <v>2.402585058641602</v>
@@ -3205,7 +3205,7 @@
         <v>2.397064021629306</v>
       </c>
       <c r="O2" t="n">
-        <v>2.434218953226642</v>
+        <v>2.434218953226643</v>
       </c>
       <c r="P2" t="n">
         <v>2.402369192417578</v>
@@ -3214,10 +3214,10 @@
         <v>2.397313029297482</v>
       </c>
       <c r="R2" t="n">
-        <v>2.412555963486853</v>
+        <v>2.412555963486852</v>
       </c>
       <c r="S2" t="n">
-        <v>2.406729142261838</v>
+        <v>2.406729142261837</v>
       </c>
       <c r="T2" t="n">
         <v>2.399034084364677</v>
@@ -3226,13 +3226,13 @@
         <v>2.434138686278785</v>
       </c>
       <c r="V2" t="n">
-        <v>2.404711985485005</v>
+        <v>2.404711985485004</v>
       </c>
       <c r="W2" t="n">
         <v>2.436934061634882</v>
       </c>
       <c r="X2" t="n">
-        <v>2.406666905606226</v>
+        <v>2.406666905606225</v>
       </c>
       <c r="Y2" t="n">
         <v>2.39967322311466</v>
@@ -3241,7 +3241,7 @@
         <v>2.417838277235574</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.406436376693291</v>
+        <v>2.40643637669329</v>
       </c>
       <c r="AB2" t="n">
         <v>2.399249723716486</v>
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.403689563504609</v>
+        <v>2.404313086820758</v>
       </c>
       <c r="C3" t="n">
-        <v>2.650092319902356</v>
+        <v>2.659220463836981</v>
       </c>
       <c r="D3" t="n">
-        <v>2.520312940472506</v>
+        <v>2.525081169175494</v>
       </c>
       <c r="E3" t="n">
-        <v>2.600664868468874</v>
+        <v>2.608233847228456</v>
       </c>
       <c r="F3" t="n">
-        <v>2.699248321616718</v>
+        <v>2.710424214585777</v>
       </c>
       <c r="G3" t="n">
-        <v>2.421369795038072</v>
+        <v>2.422615687269825</v>
       </c>
       <c r="H3" t="n">
-        <v>2.435580608119342</v>
+        <v>2.437347559870624</v>
       </c>
       <c r="I3" t="n">
-        <v>2.477231017217742</v>
+        <v>2.480472960460103</v>
       </c>
       <c r="J3" t="n">
-        <v>2.446962925914248</v>
+        <v>2.449121908897475</v>
       </c>
       <c r="K3" t="n">
-        <v>2.459291633873065</v>
+        <v>2.461904745909795</v>
       </c>
       <c r="L3" t="n">
-        <v>2.474429107368338</v>
+        <v>2.477549646555735</v>
       </c>
       <c r="M3" t="n">
-        <v>2.442692821954232</v>
+        <v>2.444715128921363</v>
       </c>
       <c r="N3" t="n">
-        <v>2.402450725645688</v>
+        <v>2.403034192373694</v>
       </c>
       <c r="O3" t="n">
-        <v>2.485151876473562</v>
+        <v>2.486713634283988</v>
       </c>
       <c r="P3" t="n">
-        <v>2.440098221081247</v>
+        <v>2.441998806312438</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.404220805546674</v>
+        <v>2.404868191222915</v>
       </c>
       <c r="R3" t="n">
-        <v>2.513559496054764</v>
+        <v>2.518096692927404</v>
       </c>
       <c r="S3" t="n">
-        <v>2.471144540746644</v>
+        <v>2.474147879845108</v>
       </c>
       <c r="T3" t="n">
-        <v>2.416579467100197</v>
+        <v>2.417665998888523</v>
       </c>
       <c r="U3" t="n">
-        <v>2.493171417240879</v>
+        <v>2.495109844819247</v>
       </c>
       <c r="V3" t="n">
-        <v>2.456624588552203</v>
+        <v>2.459118591317692</v>
       </c>
       <c r="W3" t="n">
-        <v>2.49009317857182</v>
+        <v>2.4916781159802</v>
       </c>
       <c r="X3" t="n">
-        <v>2.471109848841536</v>
+        <v>2.474131172590607</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.421054678886681</v>
+        <v>2.422295923564406</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.447490481478993</v>
+        <v>2.448566845478274</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.469349882551318</v>
+        <v>2.472296071278233</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.419037585862625</v>
+        <v>2.420212506157159</v>
       </c>
     </row>
     <row r="4">
@@ -3345,7 +3345,7 @@
         <v>2.110982984032177</v>
       </c>
       <c r="C4" t="n">
-        <v>2.489363285760985</v>
+        <v>2.489363285760984</v>
       </c>
       <c r="D4" t="n">
         <v>2.294962640985586</v>
@@ -3363,7 +3363,7 @@
         <v>2.160955308407288</v>
       </c>
       <c r="I4" t="n">
-        <v>2.226808200853314</v>
+        <v>2.226808200853315</v>
       </c>
       <c r="J4" t="n">
         <v>2.179501196613961</v>
@@ -3381,7 +3381,7 @@
         <v>2.108915528184919</v>
       </c>
       <c r="O4" t="n">
-        <v>2.153442690341442</v>
+        <v>2.153442690341441</v>
       </c>
       <c r="P4" t="n">
         <v>2.168839872737583</v>
@@ -3396,7 +3396,7 @@
         <v>2.218087511904518</v>
       </c>
       <c r="T4" t="n">
-        <v>2.131168293054568</v>
+        <v>2.131168293054567</v>
       </c>
       <c r="U4" t="n">
         <v>2.170305290930953</v>
@@ -3430,46 +3430,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.505335975131922</v>
+        <v>2.505335975131923</v>
       </c>
       <c r="C5" t="n">
         <v>9.086053435871642</v>
       </c>
       <c r="D5" t="n">
-        <v>5.953971137896854</v>
+        <v>5.953971137896855</v>
       </c>
       <c r="E5" t="n">
-        <v>8.020839313891445</v>
+        <v>8.020839313891436</v>
       </c>
       <c r="F5" t="n">
         <v>11.14294558890015</v>
       </c>
       <c r="G5" t="n">
-        <v>2.967492028741962</v>
+        <v>2.967492028741945</v>
       </c>
       <c r="H5" t="n">
-        <v>3.552923487429547</v>
+        <v>3.552923487429543</v>
       </c>
       <c r="I5" t="n">
-        <v>4.738981395964896</v>
+        <v>4.738981395964899</v>
       </c>
       <c r="J5" t="n">
-        <v>3.717304260670476</v>
+        <v>3.717304260670473</v>
       </c>
       <c r="K5" t="n">
-        <v>3.975283025667557</v>
+        <v>3.975283025667556</v>
       </c>
       <c r="L5" t="n">
         <v>4.489068113363531</v>
       </c>
       <c r="M5" t="n">
-        <v>3.72065967394227</v>
+        <v>3.720659673942273</v>
       </c>
       <c r="N5" t="n">
-        <v>2.503742816802815</v>
+        <v>2.503742816802816</v>
       </c>
       <c r="O5" t="n">
-        <v>3.157915899107184</v>
+        <v>3.157915899107181</v>
       </c>
       <c r="P5" t="n">
         <v>3.451784863892906</v>
@@ -3478,34 +3478,34 @@
         <v>2.549809762519271</v>
       </c>
       <c r="R5" t="n">
-        <v>5.879587612177378</v>
+        <v>5.879587612177375</v>
       </c>
       <c r="S5" t="n">
-        <v>4.286089369371368</v>
+        <v>4.286089369371364</v>
       </c>
       <c r="T5" t="n">
-        <v>2.932717279582491</v>
+        <v>2.932717279582492</v>
       </c>
       <c r="U5" t="n">
-        <v>3.522194173887806</v>
+        <v>3.522194173887788</v>
       </c>
       <c r="V5" t="n">
-        <v>3.819296876269221</v>
+        <v>3.819296876269218</v>
       </c>
       <c r="W5" t="n">
-        <v>3.294685304890309</v>
+        <v>3.294685304890313</v>
       </c>
       <c r="X5" t="n">
-        <v>4.485865806284004</v>
+        <v>4.485865806284003</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.015653254777988</v>
+        <v>3.015653254777987</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.813907566920795</v>
+        <v>2.813907566920797</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.380386209306148</v>
+        <v>4.380386209306149</v>
       </c>
       <c r="AB5" t="n">
         <v>3.052775460180263</v>
@@ -3518,25 +3518,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.59522945686912</v>
+        <v>15.59522945686911</v>
       </c>
       <c r="C6" t="n">
         <v>3.583985029240174</v>
       </c>
       <c r="D6" t="n">
-        <v>15.77920911382249</v>
+        <v>15.7792091138225</v>
       </c>
       <c r="E6" t="n">
         <v>15.90696680077599</v>
       </c>
       <c r="F6" t="n">
-        <v>3.672194749700047</v>
+        <v>3.672194749700046</v>
       </c>
       <c r="G6" t="n">
         <v>3.233692080069752</v>
       </c>
       <c r="H6" t="n">
-        <v>3.255577051886482</v>
+        <v>3.255577051886481</v>
       </c>
       <c r="I6" t="n">
         <v>3.321429944332499</v>
@@ -3551,10 +3551,10 @@
         <v>15.70717383709837</v>
       </c>
       <c r="M6" t="n">
-        <v>3.267114267802032</v>
+        <v>3.267114267802031</v>
       </c>
       <c r="N6" t="n">
-        <v>3.202198665227223</v>
+        <v>3.202198665227222</v>
       </c>
       <c r="O6" t="n">
         <v>15.63687495287758</v>
@@ -3572,10 +3572,10 @@
         <v>15.70233398474145</v>
       </c>
       <c r="T6" t="n">
-        <v>3.22579003653376</v>
+        <v>3.225790036533759</v>
       </c>
       <c r="U6" t="n">
-        <v>3.264563504311875</v>
+        <v>3.264563504311874</v>
       </c>
       <c r="V6" t="n">
         <v>15.6796928905347</v>
@@ -3590,10 +3590,10 @@
         <v>3.250048806481626</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.6156373474567</v>
+        <v>15.61563734745669</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.69902706296588</v>
+        <v>15.6990270629659</v>
       </c>
       <c r="AB6" t="n">
         <v>3.228163242158662</v>
@@ -3606,22 +3606,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.172224912529055</v>
+        <v>2.172224912529056</v>
       </c>
       <c r="C7" t="n">
         <v>2.550605214257862</v>
       </c>
       <c r="D7" t="n">
-        <v>2.356204569482464</v>
+        <v>2.356204569482463</v>
       </c>
       <c r="E7" t="n">
         <v>2.483962256435946</v>
       </c>
       <c r="F7" t="n">
-        <v>2.638814934717737</v>
+        <v>2.638814934717738</v>
       </c>
       <c r="G7" t="n">
-        <v>2.200312265087445</v>
+        <v>2.200312265087444</v>
       </c>
       <c r="H7" t="n">
         <v>2.222197236904166</v>
@@ -3654,7 +3654,7 @@
         <v>2.172970112843031</v>
       </c>
       <c r="R7" t="n">
-        <v>2.345146066608134</v>
+        <v>2.345146066608135</v>
       </c>
       <c r="S7" t="n">
         <v>2.279329440401396</v>
@@ -3663,7 +3663,7 @@
         <v>2.192410221551446</v>
       </c>
       <c r="U7" t="n">
-        <v>2.231194603589928</v>
+        <v>2.231194603589926</v>
       </c>
       <c r="V7" t="n">
         <v>2.256688346194661</v>
@@ -3715,13 +3715,13 @@
         <v>2.28128360651473</v>
       </c>
       <c r="I8" t="n">
-        <v>2.347136498960757</v>
+        <v>2.347136498960758</v>
       </c>
       <c r="J8" t="n">
         <v>2.299829494721405</v>
       </c>
       <c r="K8" t="n">
-        <v>2.319589069467494</v>
+        <v>2.319589069467493</v>
       </c>
       <c r="L8" t="n">
         <v>2.343255662368894</v>
@@ -3736,31 +3736,31 @@
         <v>2.245765665024911</v>
       </c>
       <c r="P8" t="n">
-        <v>2.258561462780417</v>
+        <v>2.258561462780418</v>
       </c>
       <c r="Q8" t="n">
         <v>2.17244724828513</v>
       </c>
       <c r="R8" t="n">
-        <v>2.404232436218699</v>
+        <v>2.4042324362187</v>
       </c>
       <c r="S8" t="n">
         <v>2.338415810011961</v>
       </c>
       <c r="T8" t="n">
-        <v>2.251496591162011</v>
+        <v>2.25149659116201</v>
       </c>
       <c r="U8" t="n">
         <v>2.265966122755481</v>
       </c>
       <c r="V8" t="n">
-        <v>2.302171651288139</v>
+        <v>2.302171651288138</v>
       </c>
       <c r="W8" t="n">
         <v>2.274213919138427</v>
       </c>
       <c r="X8" t="n">
-        <v>2.282669568758279</v>
+        <v>2.282669568758278</v>
       </c>
       <c r="Y8" t="n">
         <v>2.308269959648279</v>
@@ -3772,7 +3772,7 @@
         <v>2.335108888236402</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.30748543455952</v>
+        <v>2.307485434559519</v>
       </c>
     </row>
     <row r="9">
@@ -3800,7 +3800,7 @@
         <v>2.674872894599602</v>
       </c>
       <c r="H9" t="n">
-        <v>2.696757863617113</v>
+        <v>2.696757863617112</v>
       </c>
       <c r="I9" t="n">
         <v>2.762610756063139</v>
@@ -3809,7 +3809,7 @@
         <v>2.715303751823786</v>
       </c>
       <c r="K9" t="n">
-        <v>2.735063326569875</v>
+        <v>2.735063326569874</v>
       </c>
       <c r="L9" t="n">
         <v>2.758729919471277</v>
@@ -3821,16 +3821,16 @@
         <v>2.644718083394745</v>
       </c>
       <c r="O9" t="n">
-        <v>2.728280047876685</v>
+        <v>2.728280047876684</v>
       </c>
       <c r="P9" t="n">
-        <v>2.752166629445153</v>
+        <v>2.752166629445152</v>
       </c>
       <c r="Q9" t="n">
         <v>2.647530742355189</v>
       </c>
       <c r="R9" t="n">
-        <v>2.819706693321083</v>
+        <v>2.819706693321084</v>
       </c>
       <c r="S9" t="n">
         <v>2.753890067114343</v>
@@ -3839,7 +3839,7 @@
         <v>2.666970848264394</v>
       </c>
       <c r="U9" t="n">
-        <v>2.705744316042515</v>
+        <v>2.705744316042514</v>
       </c>
       <c r="V9" t="n">
         <v>2.867173763060099</v>
@@ -4041,7 +4041,7 @@
         <v>2.431153532610379</v>
       </c>
       <c r="G2" t="n">
-        <v>2.396980920355949</v>
+        <v>2.396980920355948</v>
       </c>
       <c r="H2" t="n">
         <v>2.398337671609772</v>
@@ -4050,7 +4050,7 @@
         <v>2.401069069010922</v>
       </c>
       <c r="J2" t="n">
-        <v>2.400564901043357</v>
+        <v>2.400564901043356</v>
       </c>
       <c r="K2" t="n">
         <v>2.4008830982452</v>
@@ -4065,7 +4065,7 @@
         <v>2.394521995760763</v>
       </c>
       <c r="O2" t="n">
-        <v>2.430540615560899</v>
+        <v>2.430540615560898</v>
       </c>
       <c r="P2" t="n">
         <v>2.398763709603613</v>
@@ -4104,7 +4104,7 @@
         <v>2.401838472573482</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.396895376527622</v>
+        <v>2.396895376527621</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.400862902573529</v>
+        <v>2.401449534794678</v>
       </c>
       <c r="C3" t="n">
-        <v>2.655620814773071</v>
+        <v>2.664991595790628</v>
       </c>
       <c r="D3" t="n">
-        <v>2.491147935899101</v>
+        <v>2.49495189802891</v>
       </c>
       <c r="E3" t="n">
-        <v>2.578953958633322</v>
+        <v>2.585841672329452</v>
       </c>
       <c r="F3" t="n">
-        <v>2.660936608216037</v>
+        <v>2.670813249121348</v>
       </c>
       <c r="G3" t="n">
-        <v>2.416419088906569</v>
+        <v>2.417554191821129</v>
       </c>
       <c r="H3" t="n">
-        <v>2.426477351705781</v>
+        <v>2.427982592069343</v>
       </c>
       <c r="I3" t="n">
-        <v>2.445889043724379</v>
+        <v>2.448082216842494</v>
       </c>
       <c r="J3" t="n">
-        <v>2.442059485892804</v>
+        <v>2.444110953968762</v>
       </c>
       <c r="K3" t="n">
-        <v>2.444238167144781</v>
+        <v>2.446377227811506</v>
       </c>
       <c r="L3" t="n">
-        <v>2.471692010515997</v>
+        <v>2.474784063245024</v>
       </c>
       <c r="M3" t="n">
-        <v>2.451450444594914</v>
+        <v>2.453850827125469</v>
       </c>
       <c r="N3" t="n">
-        <v>2.399029935973689</v>
+        <v>2.399554693983867</v>
       </c>
       <c r="O3" t="n">
-        <v>2.476842417978636</v>
+        <v>2.478207361430734</v>
       </c>
       <c r="P3" t="n">
-        <v>2.429060886917906</v>
+        <v>2.430638176898121</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.404021680577986</v>
+        <v>2.404725224302544</v>
       </c>
       <c r="R3" t="n">
-        <v>2.484315317851926</v>
+        <v>2.487875245962796</v>
       </c>
       <c r="S3" t="n">
-        <v>2.460478187982983</v>
+        <v>2.463169349114616</v>
       </c>
       <c r="T3" t="n">
-        <v>2.417507563880266</v>
+        <v>2.418689547018666</v>
       </c>
       <c r="U3" t="n">
-        <v>2.475202457933928</v>
+        <v>2.476581399550688</v>
       </c>
       <c r="V3" t="n">
-        <v>2.445213391992989</v>
+        <v>2.447367664239086</v>
       </c>
       <c r="W3" t="n">
-        <v>2.481272952434419</v>
+        <v>2.482616939300758</v>
       </c>
       <c r="X3" t="n">
-        <v>2.471416824516286</v>
+        <v>2.474516548142217</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.412929464210301</v>
+        <v>2.413944913572888</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.438692910484865</v>
+        <v>2.439544668882119</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.451270170009388</v>
+        <v>2.45363924234451</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.416784755220897</v>
+        <v>2.417942305799655</v>
       </c>
     </row>
     <row r="4">
@@ -4202,19 +4202,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.10735123237881</v>
+        <v>2.107351232378809</v>
       </c>
       <c r="C4" t="n">
-        <v>2.49820377428373</v>
+        <v>2.498203774283729</v>
       </c>
       <c r="D4" t="n">
-        <v>2.250106280566058</v>
+        <v>2.250106280566056</v>
       </c>
       <c r="E4" t="n">
         <v>2.390174092261345</v>
       </c>
       <c r="F4" t="n">
-        <v>2.518098257940194</v>
+        <v>2.518098257940193</v>
       </c>
       <c r="G4" t="n">
         <v>2.132102882348097</v>
@@ -4229,7 +4229,7 @@
         <v>2.172617940222276</v>
       </c>
       <c r="K4" t="n">
-        <v>2.176179776697712</v>
+        <v>2.176179776697711</v>
       </c>
       <c r="L4" t="n">
         <v>2.219683534249383</v>
@@ -4247,19 +4247,19 @@
         <v>2.152240307024035</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.112267724583825</v>
+        <v>2.112267724583824</v>
       </c>
       <c r="R4" t="n">
         <v>2.238640802322381</v>
       </c>
       <c r="S4" t="n">
-        <v>2.202062748226999</v>
+        <v>2.202062748226998</v>
       </c>
       <c r="T4" t="n">
         <v>2.133446633099813</v>
       </c>
       <c r="U4" t="n">
-        <v>2.143202243760133</v>
+        <v>2.143202243760132</v>
       </c>
       <c r="V4" t="n">
         <v>2.178149812267535</v>
@@ -4271,7 +4271,7 @@
         <v>2.218910405968356</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.126687103650241</v>
+        <v>2.12668710365024</v>
       </c>
       <c r="Z4" t="n">
         <v>2.119290015784704</v>
@@ -4293,82 +4293,82 @@
         <v>2.467791740616282</v>
       </c>
       <c r="C5" t="n">
-        <v>9.215963638568821</v>
+        <v>9.21596363856882</v>
       </c>
       <c r="D5" t="n">
         <v>5.03674415951213</v>
       </c>
       <c r="E5" t="n">
-        <v>7.153394981052307</v>
+        <v>7.153394981052309</v>
       </c>
       <c r="F5" t="n">
-        <v>10.01377583665909</v>
+        <v>10.0137758366591</v>
       </c>
       <c r="G5" t="n">
-        <v>2.862463138246377</v>
+        <v>2.862463138246375</v>
       </c>
       <c r="H5" t="n">
-        <v>3.32787944913662</v>
+        <v>3.327879449136621</v>
       </c>
       <c r="I5" t="n">
-        <v>3.83083896717647</v>
+        <v>3.830838967176469</v>
       </c>
       <c r="J5" t="n">
         <v>3.610291150038875</v>
       </c>
       <c r="K5" t="n">
-        <v>3.625991569163491</v>
+        <v>3.62599156916349</v>
       </c>
       <c r="L5" t="n">
-        <v>4.377777825765712</v>
+        <v>4.377777825765713</v>
       </c>
       <c r="M5" t="n">
-        <v>3.959538999201414</v>
+        <v>3.959538999201416</v>
       </c>
       <c r="N5" t="n">
         <v>2.454300934083968</v>
       </c>
       <c r="O5" t="n">
-        <v>3.016496690125764</v>
+        <v>3.016496690125767</v>
       </c>
       <c r="P5" t="n">
-        <v>3.176102385030336</v>
+        <v>3.176102385030358</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.581844201897618</v>
+        <v>2.58184420189762</v>
       </c>
       <c r="R5" t="n">
         <v>5.047393246961103</v>
       </c>
       <c r="S5" t="n">
-        <v>4.024611245333944</v>
+        <v>4.024611245333942</v>
       </c>
       <c r="T5" t="n">
-        <v>3.010305252750705</v>
+        <v>3.010305252750702</v>
       </c>
       <c r="U5" t="n">
-        <v>3.062593914742755</v>
+        <v>3.062593914742751</v>
       </c>
       <c r="V5" t="n">
-        <v>3.562978651221031</v>
+        <v>3.562978651221022</v>
       </c>
       <c r="W5" t="n">
         <v>3.101505273498695</v>
       </c>
       <c r="X5" t="n">
-        <v>4.474649404358018</v>
+        <v>4.474649404358019</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.845547771486353</v>
+        <v>2.845547771486364</v>
       </c>
       <c r="Z5" t="n">
         <v>2.628818718623662</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.927469514500177</v>
+        <v>3.927469514500178</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.023135270505748</v>
+        <v>3.02313527050575</v>
       </c>
     </row>
     <row r="6">
@@ -4378,49 +4378,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.200425500401616</v>
+        <v>3.200425500401615</v>
       </c>
       <c r="C6" t="n">
-        <v>3.591278042306548</v>
+        <v>3.591278042306547</v>
       </c>
       <c r="D6" t="n">
-        <v>15.7323698071585</v>
+        <v>15.73236980715848</v>
       </c>
       <c r="E6" t="n">
-        <v>15.87243761885378</v>
+        <v>15.87243761885377</v>
       </c>
       <c r="F6" t="n">
         <v>3.611172525963006</v>
       </c>
       <c r="G6" t="n">
-        <v>3.225177150370917</v>
+        <v>3.225177150370918</v>
       </c>
       <c r="H6" t="n">
-        <v>15.62969153848888</v>
+        <v>15.62969153848887</v>
       </c>
       <c r="I6" t="n">
         <v>3.271354670070123</v>
       </c>
       <c r="J6" t="n">
-        <v>15.65488146681471</v>
+        <v>15.6548814668147</v>
       </c>
       <c r="K6" t="n">
-        <v>15.65844330329016</v>
+        <v>15.65844330329015</v>
       </c>
       <c r="L6" t="n">
-        <v>3.312757802272202</v>
+        <v>3.312757802272203</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28035550783898</v>
+        <v>3.280355507838981</v>
       </c>
       <c r="N6" t="n">
-        <v>3.19613647831618</v>
+        <v>3.196136478316182</v>
       </c>
       <c r="O6" t="n">
-        <v>3.234383972970497</v>
+        <v>3.234383972970498</v>
       </c>
       <c r="P6" t="n">
-        <v>15.633572712292</v>
+        <v>15.63357271229199</v>
       </c>
       <c r="Q6" t="n">
         <v>15.59453125117625</v>
@@ -4429,34 +4429,34 @@
         <v>15.72090432891482</v>
       </c>
       <c r="S6" t="n">
-        <v>3.295137016249813</v>
+        <v>3.295137016249814</v>
       </c>
       <c r="T6" t="n">
         <v>15.61571015969225</v>
       </c>
       <c r="U6" t="n">
-        <v>15.62509794999225</v>
+        <v>15.62509794999224</v>
       </c>
       <c r="V6" t="n">
-        <v>3.271224080290352</v>
+        <v>3.271224080290353</v>
       </c>
       <c r="W6" t="n">
-        <v>3.235344468864865</v>
+        <v>3.235344468864863</v>
       </c>
       <c r="X6" t="n">
-        <v>3.311984673991172</v>
+        <v>3.311984673991173</v>
       </c>
       <c r="Y6" t="n">
         <v>3.236436054715602</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.212364283807522</v>
+        <v>3.212364283807523</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.669234695822</v>
+        <v>15.66923469582198</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.224040516291702</v>
+        <v>3.224040516291701</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>2.168158656587956</v>
       </c>
       <c r="C7" t="n">
-        <v>2.559011198492877</v>
+        <v>2.559011198492875</v>
       </c>
       <c r="D7" t="n">
-        <v>2.310913704775206</v>
+        <v>2.310913704775205</v>
       </c>
       <c r="E7" t="n">
         <v>2.450981516470493</v>
@@ -4487,7 +4487,7 @@
         <v>2.20823543610559</v>
       </c>
       <c r="I7" t="n">
-        <v>2.239087826256457</v>
+        <v>2.239087826256456</v>
       </c>
       <c r="J7" t="n">
         <v>2.233425364431424</v>
@@ -4502,10 +4502,10 @@
         <v>2.248088664025314</v>
       </c>
       <c r="N7" t="n">
-        <v>2.165135622093425</v>
+        <v>2.165135622093424</v>
       </c>
       <c r="O7" t="n">
-        <v>2.203379363652584</v>
+        <v>2.203379363652583</v>
       </c>
       <c r="P7" t="n">
         <v>2.21304328941047</v>
@@ -4514,7 +4514,7 @@
         <v>2.173075148792972</v>
       </c>
       <c r="R7" t="n">
-        <v>2.299448226531529</v>
+        <v>2.299448226531528</v>
       </c>
       <c r="S7" t="n">
         <v>2.262870172436145</v>
@@ -4535,16 +4535,16 @@
         <v>2.279717830177504</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.187126707499052</v>
+        <v>2.187126707499054</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.180097439993851</v>
+        <v>2.18009743999385</v>
       </c>
       <c r="AA7" t="n">
         <v>2.247778593438705</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.193187544043361</v>
+        <v>2.19318754404336</v>
       </c>
     </row>
     <row r="8">
@@ -4557,19 +4557,19 @@
         <v>2.177048021120553</v>
       </c>
       <c r="C8" t="n">
-        <v>2.61714712203408</v>
+        <v>2.617147122034079</v>
       </c>
       <c r="D8" t="n">
-        <v>2.36904962831641</v>
+        <v>2.369049628316408</v>
       </c>
       <c r="E8" t="n">
         <v>2.48289510002387</v>
       </c>
       <c r="F8" t="n">
-        <v>2.595467085018069</v>
+        <v>2.595467085018067</v>
       </c>
       <c r="G8" t="n">
-        <v>2.261257824919825</v>
+        <v>2.261257824919824</v>
       </c>
       <c r="H8" t="n">
         <v>2.266371359646795</v>
@@ -4578,13 +4578,13 @@
         <v>2.297223749797661</v>
       </c>
       <c r="J8" t="n">
-        <v>2.291561287972628</v>
+        <v>2.291561287972627</v>
       </c>
       <c r="K8" t="n">
         <v>2.295123124448063</v>
       </c>
       <c r="L8" t="n">
-        <v>2.338626881999735</v>
+        <v>2.338626881999733</v>
       </c>
       <c r="M8" t="n">
         <v>2.306224587566509</v>
@@ -4593,10 +4593,10 @@
         <v>2.185097223631339</v>
       </c>
       <c r="O8" t="n">
-        <v>2.233836042158077</v>
+        <v>2.233836042158076</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24092845975308</v>
+        <v>2.240928459753079</v>
       </c>
       <c r="Q8" t="n">
         <v>2.172286440484669</v>
@@ -4605,10 +4605,10 @@
         <v>2.357584150072733</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32100609597735</v>
+        <v>2.321006095977349</v>
       </c>
       <c r="T8" t="n">
-        <v>2.252389980850164</v>
+        <v>2.252389980850163</v>
       </c>
       <c r="U8" t="n">
         <v>2.237765449777247</v>
@@ -4617,16 +4617,16 @@
         <v>2.283660098455293</v>
       </c>
       <c r="W8" t="n">
-        <v>2.260064864938142</v>
+        <v>2.260064864938141</v>
       </c>
       <c r="X8" t="n">
         <v>2.283442666852267</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.294268877165522</v>
+        <v>2.294268877165524</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.188072024410404</v>
+        <v>2.188072024410403</v>
       </c>
       <c r="AA8" t="n">
         <v>2.305914516979909</v>
@@ -4645,19 +4645,19 @@
         <v>2.48230617188513</v>
       </c>
       <c r="C9" t="n">
-        <v>2.979014152892809</v>
+        <v>2.979014152892808</v>
       </c>
       <c r="D9" t="n">
-        <v>2.730916659175139</v>
+        <v>2.730916659175137</v>
       </c>
       <c r="E9" t="n">
-        <v>2.846553461296729</v>
+        <v>2.846553461296728</v>
       </c>
       <c r="F9" t="n">
-        <v>2.754882968917314</v>
+        <v>2.754882968917313</v>
       </c>
       <c r="G9" t="n">
-        <v>2.612913253150099</v>
+        <v>2.612913253150098</v>
       </c>
       <c r="H9" t="n">
         <v>2.628238390505524</v>
@@ -4681,28 +4681,28 @@
         <v>2.585138576493355</v>
       </c>
       <c r="O9" t="n">
-        <v>2.658467103393838</v>
+        <v>2.658467103393837</v>
       </c>
       <c r="P9" t="n">
-        <v>2.675760403687346</v>
+        <v>2.675760403687345</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.593078095385827</v>
+        <v>2.593078095385826</v>
       </c>
       <c r="R9" t="n">
         <v>2.719451180931459</v>
       </c>
       <c r="S9" t="n">
-        <v>2.682873126836077</v>
+        <v>2.682873126836076</v>
       </c>
       <c r="T9" t="n">
-        <v>2.614257011708894</v>
+        <v>2.614257011708893</v>
       </c>
       <c r="U9" t="n">
-        <v>2.623644802008879</v>
+        <v>2.623644802008878</v>
       </c>
       <c r="V9" t="n">
-        <v>2.781115008675864</v>
+        <v>2.781115008675863</v>
       </c>
       <c r="W9" t="n">
         <v>2.621922217444168</v>
@@ -4711,10 +4711,10 @@
         <v>2.699720784577436</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.607129661898989</v>
+        <v>2.607129661898986</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.536278974547673</v>
+        <v>2.536278974547672</v>
       </c>
       <c r="AA9" t="n">
         <v>2.667781547838635</v>
@@ -4892,13 +4892,13 @@
         <v>2.452504126082418</v>
       </c>
       <c r="D2" t="n">
-        <v>2.415279491217256</v>
+        <v>2.415279491217257</v>
       </c>
       <c r="E2" t="n">
         <v>2.442298675715666</v>
       </c>
       <c r="F2" t="n">
-        <v>2.453460097201012</v>
+        <v>2.453460097201013</v>
       </c>
       <c r="G2" t="n">
         <v>2.401101269768827</v>
@@ -4916,7 +4916,7 @@
         <v>2.412901765464472</v>
       </c>
       <c r="L2" t="n">
-        <v>2.416071217499356</v>
+        <v>2.416071217499357</v>
       </c>
       <c r="M2" t="n">
         <v>2.41899263915991</v>
@@ -4940,25 +4940,25 @@
         <v>2.421499096310511</v>
       </c>
       <c r="T2" t="n">
-        <v>2.402454361327776</v>
+        <v>2.402454361327775</v>
       </c>
       <c r="U2" t="n">
-        <v>2.43856872030646</v>
+        <v>2.438568720306459</v>
       </c>
       <c r="V2" t="n">
-        <v>2.408725936381352</v>
+        <v>2.408725936381353</v>
       </c>
       <c r="W2" t="n">
-        <v>2.442664757495297</v>
+        <v>2.442664757495296</v>
       </c>
       <c r="X2" t="n">
-        <v>2.410471442353677</v>
+        <v>2.410471442353678</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.403047752993953</v>
+        <v>2.403047752993954</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.420269260040117</v>
+        <v>2.420269260040118</v>
       </c>
       <c r="AA2" t="n">
         <v>2.416698207915214</v>
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.395856166765058</v>
+        <v>2.396107893594021</v>
       </c>
       <c r="C3" t="n">
-        <v>2.748657515080791</v>
+        <v>2.761123410078797</v>
       </c>
       <c r="D3" t="n">
-        <v>2.514634593799272</v>
+        <v>2.519105605242183</v>
       </c>
       <c r="E3" t="n">
-        <v>2.707080744328392</v>
+        <v>2.718308155487217</v>
       </c>
       <c r="F3" t="n">
-        <v>2.787595155521675</v>
+        <v>2.801830795963987</v>
       </c>
       <c r="G3" t="n">
-        <v>2.413060121059136</v>
+        <v>2.41391891870034</v>
       </c>
       <c r="H3" t="n">
-        <v>2.455038024634851</v>
+        <v>2.457401844989463</v>
       </c>
       <c r="I3" t="n">
-        <v>2.579189326497566</v>
+        <v>2.585959195199178</v>
       </c>
       <c r="J3" t="n">
-        <v>2.468753157035257</v>
+        <v>2.47159243472752</v>
       </c>
       <c r="K3" t="n">
-        <v>2.497109753239583</v>
+        <v>2.500971599979936</v>
       </c>
       <c r="L3" t="n">
-        <v>2.519214755021272</v>
+        <v>2.523844589142112</v>
       </c>
       <c r="M3" t="n">
-        <v>2.540479987298073</v>
+        <v>2.545910526356737</v>
       </c>
       <c r="N3" t="n">
-        <v>2.408657548996564</v>
+        <v>2.409364580452431</v>
       </c>
       <c r="O3" t="n">
-        <v>2.490267073288447</v>
+        <v>2.491867477213678</v>
       </c>
       <c r="P3" t="n">
-        <v>2.467909437022442</v>
+        <v>2.470689819280695</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.403268760501493</v>
+        <v>2.403785552550191</v>
       </c>
       <c r="R3" t="n">
-        <v>2.515909209990748</v>
+        <v>2.520432613507314</v>
       </c>
       <c r="S3" t="n">
-        <v>2.557194710485524</v>
+        <v>2.563171298052697</v>
       </c>
       <c r="T3" t="n">
-        <v>2.422861221219704</v>
+        <v>2.424076160544682</v>
       </c>
       <c r="U3" t="n">
-        <v>2.507481493368223</v>
+        <v>2.509838726245474</v>
       </c>
       <c r="V3" t="n">
-        <v>2.467190805885726</v>
+        <v>2.469960043912454</v>
       </c>
       <c r="W3" t="n">
-        <v>2.512999918586183</v>
+        <v>2.515297697854</v>
       </c>
       <c r="X3" t="n">
-        <v>2.480180161931621</v>
+        <v>2.483427172286548</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.427064711471524</v>
+        <v>2.428421971027611</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.450040397866841</v>
+        <v>2.451144831781782</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.524511455585242</v>
+        <v>2.529310759219372</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.484272583707952</v>
+        <v>2.487663591481988</v>
       </c>
     </row>
     <row r="4">
@@ -5074,7 +5074,7 @@
         <v>2.589442740377147</v>
       </c>
       <c r="F4" t="n">
-        <v>2.715516130561684</v>
+        <v>2.715516130561683</v>
       </c>
       <c r="G4" t="n">
         <v>2.124099088464543</v>
@@ -5083,10 +5083,10 @@
         <v>2.189832020441894</v>
       </c>
       <c r="I4" t="n">
-        <v>2.385946815874392</v>
+        <v>2.385946815874393</v>
       </c>
       <c r="J4" t="n">
-        <v>2.21234980489076</v>
+        <v>2.212349804890761</v>
       </c>
       <c r="K4" t="n">
         <v>2.257391115843077</v>
@@ -5095,40 +5095,40 @@
         <v>2.293191534597061</v>
       </c>
       <c r="M4" t="n">
-        <v>2.326025449846589</v>
+        <v>2.326025449846588</v>
       </c>
       <c r="N4" t="n">
-        <v>2.116941669381987</v>
+        <v>2.116941669381988</v>
       </c>
       <c r="O4" t="n">
         <v>2.157697330492536</v>
       </c>
       <c r="P4" t="n">
-        <v>2.211171911029284</v>
+        <v>2.211171911029283</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.108410954954085</v>
+        <v>2.108410954954084</v>
       </c>
       <c r="R4" t="n">
-        <v>2.285799462206376</v>
+        <v>2.285799462206375</v>
       </c>
       <c r="S4" t="n">
         <v>2.354501922716677</v>
       </c>
       <c r="T4" t="n">
-        <v>2.139382880075749</v>
+        <v>2.139382880075748</v>
       </c>
       <c r="U4" t="n">
-        <v>2.191711161070128</v>
+        <v>2.191711161070127</v>
       </c>
       <c r="V4" t="n">
-        <v>2.210404224242082</v>
+        <v>2.210404224242083</v>
       </c>
       <c r="W4" t="n">
         <v>2.188331035510443</v>
       </c>
       <c r="X4" t="n">
-        <v>2.229939498302784</v>
+        <v>2.229939498302783</v>
       </c>
       <c r="Y4" t="n">
         <v>2.146527813118119</v>
@@ -5137,7 +5137,7 @@
         <v>2.135164367436696</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.300273679774022</v>
+        <v>2.300273679774021</v>
       </c>
       <c r="AB4" t="n">
         <v>2.236175236944186</v>
@@ -5156,31 +5156,31 @@
         <v>12.59341393597399</v>
       </c>
       <c r="D5" t="n">
-        <v>5.940654308856484</v>
+        <v>5.940654308856471</v>
       </c>
       <c r="E5" t="n">
-        <v>11.4937154019193</v>
+        <v>11.49371540191931</v>
       </c>
       <c r="F5" t="n">
-        <v>14.35289220395061</v>
+        <v>14.35289220395057</v>
       </c>
       <c r="G5" t="n">
-        <v>2.699111292721892</v>
+        <v>2.699111292721901</v>
       </c>
       <c r="H5" t="n">
-        <v>4.189177571092249</v>
+        <v>4.18917757109225</v>
       </c>
       <c r="I5" t="n">
-        <v>8.028513220913759</v>
+        <v>8.028513220913753</v>
       </c>
       <c r="J5" t="n">
-        <v>4.342753501802332</v>
+        <v>4.342753501802334</v>
       </c>
       <c r="K5" t="n">
-        <v>5.124229972851181</v>
+        <v>5.124229972851183</v>
       </c>
       <c r="L5" t="n">
-        <v>5.514424701331864</v>
+        <v>5.51442470133186</v>
       </c>
       <c r="M5" t="n">
         <v>6.415816423523887</v>
@@ -5189,43 +5189,43 @@
         <v>2.630435288418834</v>
       </c>
       <c r="O5" t="n">
-        <v>3.259148337815348</v>
+        <v>3.259148337815347</v>
       </c>
       <c r="P5" t="n">
-        <v>4.252181059492901</v>
+        <v>4.252181059492903</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.469890142292755</v>
+        <v>2.469890142292754</v>
       </c>
       <c r="R5" t="n">
-        <v>6.133884402964029</v>
+        <v>6.133884402964032</v>
       </c>
       <c r="S5" t="n">
-        <v>6.251508164987208</v>
+        <v>6.251508164987206</v>
       </c>
       <c r="T5" t="n">
         <v>3.068191839091424</v>
       </c>
       <c r="U5" t="n">
-        <v>3.941791346348984</v>
+        <v>3.94179134634898</v>
       </c>
       <c r="V5" t="n">
-        <v>4.168136066833825</v>
+        <v>4.168136066833823</v>
       </c>
       <c r="W5" t="n">
-        <v>3.987723987278667</v>
+        <v>3.987723987278669</v>
       </c>
       <c r="X5" t="n">
-        <v>4.836395422820266</v>
+        <v>4.83639542282027</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.177363692284663</v>
+        <v>3.177363692284664</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.889109258034909</v>
+        <v>2.889109258034908</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.10540067482567</v>
+        <v>6.105400674825666</v>
       </c>
       <c r="AB5" t="n">
         <v>5.061114344965587</v>
@@ -5247,34 +5247,34 @@
         <v>16.75920941431827</v>
       </c>
       <c r="E6" t="n">
-        <v>17.06440353266677</v>
+        <v>17.06440353266676</v>
       </c>
       <c r="F6" t="n">
-        <v>3.893315315639745</v>
+        <v>3.893315315639744</v>
       </c>
       <c r="G6" t="n">
         <v>3.301898273542594</v>
       </c>
       <c r="H6" t="n">
-        <v>16.66479281273152</v>
+        <v>16.66479281273151</v>
       </c>
       <c r="I6" t="n">
-        <v>16.86090760816401</v>
+        <v>16.86090760816402</v>
       </c>
       <c r="J6" t="n">
-        <v>3.390148989968818</v>
+        <v>3.390148989968817</v>
       </c>
       <c r="K6" t="n">
-        <v>16.7323519081327</v>
+        <v>16.73235190813269</v>
       </c>
       <c r="L6" t="n">
-        <v>3.47099071967512</v>
+        <v>3.470990719675121</v>
       </c>
       <c r="M6" t="n">
-        <v>16.80098624213623</v>
+        <v>16.80098624213622</v>
       </c>
       <c r="N6" t="n">
-        <v>3.292418033535595</v>
+        <v>3.292418033535596</v>
       </c>
       <c r="O6" t="n">
         <v>16.63145970732298</v>
@@ -5283,7 +5283,7 @@
         <v>16.68493715879482</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.5833717472437</v>
+        <v>16.58337174724369</v>
       </c>
       <c r="R6" t="n">
         <v>16.760760254496</v>
@@ -5292,10 +5292,10 @@
         <v>3.532301107794731</v>
       </c>
       <c r="T6" t="n">
-        <v>3.317182065153806</v>
+        <v>3.317182065153808</v>
       </c>
       <c r="U6" t="n">
-        <v>3.369068044948938</v>
+        <v>3.369068044948936</v>
       </c>
       <c r="V6" t="n">
         <v>16.6853650165317</v>
@@ -5310,7 +5310,7 @@
         <v>3.341398044482535</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.312963552514751</v>
+        <v>3.31296355251475</v>
       </c>
       <c r="AA6" t="n">
         <v>16.77523447206364</v>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.163583354886262</v>
+        <v>2.163583354886263</v>
       </c>
       <c r="C7" t="n">
         <v>2.707398936877147</v>
@@ -5338,10 +5338,10 @@
         <v>2.656332948209083</v>
       </c>
       <c r="F7" t="n">
-        <v>2.78240633839362</v>
+        <v>2.782406338393619</v>
       </c>
       <c r="G7" t="n">
-        <v>2.190989296296478</v>
+        <v>2.190989296296479</v>
       </c>
       <c r="H7" t="n">
         <v>2.25672222827383</v>
@@ -5353,13 +5353,13 @@
         <v>2.279240012722695</v>
       </c>
       <c r="K7" t="n">
-        <v>2.324281323675013</v>
+        <v>2.324281323675012</v>
       </c>
       <c r="L7" t="n">
-        <v>2.360081742428995</v>
+        <v>2.360081742428996</v>
       </c>
       <c r="M7" t="n">
-        <v>2.392915657678524</v>
+        <v>2.392915657678523</v>
       </c>
       <c r="N7" t="n">
         <v>2.183831877213922</v>
@@ -5374,7 +5374,7 @@
         <v>2.175301162786019</v>
       </c>
       <c r="R7" t="n">
-        <v>2.352689670038311</v>
+        <v>2.35268967003831</v>
       </c>
       <c r="S7" t="n">
         <v>2.421392130548613</v>
@@ -5398,7 +5398,7 @@
         <v>2.212975719750809</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.202054575268632</v>
+        <v>2.202054575268631</v>
       </c>
       <c r="AA7" t="n">
         <v>2.367163887605957</v>
@@ -5417,7 +5417,7 @@
         <v>2.175119750331866</v>
       </c>
       <c r="C8" t="n">
-        <v>2.774164310351534</v>
+        <v>2.774164310351533</v>
       </c>
       <c r="D8" t="n">
         <v>2.417904203334972</v>
@@ -5438,10 +5438,10 @@
         <v>2.519602397180713</v>
       </c>
       <c r="J8" t="n">
-        <v>2.34600538619708</v>
+        <v>2.346005386197082</v>
       </c>
       <c r="K8" t="n">
-        <v>2.391046697149397</v>
+        <v>2.391046697149396</v>
       </c>
       <c r="L8" t="n">
         <v>2.426847115903383</v>
@@ -5462,13 +5462,13 @@
         <v>2.175983803511404</v>
       </c>
       <c r="R8" t="n">
-        <v>2.419455043512694</v>
+        <v>2.419455043512695</v>
       </c>
       <c r="S8" t="n">
-        <v>2.488157504022997</v>
+        <v>2.488157504022998</v>
       </c>
       <c r="T8" t="n">
-        <v>2.273038461382068</v>
+        <v>2.273038461382069</v>
       </c>
       <c r="U8" t="n">
         <v>2.297982733601045</v>
@@ -5477,13 +5477,13 @@
         <v>2.328981238539618</v>
       </c>
       <c r="W8" t="n">
-        <v>2.32199747088563</v>
+        <v>2.321997470885631</v>
       </c>
       <c r="X8" t="n">
         <v>2.302574192433255</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.334679360787861</v>
+        <v>2.334679360787862</v>
       </c>
       <c r="Z8" t="n">
         <v>2.212565064093594</v>
@@ -5505,31 +5505,31 @@
         <v>2.599897920836224</v>
       </c>
       <c r="C9" t="n">
-        <v>3.285226708743663</v>
+        <v>3.285226708743662</v>
       </c>
       <c r="D9" t="n">
         <v>2.928966601727101</v>
       </c>
       <c r="E9" t="n">
-        <v>3.201500020732532</v>
+        <v>3.201500020732531</v>
       </c>
       <c r="F9" t="n">
         <v>3.034007596602642</v>
       </c>
       <c r="G9" t="n">
-        <v>2.768817030930528</v>
+        <v>2.768817030930527</v>
       </c>
       <c r="H9" t="n">
         <v>2.834550000140341</v>
       </c>
       <c r="I9" t="n">
-        <v>3.030664795572844</v>
+        <v>3.030664795572843</v>
       </c>
       <c r="J9" t="n">
         <v>2.857067784589211</v>
       </c>
       <c r="K9" t="n">
-        <v>2.902109095541527</v>
+        <v>2.902109095541526</v>
       </c>
       <c r="L9" t="n">
         <v>2.93790951429551</v>
@@ -5538,19 +5538,19 @@
         <v>2.970743429545041</v>
       </c>
       <c r="N9" t="n">
-        <v>2.761659649080436</v>
+        <v>2.761659649080435</v>
       </c>
       <c r="O9" t="n">
         <v>2.849312551764913</v>
       </c>
       <c r="P9" t="n">
-        <v>2.912986485819985</v>
+        <v>2.912986485819984</v>
       </c>
       <c r="Q9" t="n">
         <v>2.75312889742007</v>
       </c>
       <c r="R9" t="n">
-        <v>2.930517441904829</v>
+        <v>2.930517441904828</v>
       </c>
       <c r="S9" t="n">
         <v>2.999219902415128</v>
@@ -5559,7 +5559,7 @@
         <v>2.7841008597742</v>
       </c>
       <c r="U9" t="n">
-        <v>2.835986839569335</v>
+        <v>2.835986839569334</v>
       </c>
       <c r="V9" t="n">
         <v>3.018425241085491</v>
@@ -5571,7 +5571,7 @@
         <v>2.874657478001233</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.790803491617326</v>
+        <v>2.790803491617325</v>
       </c>
       <c r="Z9" t="n">
         <v>2.694562453028162</v>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.392994666761364</v>
+        <v>2.392994666761363</v>
       </c>
       <c r="C2" t="n">
         <v>2.436133605672671</v>
@@ -5758,25 +5758,25 @@
         <v>2.419108345779788</v>
       </c>
       <c r="F2" t="n">
-        <v>2.436212705762627</v>
+        <v>2.436212705762628</v>
       </c>
       <c r="G2" t="n">
-        <v>2.394692237645622</v>
+        <v>2.394692237645621</v>
       </c>
       <c r="H2" t="n">
-        <v>2.399094524801902</v>
+        <v>2.399094524801901</v>
       </c>
       <c r="I2" t="n">
         <v>2.404015401308486</v>
       </c>
       <c r="J2" t="n">
-        <v>2.400545783728759</v>
+        <v>2.400545783728758</v>
       </c>
       <c r="K2" t="n">
         <v>2.400537422184499</v>
       </c>
       <c r="L2" t="n">
-        <v>2.401748761633706</v>
+        <v>2.401748761633705</v>
       </c>
       <c r="M2" t="n">
         <v>2.405237546350028</v>
@@ -5788,34 +5788,34 @@
         <v>2.431562618381026</v>
       </c>
       <c r="P2" t="n">
-        <v>2.40240405185382</v>
+        <v>2.402404051853819</v>
       </c>
       <c r="Q2" t="n">
         <v>2.393397311144202</v>
       </c>
       <c r="R2" t="n">
-        <v>2.403397701374354</v>
+        <v>2.403397701374353</v>
       </c>
       <c r="S2" t="n">
-        <v>2.407861221116392</v>
+        <v>2.407861221116391</v>
       </c>
       <c r="T2" t="n">
-        <v>2.395766817995331</v>
+        <v>2.39576681799533</v>
       </c>
       <c r="U2" t="n">
-        <v>2.431605690001691</v>
+        <v>2.43160569000169</v>
       </c>
       <c r="V2" t="n">
-        <v>2.401161660928755</v>
+        <v>2.401161660928754</v>
       </c>
       <c r="W2" t="n">
         <v>2.433778612366674</v>
       </c>
       <c r="X2" t="n">
-        <v>2.403176446932317</v>
+        <v>2.403176446932316</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.39613305288292</v>
+        <v>2.396133052882919</v>
       </c>
       <c r="Z2" t="n">
         <v>2.412216495057383</v>
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.391500735382837</v>
+        <v>2.391757111770295</v>
       </c>
       <c r="C3" t="n">
-        <v>2.671274235270132</v>
+        <v>2.681206813955807</v>
       </c>
       <c r="D3" t="n">
-        <v>2.454913424102697</v>
+        <v>2.457430973411102</v>
       </c>
       <c r="E3" t="n">
-        <v>2.577744795005074</v>
+        <v>2.584570626361304</v>
       </c>
       <c r="F3" t="n">
-        <v>2.700075527032632</v>
+        <v>2.711364193069718</v>
       </c>
       <c r="G3" t="n">
-        <v>2.403528338999614</v>
+        <v>2.404209490951083</v>
       </c>
       <c r="H3" t="n">
-        <v>2.435260680179947</v>
+        <v>2.437080655192276</v>
       </c>
       <c r="I3" t="n">
-        <v>2.470287634531326</v>
+        <v>2.473351035501668</v>
       </c>
       <c r="J3" t="n">
-        <v>2.44520529302014</v>
+        <v>2.447372596793504</v>
       </c>
       <c r="K3" t="n">
-        <v>2.445128810627193</v>
+        <v>2.447300451414448</v>
       </c>
       <c r="L3" t="n">
-        <v>2.453307219769471</v>
+        <v>2.455767324288699</v>
       </c>
       <c r="M3" t="n">
-        <v>2.478504591340397</v>
+        <v>2.481889017915944</v>
       </c>
       <c r="N3" t="n">
-        <v>2.403592703929947</v>
+        <v>2.404279678363302</v>
       </c>
       <c r="O3" t="n">
-        <v>2.485811310877656</v>
+        <v>2.487474799407891</v>
       </c>
       <c r="P3" t="n">
-        <v>2.458341710564173</v>
+        <v>2.460945683258466</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.394376812442784</v>
+        <v>2.39473754484747</v>
       </c>
       <c r="R3" t="n">
-        <v>2.46597803718885</v>
+        <v>2.468890165699591</v>
       </c>
       <c r="S3" t="n">
-        <v>2.49665006528146</v>
+        <v>2.500635554284269</v>
       </c>
       <c r="T3" t="n">
-        <v>2.411293869425605</v>
+        <v>2.412257606637854</v>
       </c>
       <c r="U3" t="n">
-        <v>2.495091415708906</v>
+        <v>2.497194745713598</v>
       </c>
       <c r="V3" t="n">
-        <v>2.449395179416743</v>
+        <v>2.451697255182757</v>
       </c>
       <c r="W3" t="n">
-        <v>2.488173504516686</v>
+        <v>2.489784110403074</v>
       </c>
       <c r="X3" t="n">
-        <v>2.46405347013769</v>
+        <v>2.466895571226681</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.413920133132809</v>
+        <v>2.414970492572488</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.431847783499503</v>
+        <v>2.432500872664455</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.441729675326958</v>
+        <v>2.443762172577146</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.449732005687201</v>
+        <v>2.452061868238145</v>
       </c>
     </row>
     <row r="4">
@@ -5925,13 +5925,13 @@
         <v>2.092315257632959</v>
       </c>
       <c r="C4" t="n">
-        <v>2.523105218013931</v>
+        <v>2.523105218013932</v>
       </c>
       <c r="D4" t="n">
         <v>2.192768302993838</v>
       </c>
       <c r="E4" t="n">
-        <v>2.387281275031917</v>
+        <v>2.387281275031916</v>
       </c>
       <c r="F4" t="n">
         <v>2.580482889432424</v>
@@ -5946,7 +5946,7 @@
         <v>2.216799524131072</v>
       </c>
       <c r="J4" t="n">
-        <v>2.177651613846193</v>
+        <v>2.177651613846192</v>
       </c>
       <c r="K4" t="n">
         <v>2.177514149976203</v>
@@ -5961,13 +5961,13 @@
         <v>2.111457575095829</v>
       </c>
       <c r="O4" t="n">
-        <v>2.155962484184635</v>
+        <v>2.155962484184636</v>
       </c>
       <c r="P4" t="n">
-        <v>2.198598590783241</v>
+        <v>2.198598590783242</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.096863311162684</v>
+        <v>2.096863311162685</v>
       </c>
       <c r="R4" t="n">
         <v>2.209822319219042</v>
@@ -5979,7 +5979,7 @@
         <v>2.123627981073181</v>
       </c>
       <c r="U4" t="n">
-        <v>2.175756036368576</v>
+        <v>2.175756036368575</v>
       </c>
       <c r="V4" t="n">
         <v>2.18477240689915</v>
@@ -5988,10 +5988,10 @@
         <v>2.152944815147938</v>
       </c>
       <c r="X4" t="n">
-        <v>2.207323148514163</v>
+        <v>2.207323148514162</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.128249954585968</v>
+        <v>2.128249954585967</v>
       </c>
       <c r="Z4" t="n">
         <v>2.110208599696772</v>
@@ -6013,82 +6013,82 @@
         <v>2.229824065247112</v>
       </c>
       <c r="C5" t="n">
-        <v>9.647356187492923</v>
+        <v>9.64735618749296</v>
       </c>
       <c r="D5" t="n">
-        <v>3.976088629539057</v>
+        <v>3.976088629539055</v>
       </c>
       <c r="E5" t="n">
-        <v>7.379120555917693</v>
+        <v>7.379120555917687</v>
       </c>
       <c r="F5" t="n">
         <v>10.92890763670037</v>
       </c>
       <c r="G5" t="n">
-        <v>2.523336036685596</v>
+        <v>2.523336036685603</v>
       </c>
       <c r="H5" t="n">
-        <v>3.565023334441089</v>
+        <v>3.565023334441092</v>
       </c>
       <c r="I5" t="n">
-        <v>4.499611500187205</v>
+        <v>4.499611500187209</v>
       </c>
       <c r="J5" t="n">
-        <v>3.640921441453488</v>
+        <v>3.64092144145349</v>
       </c>
       <c r="K5" t="n">
-        <v>3.630498870734936</v>
+        <v>3.630498870734937</v>
       </c>
       <c r="L5" t="n">
-        <v>3.630497848670789</v>
+        <v>3.63049784867079</v>
       </c>
       <c r="M5" t="n">
-        <v>4.438228503152976</v>
+        <v>4.438228503152973</v>
       </c>
       <c r="N5" t="n">
-        <v>2.566766782647715</v>
+        <v>2.566766782647717</v>
       </c>
       <c r="O5" t="n">
-        <v>3.217029977688017</v>
+        <v>3.21702997768802</v>
       </c>
       <c r="P5" t="n">
-        <v>3.946754977387684</v>
+        <v>3.946754977387688</v>
       </c>
       <c r="Q5" t="n">
         <v>2.311499358437499</v>
       </c>
       <c r="R5" t="n">
-        <v>4.427490534013718</v>
+        <v>4.427490534013719</v>
       </c>
       <c r="S5" t="n">
-        <v>4.705455841324375</v>
+        <v>4.705455841324372</v>
       </c>
       <c r="T5" t="n">
-        <v>2.787866070246442</v>
+        <v>2.787866070246443</v>
       </c>
       <c r="U5" t="n">
         <v>3.471602584617553</v>
       </c>
       <c r="V5" t="n">
-        <v>3.65754683026904</v>
+        <v>3.657546830269043</v>
       </c>
       <c r="W5" t="n">
-        <v>3.251763476359177</v>
+        <v>3.251763476359176</v>
       </c>
       <c r="X5" t="n">
-        <v>4.204261088801076</v>
+        <v>4.204261088801074</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.867472062316005</v>
+        <v>2.867472062316004</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.508388664414357</v>
+        <v>2.508388664414356</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.644521225493043</v>
+        <v>3.644521225493042</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.901785319498171</v>
+        <v>3.90178531949817</v>
       </c>
     </row>
     <row r="6">
@@ -6098,40 +6098,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.57442485238239</v>
+        <v>15.57442485238241</v>
       </c>
       <c r="C6" t="n">
-        <v>3.616928583613872</v>
+        <v>3.616928583613873</v>
       </c>
       <c r="D6" t="n">
-        <v>3.286591668593778</v>
+        <v>3.286591668593779</v>
       </c>
       <c r="E6" t="n">
         <v>3.481104640631858</v>
       </c>
       <c r="F6" t="n">
-        <v>16.06259248418184</v>
+        <v>16.06259248418186</v>
       </c>
       <c r="G6" t="n">
-        <v>15.59359969644128</v>
+        <v>15.59359969644129</v>
       </c>
       <c r="H6" t="n">
         <v>15.64332555502362</v>
       </c>
       <c r="I6" t="n">
-        <v>15.69890911888049</v>
+        <v>15.6989091188805</v>
       </c>
       <c r="J6" t="n">
         <v>15.65976120859563</v>
       </c>
       <c r="K6" t="n">
-        <v>15.65962374472565</v>
+        <v>15.65962374472567</v>
       </c>
       <c r="L6" t="n">
         <v>3.28502015189861</v>
       </c>
       <c r="M6" t="n">
-        <v>15.71287885532085</v>
+        <v>15.71287885532086</v>
       </c>
       <c r="N6" t="n">
         <v>3.204074920929994</v>
@@ -6140,22 +6140,22 @@
         <v>15.63708890348497</v>
       </c>
       <c r="P6" t="n">
-        <v>3.288321159965977</v>
+        <v>3.288321159965978</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.57897290591213</v>
+        <v>15.57897290591214</v>
       </c>
       <c r="R6" t="n">
         <v>3.303645684818982</v>
       </c>
       <c r="S6" t="n">
-        <v>15.74234942277531</v>
+        <v>15.74234942277533</v>
       </c>
       <c r="T6" t="n">
-        <v>3.217451346673117</v>
+        <v>3.217451346673118</v>
       </c>
       <c r="U6" t="n">
-        <v>3.269094219987429</v>
+        <v>3.26909421998743</v>
       </c>
       <c r="V6" t="n">
         <v>3.278595772499092</v>
@@ -6167,13 +6167,13 @@
         <v>15.6894327432636</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.238756191632721</v>
+        <v>3.23875619163272</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.204031965296721</v>
+        <v>3.204031965296722</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.65389165785065</v>
+        <v>15.65389165785066</v>
       </c>
       <c r="AB6" t="n">
         <v>3.277109589338555</v>
@@ -6189,7 +6189,7 @@
         <v>2.152737291977064</v>
       </c>
       <c r="C7" t="n">
-        <v>2.583527252358035</v>
+        <v>2.583527252358036</v>
       </c>
       <c r="D7" t="n">
         <v>2.253190337337942</v>
@@ -6222,19 +6222,19 @@
         <v>2.291191294915517</v>
       </c>
       <c r="N7" t="n">
-        <v>2.171879609439933</v>
+        <v>2.171879609439934</v>
       </c>
       <c r="O7" t="n">
-        <v>2.216380084083682</v>
+        <v>2.216380084083683</v>
       </c>
       <c r="P7" t="n">
         <v>2.259016190682289</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15728534550679</v>
+        <v>2.157285345506789</v>
       </c>
       <c r="R7" t="n">
-        <v>2.270244353563147</v>
+        <v>2.270244353563146</v>
       </c>
       <c r="S7" t="n">
         <v>2.320661862369991</v>
@@ -6280,7 +6280,7 @@
         <v>2.641189974906062</v>
       </c>
       <c r="D8" t="n">
-        <v>2.310853059885969</v>
+        <v>2.310853059885968</v>
       </c>
       <c r="E8" t="n">
         <v>2.479382033881176</v>
@@ -6289,19 +6289,19 @@
         <v>2.657371007722298</v>
       </c>
       <c r="G8" t="n">
-        <v>2.239693637456343</v>
+        <v>2.239693637456342</v>
       </c>
       <c r="H8" t="n">
         <v>2.279300717166301</v>
       </c>
       <c r="I8" t="n">
-        <v>2.334884281023203</v>
+        <v>2.334884281023202</v>
       </c>
       <c r="J8" t="n">
         <v>2.295736370738323</v>
       </c>
       <c r="K8" t="n">
-        <v>2.295598906868334</v>
+        <v>2.295598906868333</v>
       </c>
       <c r="L8" t="n">
         <v>2.309281543190797</v>
@@ -6313,13 +6313,13 @@
         <v>2.191714986728974</v>
       </c>
       <c r="O8" t="n">
-        <v>2.246615178740711</v>
+        <v>2.246615178740712</v>
       </c>
       <c r="P8" t="n">
         <v>2.286703150310052</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.156559018131584</v>
+        <v>2.156559018131585</v>
       </c>
       <c r="R8" t="n">
         <v>2.327907076111172</v>
@@ -6334,16 +6334,16 @@
         <v>2.269554326243159</v>
       </c>
       <c r="V8" t="n">
-        <v>2.289538237551176</v>
+        <v>2.289538237551175</v>
       </c>
       <c r="W8" t="n">
         <v>2.271039162423814</v>
       </c>
       <c r="X8" t="n">
-        <v>2.271491375634358</v>
+        <v>2.271491375634357</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.294397996431255</v>
+        <v>2.294397996431254</v>
       </c>
       <c r="Z8" t="n">
         <v>2.178587947451282</v>
@@ -6365,13 +6365,13 @@
         <v>2.502000737482523</v>
       </c>
       <c r="C9" t="n">
-        <v>3.048169893158228</v>
+        <v>3.048169893158229</v>
       </c>
       <c r="D9" t="n">
         <v>2.717832978138132</v>
       </c>
       <c r="E9" t="n">
-        <v>2.88571688289022</v>
+        <v>2.885716882890219</v>
       </c>
       <c r="F9" t="n">
         <v>2.839567062771328</v>
@@ -6395,7 +6395,7 @@
         <v>2.716261461442961</v>
       </c>
       <c r="M9" t="n">
-        <v>2.755833935715709</v>
+        <v>2.755833935715708</v>
       </c>
       <c r="N9" t="n">
         <v>2.636522250240126</v>
@@ -6404,7 +6404,7 @@
         <v>2.719263639587593</v>
       </c>
       <c r="P9" t="n">
-        <v>2.77021553016627</v>
+        <v>2.770215530166271</v>
       </c>
       <c r="Q9" t="n">
         <v>2.621927960780435</v>
@@ -6422,7 +6422,7 @@
         <v>2.700335529531784</v>
       </c>
       <c r="V9" t="n">
-        <v>2.8429820800119</v>
+        <v>2.842982080011901</v>
       </c>
       <c r="W9" t="n">
         <v>2.678009490292234</v>
@@ -6437,7 +6437,7 @@
         <v>2.565709869860436</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.696846738245508</v>
+        <v>2.696846738245507</v>
       </c>
       <c r="AB9" t="n">
         <v>2.709461580889275</v>
@@ -6609,10 +6609,10 @@
         <v>2.388592647785057</v>
       </c>
       <c r="C2" t="n">
-        <v>2.427284894164103</v>
+        <v>2.427284894164104</v>
       </c>
       <c r="D2" t="n">
-        <v>2.395585724985056</v>
+        <v>2.395585724985057</v>
       </c>
       <c r="E2" t="n">
         <v>2.399617950438288</v>
@@ -6645,7 +6645,7 @@
         <v>2.389347891231623</v>
       </c>
       <c r="O2" t="n">
-        <v>2.424518273979581</v>
+        <v>2.42451827397958</v>
       </c>
       <c r="P2" t="n">
         <v>2.397017729203362</v>
@@ -6660,7 +6660,7 @@
         <v>2.399673722659565</v>
       </c>
       <c r="T2" t="n">
-        <v>2.390718534059106</v>
+        <v>2.390718534059107</v>
       </c>
       <c r="U2" t="n">
         <v>2.424859841412913</v>
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.388779985354412</v>
+        <v>2.389071102515841</v>
       </c>
       <c r="C3" t="n">
-        <v>2.637647545748767</v>
+        <v>2.646515978650049</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4387128034635</v>
+        <v>2.440783152466623</v>
       </c>
       <c r="E3" t="n">
-        <v>2.467157528930707</v>
+        <v>2.47022141791355</v>
       </c>
       <c r="F3" t="n">
-        <v>2.648983174989455</v>
+        <v>2.658564316013281</v>
       </c>
       <c r="G3" t="n">
-        <v>2.393323299864142</v>
+        <v>2.393774544259072</v>
       </c>
       <c r="H3" t="n">
-        <v>2.421527272071342</v>
+        <v>2.422990298815965</v>
       </c>
       <c r="I3" t="n">
-        <v>2.423568373808191</v>
+        <v>2.425099593306699</v>
       </c>
       <c r="J3" t="n">
-        <v>2.427667545803387</v>
+        <v>2.429342375792213</v>
       </c>
       <c r="K3" t="n">
-        <v>2.420723197456427</v>
+        <v>2.422153722149748</v>
       </c>
       <c r="L3" t="n">
-        <v>2.442807063879219</v>
+        <v>2.44501907632042</v>
       </c>
       <c r="M3" t="n">
-        <v>2.449818571568446</v>
+        <v>2.45229536478089</v>
       </c>
       <c r="N3" t="n">
-        <v>2.394189777096645</v>
+        <v>2.394674356137907</v>
       </c>
       <c r="O3" t="n">
-        <v>2.472996963846885</v>
+        <v>2.474431660768374</v>
       </c>
       <c r="P3" t="n">
-        <v>2.448545775895623</v>
+        <v>2.450938799732669</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.388278828956764</v>
+        <v>2.388554254685596</v>
       </c>
       <c r="R3" t="n">
-        <v>2.435949806819071</v>
+        <v>2.437923020199857</v>
       </c>
       <c r="S3" t="n">
-        <v>2.467391751102494</v>
+        <v>2.470462692577933</v>
       </c>
       <c r="T3" t="n">
-        <v>2.403999252407788</v>
+        <v>2.404834117721427</v>
       </c>
       <c r="U3" t="n">
-        <v>2.479240076609146</v>
+        <v>2.480946026953276</v>
       </c>
       <c r="V3" t="n">
-        <v>2.427785623305987</v>
+        <v>2.429453464081797</v>
       </c>
       <c r="W3" t="n">
-        <v>2.464508883005823</v>
+        <v>2.465457979973745</v>
       </c>
       <c r="X3" t="n">
-        <v>2.445299924555049</v>
+        <v>2.447607893025343</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.403300487202289</v>
+        <v>2.404106066201587</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.419359231879</v>
+        <v>2.419730313437113</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.406817538218212</v>
+        <v>2.407747167471866</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.419398345944749</v>
+        <v>2.420779052668128</v>
       </c>
     </row>
     <row r="4">
@@ -6806,7 +6806,7 @@
         <v>2.144948469981178</v>
       </c>
       <c r="J4" t="n">
-        <v>2.151726425552898</v>
+        <v>2.151726425552899</v>
       </c>
       <c r="K4" t="n">
         <v>2.140676547115633</v>
@@ -6818,7 +6818,7 @@
         <v>2.186724209373637</v>
       </c>
       <c r="N4" t="n">
-        <v>2.098591778032932</v>
+        <v>2.098591778032933</v>
       </c>
       <c r="O4" t="n">
         <v>2.141791443596902</v>
@@ -6873,13 +6873,13 @@
         <v>2.252083345558275</v>
       </c>
       <c r="C5" t="n">
-        <v>8.913066318287189</v>
+        <v>8.913066318287182</v>
       </c>
       <c r="D5" t="n">
-        <v>3.661007955325526</v>
+        <v>3.661007955325524</v>
       </c>
       <c r="E5" t="n">
-        <v>4.293749655869026</v>
+        <v>4.293749655869022</v>
       </c>
       <c r="F5" t="n">
         <v>9.782424517134491</v>
@@ -6888,67 +6888,67 @@
         <v>2.368706367266729</v>
       </c>
       <c r="H5" t="n">
-        <v>3.252049520798748</v>
+        <v>3.252049520798749</v>
       </c>
       <c r="I5" t="n">
         <v>3.278645129730962</v>
       </c>
       <c r="J5" t="n">
-        <v>3.315029061804666</v>
+        <v>3.315029061804667</v>
       </c>
       <c r="K5" t="n">
-        <v>3.127450705082228</v>
+        <v>3.127450705082231</v>
       </c>
       <c r="L5" t="n">
-        <v>3.557585885872454</v>
+        <v>3.557585885872453</v>
       </c>
       <c r="M5" t="n">
-        <v>3.950470286172633</v>
+        <v>3.950470286172636</v>
       </c>
       <c r="N5" t="n">
-        <v>2.413112687863385</v>
+        <v>2.413112687863386</v>
       </c>
       <c r="O5" t="n">
         <v>3.057633672085279</v>
       </c>
       <c r="P5" t="n">
-        <v>3.746376923641908</v>
+        <v>3.746376923641915</v>
       </c>
       <c r="Q5" t="n">
         <v>2.248537380073234</v>
       </c>
       <c r="R5" t="n">
-        <v>3.67069605508746</v>
+        <v>3.670696055087462</v>
       </c>
       <c r="S5" t="n">
         <v>4.219992596726855</v>
       </c>
       <c r="T5" t="n">
-        <v>2.700997115589991</v>
+        <v>2.700997115589992</v>
       </c>
       <c r="U5" t="n">
-        <v>3.240711509800616</v>
+        <v>3.240711509800619</v>
       </c>
       <c r="V5" t="n">
-        <v>3.237912037102858</v>
+        <v>3.237912037102856</v>
       </c>
       <c r="W5" t="n">
         <v>2.762698687525914</v>
       </c>
       <c r="X5" t="n">
-        <v>3.7710127857012</v>
+        <v>3.771012785701199</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.67552343286575</v>
+        <v>2.675523432865749</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.30564855112497</v>
+        <v>2.305648551124971</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.769228540155101</v>
+        <v>2.769228540155106</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.18238390443864</v>
+        <v>3.182383904438638</v>
       </c>
     </row>
     <row r="6">
@@ -6958,13 +6958,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.5674216317523</v>
+        <v>15.56742163175231</v>
       </c>
       <c r="C6" t="n">
-        <v>15.94925140239225</v>
+        <v>15.94925140239226</v>
       </c>
       <c r="D6" t="n">
-        <v>15.64641165570074</v>
+        <v>15.64641165570072</v>
       </c>
       <c r="E6" t="n">
         <v>3.30531658831003</v>
@@ -6973,22 +6973,22 @@
         <v>15.97843578756416</v>
       </c>
       <c r="G6" t="n">
-        <v>15.5746461809812</v>
+        <v>15.57464618098121</v>
       </c>
       <c r="H6" t="n">
-        <v>15.61898020444486</v>
+        <v>15.61898020444487</v>
       </c>
       <c r="I6" t="n">
-        <v>15.62230914585864</v>
+        <v>15.62230914585865</v>
       </c>
       <c r="J6" t="n">
-        <v>3.242446192630061</v>
+        <v>3.242446192630062</v>
       </c>
       <c r="K6" t="n">
         <v>3.231396314192793</v>
       </c>
       <c r="L6" t="n">
-        <v>15.65359531502117</v>
+        <v>15.65359531502118</v>
       </c>
       <c r="M6" t="n">
         <v>15.66408488525109</v>
@@ -7000,31 +7000,31 @@
         <v>3.232111949234068</v>
       </c>
       <c r="P6" t="n">
-        <v>15.66158023787241</v>
+        <v>15.66158023787243</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.56659463530405</v>
+        <v>15.56659463530406</v>
       </c>
       <c r="R6" t="n">
-        <v>15.64175783337765</v>
+        <v>15.64175783337766</v>
       </c>
       <c r="S6" t="n">
         <v>15.69258747000618</v>
       </c>
       <c r="T6" t="n">
-        <v>3.204793586373376</v>
+        <v>3.204793586373377</v>
       </c>
       <c r="U6" t="n">
         <v>15.63094963861709</v>
       </c>
       <c r="V6" t="n">
-        <v>3.24302315141569</v>
+        <v>3.243023151415688</v>
       </c>
       <c r="W6" t="n">
         <v>15.59582280844969</v>
       </c>
       <c r="X6" t="n">
-        <v>3.270435989101057</v>
+        <v>3.270435989101056</v>
       </c>
       <c r="Y6" t="n">
         <v>3.221552143297163</v>
@@ -7033,10 +7033,10 @@
         <v>3.184378329391294</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.59592926457845</v>
+        <v>15.59592926457847</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.228661247631275</v>
+        <v>3.228661247631276</v>
       </c>
     </row>
     <row r="7">
@@ -7076,7 +7076,7 @@
         <v>2.199655145945622</v>
       </c>
       <c r="L7" t="n">
-        <v>2.235213237973693</v>
+        <v>2.235213237973692</v>
       </c>
       <c r="M7" t="n">
         <v>2.245702808203626</v>
@@ -7085,13 +7085,13 @@
         <v>2.157570376862921</v>
       </c>
       <c r="O7" t="n">
-        <v>2.200765658808405</v>
+        <v>2.200765658808406</v>
       </c>
       <c r="P7" t="n">
         <v>2.244200341435009</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.148212558256554</v>
+        <v>2.148212558256555</v>
       </c>
       <c r="R7" t="n">
         <v>2.223375756330173</v>
@@ -7137,7 +7137,7 @@
         <v>2.156531347103623</v>
       </c>
       <c r="C8" t="n">
-        <v>2.585163884250809</v>
+        <v>2.58516388425081</v>
       </c>
       <c r="D8" t="n">
         <v>2.282324137559261</v>
@@ -7158,10 +7158,10 @@
         <v>2.258221627717182</v>
       </c>
       <c r="J8" t="n">
-        <v>2.264999583288903</v>
+        <v>2.264999583288904</v>
       </c>
       <c r="K8" t="n">
-        <v>2.253949704851638</v>
+        <v>2.253949704851637</v>
       </c>
       <c r="L8" t="n">
         <v>2.289507796879708</v>
@@ -7197,7 +7197,7 @@
         <v>2.252795830061059</v>
       </c>
       <c r="W8" t="n">
-        <v>2.23275468754724</v>
+        <v>2.232754687547241</v>
       </c>
       <c r="X8" t="n">
         <v>2.241278367959924</v>
@@ -7209,7 +7209,7 @@
         <v>2.159259568127159</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.231841746436994</v>
+        <v>2.231841746436995</v>
       </c>
       <c r="AB8" t="n">
         <v>2.300524252695901</v>
@@ -7228,7 +7228,7 @@
         <v>2.938938380463757</v>
       </c>
       <c r="D9" t="n">
-        <v>2.636098633772206</v>
+        <v>2.636098633772205</v>
       </c>
       <c r="E9" t="n">
         <v>2.657932574716751</v>
@@ -7246,7 +7246,7 @@
         <v>2.611996123930127</v>
       </c>
       <c r="J9" t="n">
-        <v>2.618774079501849</v>
+        <v>2.618774079501848</v>
       </c>
       <c r="K9" t="n">
         <v>2.607724201064582</v>
@@ -7255,16 +7255,16 @@
         <v>2.643282293092655</v>
       </c>
       <c r="M9" t="n">
-        <v>2.653771863322587</v>
+        <v>2.653771863322588</v>
       </c>
       <c r="N9" t="n">
-        <v>2.565639431981882</v>
+        <v>2.565639431981883</v>
       </c>
       <c r="O9" t="n">
         <v>2.642886838627526</v>
       </c>
       <c r="P9" t="n">
-        <v>2.693726325808299</v>
+        <v>2.6937263258083</v>
       </c>
       <c r="Q9" t="n">
         <v>2.556281590247178</v>
@@ -7276,13 +7276,13 @@
         <v>2.682274448077632</v>
       </c>
       <c r="T9" t="n">
-        <v>2.581121473245163</v>
+        <v>2.581121473245164</v>
       </c>
       <c r="U9" t="n">
         <v>2.620636616688569</v>
       </c>
       <c r="V9" t="n">
-        <v>2.737910236282036</v>
+        <v>2.737910236282037</v>
       </c>
       <c r="W9" t="n">
         <v>2.586519985681712</v>
@@ -7475,19 +7475,19 @@
         <v>2.429825854941701</v>
       </c>
       <c r="E2" t="n">
-        <v>2.440686816564016</v>
+        <v>2.440686816564017</v>
       </c>
       <c r="F2" t="n">
-        <v>2.449806527997118</v>
+        <v>2.449806527997119</v>
       </c>
       <c r="G2" t="n">
         <v>2.403354993244746</v>
       </c>
       <c r="H2" t="n">
-        <v>2.406425700587746</v>
+        <v>2.406425700587747</v>
       </c>
       <c r="I2" t="n">
-        <v>2.421137275119836</v>
+        <v>2.421137275119837</v>
       </c>
       <c r="J2" t="n">
         <v>2.408340753814069</v>
@@ -7496,7 +7496,7 @@
         <v>2.412105325025206</v>
       </c>
       <c r="L2" t="n">
-        <v>2.413205361138126</v>
+        <v>2.413205361138125</v>
       </c>
       <c r="M2" t="n">
         <v>2.408326963266235</v>
@@ -7508,19 +7508,19 @@
         <v>2.436384056184433</v>
       </c>
       <c r="P2" t="n">
-        <v>2.406416872939385</v>
+        <v>2.406416872939387</v>
       </c>
       <c r="Q2" t="n">
         <v>2.400118557879228</v>
       </c>
       <c r="R2" t="n">
-        <v>2.414388996774198</v>
+        <v>2.414388996774199</v>
       </c>
       <c r="S2" t="n">
         <v>2.415341026968841</v>
       </c>
       <c r="T2" t="n">
-        <v>2.401423166786549</v>
+        <v>2.40142316678655</v>
       </c>
       <c r="U2" t="n">
         <v>2.440200961689088</v>
@@ -7535,7 +7535,7 @@
         <v>2.410478455489613</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.40351686644665</v>
+        <v>2.403516866446651</v>
       </c>
       <c r="Z2" t="n">
         <v>2.421261082482792</v>
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.403133100611286</v>
+        <v>2.403641181561286</v>
       </c>
       <c r="C3" t="n">
-        <v>2.736942741323777</v>
+        <v>2.749000894049046</v>
       </c>
       <c r="D3" t="n">
-        <v>2.615727900190767</v>
+        <v>2.62378135369059</v>
       </c>
       <c r="E3" t="n">
-        <v>2.692447624593673</v>
+        <v>2.703158999605757</v>
       </c>
       <c r="F3" t="n">
-        <v>2.758517266046126</v>
+        <v>2.771708591715876</v>
       </c>
       <c r="G3" t="n">
-        <v>2.425968966407595</v>
+        <v>2.427281768149556</v>
       </c>
       <c r="H3" t="n">
-        <v>2.448340890300947</v>
+        <v>2.450465971328277</v>
       </c>
       <c r="I3" t="n">
-        <v>2.553529367803363</v>
+        <v>2.559387281861029</v>
       </c>
       <c r="J3" t="n">
-        <v>2.461604671205945</v>
+        <v>2.464185507455869</v>
       </c>
       <c r="K3" t="n">
-        <v>2.488299708495691</v>
+        <v>2.491848309481259</v>
       </c>
       <c r="L3" t="n">
-        <v>2.496213100081024</v>
+        <v>2.500011440890704</v>
       </c>
       <c r="M3" t="n">
-        <v>2.462318875449238</v>
+        <v>2.464953552971442</v>
       </c>
       <c r="N3" t="n">
-        <v>2.405673862318016</v>
+        <v>2.406274769776958</v>
       </c>
       <c r="O3" t="n">
-        <v>2.48180298610749</v>
+        <v>2.483175435721201</v>
       </c>
       <c r="P3" t="n">
-        <v>2.447791633771558</v>
+        <v>2.449865343861731</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.403038296490298</v>
+        <v>2.403546809586619</v>
       </c>
       <c r="R3" t="n">
-        <v>2.505388593105514</v>
+        <v>2.509538089768835</v>
       </c>
       <c r="S3" t="n">
-        <v>2.510950293245214</v>
+        <v>2.515272352231321</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4124024835777</v>
+        <v>2.413243884823388</v>
       </c>
       <c r="U3" t="n">
-        <v>2.515562874540892</v>
+        <v>2.518198175248968</v>
       </c>
       <c r="V3" t="n">
-        <v>2.467292296303885</v>
+        <v>2.470065209314301</v>
       </c>
       <c r="W3" t="n">
-        <v>2.508491755935033</v>
+        <v>2.510632291837289</v>
       </c>
       <c r="X3" t="n">
-        <v>2.477132304249448</v>
+        <v>2.480269758506817</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.427273463681332</v>
+        <v>2.428638356295126</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.452447265800893</v>
+        <v>2.453618493797798</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.521371476142068</v>
+        <v>2.526060053725268</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.4418299174226</v>
+        <v>2.443715460772985</v>
       </c>
     </row>
     <row r="4">
@@ -7642,16 +7642,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.108608976631343</v>
+        <v>2.108608976631338</v>
       </c>
       <c r="C4" t="n">
-        <v>2.622684758614499</v>
+        <v>2.6226847586145</v>
       </c>
       <c r="D4" t="n">
         <v>2.443933279513649</v>
       </c>
       <c r="E4" t="n">
-        <v>2.56661283732689</v>
+        <v>2.566612837326889</v>
       </c>
       <c r="F4" t="n">
         <v>2.669624173238305</v>
@@ -7660,19 +7660,19 @@
         <v>2.144932719448536</v>
       </c>
       <c r="H4" t="n">
-        <v>2.179617771482894</v>
+        <v>2.179617771482893</v>
       </c>
       <c r="I4" t="n">
         <v>2.345791773481496</v>
       </c>
       <c r="J4" t="n">
-        <v>2.201279553030734</v>
+        <v>2.201279553030733</v>
       </c>
       <c r="K4" t="n">
         <v>2.243771742260328</v>
       </c>
       <c r="L4" t="n">
-        <v>2.256197156197378</v>
+        <v>2.256197156197367</v>
       </c>
       <c r="M4" t="n">
         <v>2.202468151893692</v>
@@ -7693,7 +7693,7 @@
         <v>2.269566865206103</v>
       </c>
       <c r="S4" t="n">
-        <v>2.280320484210123</v>
+        <v>2.280320484210122</v>
       </c>
       <c r="T4" t="n">
         <v>2.123111850919138</v>
@@ -7705,19 +7705,19 @@
         <v>2.210846023278775</v>
       </c>
       <c r="W4" t="n">
-        <v>2.181617776892622</v>
+        <v>2.181617776892621</v>
       </c>
       <c r="X4" t="n">
-        <v>2.225395502458848</v>
+        <v>2.225395502458844</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.147034300156727</v>
+        <v>2.147034300156726</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.138513054324449</v>
+        <v>2.138513054324448</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.295649256632633</v>
+        <v>2.295649256632632</v>
       </c>
       <c r="AB4" t="n">
         <v>2.169559693596572</v>
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.443853077843693</v>
+        <v>2.443853077843642</v>
       </c>
       <c r="C5" t="n">
-        <v>12.2755169757183</v>
+        <v>12.27551697571832</v>
       </c>
       <c r="D5" t="n">
-        <v>9.184417950449363</v>
+        <v>9.184417950449365</v>
       </c>
       <c r="E5" t="n">
-        <v>11.06161212271707</v>
+        <v>11.06161212271706</v>
       </c>
       <c r="F5" t="n">
-        <v>13.55537442035458</v>
+        <v>13.55537442035456</v>
       </c>
       <c r="G5" t="n">
-        <v>3.066515501084314</v>
+        <v>3.06651550108431</v>
       </c>
       <c r="H5" t="n">
-        <v>3.976016272862462</v>
+        <v>3.976016272862461</v>
       </c>
       <c r="I5" t="n">
-        <v>7.224375136646273</v>
+        <v>7.224375136646275</v>
       </c>
       <c r="J5" t="n">
-        <v>4.160338222041089</v>
+        <v>4.160338222041084</v>
       </c>
       <c r="K5" t="n">
-        <v>4.868164412185051</v>
+        <v>4.86816441218505</v>
       </c>
       <c r="L5" t="n">
-        <v>5.1377951783873</v>
+        <v>5.137795178387111</v>
       </c>
       <c r="M5" t="n">
-        <v>4.219896497758999</v>
+        <v>4.219896497758997</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55144311233155</v>
+        <v>2.551443112331549</v>
       </c>
       <c r="O5" t="n">
         <v>3.096190243072295</v>
       </c>
       <c r="P5" t="n">
-        <v>3.703700129759095</v>
+        <v>3.703700129759088</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.468693736476749</v>
+        <v>2.468693736476732</v>
       </c>
       <c r="R5" t="n">
-        <v>5.795370697208032</v>
+        <v>5.795370697208041</v>
       </c>
       <c r="S5" t="n">
-        <v>5.312970702041082</v>
+        <v>5.312970702041059</v>
       </c>
       <c r="T5" t="n">
-        <v>2.776871011903646</v>
+        <v>2.776871011903641</v>
       </c>
       <c r="U5" t="n">
-        <v>4.205592433763509</v>
+        <v>4.205592433763506</v>
       </c>
       <c r="V5" t="n">
-        <v>4.173453105306329</v>
+        <v>4.173453105306334</v>
       </c>
       <c r="W5" t="n">
-        <v>3.85488245419825</v>
+        <v>3.854882454198237</v>
       </c>
       <c r="X5" t="n">
-        <v>4.767442241474583</v>
+        <v>4.767442241474567</v>
       </c>
       <c r="Y5" t="n">
         <v>3.184065330137293</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.966903317707278</v>
+        <v>2.96690331770724</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.011955648608946</v>
+        <v>6.011955648608938</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.775689348747144</v>
+        <v>3.775689348747143</v>
       </c>
     </row>
     <row r="6">
@@ -7818,43 +7818,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.286356174077273</v>
+        <v>3.28635617407727</v>
       </c>
       <c r="C6" t="n">
-        <v>3.800431956060429</v>
+        <v>3.80043195606043</v>
       </c>
       <c r="D6" t="n">
-        <v>3.62168047695958</v>
+        <v>3.621680476959582</v>
       </c>
       <c r="E6" t="n">
-        <v>17.04167380859619</v>
+        <v>17.04167380859617</v>
       </c>
       <c r="F6" t="n">
-        <v>3.847371370684233</v>
+        <v>3.847371370684235</v>
       </c>
       <c r="G6" t="n">
-        <v>16.61999369071781</v>
+        <v>16.61999369071782</v>
       </c>
       <c r="H6" t="n">
-        <v>3.35736496892883</v>
+        <v>3.357364968928831</v>
       </c>
       <c r="I6" t="n">
         <v>3.523538970927423</v>
       </c>
       <c r="J6" t="n">
-        <v>3.379026750476662</v>
+        <v>3.379026750476663</v>
       </c>
       <c r="K6" t="n">
         <v>16.71883271352961</v>
       </c>
       <c r="L6" t="n">
-        <v>16.73125812746664</v>
+        <v>16.73125812746662</v>
       </c>
       <c r="M6" t="n">
-        <v>3.380215349339618</v>
+        <v>3.380215349339619</v>
       </c>
       <c r="N6" t="n">
-        <v>3.288128825213758</v>
+        <v>3.288128825213756</v>
       </c>
       <c r="O6" t="n">
         <v>16.62180330135958</v>
@@ -7863,37 +7863,37 @@
         <v>16.65360112487786</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.286122890607111</v>
+        <v>3.28612289060711</v>
       </c>
       <c r="R6" t="n">
         <v>16.74462783647538</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45806768165605</v>
+        <v>3.458067681656049</v>
       </c>
       <c r="T6" t="n">
-        <v>3.300859048365067</v>
+        <v>3.300859048365068</v>
       </c>
       <c r="U6" t="n">
-        <v>16.67916000661633</v>
+        <v>16.67916000661634</v>
       </c>
       <c r="V6" t="n">
-        <v>3.388593220724707</v>
+        <v>3.388593220724708</v>
       </c>
       <c r="W6" t="n">
         <v>3.360011832403319</v>
       </c>
       <c r="X6" t="n">
-        <v>16.70045647372812</v>
+        <v>16.7004564737281</v>
       </c>
       <c r="Y6" t="n">
         <v>3.342159577172019</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.61357402559373</v>
+        <v>16.61357402559372</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.77071022790192</v>
+        <v>16.77071022790191</v>
       </c>
       <c r="AB6" t="n">
         <v>3.3449777081442</v>
@@ -7906,16 +7906,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.175239516366381</v>
+        <v>2.175239516366377</v>
       </c>
       <c r="C7" t="n">
-        <v>2.689315298349538</v>
+        <v>2.689315298349539</v>
       </c>
       <c r="D7" t="n">
         <v>2.510563819248688</v>
       </c>
       <c r="E7" t="n">
-        <v>2.633243377061929</v>
+        <v>2.633243377061928</v>
       </c>
       <c r="F7" t="n">
         <v>2.736254712973344</v>
@@ -7936,10 +7936,10 @@
         <v>2.310402281995366</v>
       </c>
       <c r="L7" t="n">
-        <v>2.322827695932416</v>
+        <v>2.322827695932399</v>
       </c>
       <c r="M7" t="n">
-        <v>2.26909869162873</v>
+        <v>2.269098691628731</v>
       </c>
       <c r="N7" t="n">
         <v>2.179165741630503</v>
@@ -7951,7 +7951,7 @@
         <v>2.246143816604572</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.175006232896224</v>
+        <v>2.175006232896223</v>
       </c>
       <c r="R7" t="n">
         <v>2.336197404941139</v>
@@ -7972,13 +7972,13 @@
         <v>2.24824831662766</v>
       </c>
       <c r="X7" t="n">
-        <v>2.292026042193887</v>
+        <v>2.292026042193883</v>
       </c>
       <c r="Y7" t="n">
         <v>2.213391691464443</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.205143594059488</v>
+        <v>2.205143594059487</v>
       </c>
       <c r="AA7" t="n">
         <v>2.362279796367668</v>
@@ -7994,7 +7994,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.186226167885127</v>
+        <v>2.186226167885123</v>
       </c>
       <c r="C8" t="n">
         <v>2.755086590855391</v>
@@ -8003,7 +8003,7 @@
         <v>2.576335111754541</v>
       </c>
       <c r="E8" t="n">
-        <v>2.669843464289694</v>
+        <v>2.669843464289691</v>
       </c>
       <c r="F8" t="n">
         <v>2.7557761712755</v>
@@ -8015,16 +8015,16 @@
         <v>2.312019603723785</v>
       </c>
       <c r="I8" t="n">
-        <v>2.478193605722389</v>
+        <v>2.478193605722388</v>
       </c>
       <c r="J8" t="n">
-        <v>2.333681385271626</v>
+        <v>2.333681385271625</v>
       </c>
       <c r="K8" t="n">
-        <v>2.37617357450122</v>
+        <v>2.376173574501219</v>
       </c>
       <c r="L8" t="n">
-        <v>2.388598988438268</v>
+        <v>2.388598988438259</v>
       </c>
       <c r="M8" t="n">
         <v>2.334869984134567</v>
@@ -8042,16 +8042,16 @@
         <v>2.175226452064824</v>
       </c>
       <c r="R8" t="n">
-        <v>2.401968697446993</v>
+        <v>2.401968697446992</v>
       </c>
       <c r="S8" t="n">
         <v>2.412722316451014</v>
       </c>
       <c r="T8" t="n">
-        <v>2.25551368316003</v>
+        <v>2.255513683160029</v>
       </c>
       <c r="U8" t="n">
-        <v>2.30976435200253</v>
+        <v>2.309764352002529</v>
       </c>
       <c r="V8" t="n">
         <v>2.328277846529395</v>
@@ -8060,16 +8060,16 @@
         <v>2.314030375877789</v>
       </c>
       <c r="X8" t="n">
-        <v>2.297267382563084</v>
+        <v>2.297267382563081</v>
       </c>
       <c r="Y8" t="n">
         <v>2.333639471131224</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.215112592746222</v>
+        <v>2.21511259274622</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.428051088873524</v>
+        <v>2.428051088873523</v>
       </c>
       <c r="AB8" t="n">
         <v>2.359188664358439</v>
@@ -8082,19 +8082,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.617085579704216</v>
+        <v>2.617085579704209</v>
       </c>
       <c r="C9" t="n">
-        <v>3.274162926824509</v>
+        <v>3.274162926824507</v>
       </c>
       <c r="D9" t="n">
-        <v>3.095411447723652</v>
+        <v>3.095411447723653</v>
       </c>
       <c r="E9" t="n">
-        <v>3.185086829463117</v>
+        <v>3.185086829463116</v>
       </c>
       <c r="F9" t="n">
-        <v>2.991444701808744</v>
+        <v>2.991444701808745</v>
       </c>
       <c r="G9" t="n">
         <v>2.796410890085885</v>
@@ -8103,64 +8103,64 @@
         <v>2.831095939692903</v>
       </c>
       <c r="I9" t="n">
-        <v>2.997269941691502</v>
+        <v>2.997269941691501</v>
       </c>
       <c r="J9" t="n">
-        <v>2.85275772124074</v>
+        <v>2.852757721240739</v>
       </c>
       <c r="K9" t="n">
         <v>2.895249910470333</v>
       </c>
       <c r="L9" t="n">
-        <v>2.907675324407384</v>
+        <v>2.907675324407364</v>
       </c>
       <c r="M9" t="n">
-        <v>2.853946320103698</v>
+        <v>2.853946320103697</v>
       </c>
       <c r="N9" t="n">
         <v>2.76401337010547</v>
       </c>
       <c r="O9" t="n">
-        <v>2.84659110820097</v>
+        <v>2.846591108200968</v>
       </c>
       <c r="P9" t="n">
-        <v>2.888693389696294</v>
+        <v>2.888693389696293</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.759853863798538</v>
+        <v>2.759853863798537</v>
       </c>
       <c r="R9" t="n">
         <v>2.921045033416106</v>
       </c>
       <c r="S9" t="n">
-        <v>2.931798652420126</v>
+        <v>2.931798652420123</v>
       </c>
       <c r="T9" t="n">
-        <v>2.774590019129144</v>
+        <v>2.774590019129143</v>
       </c>
       <c r="U9" t="n">
         <v>2.855577203557066</v>
       </c>
       <c r="V9" t="n">
-        <v>3.027344843616931</v>
+        <v>3.02734484361693</v>
       </c>
       <c r="W9" t="n">
-        <v>2.833095945102627</v>
+        <v>2.833095945102626</v>
       </c>
       <c r="X9" t="n">
-        <v>2.876873670668854</v>
+        <v>2.876873670668849</v>
       </c>
       <c r="Y9" t="n">
         <v>2.798239319939409</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.703773995916004</v>
+        <v>2.703773995916002</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.947127424842638</v>
+        <v>2.947127424842637</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.821037861806576</v>
+        <v>2.821037861806575</v>
       </c>
     </row>
   </sheetData>
@@ -8326,73 +8326,73 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.395660550246153</v>
+        <v>2.395660550246154</v>
       </c>
       <c r="C2" t="n">
         <v>2.438852044624189</v>
       </c>
       <c r="D2" t="n">
-        <v>2.410118898304301</v>
+        <v>2.410118898304302</v>
       </c>
       <c r="E2" t="n">
-        <v>2.426841467204258</v>
+        <v>2.426841467204259</v>
       </c>
       <c r="F2" t="n">
-        <v>2.444013362847081</v>
+        <v>2.444013362847083</v>
       </c>
       <c r="G2" t="n">
-        <v>2.399183035731398</v>
+        <v>2.399183035731399</v>
       </c>
       <c r="H2" t="n">
-        <v>2.402287111571559</v>
+        <v>2.402287111571561</v>
       </c>
       <c r="I2" t="n">
-        <v>2.409270967942358</v>
+        <v>2.409270967942359</v>
       </c>
       <c r="J2" t="n">
-        <v>2.404797564377407</v>
+        <v>2.404797564377408</v>
       </c>
       <c r="K2" t="n">
         <v>2.406073454464221</v>
       </c>
       <c r="L2" t="n">
-        <v>2.407711807874861</v>
+        <v>2.407711807874862</v>
       </c>
       <c r="M2" t="n">
-        <v>2.414339700386105</v>
+        <v>2.414339700386106</v>
       </c>
       <c r="N2" t="n">
         <v>2.396915652287754</v>
       </c>
       <c r="O2" t="n">
-        <v>2.434330037122911</v>
+        <v>2.434330037122913</v>
       </c>
       <c r="P2" t="n">
-        <v>2.403497764377979</v>
+        <v>2.40349776437798</v>
       </c>
       <c r="Q2" t="n">
         <v>2.396432966958185</v>
       </c>
       <c r="R2" t="n">
-        <v>2.406877682859171</v>
+        <v>2.406877682859172</v>
       </c>
       <c r="S2" t="n">
-        <v>2.409085978819795</v>
+        <v>2.409085978819796</v>
       </c>
       <c r="T2" t="n">
-        <v>2.398356493337613</v>
+        <v>2.398356493337614</v>
       </c>
       <c r="U2" t="n">
-        <v>2.435277252673192</v>
+        <v>2.435277252673193</v>
       </c>
       <c r="V2" t="n">
-        <v>2.404035807843974</v>
+        <v>2.404035807843975</v>
       </c>
       <c r="W2" t="n">
-        <v>2.437013600742415</v>
+        <v>2.437013600742416</v>
       </c>
       <c r="X2" t="n">
-        <v>2.407612254657903</v>
+        <v>2.407612254657904</v>
       </c>
       <c r="Y2" t="n">
         <v>2.399312329961633</v>
@@ -8401,7 +8401,7 @@
         <v>2.415299866709014</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.407280692254555</v>
+        <v>2.407280692254558</v>
       </c>
       <c r="AB2" t="n">
         <v>2.402002976791292</v>
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.392680501811385</v>
+        <v>2.392903895111719</v>
       </c>
       <c r="C3" t="n">
-        <v>2.673256041899937</v>
+        <v>2.683187033930808</v>
       </c>
       <c r="D3" t="n">
-        <v>2.495993316583704</v>
+        <v>2.499890561066324</v>
       </c>
       <c r="E3" t="n">
-        <v>2.615141742057572</v>
+        <v>2.623209461750603</v>
       </c>
       <c r="F3" t="n">
-        <v>2.738146642941604</v>
+        <v>2.750711949120068</v>
       </c>
       <c r="G3" t="n">
-        <v>2.417657966211087</v>
+        <v>2.418762648075309</v>
       </c>
       <c r="H3" t="n">
-        <v>2.440271907585328</v>
+        <v>2.442192805992449</v>
       </c>
       <c r="I3" t="n">
-        <v>2.490148599648367</v>
+        <v>2.493837285978004</v>
       </c>
       <c r="J3" t="n">
-        <v>2.457742822731366</v>
+        <v>2.460278029065048</v>
       </c>
       <c r="K3" t="n">
-        <v>2.466682167537921</v>
+        <v>2.469548161078623</v>
       </c>
       <c r="L3" t="n">
-        <v>2.478252936546266</v>
+        <v>2.481509432844756</v>
       </c>
       <c r="M3" t="n">
-        <v>2.525527434229362</v>
+        <v>2.530507022845058</v>
       </c>
       <c r="N3" t="n">
-        <v>2.401662684066677</v>
+        <v>2.402205137851151</v>
       </c>
       <c r="O3" t="n">
-        <v>2.485014220743336</v>
+        <v>2.48654587127207</v>
       </c>
       <c r="P3" t="n">
-        <v>2.448355751358362</v>
+        <v>2.450534497852674</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.398192252287022</v>
+        <v>2.398613226106497</v>
       </c>
       <c r="R3" t="n">
-        <v>2.47309977923641</v>
+        <v>2.47618581746415</v>
       </c>
       <c r="S3" t="n">
-        <v>2.487872568506718</v>
+        <v>2.491463534966043</v>
       </c>
       <c r="T3" t="n">
-        <v>2.411986605673406</v>
+        <v>2.412897451898005</v>
       </c>
       <c r="U3" t="n">
-        <v>2.503329592689425</v>
+        <v>2.505639346374953</v>
       </c>
       <c r="V3" t="n">
-        <v>2.452085110336989</v>
+        <v>2.454406302371263</v>
       </c>
       <c r="W3" t="n">
-        <v>2.492948608972596</v>
+        <v>2.494642643011961</v>
       </c>
       <c r="X3" t="n">
-        <v>2.478004063665532</v>
+        <v>2.481261712434089</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.418748011640627</v>
+        <v>2.419894664848674</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.436367797261255</v>
+        <v>2.437109647071433</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.47564578839666</v>
+        <v>2.478801452671503</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.438709591339993</v>
+        <v>2.440568758796313</v>
       </c>
     </row>
     <row r="4">
@@ -8505,7 +8505,7 @@
         <v>2.09243504949362</v>
       </c>
       <c r="C4" t="n">
-        <v>2.524644669529281</v>
+        <v>2.524644669529282</v>
       </c>
       <c r="D4" t="n">
         <v>2.255748741979107</v>
@@ -8544,7 +8544,7 @@
         <v>2.151609806044521</v>
       </c>
       <c r="P4" t="n">
-        <v>2.180959988409215</v>
+        <v>2.180959988409216</v>
       </c>
       <c r="Q4" t="n">
         <v>2.101159851585256</v>
@@ -8556,7 +8556,7 @@
         <v>2.244081441235182</v>
       </c>
       <c r="T4" t="n">
-        <v>2.122886966906754</v>
+        <v>2.122886966906755</v>
       </c>
       <c r="U4" t="n">
         <v>2.186396307131262</v>
@@ -8568,7 +8568,7 @@
         <v>2.158293947527775</v>
       </c>
       <c r="X4" t="n">
-        <v>2.227435048879998</v>
+        <v>2.227435048879999</v>
       </c>
       <c r="Y4" t="n">
         <v>2.13392275027475</v>
@@ -8593,7 +8593,7 @@
         <v>2.207044082907968</v>
       </c>
       <c r="C5" t="n">
-        <v>9.655093690701239</v>
+        <v>9.655093690701236</v>
       </c>
       <c r="D5" t="n">
         <v>5.159187330708686</v>
@@ -8602,10 +8602,10 @@
         <v>8.39564156733751</v>
       </c>
       <c r="F5" t="n">
-        <v>12.05850470437159</v>
+        <v>12.05850470437158</v>
       </c>
       <c r="G5" t="n">
-        <v>2.826452149960718</v>
+        <v>2.826452149960715</v>
       </c>
       <c r="H5" t="n">
         <v>3.684962833104509</v>
@@ -8617,58 +8617,58 @@
         <v>3.955239722352926</v>
       </c>
       <c r="K5" t="n">
-        <v>4.123692260379839</v>
+        <v>4.123692260379837</v>
       </c>
       <c r="L5" t="n">
-        <v>4.387652338450336</v>
+        <v>4.387652338450339</v>
       </c>
       <c r="M5" t="n">
-        <v>5.791666377548317</v>
+        <v>5.791666377548321</v>
       </c>
       <c r="N5" t="n">
-        <v>2.470460842603512</v>
+        <v>2.470460842603511</v>
       </c>
       <c r="O5" t="n">
-        <v>3.129596989728045</v>
+        <v>3.129596989728046</v>
       </c>
       <c r="P5" t="n">
-        <v>3.638358140145077</v>
+        <v>3.638358140145076</v>
       </c>
       <c r="Q5" t="n">
         <v>2.360824852228133</v>
       </c>
       <c r="R5" t="n">
-        <v>4.635609428693595</v>
+        <v>4.635609428693597</v>
       </c>
       <c r="S5" t="n">
-        <v>4.564811021326125</v>
+        <v>4.564811021326127</v>
       </c>
       <c r="T5" t="n">
-        <v>2.779333336651753</v>
+        <v>2.779333336651757</v>
       </c>
       <c r="U5" t="n">
-        <v>3.726795484617806</v>
+        <v>3.72679548461781</v>
       </c>
       <c r="V5" t="n">
-        <v>3.688616464439599</v>
+        <v>3.688616464439598</v>
       </c>
       <c r="W5" t="n">
-        <v>3.381566654345418</v>
+        <v>3.381566654345416</v>
       </c>
       <c r="X5" t="n">
         <v>4.606998709237943</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.938963804035737</v>
+        <v>2.938963804035738</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.573385774127106</v>
+        <v>2.573385774127107</v>
       </c>
       <c r="AA5" t="n">
         <v>4.544958278951004</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.605821443678938</v>
+        <v>3.605821443678941</v>
       </c>
     </row>
     <row r="6">
@@ -8681,13 +8681,13 @@
         <v>15.57669822648971</v>
       </c>
       <c r="C6" t="n">
-        <v>16.00890784652535</v>
+        <v>16.00890784652536</v>
       </c>
       <c r="D6" t="n">
         <v>15.74001191897516</v>
       </c>
       <c r="E6" t="n">
-        <v>3.539401159802792</v>
+        <v>3.539401159802791</v>
       </c>
       <c r="F6" t="n">
         <v>3.73336562055075</v>
@@ -8699,7 +8699,7 @@
         <v>3.262048417369808</v>
       </c>
       <c r="I6" t="n">
-        <v>15.7304341554698</v>
+        <v>15.73043415546979</v>
       </c>
       <c r="J6" t="n">
         <v>15.67993624710073</v>
@@ -8708,13 +8708,13 @@
         <v>3.304816902146198</v>
       </c>
       <c r="L6" t="n">
-        <v>15.71282272525836</v>
+        <v>15.71282272525837</v>
       </c>
       <c r="M6" t="n">
-        <v>3.397828000308187</v>
+        <v>3.397828000308188</v>
       </c>
       <c r="N6" t="n">
-        <v>3.19989259713342</v>
+        <v>3.199892597133419</v>
       </c>
       <c r="O6" t="n">
         <v>15.6349519263031</v>
@@ -8726,7 +8726,7 @@
         <v>3.195923160922152</v>
       </c>
       <c r="R6" t="n">
-        <v>15.70340089948969</v>
+        <v>15.70340089948968</v>
       </c>
       <c r="S6" t="n">
         <v>3.338844750572085</v>
@@ -8735,13 +8735,13 @@
         <v>3.217650276243655</v>
       </c>
       <c r="U6" t="n">
-        <v>15.67042031513422</v>
+        <v>15.67042031513421</v>
       </c>
       <c r="V6" t="n">
-        <v>3.281928577591173</v>
+        <v>3.281928577591172</v>
       </c>
       <c r="W6" t="n">
-        <v>3.254088367472959</v>
+        <v>3.254088367472957</v>
       </c>
       <c r="X6" t="n">
         <v>15.71169822587606</v>
@@ -8802,7 +8802,7 @@
         <v>2.364600665392554</v>
       </c>
       <c r="N7" t="n">
-        <v>2.168147978850227</v>
+        <v>2.168147978850228</v>
       </c>
       <c r="O7" t="n">
         <v>2.213141340225525</v>
@@ -8811,13 +8811,13 @@
         <v>2.24249152259022</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.162695826006521</v>
+        <v>2.162695826006522</v>
       </c>
       <c r="R7" t="n">
         <v>2.28067369691487</v>
       </c>
       <c r="S7" t="n">
-        <v>2.305617415656447</v>
+        <v>2.305617415656448</v>
       </c>
       <c r="T7" t="n">
         <v>2.184422941328021</v>
@@ -8829,7 +8829,7 @@
         <v>2.248701242675536</v>
       </c>
       <c r="W7" t="n">
-        <v>2.21982992194904</v>
+        <v>2.219829921949041</v>
       </c>
       <c r="X7" t="n">
         <v>2.288971023301264</v>
@@ -8863,16 +8863,16 @@
         <v>2.377707215906796</v>
       </c>
       <c r="E8" t="n">
-        <v>2.539728682693057</v>
+        <v>2.539728682693058</v>
       </c>
       <c r="F8" t="n">
-        <v>2.717963163197226</v>
+        <v>2.717963163197225</v>
       </c>
       <c r="G8" t="n">
         <v>2.264644507858784</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2892435819606</v>
+        <v>2.289243581960599</v>
       </c>
       <c r="I8" t="n">
         <v>2.368129452401415</v>
@@ -8890,7 +8890,7 @@
         <v>2.425023164898977</v>
       </c>
       <c r="N8" t="n">
-        <v>2.189456730071121</v>
+        <v>2.189456730071122</v>
       </c>
       <c r="O8" t="n">
         <v>2.245203329330831</v>
@@ -8923,7 +8923,7 @@
         <v>2.293643441497719</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.305825508128033</v>
+        <v>2.305825508128034</v>
       </c>
       <c r="Z8" t="n">
         <v>2.186386703749386</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.50861825468246</v>
+        <v>2.508618254682461</v>
       </c>
       <c r="C9" t="n">
         <v>3.058114018740125</v>
@@ -8951,13 +8951,13 @@
         <v>2.789218091189948</v>
       </c>
       <c r="E9" t="n">
-        <v>2.951038010528004</v>
+        <v>2.951038010528005</v>
       </c>
       <c r="F9" t="n">
         <v>2.90169513131626</v>
       </c>
       <c r="G9" t="n">
-        <v>2.665692459519664</v>
+        <v>2.665692459519663</v>
       </c>
       <c r="H9" t="n">
         <v>2.700754457243753</v>
@@ -8969,28 +8969,28 @@
         <v>2.729142419315493</v>
       </c>
       <c r="K9" t="n">
-        <v>2.743522942020139</v>
+        <v>2.74352294202014</v>
       </c>
       <c r="L9" t="n">
-        <v>2.762028897473136</v>
+        <v>2.762028897473137</v>
       </c>
       <c r="M9" t="n">
-        <v>2.836534040182131</v>
+        <v>2.836534040182132</v>
       </c>
       <c r="N9" t="n">
-        <v>2.640081353639803</v>
+        <v>2.640081353639804</v>
       </c>
       <c r="O9" t="n">
-        <v>2.723947585656769</v>
+        <v>2.72394758565677</v>
       </c>
       <c r="P9" t="n">
-        <v>2.761750991976167</v>
+        <v>2.761750991976168</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.634629167632071</v>
+        <v>2.634629167632072</v>
       </c>
       <c r="R9" t="n">
-        <v>2.752607071704447</v>
+        <v>2.752607071704448</v>
       </c>
       <c r="S9" t="n">
         <v>2.777550790446023</v>
@@ -8999,10 +8999,10 @@
         <v>2.656356316117598</v>
       </c>
       <c r="U9" t="n">
-        <v>2.71962648734898</v>
+        <v>2.719626487348981</v>
       </c>
       <c r="V9" t="n">
-        <v>2.855980166249304</v>
+        <v>2.855980166249305</v>
       </c>
       <c r="W9" t="n">
         <v>2.691763296738619</v>
@@ -9020,7 +9020,7 @@
         <v>2.757159248218798</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.698544155643879</v>
+        <v>2.69854415564388</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia water use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia water use results.xlsx
@@ -598,7 +598,7 @@
         <v>2.43978725135039</v>
       </c>
       <c r="F2" t="n">
-        <v>2.440390868719063</v>
+        <v>2.440390868719064</v>
       </c>
       <c r="G2" t="n">
         <v>2.402607904871429</v>
@@ -616,13 +616,13 @@
         <v>2.407646893450393</v>
       </c>
       <c r="L2" t="n">
-        <v>2.407667404700605</v>
+        <v>2.407667404700604</v>
       </c>
       <c r="M2" t="n">
         <v>2.406967763912201</v>
       </c>
       <c r="N2" t="n">
-        <v>2.39970928814436</v>
+        <v>2.399709288144359</v>
       </c>
       <c r="O2" t="n">
         <v>2.432987340450447</v>
@@ -634,10 +634,10 @@
         <v>2.399435278854961</v>
       </c>
       <c r="R2" t="n">
-        <v>2.415999805420799</v>
+        <v>2.4159998054208</v>
       </c>
       <c r="S2" t="n">
-        <v>2.409517120984688</v>
+        <v>2.409517120984687</v>
       </c>
       <c r="T2" t="n">
         <v>2.40056788845723</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.469632691197682</v>
+        <v>2.420833545542262</v>
       </c>
       <c r="C3" t="n">
-        <v>3.465411558832883</v>
+        <v>2.771517905531131</v>
       </c>
       <c r="D3" t="n">
-        <v>3.492573392381563</v>
+        <v>2.77924025708314</v>
       </c>
       <c r="E3" t="n">
-        <v>3.382381292939867</v>
+        <v>2.735631221265011</v>
       </c>
       <c r="F3" t="n">
-        <v>3.409059988122061</v>
+        <v>2.751880465319183</v>
       </c>
       <c r="G3" t="n">
-        <v>2.521154967073683</v>
+        <v>2.438554335924814</v>
       </c>
       <c r="H3" t="n">
-        <v>2.528455884298827</v>
+        <v>2.442664230557488</v>
       </c>
       <c r="I3" t="n">
-        <v>2.890789067728372</v>
+        <v>2.569356266127389</v>
       </c>
       <c r="J3" t="n">
-        <v>2.61533638788054</v>
+        <v>2.471440101401938</v>
       </c>
       <c r="K3" t="n">
-        <v>2.64010606709585</v>
+        <v>2.481010767132668</v>
       </c>
       <c r="L3" t="n">
-        <v>2.638956222164459</v>
+        <v>2.479595093910546</v>
       </c>
       <c r="M3" t="n">
-        <v>2.628130447868437</v>
+        <v>2.477099794476872</v>
       </c>
       <c r="N3" t="n">
-        <v>2.454869937155588</v>
+        <v>2.416271357644566</v>
       </c>
       <c r="O3" t="n">
-        <v>2.53006575507341</v>
+        <v>2.461821098256054</v>
       </c>
       <c r="P3" t="n">
-        <v>2.578145635314997</v>
+        <v>2.457838156423606</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.448566354890674</v>
+        <v>2.414121889507337</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8369275608836</v>
+        <v>2.551002143325616</v>
       </c>
       <c r="S3" t="n">
-        <v>2.680933068001003</v>
+        <v>2.492967636805645</v>
       </c>
       <c r="T3" t="n">
-        <v>2.47516464239835</v>
+        <v>2.423542369659472</v>
       </c>
       <c r="U3" t="n">
-        <v>2.715552719706298</v>
+        <v>2.525931458858042</v>
       </c>
       <c r="V3" t="n">
-        <v>2.621504401236859</v>
+        <v>2.472279766644575</v>
       </c>
       <c r="W3" t="n">
-        <v>2.607073008477857</v>
+        <v>2.491885504665215</v>
       </c>
       <c r="X3" t="n">
-        <v>2.654263281200309</v>
+        <v>2.485760405131812</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.518547252651213</v>
+        <v>2.438164293567415</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.526057856679681</v>
+        <v>2.452487206171475</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.858776216629582</v>
+        <v>2.555961178042826</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.486596209498348</v>
+        <v>2.427931841145718</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.745041224125754</v>
+        <v>2.745041224125735</v>
       </c>
       <c r="C4" t="n">
-        <v>12.85462616761466</v>
+        <v>12.85462616761465</v>
       </c>
       <c r="D4" t="n">
-        <v>13.3474803911792</v>
+        <v>13.34748039117921</v>
       </c>
       <c r="E4" t="n">
-        <v>11.72082245389331</v>
+        <v>11.72082245389333</v>
       </c>
       <c r="F4" t="n">
-        <v>12.69519251411143</v>
+        <v>12.69519251411141</v>
       </c>
       <c r="G4" t="n">
-        <v>3.242913491519423</v>
+        <v>3.242913491519422</v>
       </c>
       <c r="H4" t="n">
-        <v>3.475752472588583</v>
+        <v>3.475752472588581</v>
       </c>
       <c r="I4" t="n">
-        <v>7.206377802718717</v>
+        <v>7.206377802718714</v>
       </c>
       <c r="J4" t="n">
-        <v>4.21143407804526</v>
+        <v>4.211434078045267</v>
       </c>
       <c r="K4" t="n">
-        <v>4.554877251115554</v>
+        <v>4.554877251115548</v>
       </c>
       <c r="L4" t="n">
-        <v>4.438978692482678</v>
+        <v>4.438978692482606</v>
       </c>
       <c r="M4" t="n">
-        <v>4.476448811975215</v>
+        <v>4.476448811975219</v>
       </c>
       <c r="N4" t="n">
         <v>2.651628247835907</v>
       </c>
       <c r="O4" t="n">
-        <v>2.995286672442964</v>
+        <v>2.995286672442965</v>
       </c>
       <c r="P4" t="n">
-        <v>3.762054141469439</v>
+        <v>3.76205414146944</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.592437096538006</v>
+        <v>2.592437096538001</v>
       </c>
       <c r="R4" t="n">
-        <v>6.700071034905101</v>
+        <v>6.700071034905104</v>
       </c>
       <c r="S4" t="n">
-        <v>4.750681566890083</v>
+        <v>4.750681566890093</v>
       </c>
       <c r="T4" t="n">
-        <v>2.87800444807127</v>
+        <v>2.878004448071263</v>
       </c>
       <c r="U4" t="n">
-        <v>4.83265981192804</v>
+        <v>4.832659811928037</v>
       </c>
       <c r="V4" t="n">
-        <v>4.151450374621871</v>
+        <v>4.151450374621869</v>
       </c>
       <c r="W4" t="n">
-        <v>3.793718024521736</v>
+        <v>3.793718024521735</v>
       </c>
       <c r="X4" t="n">
-        <v>4.685692459035248</v>
+        <v>4.685692459035221</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.271532993891257</v>
+        <v>3.271532993891258</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.113334554405597</v>
+        <v>3.113334554405595</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.651413257535827</v>
+        <v>6.65141325753582</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.03871431870486</v>
+        <v>3.038714318704859</v>
       </c>
     </row>
     <row r="5">
@@ -850,25 +850,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.204133878360786</v>
+        <v>2.204133878360783</v>
       </c>
       <c r="C5" t="n">
-        <v>2.740902741711363</v>
+        <v>2.740902741711362</v>
       </c>
       <c r="D5" t="n">
-        <v>2.756092839105368</v>
+        <v>2.756092839105367</v>
       </c>
       <c r="E5" t="n">
-        <v>2.676219875642809</v>
+        <v>2.676219875642808</v>
       </c>
       <c r="F5" t="n">
         <v>2.665101494703952</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29882915858975</v>
+        <v>2.298829158589749</v>
       </c>
       <c r="H5" t="n">
-        <v>2.289289205594355</v>
+        <v>2.289289205594354</v>
       </c>
       <c r="I5" t="n">
         <v>2.464564866631303</v>
@@ -886,19 +886,19 @@
         <v>2.337596300087632</v>
       </c>
       <c r="N5" t="n">
-        <v>2.651628247835907</v>
+        <v>2.209556904703816</v>
       </c>
       <c r="O5" t="n">
-        <v>2.243650935049182</v>
+        <v>2.243650935049181</v>
       </c>
       <c r="P5" t="n">
-        <v>2.279669807913123</v>
+        <v>2.279669807913121</v>
       </c>
       <c r="Q5" t="n">
         <v>2.182218494283374</v>
       </c>
       <c r="R5" t="n">
-        <v>2.438166254427457</v>
+        <v>2.438166254427456</v>
       </c>
       <c r="S5" t="n">
         <v>2.364941351539401</v>
@@ -907,28 +907,28 @@
         <v>2.263855653291412</v>
       </c>
       <c r="U5" t="n">
-        <v>2.338200679596126</v>
+        <v>2.338200679596125</v>
       </c>
       <c r="V5" t="n">
         <v>2.32035404105176</v>
       </c>
       <c r="W5" t="n">
-        <v>2.311150941741784</v>
+        <v>2.311150941741783</v>
       </c>
       <c r="X5" t="n">
-        <v>2.287071455519848</v>
+        <v>2.287071455519846</v>
       </c>
       <c r="Y5" t="n">
         <v>2.342370094015972</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.221544782200354</v>
+        <v>2.221544782200355</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.450769288803925</v>
+        <v>2.450769288803926</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.329556589132736</v>
+        <v>2.329556589132735</v>
       </c>
     </row>
     <row r="6">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.738061146542313</v>
+        <v>2.738061146542312</v>
       </c>
       <c r="C6" t="n">
         <v>3.389996726403786</v>
@@ -947,73 +947,73 @@
         <v>3.40518682379779</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3160911785792</v>
+        <v>3.316091178579199</v>
       </c>
       <c r="F6" t="n">
-        <v>2.964640308707353</v>
+        <v>2.964640308707352</v>
       </c>
       <c r="G6" t="n">
-        <v>2.935992571861912</v>
+        <v>2.935992571861911</v>
       </c>
       <c r="H6" t="n">
-        <v>2.938383190286774</v>
+        <v>2.938383190286773</v>
       </c>
       <c r="I6" t="n">
-        <v>3.113658851323727</v>
+        <v>3.113658851323728</v>
       </c>
       <c r="J6" t="n">
-        <v>2.981499626122935</v>
+        <v>2.981499626122933</v>
       </c>
       <c r="K6" t="n">
         <v>2.992910255884787</v>
       </c>
       <c r="L6" t="n">
-        <v>2.993141939891575</v>
+        <v>2.993141939891572</v>
       </c>
       <c r="M6" t="n">
         <v>2.986690284780061</v>
       </c>
       <c r="N6" t="n">
-        <v>2.651628247835907</v>
+        <v>2.903251352474305</v>
       </c>
       <c r="O6" t="n">
-        <v>2.982322442820504</v>
+        <v>2.982322442820503</v>
       </c>
       <c r="P6" t="n">
-        <v>3.033793038870423</v>
+        <v>3.033793038870421</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.900156301525829</v>
+        <v>2.900156301525826</v>
       </c>
       <c r="R6" t="n">
-        <v>3.087260239119878</v>
+        <v>3.087260239119876</v>
       </c>
       <c r="S6" t="n">
         <v>3.014035336231824</v>
       </c>
       <c r="T6" t="n">
-        <v>2.912949637983839</v>
+        <v>2.912949637983838</v>
       </c>
       <c r="U6" t="n">
-        <v>3.015382397681323</v>
+        <v>3.015382397681322</v>
       </c>
       <c r="V6" t="n">
-        <v>3.18447485001274</v>
+        <v>3.184474850012739</v>
       </c>
       <c r="W6" t="n">
         <v>2.960233618857482</v>
       </c>
       <c r="X6" t="n">
-        <v>2.999735912285565</v>
+        <v>2.999735912285564</v>
       </c>
       <c r="Y6" t="n">
         <v>2.93426517204616</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.825119385486681</v>
+        <v>2.825119385486679</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.099863273496345</v>
+        <v>3.099863273496344</v>
       </c>
       <c r="AB6" t="n">
         <v>2.918548821174753</v>
@@ -1197,7 +1197,7 @@
         <v>2.436523124788455</v>
       </c>
       <c r="G2" t="n">
-        <v>2.393861434136305</v>
+        <v>2.393861434136306</v>
       </c>
       <c r="H2" t="n">
         <v>2.397579734498809</v>
@@ -1206,7 +1206,7 @@
         <v>2.398825376240441</v>
       </c>
       <c r="J2" t="n">
-        <v>2.398963896327991</v>
+        <v>2.39896389632799</v>
       </c>
       <c r="K2" t="n">
         <v>2.400841895758791</v>
@@ -1224,7 +1224,7 @@
         <v>2.4289698906931</v>
       </c>
       <c r="P2" t="n">
-        <v>2.399479001531862</v>
+        <v>2.39947900153186</v>
       </c>
       <c r="Q2" t="n">
         <v>2.392033897098119</v>
@@ -1239,7 +1239,7 @@
         <v>2.395090493857476</v>
       </c>
       <c r="U2" t="n">
-        <v>2.429050294255112</v>
+        <v>2.42905029425511</v>
       </c>
       <c r="V2" t="n">
         <v>2.397879896977531</v>
@@ -1254,7 +1254,7 @@
         <v>2.393415436472297</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.410015106967889</v>
+        <v>2.410015106967888</v>
       </c>
       <c r="AA2" t="n">
         <v>2.397482113791852</v>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.406770653531707</v>
+        <v>2.396524357095111</v>
       </c>
       <c r="C3" t="n">
-        <v>3.269801717015369</v>
+        <v>2.693082965295958</v>
       </c>
       <c r="D3" t="n">
-        <v>2.59121335286148</v>
+        <v>2.459666791386558</v>
       </c>
       <c r="E3" t="n">
-        <v>3.016354451766623</v>
+        <v>2.599105920273773</v>
       </c>
       <c r="F3" t="n">
-        <v>3.458418365826254</v>
+        <v>2.758419879347945</v>
       </c>
       <c r="G3" t="n">
-        <v>2.458165421991657</v>
+        <v>2.413669340113317</v>
       </c>
       <c r="H3" t="n">
-        <v>2.546702350581572</v>
+        <v>2.445699202239623</v>
       </c>
       <c r="I3" t="n">
-        <v>2.575145400872332</v>
+        <v>2.454967431622262</v>
       </c>
       <c r="J3" t="n">
-        <v>2.577385324004251</v>
+        <v>2.454485439158006</v>
       </c>
       <c r="K3" t="n">
-        <v>2.621282463236027</v>
+        <v>2.468042136535358</v>
       </c>
       <c r="L3" t="n">
-        <v>2.711485875679661</v>
+        <v>2.498242418082589</v>
       </c>
       <c r="M3" t="n">
-        <v>2.669371380471766</v>
+        <v>2.486645338123839</v>
       </c>
       <c r="N3" t="n">
-        <v>2.436199987045619</v>
+        <v>2.406776126424452</v>
       </c>
       <c r="O3" t="n">
-        <v>2.551867202433457</v>
+        <v>2.466437032832322</v>
       </c>
       <c r="P3" t="n">
-        <v>2.587110769309638</v>
+        <v>2.45672435494112</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.416320976672044</v>
+        <v>2.399823838190875</v>
       </c>
       <c r="R3" t="n">
-        <v>2.600332743363212</v>
+        <v>2.464365347623414</v>
       </c>
       <c r="S3" t="n">
-        <v>2.689058416333255</v>
+        <v>2.490558826652765</v>
       </c>
       <c r="T3" t="n">
-        <v>2.487777004886995</v>
+        <v>2.424811313326933</v>
       </c>
       <c r="U3" t="n">
-        <v>2.589259676863698</v>
+        <v>2.477771859663441</v>
       </c>
       <c r="V3" t="n">
-        <v>2.550811984122521</v>
+        <v>2.444544356009613</v>
       </c>
       <c r="W3" t="n">
-        <v>2.537815144688638</v>
+        <v>2.464612104963013</v>
       </c>
       <c r="X3" t="n">
-        <v>2.676624901881659</v>
+        <v>2.488375092734702</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.448355745084098</v>
+        <v>2.410946116593448</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.451622162192781</v>
+        <v>2.422842754257007</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.542712010458808</v>
+        <v>2.443570500594926</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.495104263886295</v>
+        <v>2.427721982318883</v>
       </c>
     </row>
     <row r="4">
@@ -1358,28 +1358,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.192381894404154</v>
+        <v>2.192381894404153</v>
       </c>
       <c r="C4" t="n">
-        <v>9.346029782875133</v>
+        <v>9.34602978287514</v>
       </c>
       <c r="D4" t="n">
-        <v>3.767001739104789</v>
+        <v>3.767001739104791</v>
       </c>
       <c r="E4" t="n">
-        <v>7.055427225982798</v>
+        <v>7.055427225982794</v>
       </c>
       <c r="F4" t="n">
-        <v>11.34668998963253</v>
+        <v>11.34668998963254</v>
       </c>
       <c r="G4" t="n">
-        <v>2.591072638582551</v>
+        <v>2.59107263858255</v>
       </c>
       <c r="H4" t="n">
-        <v>3.487148920365579</v>
+        <v>3.487148920365581</v>
       </c>
       <c r="I4" t="n">
-        <v>3.68961250121</v>
+        <v>3.689612501209997</v>
       </c>
       <c r="J4" t="n">
         <v>3.61051915270409</v>
@@ -1388,10 +1388,10 @@
         <v>3.885794374412249</v>
       </c>
       <c r="L4" t="n">
-        <v>4.579813909963511</v>
+        <v>4.57981390996351</v>
       </c>
       <c r="M4" t="n">
-        <v>4.461237180095868</v>
+        <v>4.461237180095867</v>
       </c>
       <c r="N4" t="n">
         <v>2.455833555757121</v>
@@ -1400,28 +1400,28 @@
         <v>3.056438038466272</v>
       </c>
       <c r="P4" t="n">
-        <v>3.588765455416251</v>
+        <v>3.58876545541625</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.277332010408536</v>
+        <v>2.277332010408535</v>
       </c>
       <c r="R4" t="n">
-        <v>3.963566881571212</v>
+        <v>3.96356688157121</v>
       </c>
       <c r="S4" t="n">
-        <v>4.380372271055425</v>
+        <v>4.380372271055424</v>
       </c>
       <c r="T4" t="n">
-        <v>2.924524412588212</v>
+        <v>2.924524412588213</v>
       </c>
       <c r="U4" t="n">
-        <v>3.363068264434052</v>
+        <v>3.363068264434046</v>
       </c>
       <c r="V4" t="n">
         <v>3.309427374317957</v>
       </c>
       <c r="W4" t="n">
-        <v>3.020000554559961</v>
+        <v>3.020000554559962</v>
       </c>
       <c r="X4" t="n">
         <v>4.455202320790824</v>
@@ -1430,7 +1430,7 @@
         <v>2.558558566615913</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.400580144445537</v>
+        <v>2.400580144445538</v>
       </c>
       <c r="AA4" t="n">
         <v>3.378448324556245</v>
@@ -1461,7 +1461,7 @@
         <v>2.671938335806309</v>
       </c>
       <c r="G5" t="n">
-        <v>2.241275657958985</v>
+        <v>2.241275657958984</v>
       </c>
       <c r="H5" t="n">
         <v>2.273175460761565</v>
@@ -1473,7 +1473,7 @@
         <v>2.288838435435109</v>
       </c>
       <c r="K5" t="n">
-        <v>2.310023072861388</v>
+        <v>2.310023072861389</v>
       </c>
       <c r="L5" t="n">
         <v>2.354756573550275</v>
@@ -1482,7 +1482,7 @@
         <v>2.332655550625271</v>
       </c>
       <c r="N5" t="n">
-        <v>2.455833555757121</v>
+        <v>2.182438598247387</v>
       </c>
       <c r="O5" t="n">
         <v>2.233939021605889</v>
@@ -1518,13 +1518,13 @@
         <v>2.274579928396684</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.169917775308947</v>
+        <v>2.169917775308946</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.272072789968753</v>
+        <v>2.272072789968752</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.299517061685132</v>
+        <v>2.299517061685131</v>
       </c>
     </row>
     <row r="6">
@@ -1537,7 +1537,7 @@
         <v>2.458697854599865</v>
       </c>
       <c r="C6" t="n">
-        <v>2.979242327496935</v>
+        <v>2.979242327496936</v>
       </c>
       <c r="D6" t="n">
         <v>2.652513284225457</v>
@@ -1570,7 +1570,7 @@
         <v>2.68995875524488</v>
       </c>
       <c r="N6" t="n">
-        <v>2.455833555757121</v>
+        <v>2.577499358801855</v>
       </c>
       <c r="O6" t="n">
         <v>2.653276998893956</v>
@@ -1588,10 +1588,10 @@
         <v>2.701484500088024</v>
       </c>
       <c r="T6" t="n">
-        <v>2.60236154723005</v>
+        <v>2.602361547230049</v>
       </c>
       <c r="U6" t="n">
-        <v>2.637369871894117</v>
+        <v>2.637369871894116</v>
       </c>
       <c r="V6" t="n">
         <v>2.754643928962847</v>
@@ -1609,7 +1609,7 @@
         <v>2.513790110551994</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.629375994588365</v>
+        <v>2.629375994588364</v>
       </c>
       <c r="AB6" t="n">
         <v>2.605939734337047</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.399905025709628</v>
+        <v>2.399905025709627</v>
       </c>
       <c r="C2" t="n">
         <v>2.446788843352677</v>
@@ -1799,16 +1799,16 @@
         <v>2.404663374949535</v>
       </c>
       <c r="I2" t="n">
-        <v>2.421984341041819</v>
+        <v>2.42198434104182</v>
       </c>
       <c r="J2" t="n">
-        <v>2.406821317345763</v>
+        <v>2.406821317345762</v>
       </c>
       <c r="K2" t="n">
         <v>2.409461462067402</v>
       </c>
       <c r="L2" t="n">
-        <v>2.410181645404037</v>
+        <v>2.410181645404036</v>
       </c>
       <c r="M2" t="n">
         <v>2.407057931686444</v>
@@ -1817,7 +1817,7 @@
         <v>2.399691757147234</v>
       </c>
       <c r="O2" t="n">
-        <v>2.435373547595247</v>
+        <v>2.435373547595248</v>
       </c>
       <c r="P2" t="n">
         <v>2.405117262765831</v>
@@ -1829,19 +1829,19 @@
         <v>2.415299231874284</v>
       </c>
       <c r="S2" t="n">
-        <v>2.412439754889514</v>
+        <v>2.412439754889515</v>
       </c>
       <c r="T2" t="n">
         <v>2.400510686421862</v>
       </c>
       <c r="U2" t="n">
-        <v>2.440034161760514</v>
+        <v>2.440034161760512</v>
       </c>
       <c r="V2" t="n">
         <v>2.407805149847364</v>
       </c>
       <c r="W2" t="n">
-        <v>2.439234158094774</v>
+        <v>2.439234158094773</v>
       </c>
       <c r="X2" t="n">
         <v>2.408695359304019</v>
@@ -1850,10 +1850,10 @@
         <v>2.402454906782244</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.420565595965297</v>
+        <v>2.420565595965296</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.413572367190198</v>
+        <v>2.413572367190196</v>
       </c>
       <c r="AB2" t="n">
         <v>2.400857717531878</v>
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.457805817259851</v>
+        <v>2.417053125492189</v>
       </c>
       <c r="C3" t="n">
-        <v>3.433900964334673</v>
+        <v>2.75729173178782</v>
       </c>
       <c r="D3" t="n">
-        <v>3.083124662552831</v>
+        <v>2.636321077182247</v>
       </c>
       <c r="E3" t="n">
-        <v>3.344493850917455</v>
+        <v>2.722147367898691</v>
       </c>
       <c r="F3" t="n">
-        <v>3.488114944529662</v>
+        <v>2.7767653646721</v>
       </c>
       <c r="G3" t="n">
-        <v>2.515352271652847</v>
+        <v>2.436722769929158</v>
       </c>
       <c r="H3" t="n">
-        <v>2.57070503785797</v>
+        <v>2.457748585583795</v>
       </c>
       <c r="I3" t="n">
-        <v>2.975050835082453</v>
+        <v>2.59914664880765</v>
       </c>
       <c r="J3" t="n">
-        <v>2.618739609132149</v>
+        <v>2.472631624083977</v>
       </c>
       <c r="K3" t="n">
-        <v>2.681085092345392</v>
+        <v>2.493346056968293</v>
       </c>
       <c r="L3" t="n">
-        <v>2.696167452209754</v>
+        <v>2.499558129251012</v>
       </c>
       <c r="M3" t="n">
-        <v>2.628873462039613</v>
+        <v>2.477465206471424</v>
       </c>
       <c r="N3" t="n">
-        <v>2.453432945528374</v>
+        <v>2.416012094281263</v>
       </c>
       <c r="O3" t="n">
-        <v>2.554892118245458</v>
+        <v>2.471149843358712</v>
       </c>
       <c r="P3" t="n">
-        <v>2.577583569316789</v>
+        <v>2.457841650873151</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.449147365993823</v>
+        <v>2.41454175301767</v>
       </c>
       <c r="R3" t="n">
-        <v>2.819475397313554</v>
+        <v>2.545099619073348</v>
       </c>
       <c r="S3" t="n">
-        <v>2.747346060602953</v>
+        <v>2.515451280972767</v>
       </c>
       <c r="T3" t="n">
-        <v>2.472789075088861</v>
+        <v>2.422918903203981</v>
       </c>
       <c r="U3" t="n">
-        <v>2.69057140170673</v>
+        <v>2.517644675478156</v>
       </c>
       <c r="V3" t="n">
-        <v>2.639920485612755</v>
+        <v>2.47782571496625</v>
       </c>
       <c r="W3" t="n">
-        <v>2.582600252259739</v>
+        <v>2.483771305597245</v>
       </c>
       <c r="X3" t="n">
-        <v>2.66356936593971</v>
+        <v>2.489082813322992</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.517501999330741</v>
+        <v>2.437922178796267</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.522238127418857</v>
+        <v>2.451387790144784</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.775456164796568</v>
+        <v>2.527001564029673</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.484900778482065</v>
+        <v>2.427580744776947</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.598093633823607</v>
+        <v>2.598093633823587</v>
       </c>
       <c r="C4" t="n">
-        <v>11.64030007222657</v>
+        <v>11.64030007222658</v>
       </c>
       <c r="D4" t="n">
-        <v>8.698060748477644</v>
+        <v>8.698060748477632</v>
       </c>
       <c r="E4" t="n">
-        <v>10.75526746620947</v>
+        <v>10.7552674662095</v>
       </c>
       <c r="F4" t="n">
-        <v>12.5846883388721</v>
+        <v>12.58468833887212</v>
       </c>
       <c r="G4" t="n">
-        <v>3.110875793924021</v>
+        <v>3.110875793924011</v>
       </c>
       <c r="H4" t="n">
         <v>3.804008271465176</v>
       </c>
       <c r="I4" t="n">
-        <v>7.711932332913299</v>
+        <v>7.711932332913301</v>
       </c>
       <c r="J4" t="n">
-        <v>4.094940026115978</v>
+        <v>4.09494002611598</v>
       </c>
       <c r="K4" t="n">
-        <v>4.628117612056676</v>
+        <v>4.62811761205668</v>
       </c>
       <c r="L4" t="n">
-        <v>4.817798194477152</v>
+        <v>4.817798194477269</v>
       </c>
       <c r="M4" t="n">
-        <v>4.322921213304488</v>
+        <v>4.322921213304497</v>
       </c>
       <c r="N4" t="n">
-        <v>2.600155173142275</v>
+        <v>2.600155173142274</v>
       </c>
       <c r="O4" t="n">
-        <v>3.125706242224059</v>
+        <v>3.125706242224062</v>
       </c>
       <c r="P4" t="n">
-        <v>3.648438941639363</v>
+        <v>3.648438941639369</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.561990806803993</v>
+        <v>2.561990806803989</v>
       </c>
       <c r="R4" t="n">
-        <v>6.241327391114027</v>
+        <v>6.241327391114019</v>
       </c>
       <c r="S4" t="n">
-        <v>5.14403780306874</v>
+        <v>5.144037803068739</v>
       </c>
       <c r="T4" t="n">
-        <v>2.800725732797912</v>
+        <v>2.800725732797915</v>
       </c>
       <c r="U4" t="n">
-        <v>4.4305576650771</v>
+        <v>4.430557665077099</v>
       </c>
       <c r="V4" t="n">
-        <v>4.112500651115878</v>
+        <v>4.112500651115877</v>
       </c>
       <c r="W4" t="n">
-        <v>3.458500718529082</v>
+        <v>3.458500718529085</v>
       </c>
       <c r="X4" t="n">
-        <v>4.600217081060602</v>
+        <v>4.600217081060601</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.177011064843009</v>
+        <v>3.177011064843014</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.007820815267599</v>
+        <v>3.00782081526761</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.56530007663874</v>
+        <v>5.565300076638742</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.959868661974343</v>
+        <v>2.959868661974356</v>
       </c>
     </row>
     <row r="5">
@@ -2042,16 +2042,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.193648084736354</v>
+        <v>2.193648084736353</v>
       </c>
       <c r="C5" t="n">
-        <v>2.718043119677115</v>
+        <v>2.718043119677114</v>
       </c>
       <c r="D5" t="n">
-        <v>2.550090506972066</v>
+        <v>2.550090506972067</v>
       </c>
       <c r="E5" t="n">
-        <v>2.651779360441461</v>
+        <v>2.651779360441463</v>
       </c>
       <c r="F5" t="n">
         <v>2.698212096545177</v>
@@ -2060,10 +2060,10 @@
         <v>2.287406179119505</v>
       </c>
       <c r="H5" t="n">
-        <v>2.301702500713619</v>
+        <v>2.30170250071362</v>
       </c>
       <c r="I5" t="n">
-        <v>2.497350780764051</v>
+        <v>2.49735078076405</v>
       </c>
       <c r="J5" t="n">
         <v>2.326108303807048</v>
@@ -2072,19 +2072,19 @@
         <v>2.355899101939054</v>
       </c>
       <c r="L5" t="n">
-        <v>2.364033904027041</v>
+        <v>2.364033904027049</v>
       </c>
       <c r="M5" t="n">
         <v>2.330044787619686</v>
       </c>
       <c r="N5" t="n">
-        <v>2.600155173142275</v>
+        <v>2.203449034187501</v>
       </c>
       <c r="O5" t="n">
         <v>2.24910456403562</v>
       </c>
       <c r="P5" t="n">
-        <v>2.273465438015519</v>
+        <v>2.273465438015521</v>
       </c>
       <c r="Q5" t="n">
         <v>2.178452748699444</v>
@@ -2111,16 +2111,16 @@
         <v>2.287243760258353</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.330744287308032</v>
+        <v>2.330744287308033</v>
       </c>
       <c r="Z5" t="n">
         <v>2.215026961220941</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.402333666410808</v>
+        <v>2.402333666410809</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.317443465884764</v>
+        <v>2.317443465884765</v>
       </c>
     </row>
     <row r="6">
@@ -2133,19 +2133,19 @@
         <v>2.622795268792752</v>
       </c>
       <c r="C6" t="n">
-        <v>3.235203632827642</v>
+        <v>3.235203632827641</v>
       </c>
       <c r="D6" t="n">
-        <v>3.067251020122597</v>
+        <v>3.067251020122598</v>
       </c>
       <c r="E6" t="n">
         <v>3.165009701378811</v>
       </c>
       <c r="F6" t="n">
-        <v>2.933132486742304</v>
+        <v>2.933132486742303</v>
       </c>
       <c r="G6" t="n">
-        <v>2.793305853263676</v>
+        <v>2.793305853263675</v>
       </c>
       <c r="H6" t="n">
         <v>2.818863013864144</v>
@@ -2157,25 +2157,25 @@
         <v>2.843268816957574</v>
       </c>
       <c r="K6" t="n">
-        <v>2.873059615089578</v>
+        <v>2.873059615089579</v>
       </c>
       <c r="L6" t="n">
-        <v>2.881194417177566</v>
+        <v>2.881194417177563</v>
       </c>
       <c r="M6" t="n">
         <v>2.847205300770227</v>
       </c>
       <c r="N6" t="n">
-        <v>2.600155173142275</v>
+        <v>2.762706303729981</v>
       </c>
       <c r="O6" t="n">
-        <v>2.843957945907069</v>
+        <v>2.843957945907068</v>
       </c>
       <c r="P6" t="n">
-        <v>2.88141205709035</v>
+        <v>2.881412057090351</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.760592438103174</v>
+        <v>2.760592438103173</v>
       </c>
       <c r="R6" t="n">
         <v>2.938999910565105</v>
@@ -2196,19 +2196,19 @@
         <v>2.808397459911562</v>
       </c>
       <c r="X6" t="n">
-        <v>2.864406131952482</v>
+        <v>2.864406131952484</v>
       </c>
       <c r="Y6" t="n">
         <v>2.793917349969054</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.70169661706752</v>
+        <v>2.701696617067519</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.919494179561337</v>
+        <v>2.919494179561336</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.777876118708111</v>
+        <v>2.777876118708113</v>
       </c>
     </row>
   </sheetData>
@@ -2386,7 +2386,7 @@
         <v>2.424845519604842</v>
       </c>
       <c r="F2" t="n">
-        <v>2.438554804394502</v>
+        <v>2.438554804394503</v>
       </c>
       <c r="G2" t="n">
         <v>2.399733661320384</v>
@@ -2395,13 +2395,13 @@
         <v>2.401671162915953</v>
       </c>
       <c r="I2" t="n">
-        <v>2.407501194832627</v>
+        <v>2.407501194832628</v>
       </c>
       <c r="J2" t="n">
         <v>2.403310074476366</v>
       </c>
       <c r="K2" t="n">
-        <v>2.405062389380008</v>
+        <v>2.405062389380009</v>
       </c>
       <c r="L2" t="n">
         <v>2.407157619928723</v>
@@ -2410,16 +2410,16 @@
         <v>2.402585058641602</v>
       </c>
       <c r="N2" t="n">
-        <v>2.397064021629306</v>
+        <v>2.397064021629307</v>
       </c>
       <c r="O2" t="n">
         <v>2.434218953226643</v>
       </c>
       <c r="P2" t="n">
-        <v>2.402369192417578</v>
+        <v>2.402369192417579</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.397313029297482</v>
+        <v>2.397313029297483</v>
       </c>
       <c r="R2" t="n">
         <v>2.412555963486853</v>
@@ -2428,7 +2428,7 @@
         <v>2.406729142261838</v>
       </c>
       <c r="T2" t="n">
-        <v>2.399034084364677</v>
+        <v>2.399034084364678</v>
       </c>
       <c r="U2" t="n">
         <v>2.434138686278785</v>
@@ -2440,13 +2440,13 @@
         <v>2.436934061634882</v>
       </c>
       <c r="X2" t="n">
-        <v>2.406666905606225</v>
+        <v>2.406666905606226</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.39967322311466</v>
+        <v>2.399673223114661</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.417838277235574</v>
+        <v>2.417838277235575</v>
       </c>
       <c r="AA2" t="n">
         <v>2.406436376693291</v>
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.44840405879164</v>
+        <v>2.412780243233164</v>
       </c>
       <c r="C3" t="n">
-        <v>3.234156229085298</v>
+        <v>2.683779913693437</v>
       </c>
       <c r="D3" t="n">
-        <v>2.829310446094997</v>
+        <v>2.545934363694573</v>
       </c>
       <c r="E3" t="n">
-        <v>3.084893594197873</v>
+        <v>2.630561307981343</v>
       </c>
       <c r="F3" t="n">
-        <v>3.417072178169327</v>
+        <v>2.748939693610218</v>
       </c>
       <c r="G3" t="n">
-        <v>2.505706140316333</v>
+        <v>2.432144864486277</v>
       </c>
       <c r="H3" t="n">
-        <v>2.553311441274203</v>
+        <v>2.450607436007507</v>
       </c>
       <c r="I3" t="n">
-        <v>2.688961512192732</v>
+        <v>2.497543068642099</v>
       </c>
       <c r="J3" t="n">
-        <v>2.589539921795325</v>
+        <v>2.461277132348853</v>
       </c>
       <c r="K3" t="n">
-        <v>2.630875481259691</v>
+        <v>2.473951675852922</v>
       </c>
       <c r="L3" t="n">
-        <v>2.678212860407755</v>
+        <v>2.492072618617331</v>
       </c>
       <c r="M3" t="n">
-        <v>2.576678241285139</v>
+        <v>2.458128372820194</v>
       </c>
       <c r="N3" t="n">
-        <v>2.44465048908282</v>
+        <v>2.411841267324786</v>
       </c>
       <c r="O3" t="n">
-        <v>2.567970188638088</v>
+        <v>2.474584458221359</v>
       </c>
       <c r="P3" t="n">
-        <v>2.566083947880925</v>
+        <v>2.452579868501</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.450499655936504</v>
+        <v>2.413779806182365</v>
       </c>
       <c r="R3" t="n">
-        <v>2.807934948353364</v>
+        <v>2.539915911344435</v>
       </c>
       <c r="S3" t="n">
-        <v>2.667405738590282</v>
+        <v>2.486904325531417</v>
       </c>
       <c r="T3" t="n">
-        <v>2.490867279617071</v>
+        <v>2.428123838936383</v>
       </c>
       <c r="U3" t="n">
-        <v>2.60104211452043</v>
+        <v>2.485802270617608</v>
       </c>
       <c r="V3" t="n">
-        <v>2.62043289430885</v>
+        <v>2.469833687245938</v>
       </c>
       <c r="W3" t="n">
-        <v>2.572728983568373</v>
+        <v>2.479489788592571</v>
       </c>
       <c r="X3" t="n">
-        <v>2.668722417911564</v>
+        <v>2.489583837595127</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.505159661175384</v>
+        <v>2.432565081732301</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.508815351139638</v>
+        <v>2.445235009306406</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.662071888353096</v>
+        <v>2.486839043845102</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.498957694997705</v>
+        <v>2.431524757362883</v>
       </c>
     </row>
     <row r="4">
@@ -2550,40 +2550,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.505335975131908</v>
+        <v>2.505335975131925</v>
       </c>
       <c r="C4" t="n">
         <v>9.086053435871641</v>
       </c>
       <c r="D4" t="n">
-        <v>5.953971137896849</v>
+        <v>5.953971137896853</v>
       </c>
       <c r="E4" t="n">
-        <v>8.020839313891443</v>
+        <v>8.020839313891436</v>
       </c>
       <c r="F4" t="n">
-        <v>11.14294558890015</v>
+        <v>11.14294558890016</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96749202874196</v>
+        <v>2.967492028741962</v>
       </c>
       <c r="H4" t="n">
-        <v>3.552923487429545</v>
+        <v>3.552923487429547</v>
       </c>
       <c r="I4" t="n">
-        <v>4.738981395964891</v>
+        <v>4.738981395964896</v>
       </c>
       <c r="J4" t="n">
-        <v>3.717304260670476</v>
+        <v>3.717304260670477</v>
       </c>
       <c r="K4" t="n">
         <v>3.975283025667559</v>
       </c>
       <c r="L4" t="n">
-        <v>4.489068113363555</v>
+        <v>4.489068113363532</v>
       </c>
       <c r="M4" t="n">
-        <v>3.720659673942277</v>
+        <v>3.720659673942274</v>
       </c>
       <c r="N4" t="n">
         <v>2.503742816802816</v>
@@ -2595,40 +2595,40 @@
         <v>3.451784863892905</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.549809762519265</v>
+        <v>2.54980976251927</v>
       </c>
       <c r="R4" t="n">
-        <v>5.879587612177375</v>
+        <v>5.879587612177374</v>
       </c>
       <c r="S4" t="n">
-        <v>4.286089369371364</v>
+        <v>4.286089369371362</v>
       </c>
       <c r="T4" t="n">
         <v>2.932717279582493</v>
       </c>
       <c r="U4" t="n">
-        <v>3.522194173887786</v>
+        <v>3.522194173887785</v>
       </c>
       <c r="V4" t="n">
-        <v>3.819296876269214</v>
+        <v>3.819296876269213</v>
       </c>
       <c r="W4" t="n">
-        <v>3.29468530489031</v>
+        <v>3.294685304890311</v>
       </c>
       <c r="X4" t="n">
-        <v>4.48586580628398</v>
+        <v>4.485865806284001</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.015653254777984</v>
+        <v>3.015653254777989</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.81390756692079</v>
+        <v>2.813907566920796</v>
       </c>
       <c r="AA4" t="n">
         <v>4.380386209306151</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.052775460180265</v>
+        <v>3.052775460180267</v>
       </c>
     </row>
     <row r="5">
@@ -2641,16 +2641,16 @@
         <v>2.181492563281421</v>
       </c>
       <c r="C5" t="n">
-        <v>2.609691583868428</v>
+        <v>2.609691583868429</v>
       </c>
       <c r="D5" t="n">
-        <v>2.415290939093028</v>
+        <v>2.415290939093029</v>
       </c>
       <c r="E5" t="n">
         <v>2.516521627816436</v>
       </c>
       <c r="F5" t="n">
-        <v>2.655843759623816</v>
+        <v>2.655843759623818</v>
       </c>
       <c r="G5" t="n">
         <v>2.269728870591483</v>
@@ -2662,7 +2662,7 @@
         <v>2.347136498960757</v>
       </c>
       <c r="J5" t="n">
-        <v>2.299829494721404</v>
+        <v>2.299829494721405</v>
       </c>
       <c r="K5" t="n">
         <v>2.319589069467493</v>
@@ -2674,13 +2674,13 @@
         <v>2.292820822430263</v>
       </c>
       <c r="N5" t="n">
-        <v>2.503742816802816</v>
+        <v>2.190625984685393</v>
       </c>
       <c r="O5" t="n">
         <v>2.245765665024911</v>
       </c>
       <c r="P5" t="n">
-        <v>2.258561462780417</v>
+        <v>2.258561462780418</v>
       </c>
       <c r="Q5" t="n">
         <v>2.17244724828513</v>
@@ -2692,7 +2692,7 @@
         <v>2.338415810011961</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25149659116201</v>
+        <v>2.251496591162011</v>
       </c>
       <c r="U5" t="n">
         <v>2.265966122755481</v>
@@ -2704,19 +2704,19 @@
         <v>2.274213919138427</v>
       </c>
       <c r="X5" t="n">
-        <v>2.282669568758278</v>
+        <v>2.282669568758279</v>
       </c>
       <c r="Y5" t="n">
         <v>2.308269959648279</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.200975045590018</v>
+        <v>2.200975045590019</v>
       </c>
       <c r="AA5" t="n">
         <v>2.335108888236402</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.30748543455952</v>
+        <v>2.307485434559519</v>
       </c>
     </row>
     <row r="6">
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.528997510187521</v>
+        <v>2.528997510187523</v>
       </c>
       <c r="C6" t="n">
         <v>3.025165840970808</v>
@@ -2738,13 +2738,13 @@
         <v>2.93133788864489</v>
       </c>
       <c r="F6" t="n">
-        <v>2.841842003403122</v>
+        <v>2.841842003403121</v>
       </c>
       <c r="G6" t="n">
-        <v>2.674872894599602</v>
+        <v>2.674872894599603</v>
       </c>
       <c r="H6" t="n">
-        <v>2.696757863617113</v>
+        <v>2.696757863617112</v>
       </c>
       <c r="I6" t="n">
         <v>2.762610756063139</v>
@@ -2753,28 +2753,28 @@
         <v>2.715303751823786</v>
       </c>
       <c r="K6" t="n">
-        <v>2.735063326569876</v>
+        <v>2.735063326569875</v>
       </c>
       <c r="L6" t="n">
-        <v>2.758729919471279</v>
+        <v>2.758729919471277</v>
       </c>
       <c r="M6" t="n">
         <v>2.708295079532665</v>
       </c>
       <c r="N6" t="n">
-        <v>2.503742816802816</v>
+        <v>2.644718083394745</v>
       </c>
       <c r="O6" t="n">
         <v>2.728280047876684</v>
       </c>
       <c r="P6" t="n">
-        <v>2.752166629445152</v>
+        <v>2.752166629445153</v>
       </c>
       <c r="Q6" t="n">
         <v>2.647530742355189</v>
       </c>
       <c r="R6" t="n">
-        <v>2.819706693321083</v>
+        <v>2.819706693321084</v>
       </c>
       <c r="S6" t="n">
         <v>2.753890067114343</v>
@@ -2786,25 +2786,25 @@
         <v>2.705744316042514</v>
       </c>
       <c r="V6" t="n">
-        <v>2.867173763060099</v>
+        <v>2.8671737630601</v>
       </c>
       <c r="W6" t="n">
         <v>2.689678385442267</v>
       </c>
       <c r="X6" t="n">
-        <v>2.753187075458926</v>
+        <v>2.753187075458925</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.674190214463802</v>
+        <v>2.674190214463803</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.596177723541541</v>
+        <v>2.596177723541542</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.750583145338784</v>
+        <v>2.750583145338785</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.670919874047958</v>
+        <v>2.670919874047959</v>
       </c>
     </row>
   </sheetData>
@@ -2979,7 +2979,7 @@
         <v>2.407427896218864</v>
       </c>
       <c r="E2" t="n">
-        <v>2.419828259852878</v>
+        <v>2.419828259852877</v>
       </c>
       <c r="F2" t="n">
         <v>2.431153532610379</v>
@@ -3006,7 +3006,7 @@
         <v>2.4017989787279</v>
       </c>
       <c r="N2" t="n">
-        <v>2.394521995760764</v>
+        <v>2.394521995760763</v>
       </c>
       <c r="O2" t="n">
         <v>2.430540615560899</v>
@@ -3015,7 +3015,7 @@
         <v>2.398763709603613</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.395224891143827</v>
+        <v>2.395224891143826</v>
       </c>
       <c r="R2" t="n">
         <v>2.40641284431123</v>
@@ -3042,13 +3042,13 @@
         <v>2.396468891713773</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.414253027972946</v>
+        <v>2.414253027972945</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.401838472573483</v>
+        <v>2.401838472573482</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.396895376527622</v>
+        <v>2.396895376527621</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.44305397454715</v>
+        <v>2.409660533241613</v>
       </c>
       <c r="C3" t="n">
-        <v>3.254762018208486</v>
+        <v>2.68907041410962</v>
       </c>
       <c r="D3" t="n">
-        <v>2.738496921206513</v>
+        <v>2.511406341114246</v>
       </c>
       <c r="E3" t="n">
-        <v>3.019379956306095</v>
+        <v>2.602053602358178</v>
       </c>
       <c r="F3" t="n">
-        <v>3.295717680039115</v>
+        <v>2.704736622717597</v>
       </c>
       <c r="G3" t="n">
-        <v>2.493527522855588</v>
+        <v>2.426539935823812</v>
       </c>
       <c r="H3" t="n">
-        <v>2.527337869214932</v>
+        <v>2.440293298387847</v>
       </c>
       <c r="I3" t="n">
-        <v>2.590571886281654</v>
+        <v>2.461501927214632</v>
       </c>
       <c r="J3" t="n">
-        <v>2.577625514121114</v>
+        <v>2.455683411772949</v>
       </c>
       <c r="K3" t="n">
-        <v>2.585429511773951</v>
+        <v>2.457534894341598</v>
       </c>
       <c r="L3" t="n">
-        <v>2.673486230110942</v>
+        <v>2.488040422288871</v>
       </c>
       <c r="M3" t="n">
-        <v>2.609372366527266</v>
+        <v>2.467367143744248</v>
       </c>
       <c r="N3" t="n">
-        <v>2.437313341078348</v>
+        <v>2.408118047567134</v>
       </c>
       <c r="O3" t="n">
-        <v>2.547336127611866</v>
+        <v>2.466120353185972</v>
       </c>
       <c r="P3" t="n">
-        <v>2.53429561100769</v>
+        <v>2.440156525734406</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.453704716215476</v>
+        <v>2.413550825786589</v>
       </c>
       <c r="R3" t="n">
-        <v>2.716189986256074</v>
+        <v>2.506451436880911</v>
       </c>
       <c r="S3" t="n">
-        <v>2.636686183979688</v>
+        <v>2.47494460139278</v>
       </c>
       <c r="T3" t="n">
-        <v>2.497705794937954</v>
+        <v>2.429344293420639</v>
       </c>
       <c r="U3" t="n">
-        <v>2.547381550699742</v>
+        <v>2.465787560724034</v>
       </c>
       <c r="V3" t="n">
-        <v>2.587217177335669</v>
+        <v>2.457385988873233</v>
       </c>
       <c r="W3" t="n">
-        <v>2.548476319312868</v>
+        <v>2.469849973720202</v>
       </c>
       <c r="X3" t="n">
-        <v>2.673851936178985</v>
+        <v>2.489159841100661</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.482472730318777</v>
+        <v>2.423717825518324</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.48578953390443</v>
+        <v>2.435777610459349</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.607048748670281</v>
+        <v>2.466784822039403</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.495422349875019</v>
+        <v>2.428944871155492</v>
       </c>
     </row>
     <row r="4">
@@ -3146,49 +3146,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.467791740616282</v>
+        <v>2.467791740616283</v>
       </c>
       <c r="C4" t="n">
-        <v>9.215963638568809</v>
+        <v>9.21596363856882</v>
       </c>
       <c r="D4" t="n">
-        <v>5.03674415951214</v>
+        <v>5.03674415951215</v>
       </c>
       <c r="E4" t="n">
-        <v>7.153394981052307</v>
+        <v>7.153394981052305</v>
       </c>
       <c r="F4" t="n">
-        <v>10.01377583665909</v>
+        <v>10.0137758366591</v>
       </c>
       <c r="G4" t="n">
-        <v>2.862463138246381</v>
+        <v>2.862463138246374</v>
       </c>
       <c r="H4" t="n">
         <v>3.327879449136621</v>
       </c>
       <c r="I4" t="n">
-        <v>3.83083896717647</v>
+        <v>3.830838967176473</v>
       </c>
       <c r="J4" t="n">
         <v>3.610291150038878</v>
       </c>
       <c r="K4" t="n">
-        <v>3.625991569163495</v>
+        <v>3.625991569163496</v>
       </c>
       <c r="L4" t="n">
-        <v>4.377777825765714</v>
+        <v>4.377777825765713</v>
       </c>
       <c r="M4" t="n">
-        <v>3.959538999201418</v>
+        <v>3.959538999201417</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45430093408397</v>
+        <v>2.454300934083969</v>
       </c>
       <c r="O4" t="n">
         <v>3.016496690125777</v>
       </c>
       <c r="P4" t="n">
-        <v>3.176102385030362</v>
+        <v>3.176102385030363</v>
       </c>
       <c r="Q4" t="n">
         <v>2.581844201897619</v>
@@ -3197,34 +3197,34 @@
         <v>5.047393246961105</v>
       </c>
       <c r="S4" t="n">
-        <v>4.024611245333946</v>
+        <v>4.024611245333948</v>
       </c>
       <c r="T4" t="n">
         <v>3.010305252750704</v>
       </c>
       <c r="U4" t="n">
-        <v>3.062593914742756</v>
+        <v>3.062593914742752</v>
       </c>
       <c r="V4" t="n">
-        <v>3.562978651221025</v>
+        <v>3.562978651221029</v>
       </c>
       <c r="W4" t="n">
-        <v>3.101505273498697</v>
+        <v>3.101505273498695</v>
       </c>
       <c r="X4" t="n">
         <v>4.474649404358032</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.84554777148638</v>
+        <v>2.845547771486379</v>
       </c>
       <c r="Z4" t="n">
         <v>2.628818718623662</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.927469514500177</v>
+        <v>3.92746951450018</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.02313527050575</v>
+        <v>3.023135270505751</v>
       </c>
     </row>
     <row r="5">
@@ -3237,13 +3237,13 @@
         <v>2.177048021120553</v>
       </c>
       <c r="C5" t="n">
-        <v>2.61714712203408</v>
+        <v>2.617147122034081</v>
       </c>
       <c r="D5" t="n">
-        <v>2.369049628316409</v>
+        <v>2.36904962831641</v>
       </c>
       <c r="E5" t="n">
-        <v>2.48289510002387</v>
+        <v>2.482895100023871</v>
       </c>
       <c r="F5" t="n">
         <v>2.595467085018068</v>
@@ -3267,10 +3267,10 @@
         <v>2.338626881999735</v>
       </c>
       <c r="M5" t="n">
-        <v>2.306224587566509</v>
+        <v>2.30622458756651</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45430093408397</v>
+        <v>2.18509722363134</v>
       </c>
       <c r="O5" t="n">
         <v>2.233836042158078</v>
@@ -3279,13 +3279,13 @@
         <v>2.24092845975308</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.17228644048467</v>
+        <v>2.172286440484669</v>
       </c>
       <c r="R5" t="n">
         <v>2.357584150072733</v>
       </c>
       <c r="S5" t="n">
-        <v>2.321006095977351</v>
+        <v>2.32100609597735</v>
       </c>
       <c r="T5" t="n">
         <v>2.252389980850164</v>
@@ -3303,7 +3303,7 @@
         <v>2.283442666852268</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.294268877165525</v>
+        <v>2.294268877165526</v>
       </c>
       <c r="Z5" t="n">
         <v>2.188072024410404</v>
@@ -3312,7 +3312,7 @@
         <v>2.30591451697991</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.30276561639234</v>
+        <v>2.302765616392341</v>
       </c>
     </row>
     <row r="6">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.482306171885131</v>
+        <v>2.48230617188513</v>
       </c>
       <c r="C6" t="n">
         <v>2.979014152892809</v>
@@ -3337,7 +3337,7 @@
         <v>2.754882968917314</v>
       </c>
       <c r="G6" t="n">
-        <v>2.612913253150098</v>
+        <v>2.612913253150099</v>
       </c>
       <c r="H6" t="n">
         <v>2.628238390505524</v>
@@ -3349,16 +3349,16 @@
         <v>2.653428318831357</v>
       </c>
       <c r="K6" t="n">
-        <v>2.656990155306794</v>
+        <v>2.656990155306795</v>
       </c>
       <c r="L6" t="n">
-        <v>2.700493912858462</v>
+        <v>2.700493912858463</v>
       </c>
       <c r="M6" t="n">
         <v>2.668091618425247</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45430093408397</v>
+        <v>2.585138576493356</v>
       </c>
       <c r="O6" t="n">
         <v>2.65846710339384</v>
@@ -3370,13 +3370,13 @@
         <v>2.593078095385827</v>
       </c>
       <c r="R6" t="n">
-        <v>2.719451180931459</v>
+        <v>2.71945118093146</v>
       </c>
       <c r="S6" t="n">
         <v>2.682873126836077</v>
       </c>
       <c r="T6" t="n">
-        <v>2.614257011708893</v>
+        <v>2.614257011708894</v>
       </c>
       <c r="U6" t="n">
         <v>2.623644802008879</v>
@@ -3385,7 +3385,7 @@
         <v>2.781115008675865</v>
       </c>
       <c r="W6" t="n">
-        <v>2.621922217444168</v>
+        <v>2.621922217444169</v>
       </c>
       <c r="X6" t="n">
         <v>2.699720784577437</v>
@@ -3575,7 +3575,7 @@
         <v>2.415279491217256</v>
       </c>
       <c r="E2" t="n">
-        <v>2.442298675715667</v>
+        <v>2.442298675715666</v>
       </c>
       <c r="F2" t="n">
         <v>2.453460097201013</v>
@@ -3590,55 +3590,55 @@
         <v>2.424282948680796</v>
       </c>
       <c r="J2" t="n">
-        <v>2.408910760303995</v>
+        <v>2.408910760303996</v>
       </c>
       <c r="K2" t="n">
         <v>2.412901765464472</v>
       </c>
       <c r="L2" t="n">
-        <v>2.416071217499357</v>
+        <v>2.416071217499356</v>
       </c>
       <c r="M2" t="n">
         <v>2.41899263915991</v>
       </c>
       <c r="N2" t="n">
-        <v>2.400467615267979</v>
+        <v>2.400467615267978</v>
       </c>
       <c r="O2" t="n">
-        <v>2.438069652145244</v>
+        <v>2.438069652145243</v>
       </c>
       <c r="P2" t="n">
         <v>2.40880992637861</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.399712381358892</v>
+        <v>2.399712381358891</v>
       </c>
       <c r="R2" t="n">
         <v>2.41541678887265</v>
       </c>
       <c r="S2" t="n">
-        <v>2.421499096310512</v>
+        <v>2.421499096310511</v>
       </c>
       <c r="T2" t="n">
-        <v>2.402454361327777</v>
+        <v>2.402454361327776</v>
       </c>
       <c r="U2" t="n">
         <v>2.43856872030646</v>
       </c>
       <c r="V2" t="n">
-        <v>2.408725936381353</v>
+        <v>2.408725936381352</v>
       </c>
       <c r="W2" t="n">
         <v>2.442664757495297</v>
       </c>
       <c r="X2" t="n">
-        <v>2.410471442353678</v>
+        <v>2.410471442353677</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.403047752993954</v>
+        <v>2.403047752993953</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.420269260040118</v>
+        <v>2.420269260040117</v>
       </c>
       <c r="AA2" t="n">
         <v>2.416698207915214</v>
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.416954507595198</v>
+        <v>2.403957064104092</v>
       </c>
       <c r="C3" t="n">
-        <v>3.544973216886795</v>
+        <v>2.795622184211465</v>
       </c>
       <c r="D3" t="n">
-        <v>2.804735258194576</v>
+        <v>2.5388380675404</v>
       </c>
       <c r="E3" t="n">
-        <v>3.42696156659404</v>
+        <v>2.751480614245914</v>
       </c>
       <c r="F3" t="n">
-        <v>3.700624120989774</v>
+        <v>2.847862555343965</v>
       </c>
       <c r="G3" t="n">
-        <v>2.472805131682204</v>
+        <v>2.422490358319551</v>
       </c>
       <c r="H3" t="n">
-        <v>2.610895718860305</v>
+        <v>2.47246935362665</v>
       </c>
       <c r="I3" t="n">
-        <v>3.01592148172041</v>
+        <v>2.613132621369758</v>
       </c>
       <c r="J3" t="n">
-        <v>2.654740702182769</v>
+        <v>2.484615189253013</v>
       </c>
       <c r="K3" t="n">
-        <v>2.748342731574684</v>
+        <v>2.515578592378334</v>
       </c>
       <c r="L3" t="n">
-        <v>2.819184623555934</v>
+        <v>2.536937545567933</v>
       </c>
       <c r="M3" t="n">
-        <v>2.891875111583571</v>
+        <v>2.564148958741832</v>
       </c>
       <c r="N3" t="n">
-        <v>2.458782761427269</v>
+        <v>2.41835099096437</v>
       </c>
       <c r="O3" t="n">
-        <v>2.575088178097104</v>
+        <v>2.479221307795828</v>
       </c>
       <c r="P3" t="n">
-        <v>2.649940514111364</v>
+        <v>2.482809777972255</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.441275288763837</v>
+        <v>2.412323194225879</v>
       </c>
       <c r="R3" t="n">
-        <v>2.809456191348778</v>
+        <v>2.542212239405445</v>
       </c>
       <c r="S3" t="n">
-        <v>2.942830567006857</v>
+        <v>2.574510177662166</v>
       </c>
       <c r="T3" t="n">
-        <v>2.505386894006786</v>
+        <v>2.434431212119065</v>
       </c>
       <c r="U3" t="n">
-        <v>2.642175049671425</v>
+        <v>2.501180112866471</v>
       </c>
       <c r="V3" t="n">
-        <v>2.648573923626563</v>
+        <v>2.481244719744409</v>
       </c>
       <c r="W3" t="n">
-        <v>2.641107088325454</v>
+        <v>2.504858448335207</v>
       </c>
       <c r="X3" t="n">
-        <v>2.692230460273994</v>
+        <v>2.499315681331951</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.518612801652565</v>
+        <v>2.438923243667297</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.513591319035049</v>
+        <v>2.448245368110515</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.835347403084004</v>
+        <v>2.548238448346643</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.705526048189519</v>
+        <v>2.505162724426884</v>
       </c>
     </row>
     <row r="4">
@@ -3745,79 +3745,79 @@
         <v>2.243501948472979</v>
       </c>
       <c r="C4" t="n">
-        <v>12.59341393597399</v>
+        <v>12.59341393597401</v>
       </c>
       <c r="D4" t="n">
         <v>5.940654308856477</v>
       </c>
       <c r="E4" t="n">
-        <v>11.49371540191929</v>
+        <v>11.49371540191928</v>
       </c>
       <c r="F4" t="n">
         <v>14.35289220395059</v>
       </c>
       <c r="G4" t="n">
-        <v>2.699111292721895</v>
+        <v>2.699111292721893</v>
       </c>
       <c r="H4" t="n">
-        <v>4.189177571092252</v>
+        <v>4.189177571092248</v>
       </c>
       <c r="I4" t="n">
-        <v>8.028513220913748</v>
+        <v>8.028513220913755</v>
       </c>
       <c r="J4" t="n">
-        <v>4.342753501802331</v>
+        <v>4.34275350180233</v>
       </c>
       <c r="K4" t="n">
         <v>5.124229972851177</v>
       </c>
       <c r="L4" t="n">
-        <v>5.514424701331863</v>
+        <v>5.514424701331861</v>
       </c>
       <c r="M4" t="n">
         <v>6.415816423523884</v>
       </c>
       <c r="N4" t="n">
-        <v>2.630435288418835</v>
+        <v>2.630435288418834</v>
       </c>
       <c r="O4" t="n">
         <v>3.259148337815348</v>
       </c>
       <c r="P4" t="n">
-        <v>4.2521810594929</v>
+        <v>4.252181059492906</v>
       </c>
       <c r="Q4" t="n">
         <v>2.469890142292754</v>
       </c>
       <c r="R4" t="n">
-        <v>6.133884402964031</v>
+        <v>6.133884402964032</v>
       </c>
       <c r="S4" t="n">
-        <v>6.251508164987206</v>
+        <v>6.251508164987211</v>
       </c>
       <c r="T4" t="n">
         <v>3.068191839091423</v>
       </c>
       <c r="U4" t="n">
-        <v>3.941791346348982</v>
+        <v>3.941791346348985</v>
       </c>
       <c r="V4" t="n">
-        <v>4.168136066833824</v>
+        <v>4.168136066833811</v>
       </c>
       <c r="W4" t="n">
-        <v>3.987723987278667</v>
+        <v>3.987723987278669</v>
       </c>
       <c r="X4" t="n">
-        <v>4.836395422820264</v>
+        <v>4.836395422820268</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.177363692284665</v>
+        <v>3.177363692284663</v>
       </c>
       <c r="Z4" t="n">
         <v>2.889109258034908</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.10540067482567</v>
+        <v>6.105400674825666</v>
       </c>
       <c r="AB4" t="n">
         <v>5.061114344965588</v>
@@ -3836,13 +3836,13 @@
         <v>2.774164310351533</v>
       </c>
       <c r="D5" t="n">
-        <v>2.417904203334973</v>
+        <v>2.417904203334972</v>
       </c>
       <c r="E5" t="n">
         <v>2.693690520037886</v>
       </c>
       <c r="F5" t="n">
-        <v>2.802546763140626</v>
+        <v>2.802546763140627</v>
       </c>
       <c r="G5" t="n">
         <v>2.269206758147855</v>
@@ -3851,10 +3851,10 @@
         <v>2.323487601748214</v>
       </c>
       <c r="I5" t="n">
-        <v>2.519602397180713</v>
+        <v>2.519602397180712</v>
       </c>
       <c r="J5" t="n">
-        <v>2.346005386197082</v>
+        <v>2.346005386197081</v>
       </c>
       <c r="K5" t="n">
         <v>2.391046697149396</v>
@@ -3863,16 +3863,16 @@
         <v>2.426847115903383</v>
       </c>
       <c r="M5" t="n">
-        <v>2.459681031152896</v>
+        <v>2.459681031152895</v>
       </c>
       <c r="N5" t="n">
-        <v>2.630435288418835</v>
+        <v>2.207785553107362</v>
       </c>
       <c r="O5" t="n">
         <v>2.260306240436872</v>
       </c>
       <c r="P5" t="n">
-        <v>2.310896928764907</v>
+        <v>2.310896928764908</v>
       </c>
       <c r="Q5" t="n">
         <v>2.175983803511404</v>
@@ -3887,13 +3887,13 @@
         <v>2.273038461382069</v>
       </c>
       <c r="U5" t="n">
-        <v>2.297982733601046</v>
+        <v>2.297982733601045</v>
       </c>
       <c r="V5" t="n">
         <v>2.328981238539618</v>
       </c>
       <c r="W5" t="n">
-        <v>2.32199747088563</v>
+        <v>2.321997470885631</v>
       </c>
       <c r="X5" t="n">
         <v>2.302574192433255</v>
@@ -3905,7 +3905,7 @@
         <v>2.212565064093594</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.433929261080345</v>
+        <v>2.433929261080344</v>
       </c>
       <c r="AB5" t="n">
         <v>2.42752210396601</v>
@@ -3921,22 +3921,22 @@
         <v>2.599897920836225</v>
       </c>
       <c r="C6" t="n">
-        <v>3.285226708743662</v>
+        <v>3.285226708743663</v>
       </c>
       <c r="D6" t="n">
         <v>2.928966601727102</v>
       </c>
       <c r="E6" t="n">
-        <v>3.201500020732532</v>
+        <v>3.201500020732531</v>
       </c>
       <c r="F6" t="n">
         <v>3.034007596602643</v>
       </c>
       <c r="G6" t="n">
-        <v>2.768817030930526</v>
+        <v>2.768817030930527</v>
       </c>
       <c r="H6" t="n">
-        <v>2.834550000140341</v>
+        <v>2.834550000140342</v>
       </c>
       <c r="I6" t="n">
         <v>3.030664795572843</v>
@@ -3948,13 +3948,13 @@
         <v>2.902109095541527</v>
       </c>
       <c r="L6" t="n">
-        <v>2.93790951429551</v>
+        <v>2.937909514295511</v>
       </c>
       <c r="M6" t="n">
-        <v>2.970743429545042</v>
+        <v>2.970743429545041</v>
       </c>
       <c r="N6" t="n">
-        <v>2.630435288418835</v>
+        <v>2.761659649080436</v>
       </c>
       <c r="O6" t="n">
         <v>2.849312551764913</v>
@@ -3963,19 +3963,19 @@
         <v>2.912986485819984</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75312889742007</v>
+        <v>2.753128897420071</v>
       </c>
       <c r="R6" t="n">
-        <v>2.930517441904829</v>
+        <v>2.93051744190483</v>
       </c>
       <c r="S6" t="n">
-        <v>2.999219902415127</v>
+        <v>2.999219902415128</v>
       </c>
       <c r="T6" t="n">
         <v>2.7841008597742</v>
       </c>
       <c r="U6" t="n">
-        <v>2.835986839569335</v>
+        <v>2.835986839569334</v>
       </c>
       <c r="V6" t="n">
         <v>3.018425241085492</v>
@@ -3984,16 +3984,16 @@
         <v>2.833049015208893</v>
       </c>
       <c r="X6" t="n">
-        <v>2.874657478001233</v>
+        <v>2.874657478001234</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.790803491617325</v>
+        <v>2.790803491617326</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.694562453028161</v>
+        <v>2.694562453028162</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.944991659472471</v>
+        <v>2.944991659472472</v>
       </c>
       <c r="AB6" t="n">
         <v>2.880893216642638</v>
@@ -4168,7 +4168,7 @@
         <v>2.436133605672671</v>
       </c>
       <c r="D2" t="n">
-        <v>2.401887889804848</v>
+        <v>2.401887889804847</v>
       </c>
       <c r="E2" t="n">
         <v>2.419108345779788</v>
@@ -4177,7 +4177,7 @@
         <v>2.436212705762628</v>
       </c>
       <c r="G2" t="n">
-        <v>2.394692237645622</v>
+        <v>2.394692237645621</v>
       </c>
       <c r="H2" t="n">
         <v>2.399094524801901</v>
@@ -4192,7 +4192,7 @@
         <v>2.400537422184499</v>
       </c>
       <c r="L2" t="n">
-        <v>2.401748761633706</v>
+        <v>2.401748761633705</v>
       </c>
       <c r="M2" t="n">
         <v>2.405237546350028</v>
@@ -4201,13 +4201,13 @@
         <v>2.39468935802886</v>
       </c>
       <c r="O2" t="n">
-        <v>2.431562618381026</v>
+        <v>2.431562618381025</v>
       </c>
       <c r="P2" t="n">
         <v>2.402404051853819</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.393397311144202</v>
+        <v>2.393397311144201</v>
       </c>
       <c r="R2" t="n">
         <v>2.403397701374353</v>
@@ -4225,19 +4225,19 @@
         <v>2.401161660928754</v>
       </c>
       <c r="W2" t="n">
-        <v>2.433778612366674</v>
+        <v>2.433778612366673</v>
       </c>
       <c r="X2" t="n">
-        <v>2.403176446932317</v>
+        <v>2.403176446932316</v>
       </c>
       <c r="Y2" t="n">
         <v>2.396133052882919</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.412216495057383</v>
+        <v>2.412216495057382</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.400029953974842</v>
+        <v>2.400029953974841</v>
       </c>
       <c r="AB2" t="n">
         <v>2.401112489812887</v>
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.412601537488262</v>
+        <v>2.399361365866212</v>
       </c>
       <c r="C3" t="n">
-        <v>3.306229209660458</v>
+        <v>2.706419193523263</v>
       </c>
       <c r="D3" t="n">
-        <v>2.620184536424405</v>
+        <v>2.470048374584968</v>
       </c>
       <c r="E3" t="n">
-        <v>3.014150514201168</v>
+        <v>2.603999017964848</v>
       </c>
       <c r="F3" t="n">
-        <v>3.424849915538811</v>
+        <v>2.746078332677304</v>
       </c>
       <c r="G3" t="n">
-        <v>2.451670920522295</v>
+        <v>2.412257342832503</v>
       </c>
       <c r="H3" t="n">
-        <v>2.556131748492847</v>
+        <v>2.449888800569513</v>
       </c>
       <c r="I3" t="n">
-        <v>2.67039150371334</v>
+        <v>2.488523520587542</v>
       </c>
       <c r="J3" t="n">
-        <v>2.58809055701294</v>
+        <v>2.458311396662514</v>
       </c>
       <c r="K3" t="n">
-        <v>2.588329727164052</v>
+        <v>2.458126478771925</v>
       </c>
       <c r="L3" t="n">
-        <v>2.614782086093753</v>
+        <v>2.464222273381927</v>
       </c>
       <c r="M3" t="n">
-        <v>2.699116371521388</v>
+        <v>2.49387070536045</v>
       </c>
       <c r="N3" t="n">
-        <v>2.452146282099007</v>
+        <v>2.412892474158624</v>
       </c>
       <c r="O3" t="n">
-        <v>2.575044409962595</v>
+        <v>2.475286430309808</v>
       </c>
       <c r="P3" t="n">
-        <v>2.628851778663661</v>
+        <v>2.472156546446385</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.422143248656899</v>
+        <v>2.402603327664498</v>
       </c>
       <c r="R3" t="n">
-        <v>2.656471922848232</v>
+        <v>2.484346757794242</v>
       </c>
       <c r="S3" t="n">
-        <v>2.755207944109922</v>
+        <v>2.510917030229004</v>
       </c>
       <c r="T3" t="n">
-        <v>2.477510600674105</v>
+        <v>2.4216012977847</v>
       </c>
       <c r="U3" t="n">
-        <v>2.613485825566235</v>
+        <v>2.486021611355458</v>
       </c>
       <c r="V3" t="n">
-        <v>2.6007421826725</v>
+        <v>2.461634282256975</v>
       </c>
       <c r="W3" t="n">
-        <v>2.572510191872972</v>
+        <v>2.476953410635662</v>
       </c>
       <c r="X3" t="n">
-        <v>2.649999094505704</v>
+        <v>2.479919722734173</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.485620490328952</v>
+        <v>2.424615301513181</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.466729353355062</v>
+        <v>2.429102428567953</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.575997684877539</v>
+        <v>2.455750374409049</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.603040827281171</v>
+        <v>2.465173024948815</v>
       </c>
     </row>
     <row r="4">
@@ -4341,49 +4341,49 @@
         <v>2.229824065247112</v>
       </c>
       <c r="C4" t="n">
-        <v>9.647356187492949</v>
+        <v>9.647356187492944</v>
       </c>
       <c r="D4" t="n">
-        <v>3.976088629539056</v>
+        <v>3.976088629539054</v>
       </c>
       <c r="E4" t="n">
-        <v>7.379120555917687</v>
+        <v>7.379120555917691</v>
       </c>
       <c r="F4" t="n">
-        <v>10.92890763670037</v>
+        <v>10.92890763670036</v>
       </c>
       <c r="G4" t="n">
         <v>2.523336036685603</v>
       </c>
       <c r="H4" t="n">
-        <v>3.565023334441089</v>
+        <v>3.56502333444109</v>
       </c>
       <c r="I4" t="n">
-        <v>4.499611500187206</v>
+        <v>4.499611500187201</v>
       </c>
       <c r="J4" t="n">
-        <v>3.640921441453489</v>
+        <v>3.640921441453488</v>
       </c>
       <c r="K4" t="n">
-        <v>3.630498870734937</v>
+        <v>3.630498870734938</v>
       </c>
       <c r="L4" t="n">
-        <v>3.63049784867079</v>
+        <v>3.630497848670788</v>
       </c>
       <c r="M4" t="n">
         <v>4.43822850315297</v>
       </c>
       <c r="N4" t="n">
-        <v>2.566766782647717</v>
+        <v>2.566766782647716</v>
       </c>
       <c r="O4" t="n">
-        <v>3.217029977688018</v>
+        <v>3.217029977688017</v>
       </c>
       <c r="P4" t="n">
-        <v>3.946754977387688</v>
+        <v>3.946754977387689</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.311499358437498</v>
+        <v>2.311499358437499</v>
       </c>
       <c r="R4" t="n">
         <v>4.427490534013717</v>
@@ -4392,31 +4392,31 @@
         <v>4.705455841324375</v>
       </c>
       <c r="T4" t="n">
-        <v>2.787866070246442</v>
+        <v>2.787866070246443</v>
       </c>
       <c r="U4" t="n">
-        <v>3.471602584617553</v>
+        <v>3.471602584617552</v>
       </c>
       <c r="V4" t="n">
-        <v>3.657546830269039</v>
+        <v>3.657546830269038</v>
       </c>
       <c r="W4" t="n">
         <v>3.251763476359176</v>
       </c>
       <c r="X4" t="n">
-        <v>4.204261088801072</v>
+        <v>4.204261088801077</v>
       </c>
       <c r="Y4" t="n">
         <v>2.867472062316004</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.508388664414357</v>
+        <v>2.508388664414356</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.64452122549304</v>
+        <v>3.644521225493039</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.90178531949817</v>
+        <v>3.901785319498172</v>
       </c>
     </row>
     <row r="5">
@@ -4429,82 +4429,82 @@
         <v>2.161601070819474</v>
       </c>
       <c r="C5" t="n">
-        <v>2.641189974906063</v>
+        <v>2.641189974906062</v>
       </c>
       <c r="D5" t="n">
-        <v>2.310853059885969</v>
+        <v>2.310853059885968</v>
       </c>
       <c r="E5" t="n">
         <v>2.479382033881176</v>
       </c>
       <c r="F5" t="n">
-        <v>2.657371007722299</v>
+        <v>2.657371007722297</v>
       </c>
       <c r="G5" t="n">
-        <v>2.239693637456343</v>
+        <v>2.239693637456342</v>
       </c>
       <c r="H5" t="n">
-        <v>2.279300717166302</v>
+        <v>2.279300717166301</v>
       </c>
       <c r="I5" t="n">
-        <v>2.334884281023203</v>
+        <v>2.334884281023202</v>
       </c>
       <c r="J5" t="n">
         <v>2.295736370738323</v>
       </c>
       <c r="K5" t="n">
-        <v>2.295598906868334</v>
+        <v>2.295598906868333</v>
       </c>
       <c r="L5" t="n">
-        <v>2.309281543190798</v>
+        <v>2.309281543190797</v>
       </c>
       <c r="M5" t="n">
-        <v>2.348854017463542</v>
+        <v>2.348854017463541</v>
       </c>
       <c r="N5" t="n">
-        <v>2.566766782647717</v>
+        <v>2.191714986728974</v>
       </c>
       <c r="O5" t="n">
-        <v>2.246615178740712</v>
+        <v>2.246615178740711</v>
       </c>
       <c r="P5" t="n">
-        <v>2.286703150310053</v>
+        <v>2.286703150310052</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.156559018131585</v>
+        <v>2.156559018131584</v>
       </c>
       <c r="R5" t="n">
-        <v>2.327907076111173</v>
+        <v>2.327907076111172</v>
       </c>
       <c r="S5" t="n">
-        <v>2.378324584918017</v>
+        <v>2.378324584918016</v>
       </c>
       <c r="T5" t="n">
-        <v>2.241712737965313</v>
+        <v>2.241712737965312</v>
       </c>
       <c r="U5" t="n">
         <v>2.269554326243159</v>
       </c>
       <c r="V5" t="n">
-        <v>2.289538237551176</v>
+        <v>2.289538237551175</v>
       </c>
       <c r="W5" t="n">
-        <v>2.271039162423815</v>
+        <v>2.271039162423814</v>
       </c>
       <c r="X5" t="n">
         <v>2.271491375634358</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.294397996431255</v>
+        <v>2.294397996431254</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.178587947451283</v>
+        <v>2.178587947451282</v>
       </c>
       <c r="AA5" t="n">
         <v>2.289866819993343</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.353456239832206</v>
+        <v>2.353456239832205</v>
       </c>
     </row>
     <row r="6">
@@ -4517,19 +4517,19 @@
         <v>2.502000737482523</v>
       </c>
       <c r="C6" t="n">
-        <v>3.048169893158229</v>
+        <v>3.048169893158228</v>
       </c>
       <c r="D6" t="n">
-        <v>2.717832978138133</v>
+        <v>2.717832978138132</v>
       </c>
       <c r="E6" t="n">
         <v>2.885716882890219</v>
       </c>
       <c r="F6" t="n">
-        <v>2.839567062771328</v>
+        <v>2.839567062771329</v>
       </c>
       <c r="G6" t="n">
-        <v>2.636554751309594</v>
+        <v>2.636554751309593</v>
       </c>
       <c r="H6" t="n">
         <v>2.686280635418467</v>
@@ -4541,7 +4541,7 @@
         <v>2.702716288990489</v>
       </c>
       <c r="K6" t="n">
-        <v>2.702578825120499</v>
+        <v>2.702578825120498</v>
       </c>
       <c r="L6" t="n">
         <v>2.716261461442961</v>
@@ -4550,10 +4550,10 @@
         <v>2.755833935715708</v>
       </c>
       <c r="N6" t="n">
-        <v>2.566766782647717</v>
+        <v>2.636522250240126</v>
       </c>
       <c r="O6" t="n">
-        <v>2.719263639587593</v>
+        <v>2.719263639587592</v>
       </c>
       <c r="P6" t="n">
         <v>2.77021553016627</v>
@@ -4565,7 +4565,7 @@
         <v>2.734886994363336</v>
       </c>
       <c r="S6" t="n">
-        <v>2.785304503170184</v>
+        <v>2.785304503170183</v>
       </c>
       <c r="T6" t="n">
         <v>2.648692656217476</v>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.388592647785058</v>
+        <v>2.388592647785057</v>
       </c>
       <c r="C2" t="n">
         <v>2.427284894164104</v>
@@ -4776,7 +4776,7 @@
         <v>2.389232245394572</v>
       </c>
       <c r="H2" t="n">
-        <v>2.393157187218497</v>
+        <v>2.393157187218496</v>
       </c>
       <c r="I2" t="n">
         <v>2.393451902210811</v>
@@ -4788,16 +4788,16 @@
         <v>2.393073703991619</v>
       </c>
       <c r="L2" t="n">
-        <v>2.39622170256419</v>
+        <v>2.396221702564189</v>
       </c>
       <c r="M2" t="n">
-        <v>2.397133883004429</v>
+        <v>2.397133883004428</v>
       </c>
       <c r="N2" t="n">
         <v>2.389347891231623</v>
       </c>
       <c r="O2" t="n">
-        <v>2.424518273979581</v>
+        <v>2.42451827397958</v>
       </c>
       <c r="P2" t="n">
         <v>2.397017729203362</v>
@@ -4809,7 +4809,7 @@
         <v>2.395173716769923</v>
       </c>
       <c r="S2" t="n">
-        <v>2.399673722659566</v>
+        <v>2.399673722659565</v>
       </c>
       <c r="T2" t="n">
         <v>2.390718534059107</v>
@@ -4818,7 +4818,7 @@
         <v>2.424859841412913</v>
       </c>
       <c r="V2" t="n">
-        <v>2.394088226860249</v>
+        <v>2.39408822686025</v>
       </c>
       <c r="W2" t="n">
         <v>2.42582683615824</v>
@@ -4830,13 +4830,13 @@
         <v>2.390622317612847</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.406071023236946</v>
+        <v>2.406071023236945</v>
       </c>
       <c r="AA2" t="n">
         <v>2.391116461137397</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.392821552710731</v>
+        <v>2.39282155271073</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.411871938265233</v>
+        <v>2.396438479502596</v>
       </c>
       <c r="C3" t="n">
-        <v>3.204618292586026</v>
+        <v>2.67032896019623</v>
       </c>
       <c r="D3" t="n">
-        <v>2.575254126993579</v>
+        <v>2.452550819564667</v>
       </c>
       <c r="E3" t="n">
-        <v>2.661359566717026</v>
+        <v>2.476714991939989</v>
       </c>
       <c r="F3" t="n">
-        <v>3.264629783084966</v>
+        <v>2.691394444891007</v>
       </c>
       <c r="G3" t="n">
-        <v>2.426609641933409</v>
+        <v>2.401386315476926</v>
       </c>
       <c r="H3" t="n">
-        <v>2.519407753464491</v>
+        <v>2.434263489989134</v>
       </c>
       <c r="I3" t="n">
-        <v>2.525755951727607</v>
+        <v>2.436134980682406</v>
       </c>
       <c r="J3" t="n">
-        <v>2.538962437032128</v>
+        <v>2.439675484829571</v>
       </c>
       <c r="K3" t="n">
-        <v>2.516463111735424</v>
+        <v>2.431989197568817</v>
       </c>
       <c r="L3" t="n">
-        <v>2.588259397846314</v>
+        <v>2.454213284623822</v>
       </c>
       <c r="M3" t="n">
-        <v>2.612326432582378</v>
+        <v>2.464722699008089</v>
       </c>
       <c r="N3" t="n">
-        <v>2.429625370990034</v>
+        <v>2.402631140451645</v>
       </c>
       <c r="O3" t="n">
-        <v>2.548479993031534</v>
+        <v>2.462773499979434</v>
       </c>
       <c r="P3" t="n">
-        <v>2.605409762233136</v>
+        <v>2.460984980343075</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.410388013405742</v>
+        <v>2.396020583798454</v>
       </c>
       <c r="R3" t="n">
-        <v>2.566343990026141</v>
+        <v>2.450621641296488</v>
       </c>
       <c r="S3" t="n">
-        <v>2.667494946100367</v>
+        <v>2.481394667973639</v>
       </c>
       <c r="T3" t="n">
-        <v>2.461779610969645</v>
+        <v>2.413804371262822</v>
       </c>
       <c r="U3" t="n">
-        <v>2.572511370209095</v>
+        <v>2.470057279911611</v>
       </c>
       <c r="V3" t="n">
-        <v>2.538532215745976</v>
+        <v>2.438711547549036</v>
       </c>
       <c r="W3" t="n">
-        <v>2.506995034117885</v>
+        <v>2.45174886092641</v>
       </c>
       <c r="X3" t="n">
-        <v>2.596976799431994</v>
+        <v>2.458941902868788</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.459184380615894</v>
+        <v>2.412935130277504</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.436377861650883</v>
+        <v>2.415996194865814</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.470601137711536</v>
+        <v>2.416811342623415</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.511975608744487</v>
+        <v>2.431717793686352</v>
       </c>
     </row>
     <row r="4">
@@ -4937,55 +4937,55 @@
         <v>2.252083345558275</v>
       </c>
       <c r="C4" t="n">
-        <v>8.913066318287179</v>
+        <v>8.913066318287184</v>
       </c>
       <c r="D4" t="n">
-        <v>3.661007955325527</v>
+        <v>3.661007955325525</v>
       </c>
       <c r="E4" t="n">
-        <v>4.293749655869026</v>
+        <v>4.293749655869025</v>
       </c>
       <c r="F4" t="n">
-        <v>9.782424517134483</v>
+        <v>9.782424517134487</v>
       </c>
       <c r="G4" t="n">
-        <v>2.368706367266723</v>
+        <v>2.368706367266729</v>
       </c>
       <c r="H4" t="n">
-        <v>3.252049520798749</v>
+        <v>3.25204952079875</v>
       </c>
       <c r="I4" t="n">
-        <v>3.278645129730963</v>
+        <v>3.278645129730964</v>
       </c>
       <c r="J4" t="n">
-        <v>3.315029061804667</v>
+        <v>3.315029061804668</v>
       </c>
       <c r="K4" t="n">
-        <v>3.127450705082231</v>
+        <v>3.12745070508223</v>
       </c>
       <c r="L4" t="n">
-        <v>3.557585885872454</v>
+        <v>3.557585885872455</v>
       </c>
       <c r="M4" t="n">
         <v>3.950470286172636</v>
       </c>
       <c r="N4" t="n">
-        <v>2.413112687863385</v>
+        <v>2.413112687863386</v>
       </c>
       <c r="O4" t="n">
-        <v>3.057633672085278</v>
+        <v>3.057633672085279</v>
       </c>
       <c r="P4" t="n">
-        <v>3.74637692364191</v>
+        <v>3.746376923641908</v>
       </c>
       <c r="Q4" t="n">
         <v>2.248537380073234</v>
       </c>
       <c r="R4" t="n">
-        <v>3.670696055087464</v>
+        <v>3.670696055087462</v>
       </c>
       <c r="S4" t="n">
-        <v>4.219992596726854</v>
+        <v>4.219992596726858</v>
       </c>
       <c r="T4" t="n">
         <v>2.700997115589992</v>
@@ -4997,19 +4997,19 @@
         <v>3.237912037102857</v>
       </c>
       <c r="W4" t="n">
-        <v>2.762698687525913</v>
+        <v>2.762698687525914</v>
       </c>
       <c r="X4" t="n">
-        <v>3.771012785701201</v>
+        <v>3.771012785701198</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.675523432865749</v>
+        <v>2.67552343286575</v>
       </c>
       <c r="Z4" t="n">
         <v>2.30564855112497</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.7692285401551</v>
+        <v>2.769228540155101</v>
       </c>
       <c r="AB4" t="n">
         <v>3.182383904438641</v>
@@ -5058,7 +5058,7 @@
         <v>2.299997367109652</v>
       </c>
       <c r="N5" t="n">
-        <v>2.413112687863386</v>
+        <v>2.175584961792073</v>
       </c>
       <c r="O5" t="n">
         <v>2.228754679215432</v>
@@ -5082,10 +5082,10 @@
         <v>2.244028459935142</v>
       </c>
       <c r="V5" t="n">
-        <v>2.252795830061059</v>
+        <v>2.25279583006106</v>
       </c>
       <c r="W5" t="n">
-        <v>2.232754687547241</v>
+        <v>2.23275468754724</v>
       </c>
       <c r="X5" t="n">
         <v>2.241278367959924</v>
@@ -5097,7 +5097,7 @@
         <v>2.159259568127159</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.231841746436995</v>
+        <v>2.231841746436994</v>
       </c>
       <c r="AB5" t="n">
         <v>2.300524252695901</v>
@@ -5113,13 +5113,13 @@
         <v>2.45436900089019</v>
       </c>
       <c r="C6" t="n">
-        <v>2.938938380463758</v>
+        <v>2.938938380463757</v>
       </c>
       <c r="D6" t="n">
-        <v>2.636098633772207</v>
+        <v>2.636098633772206</v>
       </c>
       <c r="E6" t="n">
-        <v>2.657932574716752</v>
+        <v>2.657932574716751</v>
       </c>
       <c r="F6" t="n">
         <v>2.731279956932775</v>
@@ -5140,13 +5140,13 @@
         <v>2.607724201064582</v>
       </c>
       <c r="L6" t="n">
-        <v>2.643282293092656</v>
+        <v>2.643282293092655</v>
       </c>
       <c r="M6" t="n">
         <v>2.653771863322588</v>
       </c>
       <c r="N6" t="n">
-        <v>2.413112687863385</v>
+        <v>2.565639431981882</v>
       </c>
       <c r="O6" t="n">
         <v>2.642886838627526</v>
@@ -5158,10 +5158,10 @@
         <v>2.556281590247178</v>
       </c>
       <c r="R6" t="n">
-        <v>2.631444811449137</v>
+        <v>2.631444811449136</v>
       </c>
       <c r="S6" t="n">
-        <v>2.682274448077633</v>
+        <v>2.682274448077632</v>
       </c>
       <c r="T6" t="n">
         <v>2.581121473245163</v>
@@ -5188,7 +5188,7 @@
         <v>2.58561624264994</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.605409345714414</v>
+        <v>2.605409345714413</v>
       </c>
     </row>
   </sheetData>
@@ -5354,76 +5354,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.400139210731763</v>
+        <v>2.400139210731762</v>
       </c>
       <c r="C2" t="n">
-        <v>2.451155470962895</v>
+        <v>2.451155470962897</v>
       </c>
       <c r="D2" t="n">
         <v>2.429825854941701</v>
       </c>
       <c r="E2" t="n">
-        <v>2.440686816564018</v>
+        <v>2.440686816564016</v>
       </c>
       <c r="F2" t="n">
         <v>2.449806527997119</v>
       </c>
       <c r="G2" t="n">
-        <v>2.403354993244745</v>
+        <v>2.403354993244746</v>
       </c>
       <c r="H2" t="n">
-        <v>2.406425700587746</v>
+        <v>2.406425700587748</v>
       </c>
       <c r="I2" t="n">
-        <v>2.421137275119837</v>
+        <v>2.421137275119838</v>
       </c>
       <c r="J2" t="n">
-        <v>2.40834075381407</v>
+        <v>2.408340753814069</v>
       </c>
       <c r="K2" t="n">
         <v>2.412105325025208</v>
       </c>
       <c r="L2" t="n">
-        <v>2.413205361138127</v>
+        <v>2.413205361138129</v>
       </c>
       <c r="M2" t="n">
-        <v>2.408326963266236</v>
+        <v>2.408326963266235</v>
       </c>
       <c r="N2" t="n">
-        <v>2.400486803946754</v>
+        <v>2.400486803946756</v>
       </c>
       <c r="O2" t="n">
-        <v>2.436384056184434</v>
+        <v>2.436384056184435</v>
       </c>
       <c r="P2" t="n">
-        <v>2.406416872939387</v>
+        <v>2.406416872939386</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.400118557879227</v>
+        <v>2.400118557879229</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4143889967742</v>
+        <v>2.414388996774201</v>
       </c>
       <c r="S2" t="n">
-        <v>2.415341026968843</v>
+        <v>2.415341026968842</v>
       </c>
       <c r="T2" t="n">
-        <v>2.40142316678655</v>
+        <v>2.401423166786552</v>
       </c>
       <c r="U2" t="n">
-        <v>2.440200961689088</v>
+        <v>2.440200961689091</v>
       </c>
       <c r="V2" t="n">
         <v>2.409179519438776</v>
       </c>
       <c r="W2" t="n">
-        <v>2.442450324560926</v>
+        <v>2.442450324560927</v>
       </c>
       <c r="X2" t="n">
-        <v>2.410478455489613</v>
+        <v>2.410478455489615</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.403516866446652</v>
+        <v>2.40351686644665</v>
       </c>
       <c r="Z2" t="n">
         <v>2.421261082482792</v>
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.44065305117052</v>
+        <v>2.411881332057094</v>
       </c>
       <c r="C3" t="n">
-        <v>3.507469294620095</v>
+        <v>2.782919492216183</v>
       </c>
       <c r="D3" t="n">
-        <v>3.13431757185119</v>
+        <v>2.654824393747123</v>
       </c>
       <c r="E3" t="n">
-        <v>3.379177914195156</v>
+        <v>2.734767526546186</v>
       </c>
       <c r="F3" t="n">
-        <v>3.605041836769897</v>
+        <v>2.816157071514728</v>
       </c>
       <c r="G3" t="n">
-        <v>2.514718899910516</v>
+        <v>2.436703357251612</v>
       </c>
       <c r="H3" t="n">
-        <v>2.589071950226085</v>
+        <v>2.464794750241478</v>
       </c>
       <c r="I3" t="n">
-        <v>2.932215805081052</v>
+        <v>2.583915928369847</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6312056018162</v>
+        <v>2.476981176781356</v>
       </c>
       <c r="K3" t="n">
-        <v>2.719668559716122</v>
+        <v>2.505790709722187</v>
       </c>
       <c r="L3" t="n">
-        <v>2.743323790065973</v>
+        <v>2.515018366986647</v>
       </c>
       <c r="M3" t="n">
-        <v>2.63551223559282</v>
+        <v>2.478265497531912</v>
       </c>
       <c r="N3" t="n">
-        <v>2.449139276088276</v>
+        <v>2.415126182684886</v>
       </c>
       <c r="O3" t="n">
-        <v>2.553006278950141</v>
+        <v>2.471139475788128</v>
       </c>
       <c r="P3" t="n">
-        <v>2.584949907059425</v>
+        <v>2.460937087109729</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.440620208310187</v>
+        <v>2.412126349007969</v>
       </c>
       <c r="R3" t="n">
-        <v>2.775192623142335</v>
+        <v>2.530117735854358</v>
       </c>
       <c r="S3" t="n">
-        <v>2.791335975863664</v>
+        <v>2.528216721876269</v>
       </c>
       <c r="T3" t="n">
-        <v>2.471216187880526</v>
+        <v>2.422968783742395</v>
       </c>
       <c r="U3" t="n">
-        <v>2.668012698163245</v>
+        <v>2.510473952936253</v>
       </c>
       <c r="V3" t="n">
-        <v>2.649011869420672</v>
+        <v>2.481378173244551</v>
       </c>
       <c r="W3" t="n">
-        <v>2.626703811499606</v>
+        <v>2.499831610559635</v>
       </c>
       <c r="X3" t="n">
-        <v>2.682301939872951</v>
+        <v>2.496166337645644</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.519410926444412</v>
+        <v>2.439153627890113</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.520167382806838</v>
+        <v>2.450935023870964</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.825256043170682</v>
+        <v>2.544718047508422</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.567208686061145</v>
+        <v>2.457374805269649</v>
       </c>
     </row>
     <row r="4">
@@ -5530,85 +5530,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.44385307784368</v>
+        <v>2.443853077843693</v>
       </c>
       <c r="C4" t="n">
-        <v>12.27551697571832</v>
+        <v>12.27551697571833</v>
       </c>
       <c r="D4" t="n">
         <v>9.184417950449367</v>
       </c>
       <c r="E4" t="n">
-        <v>11.06161212271706</v>
+        <v>11.06161212271707</v>
       </c>
       <c r="F4" t="n">
         <v>13.55537442035458</v>
       </c>
       <c r="G4" t="n">
-        <v>3.066515501084315</v>
+        <v>3.066515501084321</v>
       </c>
       <c r="H4" t="n">
-        <v>3.976016272862463</v>
+        <v>3.976016272862462</v>
       </c>
       <c r="I4" t="n">
-        <v>7.224375136646269</v>
+        <v>7.224375136646273</v>
       </c>
       <c r="J4" t="n">
-        <v>4.160338222041087</v>
+        <v>4.16033822204109</v>
       </c>
       <c r="K4" t="n">
         <v>4.868164412185052</v>
       </c>
       <c r="L4" t="n">
-        <v>5.137795178387255</v>
+        <v>5.137795178387303</v>
       </c>
       <c r="M4" t="n">
         <v>4.219896497759</v>
       </c>
       <c r="N4" t="n">
-        <v>2.551443112331552</v>
+        <v>2.551443112331553</v>
       </c>
       <c r="O4" t="n">
-        <v>3.096190243072295</v>
+        <v>3.096190243072294</v>
       </c>
       <c r="P4" t="n">
-        <v>3.703700129759094</v>
+        <v>3.703700129759095</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.468693736476752</v>
+        <v>2.46869373647675</v>
       </c>
       <c r="R4" t="n">
-        <v>5.795370697208034</v>
+        <v>5.795370697208032</v>
       </c>
       <c r="S4" t="n">
         <v>5.31297070204108</v>
       </c>
       <c r="T4" t="n">
-        <v>2.776871011903645</v>
+        <v>2.776871011903646</v>
       </c>
       <c r="U4" t="n">
-        <v>4.205592433763508</v>
+        <v>4.205592433763566</v>
       </c>
       <c r="V4" t="n">
-        <v>4.173453105306336</v>
+        <v>4.173453105306333</v>
       </c>
       <c r="W4" t="n">
-        <v>3.854882454198248</v>
+        <v>3.854882454198251</v>
       </c>
       <c r="X4" t="n">
-        <v>4.767442241474586</v>
+        <v>4.767442241474582</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.184065330137293</v>
+        <v>3.184065330137294</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.96690331770728</v>
+        <v>2.966903317707277</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.01195564860895</v>
+        <v>6.011955648608959</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.775689348747147</v>
+        <v>3.775689348747142</v>
       </c>
     </row>
     <row r="5">
@@ -5624,19 +5624,19 @@
         <v>2.755086590855392</v>
       </c>
       <c r="D5" t="n">
-        <v>2.576335111754541</v>
+        <v>2.576335111754542</v>
       </c>
       <c r="E5" t="n">
-        <v>2.669843464289693</v>
+        <v>2.669843464289694</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7557761712755</v>
+        <v>2.755776171275501</v>
       </c>
       <c r="G5" t="n">
         <v>2.28869450388629</v>
       </c>
       <c r="H5" t="n">
-        <v>2.312019603723785</v>
+        <v>2.312019603723786</v>
       </c>
       <c r="I5" t="n">
         <v>2.478193605722389</v>
@@ -5651,10 +5651,10 @@
         <v>2.388598988438269</v>
       </c>
       <c r="M5" t="n">
-        <v>2.334869984134567</v>
+        <v>2.334869984134568</v>
       </c>
       <c r="N5" t="n">
-        <v>2.551443112331552</v>
+        <v>2.202469772098759</v>
       </c>
       <c r="O5" t="n">
         <v>2.249327347861612</v>
@@ -5663,19 +5663,19 @@
         <v>2.278262311422074</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.175226452064824</v>
+        <v>2.175226452064825</v>
       </c>
       <c r="R5" t="n">
         <v>2.401968697446993</v>
       </c>
       <c r="S5" t="n">
-        <v>2.412722316451014</v>
+        <v>2.412722316451015</v>
       </c>
       <c r="T5" t="n">
         <v>2.25551368316003</v>
       </c>
       <c r="U5" t="n">
-        <v>2.30976435200253</v>
+        <v>2.309764352002532</v>
       </c>
       <c r="V5" t="n">
         <v>2.328277846529396</v>
@@ -5684,7 +5684,7 @@
         <v>2.31403037587779</v>
       </c>
       <c r="X5" t="n">
-        <v>2.297267382563083</v>
+        <v>2.297267382563084</v>
       </c>
       <c r="Y5" t="n">
         <v>2.333639471131224</v>
@@ -5693,7 +5693,7 @@
         <v>2.215112592746222</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.428051088873524</v>
+        <v>2.428051088873525</v>
       </c>
       <c r="AB5" t="n">
         <v>2.35918866435844</v>
@@ -5706,55 +5706,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.617085579704216</v>
+        <v>2.617085579704217</v>
       </c>
       <c r="C6" t="n">
-        <v>3.274162926824509</v>
+        <v>3.27416292682451</v>
       </c>
       <c r="D6" t="n">
         <v>3.095411447723653</v>
       </c>
       <c r="E6" t="n">
-        <v>3.185086829463117</v>
+        <v>3.185086829463118</v>
       </c>
       <c r="F6" t="n">
         <v>2.991444701808745</v>
       </c>
       <c r="G6" t="n">
-        <v>2.796410890085885</v>
+        <v>2.796410890085887</v>
       </c>
       <c r="H6" t="n">
-        <v>2.831095939692903</v>
+        <v>2.831095939692904</v>
       </c>
       <c r="I6" t="n">
-        <v>2.997269941691501</v>
+        <v>2.997269941691503</v>
       </c>
       <c r="J6" t="n">
-        <v>2.85275772124074</v>
+        <v>2.852757721240741</v>
       </c>
       <c r="K6" t="n">
-        <v>2.895249910470333</v>
+        <v>2.895249910470334</v>
       </c>
       <c r="L6" t="n">
         <v>2.907675324407384</v>
       </c>
       <c r="M6" t="n">
-        <v>2.853946320103698</v>
+        <v>2.853946320103699</v>
       </c>
       <c r="N6" t="n">
-        <v>2.551443112331552</v>
+        <v>2.764013370105471</v>
       </c>
       <c r="O6" t="n">
         <v>2.84659110820097</v>
       </c>
       <c r="P6" t="n">
-        <v>2.888693389696294</v>
+        <v>2.888693389696295</v>
       </c>
       <c r="Q6" t="n">
         <v>2.759853863798538</v>
       </c>
       <c r="R6" t="n">
-        <v>2.921045033416106</v>
+        <v>2.921045033416107</v>
       </c>
       <c r="S6" t="n">
         <v>2.931798652420126</v>
@@ -5763,7 +5763,7 @@
         <v>2.774590019129145</v>
       </c>
       <c r="U6" t="n">
-        <v>2.855577203557066</v>
+        <v>2.855577203557067</v>
       </c>
       <c r="V6" t="n">
         <v>3.027344843616931</v>
@@ -5772,19 +5772,19 @@
         <v>2.833095945102627</v>
       </c>
       <c r="X6" t="n">
-        <v>2.876873670668854</v>
+        <v>2.876873670668855</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.798239319939409</v>
+        <v>2.79823931993941</v>
       </c>
       <c r="Z6" t="n">
         <v>2.703773995916004</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.947127424842638</v>
+        <v>2.947127424842639</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.821037861806576</v>
+        <v>2.821037861806577</v>
       </c>
     </row>
   </sheetData>
@@ -5950,22 +5950,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.395660550246154</v>
+        <v>2.395660550246155</v>
       </c>
       <c r="C2" t="n">
         <v>2.438852044624189</v>
       </c>
       <c r="D2" t="n">
-        <v>2.410118898304302</v>
+        <v>2.410118898304304</v>
       </c>
       <c r="E2" t="n">
-        <v>2.426841467204259</v>
+        <v>2.426841467204261</v>
       </c>
       <c r="F2" t="n">
-        <v>2.444013362847083</v>
+        <v>2.444013362847084</v>
       </c>
       <c r="G2" t="n">
-        <v>2.399183035731399</v>
+        <v>2.399183035731401</v>
       </c>
       <c r="H2" t="n">
         <v>2.402287111571561</v>
@@ -5977,7 +5977,7 @@
         <v>2.404797564377409</v>
       </c>
       <c r="K2" t="n">
-        <v>2.406073454464222</v>
+        <v>2.406073454464223</v>
       </c>
       <c r="L2" t="n">
         <v>2.407711807874863</v>
@@ -5986,16 +5986,16 @@
         <v>2.414339700386105</v>
       </c>
       <c r="N2" t="n">
-        <v>2.396915652287753</v>
+        <v>2.396915652287755</v>
       </c>
       <c r="O2" t="n">
         <v>2.434330037122912</v>
       </c>
       <c r="P2" t="n">
-        <v>2.40349776437798</v>
+        <v>2.403497764377981</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.396432966958185</v>
+        <v>2.396432966958187</v>
       </c>
       <c r="R2" t="n">
         <v>2.406877682859172</v>
@@ -6010,22 +6010,22 @@
         <v>2.435277252673192</v>
       </c>
       <c r="V2" t="n">
-        <v>2.404035807843976</v>
+        <v>2.404035807843977</v>
       </c>
       <c r="W2" t="n">
-        <v>2.437013600742415</v>
+        <v>2.437013600742416</v>
       </c>
       <c r="X2" t="n">
-        <v>2.407612254657904</v>
+        <v>2.407612254657903</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.399312329961633</v>
+        <v>2.399312329961635</v>
       </c>
       <c r="Z2" t="n">
         <v>2.415299866709015</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.407280692254557</v>
+        <v>2.407280692254559</v>
       </c>
       <c r="AB2" t="n">
         <v>2.402002976791292</v>
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.411717796501902</v>
+        <v>2.400455414082764</v>
       </c>
       <c r="C3" t="n">
-        <v>3.308178392258723</v>
+        <v>2.708524170197118</v>
       </c>
       <c r="D3" t="n">
-        <v>2.749258071161603</v>
+        <v>2.517037976503119</v>
       </c>
       <c r="E3" t="n">
-        <v>3.131436083420279</v>
+        <v>2.646749819020178</v>
       </c>
       <c r="F3" t="n">
-        <v>3.544382516078484</v>
+        <v>2.790113745146673</v>
       </c>
       <c r="G3" t="n">
-        <v>2.492798573148044</v>
+        <v>2.427367171531918</v>
       </c>
       <c r="H3" t="n">
-        <v>2.567617150037254</v>
+        <v>2.455747796903632</v>
       </c>
       <c r="I3" t="n">
-        <v>2.730158468758699</v>
+        <v>2.511845930259478</v>
       </c>
       <c r="J3" t="n">
-        <v>2.624110505130553</v>
+        <v>2.472385542301002</v>
       </c>
       <c r="K3" t="n">
-        <v>2.654179176607002</v>
+        <v>2.481328995639676</v>
       </c>
       <c r="L3" t="n">
-        <v>2.690490259675881</v>
+        <v>2.493460157473809</v>
       </c>
       <c r="M3" t="n">
-        <v>2.847905981897059</v>
+        <v>2.547594479559339</v>
       </c>
       <c r="N3" t="n">
-        <v>2.441042623842861</v>
+        <v>2.410681160687715</v>
       </c>
       <c r="O3" t="n">
-        <v>2.565568220946464</v>
+        <v>2.473926428429616</v>
       </c>
       <c r="P3" t="n">
-        <v>2.591838620953069</v>
+        <v>2.461106100373605</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.429834288381087</v>
+        <v>2.406627830305142</v>
       </c>
       <c r="R3" t="n">
-        <v>2.674720858822357</v>
+        <v>2.492957318076416</v>
       </c>
       <c r="S3" t="n">
-        <v>2.721345050184479</v>
+        <v>2.502994844279467</v>
       </c>
       <c r="T3" t="n">
-        <v>2.474867302989969</v>
+        <v>2.422518817056124</v>
       </c>
       <c r="U3" t="n">
-        <v>2.634872886737672</v>
+        <v>2.496076588848102</v>
       </c>
       <c r="V3" t="n">
-        <v>2.604684697802328</v>
+        <v>2.464574241720308</v>
       </c>
       <c r="W3" t="n">
-        <v>2.582567125798736</v>
+        <v>2.482739339275374</v>
       </c>
       <c r="X3" t="n">
-        <v>2.690475090470815</v>
+        <v>2.496227472995783</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.496619821508959</v>
+        <v>2.429691787176531</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.476981147274862</v>
+        <v>2.433877289679043</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.681507325908382</v>
+        <v>2.493609355174748</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.562046226860974</v>
+        <v>2.453485698292941</v>
       </c>
     </row>
     <row r="4">
@@ -6129,37 +6129,37 @@
         <v>2.207044082907968</v>
       </c>
       <c r="C4" t="n">
-        <v>9.655093690701234</v>
+        <v>9.655093690701239</v>
       </c>
       <c r="D4" t="n">
-        <v>5.15918733070868</v>
+        <v>5.159187330708686</v>
       </c>
       <c r="E4" t="n">
-        <v>8.395641567337499</v>
+        <v>8.395641567337503</v>
       </c>
       <c r="F4" t="n">
         <v>12.05850470437159</v>
       </c>
       <c r="G4" t="n">
-        <v>2.826452149960714</v>
+        <v>2.826452149960712</v>
       </c>
       <c r="H4" t="n">
-        <v>3.684962833104511</v>
+        <v>3.684962833104509</v>
       </c>
       <c r="I4" t="n">
-        <v>5.097063530192059</v>
+        <v>5.097063530192061</v>
       </c>
       <c r="J4" t="n">
         <v>3.955239722352926</v>
       </c>
       <c r="K4" t="n">
-        <v>4.123692260379839</v>
+        <v>4.123692260379836</v>
       </c>
       <c r="L4" t="n">
-        <v>4.38765233845034</v>
+        <v>4.387652338450341</v>
       </c>
       <c r="M4" t="n">
-        <v>5.791666377548319</v>
+        <v>5.791666377548318</v>
       </c>
       <c r="N4" t="n">
         <v>2.470460842603511</v>
@@ -6168,7 +6168,7 @@
         <v>3.129596989728046</v>
       </c>
       <c r="P4" t="n">
-        <v>3.638358140145076</v>
+        <v>3.638358140145078</v>
       </c>
       <c r="Q4" t="n">
         <v>2.360824852228133</v>
@@ -6177,10 +6177,10 @@
         <v>4.635609428693598</v>
       </c>
       <c r="S4" t="n">
-        <v>4.564811021326127</v>
+        <v>4.564811021326125</v>
       </c>
       <c r="T4" t="n">
-        <v>2.779333336651756</v>
+        <v>2.779333336651755</v>
       </c>
       <c r="U4" t="n">
         <v>3.726795484617807</v>
@@ -6195,13 +6195,13 @@
         <v>4.606998709237947</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.938963804035738</v>
+        <v>2.938963804035737</v>
       </c>
       <c r="Z4" t="n">
         <v>2.573385774127106</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.544958278951006</v>
+        <v>4.544958278951003</v>
       </c>
       <c r="AB4" t="n">
         <v>3.605821443678939</v>
@@ -6223,19 +6223,19 @@
         <v>2.377707215906796</v>
       </c>
       <c r="E5" t="n">
-        <v>2.539728682693057</v>
+        <v>2.539728682693058</v>
       </c>
       <c r="F5" t="n">
-        <v>2.717963163197226</v>
+        <v>2.717963163197225</v>
       </c>
       <c r="G5" t="n">
         <v>2.264644507858784</v>
       </c>
       <c r="H5" t="n">
-        <v>2.289243581960599</v>
+        <v>2.2892435819606</v>
       </c>
       <c r="I5" t="n">
-        <v>2.368129452401414</v>
+        <v>2.368129452401415</v>
       </c>
       <c r="J5" t="n">
         <v>2.317631544032341</v>
@@ -6250,7 +6250,7 @@
         <v>2.425023164898977</v>
       </c>
       <c r="N5" t="n">
-        <v>2.470460842603511</v>
+        <v>2.189456730071122</v>
       </c>
       <c r="O5" t="n">
         <v>2.245203329330831</v>
@@ -6314,7 +6314,7 @@
         <v>2.951038010528004</v>
       </c>
       <c r="F6" t="n">
-        <v>2.901695131316261</v>
+        <v>2.901695131316259</v>
       </c>
       <c r="G6" t="n">
         <v>2.665692459519663</v>
@@ -6338,7 +6338,7 @@
         <v>2.836534040182131</v>
       </c>
       <c r="N6" t="n">
-        <v>2.470460842603511</v>
+        <v>2.640081353639803</v>
       </c>
       <c r="O6" t="n">
         <v>2.723947585656769</v>
@@ -6347,10 +6347,10 @@
         <v>2.761750991976167</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.634629167632072</v>
+        <v>2.634629167632071</v>
       </c>
       <c r="R6" t="n">
-        <v>2.752607071704446</v>
+        <v>2.752607071704447</v>
       </c>
       <c r="S6" t="n">
         <v>2.777550790446023</v>

--- a/Results/Phase 2/Ammonia/ammonia water use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia water use results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.420833545542262</v>
+        <v>2.413790475288299</v>
       </c>
       <c r="C3" t="n">
-        <v>2.771517905531131</v>
+        <v>2.657061581378201</v>
       </c>
       <c r="D3" t="n">
-        <v>2.77924025708314</v>
+        <v>2.659456250761499</v>
       </c>
       <c r="E3" t="n">
-        <v>2.735631221265011</v>
+        <v>2.63344116835636</v>
       </c>
       <c r="F3" t="n">
-        <v>2.751880465319183</v>
+        <v>2.638898709931114</v>
       </c>
       <c r="G3" t="n">
-        <v>2.438554335924814</v>
+        <v>2.426239574577284</v>
       </c>
       <c r="H3" t="n">
-        <v>2.442664230557488</v>
+        <v>2.427779136811548</v>
       </c>
       <c r="I3" t="n">
-        <v>2.569356266127389</v>
+        <v>2.514816167959358</v>
       </c>
       <c r="J3" t="n">
-        <v>2.471440101401938</v>
+        <v>2.448830401802842</v>
       </c>
       <c r="K3" t="n">
-        <v>2.481010767132668</v>
+        <v>2.454697704095756</v>
       </c>
       <c r="L3" t="n">
-        <v>2.479595093910546</v>
+        <v>2.454577302988622</v>
       </c>
       <c r="M3" t="n">
-        <v>2.477099794476872</v>
+        <v>2.451592116953559</v>
       </c>
       <c r="N3" t="n">
-        <v>2.416271357644566</v>
+        <v>2.410186381891264</v>
       </c>
       <c r="O3" t="n">
-        <v>2.461821098256054</v>
+        <v>2.452146654821476</v>
       </c>
       <c r="P3" t="n">
-        <v>2.457838156423606</v>
+        <v>2.440046733648139</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.414121889507337</v>
+        <v>2.408662587996201</v>
       </c>
       <c r="R3" t="n">
-        <v>2.551002143325616</v>
+        <v>2.50181475636862</v>
       </c>
       <c r="S3" t="n">
-        <v>2.492967636805645</v>
+        <v>2.464706268679773</v>
       </c>
       <c r="T3" t="n">
-        <v>2.423542369659472</v>
+        <v>2.415040651682103</v>
       </c>
       <c r="U3" t="n">
-        <v>2.525931458858042</v>
+        <v>2.496770761484881</v>
       </c>
       <c r="V3" t="n">
-        <v>2.472279766644575</v>
+        <v>2.450380141061821</v>
       </c>
       <c r="W3" t="n">
-        <v>2.491885504665215</v>
+        <v>2.473697656585864</v>
       </c>
       <c r="X3" t="n">
-        <v>2.485760405131812</v>
+        <v>2.458064410267823</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.438164293567415</v>
+        <v>2.425511054642466</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.452487206171475</v>
+        <v>2.441542448788068</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.555961178042826</v>
+        <v>2.507457070646711</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.427931841145718</v>
+        <v>2.417700078146358</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.396524357095111</v>
+        <v>2.39509434480313</v>
       </c>
       <c r="C3" t="n">
-        <v>2.693082965295958</v>
+        <v>2.605464436365719</v>
       </c>
       <c r="D3" t="n">
-        <v>2.459666791386558</v>
+        <v>2.439235856362949</v>
       </c>
       <c r="E3" t="n">
-        <v>2.599105920273773</v>
+        <v>2.539293447233661</v>
       </c>
       <c r="F3" t="n">
-        <v>2.758419879347945</v>
+        <v>2.646374442830892</v>
       </c>
       <c r="G3" t="n">
-        <v>2.413669340113317</v>
+        <v>2.407461799594419</v>
       </c>
       <c r="H3" t="n">
-        <v>2.445699202239623</v>
+        <v>2.428566286714643</v>
       </c>
       <c r="I3" t="n">
-        <v>2.454967431622262</v>
+        <v>2.435424580006457</v>
       </c>
       <c r="J3" t="n">
-        <v>2.454485439158006</v>
+        <v>2.435974728597348</v>
       </c>
       <c r="K3" t="n">
-        <v>2.468042136535358</v>
+        <v>2.446281090266353</v>
       </c>
       <c r="L3" t="n">
-        <v>2.498242418082589</v>
+        <v>2.468175681974634</v>
       </c>
       <c r="M3" t="n">
-        <v>2.486645338123839</v>
+        <v>2.45781272265892</v>
       </c>
       <c r="N3" t="n">
-        <v>2.406776126424452</v>
+        <v>2.402158120230574</v>
       </c>
       <c r="O3" t="n">
-        <v>2.466437032832322</v>
+        <v>2.454662136669954</v>
       </c>
       <c r="P3" t="n">
-        <v>2.45672435494112</v>
+        <v>2.438565985864042</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.399823838190875</v>
+        <v>2.397365614503483</v>
       </c>
       <c r="R3" t="n">
-        <v>2.464365347623414</v>
+        <v>2.441471112964352</v>
       </c>
       <c r="S3" t="n">
-        <v>2.490558826652765</v>
+        <v>2.462908075688194</v>
       </c>
       <c r="T3" t="n">
-        <v>2.424811313326933</v>
+        <v>2.414515835166219</v>
       </c>
       <c r="U3" t="n">
-        <v>2.477771859663441</v>
+        <v>2.462314340818332</v>
       </c>
       <c r="V3" t="n">
-        <v>2.444544356009613</v>
+        <v>2.429729599244751</v>
       </c>
       <c r="W3" t="n">
-        <v>2.464612104963013</v>
+        <v>2.45319315395941</v>
       </c>
       <c r="X3" t="n">
-        <v>2.488375092734702</v>
+        <v>2.459671575640805</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.410946116593448</v>
+        <v>2.405090054168974</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.422842754257007</v>
+        <v>2.418923049121965</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.443570500594926</v>
+        <v>2.427813981518534</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.427721982318883</v>
+        <v>2.416250951399763</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.417053125492189</v>
+        <v>2.411213496006943</v>
       </c>
       <c r="C3" t="n">
-        <v>2.75729173178782</v>
+        <v>2.649275329399403</v>
       </c>
       <c r="D3" t="n">
-        <v>2.636321077182247</v>
+        <v>2.561373242064506</v>
       </c>
       <c r="E3" t="n">
-        <v>2.722147367898691</v>
+        <v>2.624235092979301</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7767653646721</v>
+        <v>2.657802264539159</v>
       </c>
       <c r="G3" t="n">
-        <v>2.436722769929158</v>
+        <v>2.425106971308083</v>
       </c>
       <c r="H3" t="n">
-        <v>2.457748585583795</v>
+        <v>2.438175513087579</v>
       </c>
       <c r="I3" t="n">
-        <v>2.59914664880765</v>
+        <v>2.53532449386593</v>
       </c>
       <c r="J3" t="n">
-        <v>2.472631624083977</v>
+        <v>2.449881651621593</v>
       </c>
       <c r="K3" t="n">
-        <v>2.493346056968293</v>
+        <v>2.464595882800168</v>
       </c>
       <c r="L3" t="n">
-        <v>2.499558129251012</v>
+        <v>2.4686439902606</v>
       </c>
       <c r="M3" t="n">
-        <v>2.477465206471424</v>
+        <v>2.452044696275601</v>
       </c>
       <c r="N3" t="n">
-        <v>2.416012094281263</v>
+        <v>2.410119177865544</v>
       </c>
       <c r="O3" t="n">
-        <v>2.471149843358712</v>
+        <v>2.459398839756387</v>
       </c>
       <c r="P3" t="n">
-        <v>2.457841650873151</v>
+        <v>2.440184023211317</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.41454175301767</v>
+        <v>2.409078546442184</v>
       </c>
       <c r="R3" t="n">
-        <v>2.545099619073348</v>
+        <v>2.497906511519857</v>
       </c>
       <c r="S3" t="n">
-        <v>2.515451280972767</v>
+        <v>2.480952502809562</v>
       </c>
       <c r="T3" t="n">
-        <v>2.422918903203981</v>
+        <v>2.414745512054208</v>
       </c>
       <c r="U3" t="n">
-        <v>2.517644675478156</v>
+        <v>2.491132690146785</v>
       </c>
       <c r="V3" t="n">
-        <v>2.47782571496625</v>
+        <v>2.455000016877106</v>
       </c>
       <c r="W3" t="n">
-        <v>2.483771305597245</v>
+        <v>2.468191821376452</v>
       </c>
       <c r="X3" t="n">
-        <v>2.489082813322992</v>
+        <v>2.46056205751107</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.437922178796267</v>
+        <v>2.425525358798335</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.451387790144784</v>
+        <v>2.440931203344142</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.527001564029673</v>
+        <v>2.487633973594241</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.427580744776947</v>
+        <v>2.417580983307626</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.412780243233164</v>
+        <v>2.407634645457359</v>
       </c>
       <c r="C3" t="n">
-        <v>2.683779913693437</v>
+        <v>2.599293800407749</v>
       </c>
       <c r="D3" t="n">
-        <v>2.545934363694573</v>
+        <v>2.499027177641202</v>
       </c>
       <c r="E3" t="n">
-        <v>2.630561307981343</v>
+        <v>2.558848952217448</v>
       </c>
       <c r="F3" t="n">
-        <v>2.748939693610218</v>
+        <v>2.63927012527028</v>
       </c>
       <c r="G3" t="n">
-        <v>2.432144864486277</v>
+        <v>2.421446644589937</v>
       </c>
       <c r="H3" t="n">
-        <v>2.450607436007507</v>
+        <v>2.432700309591604</v>
       </c>
       <c r="I3" t="n">
-        <v>2.497543068642099</v>
+        <v>2.465306240184095</v>
       </c>
       <c r="J3" t="n">
-        <v>2.461277132348853</v>
+        <v>2.441504480944336</v>
       </c>
       <c r="K3" t="n">
-        <v>2.473951675852922</v>
+        <v>2.451131716171814</v>
       </c>
       <c r="L3" t="n">
-        <v>2.492072618617331</v>
+        <v>2.462983045878919</v>
       </c>
       <c r="M3" t="n">
-        <v>2.458128372820194</v>
+        <v>2.438223143667924</v>
       </c>
       <c r="N3" t="n">
-        <v>2.411841267324786</v>
+        <v>2.406689602318414</v>
       </c>
       <c r="O3" t="n">
-        <v>2.474584458221359</v>
+        <v>2.461634181120391</v>
       </c>
       <c r="P3" t="n">
-        <v>2.452579868501</v>
+        <v>2.436067370546294</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.413779806182365</v>
+        <v>2.408074830779712</v>
       </c>
       <c r="R3" t="n">
-        <v>2.539915911344435</v>
+        <v>2.493818781214888</v>
       </c>
       <c r="S3" t="n">
-        <v>2.486904325531417</v>
+        <v>2.460349352477265</v>
       </c>
       <c r="T3" t="n">
-        <v>2.428123838936383</v>
+        <v>2.417769375637378</v>
       </c>
       <c r="U3" t="n">
-        <v>2.485802270617608</v>
+        <v>2.468403189679551</v>
       </c>
       <c r="V3" t="n">
-        <v>2.469833687245938</v>
+        <v>2.448960314538457</v>
       </c>
       <c r="W3" t="n">
-        <v>2.479489788592571</v>
+        <v>2.464795493173789</v>
       </c>
       <c r="X3" t="n">
-        <v>2.489583837595127</v>
+        <v>2.460464324625791</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.432565081732301</v>
+        <v>2.421242048902748</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.445235009306406</v>
+        <v>2.436403211309878</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.486839043845102</v>
+        <v>2.459035520031572</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.431524757362883</v>
+        <v>2.419685021663781</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.409660533241613</v>
+        <v>2.40494986697487</v>
       </c>
       <c r="C3" t="n">
-        <v>2.68907041410962</v>
+        <v>2.603036694606892</v>
       </c>
       <c r="D3" t="n">
-        <v>2.511406341114246</v>
+        <v>2.475659672581635</v>
       </c>
       <c r="E3" t="n">
-        <v>2.602053602358178</v>
+        <v>2.541022414308383</v>
       </c>
       <c r="F3" t="n">
-        <v>2.704736622717597</v>
+        <v>2.608751752397829</v>
       </c>
       <c r="G3" t="n">
-        <v>2.426539935823812</v>
+        <v>2.417097243108933</v>
       </c>
       <c r="H3" t="n">
-        <v>2.440293298387847</v>
+        <v>2.425093023419925</v>
       </c>
       <c r="I3" t="n">
-        <v>2.461501927214632</v>
+        <v>2.440262441229588</v>
       </c>
       <c r="J3" t="n">
-        <v>2.455683411772949</v>
+        <v>2.437192746825673</v>
       </c>
       <c r="K3" t="n">
-        <v>2.457534894341598</v>
+        <v>2.438888952217308</v>
       </c>
       <c r="L3" t="n">
-        <v>2.488040422288871</v>
+        <v>2.460334105476686</v>
       </c>
       <c r="M3" t="n">
-        <v>2.467367143744248</v>
+        <v>2.444596461448052</v>
       </c>
       <c r="N3" t="n">
-        <v>2.408118047567134</v>
+        <v>2.403541285409186</v>
       </c>
       <c r="O3" t="n">
-        <v>2.466120353185972</v>
+        <v>2.454841235214523</v>
       </c>
       <c r="P3" t="n">
-        <v>2.440156525734406</v>
+        <v>2.426959347368048</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.413550825786589</v>
+        <v>2.407444088357446</v>
       </c>
       <c r="R3" t="n">
-        <v>2.506451436880911</v>
+        <v>2.470421878044637</v>
       </c>
       <c r="S3" t="n">
-        <v>2.47494460139278</v>
+        <v>2.451530598207391</v>
       </c>
       <c r="T3" t="n">
-        <v>2.429344293420639</v>
+        <v>2.418027588474001</v>
       </c>
       <c r="U3" t="n">
-        <v>2.465787560724034</v>
+        <v>2.453922066314874</v>
       </c>
       <c r="V3" t="n">
-        <v>2.457385988873233</v>
+        <v>2.439571310980287</v>
       </c>
       <c r="W3" t="n">
-        <v>2.469849973720202</v>
+        <v>2.457464688476135</v>
       </c>
       <c r="X3" t="n">
-        <v>2.489159841100661</v>
+        <v>2.460204449757128</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.423717825518324</v>
+        <v>2.414417530768174</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.435777610459349</v>
+        <v>2.429159802753362</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.466784822039403</v>
+        <v>2.444420407287771</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.428944871155492</v>
+        <v>2.417450401294321</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.403957064104092</v>
+        <v>2.402105894935697</v>
       </c>
       <c r="C3" t="n">
-        <v>2.795622184211465</v>
+        <v>2.676885634250429</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5388380675404</v>
+        <v>2.495153680400661</v>
       </c>
       <c r="E3" t="n">
-        <v>2.751480614245914</v>
+        <v>2.645243412579088</v>
       </c>
       <c r="F3" t="n">
-        <v>2.847862555343965</v>
+        <v>2.709047677522551</v>
       </c>
       <c r="G3" t="n">
-        <v>2.422490358319551</v>
+        <v>2.415535148182378</v>
       </c>
       <c r="H3" t="n">
-        <v>2.47246935362665</v>
+        <v>2.44853656763419</v>
       </c>
       <c r="I3" t="n">
-        <v>2.613132621369758</v>
+        <v>2.545773864504968</v>
       </c>
       <c r="J3" t="n">
-        <v>2.484615189253013</v>
+        <v>2.459120234105954</v>
       </c>
       <c r="K3" t="n">
-        <v>2.515578592378334</v>
+        <v>2.48130557707794</v>
       </c>
       <c r="L3" t="n">
-        <v>2.536937545567933</v>
+        <v>2.498440268937631</v>
       </c>
       <c r="M3" t="n">
-        <v>2.564148958741832</v>
+        <v>2.515298764313592</v>
       </c>
       <c r="N3" t="n">
-        <v>2.41835099096437</v>
+        <v>2.41212906173348</v>
       </c>
       <c r="O3" t="n">
-        <v>2.479221307795828</v>
+        <v>2.46599112366128</v>
       </c>
       <c r="P3" t="n">
-        <v>2.482809777972255</v>
+        <v>2.458380375865267</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.412323194225879</v>
+        <v>2.407913226044549</v>
       </c>
       <c r="R3" t="n">
-        <v>2.542212239405445</v>
+        <v>2.496243099836285</v>
       </c>
       <c r="S3" t="n">
-        <v>2.574510177662166</v>
+        <v>2.527957912584165</v>
       </c>
       <c r="T3" t="n">
-        <v>2.434431212119065</v>
+        <v>2.423258863306824</v>
       </c>
       <c r="U3" t="n">
-        <v>2.501180112866471</v>
+        <v>2.480213214359007</v>
       </c>
       <c r="V3" t="n">
-        <v>2.481244719744409</v>
+        <v>2.457807955197332</v>
       </c>
       <c r="W3" t="n">
-        <v>2.504858448335207</v>
+        <v>2.483309030269631</v>
       </c>
       <c r="X3" t="n">
-        <v>2.499315681331951</v>
+        <v>2.468146343270439</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.438923243667297</v>
+        <v>2.426529496098432</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.448245368110515</v>
+        <v>2.439157340355167</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.548238448346643</v>
+        <v>2.502781353084847</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.505162724426884</v>
+        <v>2.471389140083815</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.399361365866212</v>
+        <v>2.397506204225953</v>
       </c>
       <c r="C3" t="n">
-        <v>2.706419193523263</v>
+        <v>2.615189379933996</v>
       </c>
       <c r="D3" t="n">
-        <v>2.470048374584968</v>
+        <v>2.447139933995758</v>
       </c>
       <c r="E3" t="n">
-        <v>2.603999017964848</v>
+        <v>2.540047089842754</v>
       </c>
       <c r="F3" t="n">
-        <v>2.746078332677304</v>
+        <v>2.639188844982389</v>
       </c>
       <c r="G3" t="n">
-        <v>2.412257342832503</v>
+        <v>2.406892850991099</v>
       </c>
       <c r="H3" t="n">
-        <v>2.449888800569513</v>
+        <v>2.431835103041252</v>
       </c>
       <c r="I3" t="n">
-        <v>2.488523520587542</v>
+        <v>2.459225565215586</v>
       </c>
       <c r="J3" t="n">
-        <v>2.458311396662514</v>
+        <v>2.439497053334374</v>
       </c>
       <c r="K3" t="n">
-        <v>2.458126478771925</v>
+        <v>2.43944370289304</v>
       </c>
       <c r="L3" t="n">
-        <v>2.464222273381927</v>
+        <v>2.445714539343341</v>
       </c>
       <c r="M3" t="n">
-        <v>2.49387070536045</v>
+        <v>2.46553666481055</v>
       </c>
       <c r="N3" t="n">
-        <v>2.412892474158624</v>
+        <v>2.406971998603001</v>
       </c>
       <c r="O3" t="n">
-        <v>2.475286430309808</v>
+        <v>2.46161707341323</v>
       </c>
       <c r="P3" t="n">
-        <v>2.472156546446385</v>
+        <v>2.449697924216085</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.402603327664498</v>
+        <v>2.399761551656518</v>
       </c>
       <c r="R3" t="n">
-        <v>2.484346757794242</v>
+        <v>2.455882123712024</v>
       </c>
       <c r="S3" t="n">
-        <v>2.510917030229004</v>
+        <v>2.479541596689488</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4216012977847</v>
+        <v>2.413008196612673</v>
       </c>
       <c r="U3" t="n">
-        <v>2.486021611355458</v>
+        <v>2.469342746051904</v>
       </c>
       <c r="V3" t="n">
-        <v>2.461634282256975</v>
+        <v>2.442698355804895</v>
       </c>
       <c r="W3" t="n">
-        <v>2.476953410635662</v>
+        <v>2.462801139471405</v>
       </c>
       <c r="X3" t="n">
-        <v>2.479919722734173</v>
+        <v>2.454278678102045</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.424615301513181</v>
+        <v>2.415056795668321</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.429102428567953</v>
+        <v>2.423912751020711</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.455750374409049</v>
+        <v>2.436814899016643</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.465173024948815</v>
+        <v>2.443107987711498</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.396438479502596</v>
+        <v>2.394273912560874</v>
       </c>
       <c r="C3" t="n">
-        <v>2.67032896019623</v>
+        <v>2.587841244214554</v>
       </c>
       <c r="D3" t="n">
-        <v>2.452550819564667</v>
+        <v>2.433373682533944</v>
       </c>
       <c r="E3" t="n">
-        <v>2.476714991939989</v>
+        <v>2.450026424786305</v>
       </c>
       <c r="F3" t="n">
-        <v>2.691394444891007</v>
+        <v>2.598159195876873</v>
       </c>
       <c r="G3" t="n">
-        <v>2.401386315476926</v>
+        <v>2.397822319420018</v>
       </c>
       <c r="H3" t="n">
-        <v>2.434263489989134</v>
+        <v>2.419966859573512</v>
       </c>
       <c r="I3" t="n">
-        <v>2.436134980682406</v>
+        <v>2.421540722235966</v>
       </c>
       <c r="J3" t="n">
-        <v>2.439675484829571</v>
+        <v>2.424702505688396</v>
       </c>
       <c r="K3" t="n">
-        <v>2.431989197568817</v>
+        <v>2.419274376942771</v>
       </c>
       <c r="L3" t="n">
-        <v>2.454213284623822</v>
+        <v>2.436451019973341</v>
       </c>
       <c r="M3" t="n">
-        <v>2.464722699008089</v>
+        <v>2.442068826215666</v>
       </c>
       <c r="N3" t="n">
-        <v>2.402631140451645</v>
+        <v>2.398515807066119</v>
       </c>
       <c r="O3" t="n">
-        <v>2.462773499979434</v>
+        <v>2.45096604309493</v>
       </c>
       <c r="P3" t="n">
-        <v>2.460984980343075</v>
+        <v>2.440922713503994</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.396020583798454</v>
+        <v>2.393890798004467</v>
       </c>
       <c r="R3" t="n">
-        <v>2.450621641296488</v>
+        <v>2.431261041893041</v>
       </c>
       <c r="S3" t="n">
-        <v>2.481394667973639</v>
+        <v>2.455657662355201</v>
       </c>
       <c r="T3" t="n">
-        <v>2.413804371262822</v>
+        <v>2.406204456950133</v>
       </c>
       <c r="U3" t="n">
-        <v>2.470057279911611</v>
+        <v>2.456058799155969</v>
       </c>
       <c r="V3" t="n">
-        <v>2.438711547549036</v>
+        <v>2.424732432582586</v>
       </c>
       <c r="W3" t="n">
-        <v>2.45174886092641</v>
+        <v>2.443428715892472</v>
       </c>
       <c r="X3" t="n">
-        <v>2.458941902868788</v>
+        <v>2.438494010325379</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.412935130277504</v>
+        <v>2.405647173712609</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.415996194865814</v>
+        <v>2.413192440635184</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.416811342623415</v>
+        <v>2.408396106771821</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.431717793686352</v>
+        <v>2.418270653927065</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.411881332057094</v>
+        <v>2.407782764992243</v>
       </c>
       <c r="C3" t="n">
-        <v>2.782919492216183</v>
+        <v>2.667758399355339</v>
       </c>
       <c r="D3" t="n">
-        <v>2.654824393747123</v>
+        <v>2.574377507014529</v>
       </c>
       <c r="E3" t="n">
-        <v>2.734767526546186</v>
+        <v>2.633407413965484</v>
       </c>
       <c r="F3" t="n">
-        <v>2.816157071514728</v>
+        <v>2.68630000918094</v>
       </c>
       <c r="G3" t="n">
-        <v>2.436703357251612</v>
+        <v>2.42561582973801</v>
       </c>
       <c r="H3" t="n">
-        <v>2.464794750241478</v>
+        <v>2.443279712707866</v>
       </c>
       <c r="I3" t="n">
-        <v>2.583915928369847</v>
+        <v>2.52566228085881</v>
       </c>
       <c r="J3" t="n">
-        <v>2.476981176781356</v>
+        <v>2.453527284595793</v>
       </c>
       <c r="K3" t="n">
-        <v>2.505790709722187</v>
+        <v>2.474406259357787</v>
       </c>
       <c r="L3" t="n">
-        <v>2.515018366986647</v>
+        <v>2.480568115074087</v>
       </c>
       <c r="M3" t="n">
-        <v>2.478265497531912</v>
+        <v>2.454115858371833</v>
       </c>
       <c r="N3" t="n">
-        <v>2.415126182684886</v>
+        <v>2.409791977776549</v>
       </c>
       <c r="O3" t="n">
-        <v>2.471139475788128</v>
+        <v>2.459731487421176</v>
       </c>
       <c r="P3" t="n">
-        <v>2.460937087109729</v>
+        <v>2.442666778146075</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.412126349007969</v>
+        <v>2.407728908961504</v>
       </c>
       <c r="R3" t="n">
-        <v>2.530117735854358</v>
+        <v>2.487988766715806</v>
       </c>
       <c r="S3" t="n">
-        <v>2.528216721876269</v>
+        <v>2.491965978445275</v>
       </c>
       <c r="T3" t="n">
-        <v>2.422968783742395</v>
+        <v>2.415073623975404</v>
       </c>
       <c r="U3" t="n">
-        <v>2.510473952936253</v>
+        <v>2.486514253006164</v>
       </c>
       <c r="V3" t="n">
-        <v>2.481378173244551</v>
+        <v>2.457881985165742</v>
       </c>
       <c r="W3" t="n">
-        <v>2.499831610559635</v>
+        <v>2.479784286917481</v>
       </c>
       <c r="X3" t="n">
-        <v>2.496166337645644</v>
+        <v>2.465763423163925</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.439153627890113</v>
+        <v>2.42668674013282</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.450935023870964</v>
+        <v>2.440958319923905</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.544718047508422</v>
+        <v>2.500318351737806</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.457374805269649</v>
+        <v>2.438127708578629</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.400455414082764</v>
+        <v>2.398888100869235</v>
       </c>
       <c r="C3" t="n">
-        <v>2.708524170197118</v>
+        <v>2.617209984620347</v>
       </c>
       <c r="D3" t="n">
-        <v>2.517037976503119</v>
+        <v>2.479795857338989</v>
       </c>
       <c r="E3" t="n">
-        <v>2.646749819020178</v>
+        <v>2.570523139339946</v>
       </c>
       <c r="F3" t="n">
-        <v>2.790113745146673</v>
+        <v>2.669512791354586</v>
       </c>
       <c r="G3" t="n">
-        <v>2.427367171531918</v>
+        <v>2.418385339196888</v>
       </c>
       <c r="H3" t="n">
-        <v>2.455747796903632</v>
+        <v>2.436232379541953</v>
       </c>
       <c r="I3" t="n">
-        <v>2.511845930259478</v>
+        <v>2.475275981852532</v>
       </c>
       <c r="J3" t="n">
-        <v>2.472385542301002</v>
+        <v>2.449775873258658</v>
       </c>
       <c r="K3" t="n">
-        <v>2.481328995639676</v>
+        <v>2.456748431947795</v>
       </c>
       <c r="L3" t="n">
-        <v>2.493460157473809</v>
+        <v>2.465739735995543</v>
       </c>
       <c r="M3" t="n">
-        <v>2.547594479559339</v>
+        <v>2.502866933426259</v>
       </c>
       <c r="N3" t="n">
-        <v>2.410681160687715</v>
+        <v>2.405925563108425</v>
       </c>
       <c r="O3" t="n">
-        <v>2.473926428429616</v>
+        <v>2.461314751492195</v>
       </c>
       <c r="P3" t="n">
-        <v>2.461106100373605</v>
+        <v>2.442361781438303</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.406627830305142</v>
+        <v>2.403204956047019</v>
       </c>
       <c r="R3" t="n">
-        <v>2.492957318076416</v>
+        <v>2.461944496434431</v>
       </c>
       <c r="S3" t="n">
-        <v>2.502994844279467</v>
+        <v>2.473206759288644</v>
       </c>
       <c r="T3" t="n">
-        <v>2.422518817056124</v>
+        <v>2.414020301541779</v>
       </c>
       <c r="U3" t="n">
-        <v>2.496076588848102</v>
+        <v>2.476267458408234</v>
       </c>
       <c r="V3" t="n">
-        <v>2.464574241720308</v>
+        <v>2.445266394687969</v>
       </c>
       <c r="W3" t="n">
-        <v>2.482739339275374</v>
+        <v>2.466989961282102</v>
       </c>
       <c r="X3" t="n">
-        <v>2.496227472995783</v>
+        <v>2.465686780376858</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.429691787176531</v>
+        <v>2.419289383769553</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.433877289679043</v>
+        <v>2.427922912689966</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.493609355174748</v>
+        <v>2.46381437783723</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.453485698292941</v>
+        <v>2.434954386117798</v>
       </c>
     </row>
     <row r="4">
